--- a/translations/Eng-Sv.xlsx
+++ b/translations/Eng-Sv.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B466"/>
+  <dimension ref="A1:B478"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -3427,154 +3427,154 @@
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>REPORT</v>
+        <v>HDR</v>
       </c>
       <c r="B378" t="str">
-        <v>RAPPORT</v>
+        <v>HDR</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>FAIL</v>
+        <v>Code points</v>
       </c>
       <c r="B379" t="str">
-        <v>UNDERKÄND</v>
+        <v>Kodpunkter</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>checks</v>
+        <v>Gain curve</v>
       </c>
       <c r="B380" t="str">
-        <v>kontroller</v>
+        <v>Förstärkningskurva</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B381" t="str">
-        <v>Genererad av iccPawgReport (iccDEV) · checklista från ICC Profile Assessment Working Group.</v>
+        <v>Färgprimärer</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B382" t="str">
-        <v>ICC-profilverktyg · drivs av IccProfLib</v>
+        <v>Överföringsfunktion</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B383" t="str">
-        <v>ICC-profilverktyg</v>
+        <v>Matriskoefficienter</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>Powered by {lib}</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B384" t="str">
-        <v>Drivs av {lib}</v>
+        <v>Flagga för fullt videoomfång</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Subscribe</v>
+        <v>Full range</v>
       </c>
       <c r="B385" t="str">
-        <v>Prenumerera</v>
+        <v>Fullt omfång</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Narrow range</v>
       </c>
       <c r="B386" t="str">
-        <v>Få besked om nya profiletool-versioner</v>
+        <v>Begränsat omfång</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>Get notified about new releases</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B387" t="str">
-        <v>Få besked om nya versioner</v>
+        <v>inte tilldelad av ITU-T H.273</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Close</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B388" t="str">
-        <v>Stäng</v>
+        <v>Färgprimärer 2 (Ospecificerad) hänvisar till profilen själv — primärerna hämtas från färgämnestaggarna och inte från den här taggen.</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B389" t="str">
-        <v>Vi mejlar dig när en ny större eller mindre version av profiletool släpps. Patchversioner hoppas över. Din adress granskas manuellt innan den läggs till.</v>
+        <v>De fyra reserverade byten i den här taggen är inte alla noll.</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>Email address</v>
+        <v>REPORT</v>
       </c>
       <c r="B390" t="str">
-        <v>E-postadress</v>
+        <v>RAPPORT</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>you@example.com</v>
+        <v>FAIL</v>
       </c>
       <c r="B391" t="str">
-        <v>du@exempel.com</v>
+        <v>UNDERKÄND</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>How will you use profiletool?</v>
+        <v>checks</v>
       </c>
       <c r="B392" t="str">
-        <v>Hur kommer du att använda profiletool?</v>
+        <v>kontroller</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>(optional)</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B393" t="str">
-        <v>(valfritt)</v>
+        <v>Genererad av iccPawgReport (iccDEV) · checklista från ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B394" t="str">
-        <v>t.ex. utvärdera ICC-profiler för tryckkalibrering</v>
+        <v>ICC-profilverktyg · drivs av IccProfLib</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B395" t="str">
-        <v>Jag godkänner att ta emot e-post om profiletool-versioner. Jag kan avsluta prenumerationen när som helst.</v>
+        <v>ICC-profilverktyg</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Cancel</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B396" t="str">
-        <v>Avbryt</v>
+        <v>Drivs av {lib}</v>
       </c>
     </row>
     <row r="397">
@@ -3587,18 +3587,18 @@
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B398" t="str">
-        <v>Tack — vi hör av oss.</v>
+        <v>Få besked om nya profiletool-versioner</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B399" t="str">
-        <v>När du har godkänts får du ett välkomstmejl. Därefter hör du bara från oss när en ny version av profiletool släpps.</v>
+        <v>Få besked om nya versioner</v>
       </c>
     </row>
     <row r="400">
@@ -3611,535 +3611,631 @@
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>Privacy notice</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B401" t="str">
-        <v>Integritetsmeddelande</v>
+        <v>Vi mejlar dig när en ny större eller mindre version av profiletool släpps. Patchversioner hoppas över. Din adress granskas manuellt innan den läggs till.</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Email address</v>
       </c>
       <c r="B402" t="str">
-        <v>Ange en giltig e-postadress.</v>
+        <v>E-postadress</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>you@example.com</v>
       </c>
       <c r="B403" t="str">
-        <v>För många förfrågningar. Försök igen senare.</v>
+        <v>du@exempel.com</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>Please check the form and try again.</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B404" t="str">
-        <v>Kontrollera formuläret och försök igen.</v>
+        <v>Hur kommer du att använda profiletool?</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>(optional)</v>
       </c>
       <c r="B405" t="str">
-        <v>Det gick inte att skicka din förfrågan. Försök igen.</v>
+        <v>(valfritt)</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>Network error. Please try again.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B406" t="str">
-        <v>Nätverksfel. Försök igen.</v>
+        <v>t.ex. utvärdera ICC-profiler för tryckkalibrering</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>Error:</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B407" t="str">
-        <v>Fel:</v>
+        <v>Jag godkänner att ta emot e-post om profiletool-versioner. Jag kan avsluta prenumerationen när som helst.</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>Convert to XML</v>
+        <v>Cancel</v>
       </c>
       <c r="B408" t="str">
-        <v>Konvertera till XML</v>
+        <v>Avbryt</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>Convert to JSON</v>
+        <v>Subscribe</v>
       </c>
       <c r="B409" t="str">
-        <v>Konvertera till JSON</v>
+        <v>Prenumerera</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>Convert to ICC</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B410" t="str">
-        <v>Konvertera till ICC</v>
+        <v>Tack — vi hör av oss.</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>Converting to XML…</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B411" t="str">
-        <v>Konverterar till XML…</v>
+        <v>När du har godkänts får du ett välkomstmejl. Därefter hör du bara från oss när en ny version av profiletool släpps.</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>Converting to JSON…</v>
+        <v>Close</v>
       </c>
       <c r="B412" t="str">
-        <v>Konverterar till JSON…</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>Converting to ICC…</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B413" t="str">
-        <v>Konverterar till ICC…</v>
+        <v>Integritetsmeddelande</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>Load ICC profile</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B414" t="str">
-        <v>Läs in ICC-profil</v>
+        <v>Ange en giltig e-postadress.</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B415" t="str">
-        <v>Släppzon för ICC-profilfiler</v>
+        <v>För många förfrågningar. Försök igen senare.</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>Profile ID</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B416" t="str">
-        <v>Profil-ID</v>
+        <v>Kontrollera formuläret och försök igen.</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>No tags found.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B417" t="str">
-        <v>Inga taggar hittades.</v>
+        <v>Det gick inte att skicka din förfrågan. Försök igen.</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>Tag Name</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B418" t="str">
-        <v>Taggnamn</v>
+        <v>Nätverksfel. Försök igen.</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>ID</v>
+        <v>Error:</v>
       </c>
       <c r="B419" t="str">
-        <v>ID</v>
+        <v>Fel:</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>Offset</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B420" t="str">
-        <v>Offset</v>
+        <v>Konvertera till XML</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>Size</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B421" t="str">
-        <v>Storlek</v>
+        <v>Konvertera till JSON</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Pad</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B422" t="str">
-        <v>Utfyllnad</v>
+        <v>Konvertera till ICC</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>Bytes changed since load</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B423" t="str">
-        <v>Byte ändrade sedan inläsning</v>
+        <v>Konverterar till XML…</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>Type</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B424" t="str">
-        <v>Typ</v>
+        <v>Konverterar till JSON…</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>Array of {type}</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B425" t="str">
-        <v>Array av {type}</v>
+        <v>Konverterar till ICC…</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>(No content)</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B426" t="str">
-        <v>(Inget innehåll)</v>
+        <v>Läs in ICC-profil</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>bytes</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B427" t="str">
-        <v>byte</v>
+        <v>Släppzon för ICC-profilfiler</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>Loading full description…</v>
+        <v>Profile ID</v>
       </c>
       <c r="B428" t="str">
-        <v>Läser in fullständig beskrivning…</v>
+        <v>Profil-ID</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>Could not load full description:</v>
+        <v>No tags found.</v>
       </c>
       <c r="B429" t="str">
-        <v>Kunde inte läsa in fullständig beskrivning:</v>
+        <v>Inga taggar hittades.</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Tag Name</v>
       </c>
       <c r="B430" t="str">
-        <v>Den här profilen kunde inte tolkas helt och får inte tillämpas. Huvudet och taggkatalogen nedan visas endast för granskning.</v>
+        <v>Taggnamn</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>ID</v>
       </c>
       <c r="B431" t="str">
-        <v>Tagginnehåll otillgängligt — profilen kunde inte tolkas helt.</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>No validation output</v>
+        <v>Offset</v>
       </c>
       <c r="B432" t="str">
-        <v>Ingen valideringsutdata</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Profile is valid</v>
+        <v>Size</v>
       </c>
       <c r="B433" t="str">
-        <v>Profilen är giltig</v>
+        <v>Storlek</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Pad</v>
       </c>
       <c r="B434" t="str">
-        <v>Profilen har varning(ar)</v>
+        <v>Utfyllnad</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B435" t="str">
-        <v>Profilen följer inte specifikationen</v>
+        <v>Byte ändrade sedan inläsning</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Critical validation error</v>
+        <v>Type</v>
       </c>
       <c r="B436" t="str">
-        <v>Kritiskt valideringsfel</v>
+        <v>Typ</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>Unknown validation status</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B437" t="str">
-        <v>Okänd valideringsstatus</v>
+        <v>Array av {type}</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>(No content)</v>
       </c>
       <c r="B438" t="str">
-        <v>Kritiskt — visas endast för granskning</v>
+        <v>(Inget innehåll)</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>No warnings or errors found.</v>
+        <v>bytes</v>
       </c>
       <c r="B439" t="str">
-        <v>Inga varningar eller fel hittades.</v>
+        <v>byte</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>Valid</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B440" t="str">
-        <v>Giltig</v>
+        <v>Läser in fullständig beskrivning…</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>Warning</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B441" t="str">
-        <v>Varning</v>
+        <v>Kunde inte läsa in fullständig beskrivning:</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>Error</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B442" t="str">
-        <v>Fel</v>
+        <v>Den här profilen kunde inte tolkas helt och får inte tillämpas. Huvudet och taggkatalogen nedan visas endast för granskning.</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>Unknown</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B443" t="str">
-        <v>Okänd</v>
+        <v>Tagginnehåll otillgängligt — profilen kunde inte tolkas helt.</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>Pass</v>
+        <v>No validation output</v>
       </c>
       <c r="B444" t="str">
-        <v>Godkänd</v>
+        <v>Ingen valideringsutdata</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>Fail</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B445" t="str">
-        <v>Underkänd</v>
+        <v>Profilen är giltig</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>View in context</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B446" t="str">
-        <v>Visa i sammanhang</v>
+        <v>Profilen har varning(ar)</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>Validation detail</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B447" t="str">
-        <v>Valideringsdetalj</v>
+        <v>Profilen följer inte specifikationen</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Triggered by</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B448" t="str">
-        <v>Utlöst av</v>
+        <v>Kritiskt valideringsfel</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>Field</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B449" t="str">
-        <v>Fält</v>
+        <v>Okänd valideringsstatus</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Current value</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B450" t="str">
-        <v>Aktuellt värde</v>
+        <v>Kritiskt — visas endast för granskning</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>Required: 0</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B451" t="str">
-        <v>Krävs: 0</v>
+        <v>Inga varningar eller fel hittades.</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>Expected: {value}</v>
+        <v>Valid</v>
       </c>
       <c r="B452" t="str">
-        <v>Förväntat: {value}</v>
+        <v>Giltig</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>Invalid</v>
+        <v>Warning</v>
       </c>
       <c r="B453" t="str">
-        <v>Ogiltigt</v>
+        <v>Varning</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Error</v>
       </c>
       <c r="B454" t="str">
-        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
+        <v>Fel</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>Close</v>
+        <v>Unknown</v>
       </c>
       <c r="B455" t="str">
-        <v>Stäng</v>
+        <v>Okänd</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>Loading XML editor…</v>
+        <v>Pass</v>
       </c>
       <c r="B456" t="str">
-        <v>Läser in XML-redigeraren…</v>
+        <v>Godkänd</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Fail</v>
       </c>
       <c r="B457" t="str">
-        <v>Läser in JSON-redigeraren…</v>
+        <v>Underkänd</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>View in context</v>
       </c>
       <c r="B458" t="str">
-        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>Visa i sammanhang</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Validation detail</v>
       </c>
       <c r="B459" t="str">
-        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>Valideringsdetalj</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Triggered by</v>
       </c>
       <c r="B460" t="str">
-        <v>● osparade XML-ändringar</v>
+        <v>Utlöst av</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Field</v>
       </c>
       <c r="B461" t="str">
-        <v>● osparade JSON-ändringar</v>
+        <v>Fält</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Current value</v>
       </c>
       <c r="B462" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
+        <v>Aktuellt värde</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Required: 0</v>
       </c>
       <c r="B463" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
+        <v>Krävs: 0</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>indent</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B464" t="str">
-        <v>indrag</v>
+        <v>Förväntat: {value}</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>sort keys</v>
+        <v>Invalid</v>
       </c>
       <c r="B465" t="str">
-        <v>sortera nycklar</v>
+        <v>Ogiltigt</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B466" t="str">
+        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B467" t="str">
+        <v>Stäng</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B468" t="str">
+        <v>Läser in XML-redigeraren…</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B469" t="str">
+        <v>Läser in JSON-redigeraren…</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B470" t="str">
+        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B471" t="str">
+        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B472" t="str">
+        <v>● osparade XML-ändringar</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B473" t="str">
+        <v>● osparade JSON-ändringar</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B474" t="str">
+        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B475" t="str">
+        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B476" t="str">
+        <v>indrag</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B477" t="str">
+        <v>sortera nycklar</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B466" t="str">
+      <c r="B478" t="str">
         <v>Profilen skrevs från ändringarna, men omvalideringen misslyckades:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B466"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B478"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Sv.xlsx
+++ b/translations/Eng-Sv.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B478"/>
+  <dimension ref="A1:B498"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -3451,791 +3451,951 @@
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Colour primaries</v>
+        <v>Environment</v>
       </c>
       <c r="B381" t="str">
-        <v>Färgprimärer</v>
+        <v>Miljö</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>Transfer characteristics</v>
+        <v>Detecting…</v>
       </c>
       <c r="B382" t="str">
-        <v>Överföringsfunktion</v>
+        <v>Identifierar…</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>Matrix coefficients</v>
+        <v>Could not detect environment.</v>
       </c>
       <c r="B383" t="str">
-        <v>Matriskoefficienter</v>
+        <v>Kunde inte identifiera miljön.</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>Video full-range flag</v>
+        <v>HDR display</v>
       </c>
       <c r="B384" t="str">
-        <v>Flagga för fullt videoomfång</v>
+        <v>HDR-skärm</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Full range</v>
+        <v>Wide gamut</v>
       </c>
       <c r="B385" t="str">
-        <v>Fullt omfång</v>
+        <v>Brett färgomfång</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>Narrow range</v>
+        <v>HDR canvas path</v>
       </c>
       <c r="B386" t="str">
-        <v>Begränsat omfång</v>
+        <v>HDR-canvasväg</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>sRGB</v>
       </c>
       <c r="B387" t="str">
-        <v>inte tilldelad av ITU-T H.273</v>
+        <v>sRGB</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>none</v>
       </c>
       <c r="B388" t="str">
-        <v>Färgprimärer 2 (Ospecificerad) hänvisar till profilen själv — primärerna hämtas från färgämnestaggarna och inte från den här taggen.</v>
+        <v>ingen</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>yes</v>
       </c>
       <c r="B389" t="str">
-        <v>De fyra reserverade byten i den här taggen är inte alla noll.</v>
+        <v>ja</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>REPORT</v>
+        <v>no</v>
       </c>
       <c r="B390" t="str">
-        <v>RAPPORT</v>
+        <v>nej</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>FAIL</v>
+        <v>not reported</v>
       </c>
       <c r="B391" t="str">
-        <v>UNDERKÄND</v>
+        <v>ej rapporterat</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>checks</v>
+        <v>Format</v>
       </c>
       <c r="B392" t="str">
-        <v>kontroller</v>
+        <v>Format</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Inspect</v>
       </c>
       <c r="B393" t="str">
-        <v>Genererad av iccPawgReport (iccDEV) · checklista från ICC Profile Assessment Working Group.</v>
+        <v>Granska</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Display</v>
       </c>
       <c r="B394" t="str">
-        <v>ICC-profilverktyg · drivs av IccProfLib</v>
+        <v>Visa</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>ICC Profile Tool</v>
+        <v>HDR</v>
       </c>
       <c r="B395" t="str">
-        <v>ICC-profilverktyg</v>
+        <v>HDR</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Powered by {lib}</v>
+        <v>Read the embedded ICC profile — needs no codec</v>
       </c>
       <c r="B396" t="str">
-        <v>Drivs av {lib}</v>
+        <v>Läs den inbäddade ICC-profilen — kräver ingen codec</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Subscribe</v>
+        <v>Show the pixels</v>
       </c>
       <c r="B397" t="str">
-        <v>Prenumerera</v>
+        <v>Visa pixlarna</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Render brighter-than-white</v>
       </c>
       <c r="B398" t="str">
-        <v>Få besked om nya profiletool-versioner</v>
+        <v>Rendera ljusare än vitt</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>Get notified about new releases</v>
+        <v>Decoded by profiletool itself, so browser-independent</v>
       </c>
       <c r="B399" t="str">
-        <v>Få besked om nya versioner</v>
+        <v>Avkodas av profiletool själv, alltså webbläsaroberoende</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>Close</v>
+        <v>Browsers cannot report how much HDR headroom a display has, only whether an HDR path exists.</v>
       </c>
       <c r="B400" t="str">
-        <v>Stäng</v>
+        <v>Webbläsare kan inte rapportera hur mycket HDR-utrymme en skärm har, bara om en HDR-väg finns.</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B401" t="str">
-        <v>Vi mejlar dig när en ny större eller mindre version av profiletool släpps. Patchversioner hoppas över. Din adress granskas manuellt innan den läggs till.</v>
+        <v>Färgprimärer</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>Email address</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B402" t="str">
-        <v>E-postadress</v>
+        <v>Överföringsfunktion</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>you@example.com</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B403" t="str">
-        <v>du@exempel.com</v>
+        <v>Matriskoefficienter</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B404" t="str">
-        <v>Hur kommer du att använda profiletool?</v>
+        <v>Flagga för fullt videoomfång</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>(optional)</v>
+        <v>Full range</v>
       </c>
       <c r="B405" t="str">
-        <v>(valfritt)</v>
+        <v>Fullt omfång</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Narrow range</v>
       </c>
       <c r="B406" t="str">
-        <v>t.ex. utvärdera ICC-profiler för tryckkalibrering</v>
+        <v>Begränsat omfång</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B407" t="str">
-        <v>Jag godkänner att ta emot e-post om profiletool-versioner. Jag kan avsluta prenumerationen när som helst.</v>
+        <v>inte tilldelad av ITU-T H.273</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>Cancel</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B408" t="str">
-        <v>Avbryt</v>
+        <v>Färgprimärer 2 (Ospecificerad) hänvisar till profilen själv — primärerna hämtas från färgämnestaggarna och inte från den här taggen.</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>Subscribe</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B409" t="str">
-        <v>Prenumerera</v>
+        <v>De fyra reserverade byten i den här taggen är inte alla noll.</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>REPORT</v>
       </c>
       <c r="B410" t="str">
-        <v>Tack — vi hör av oss.</v>
+        <v>RAPPORT</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>FAIL</v>
       </c>
       <c r="B411" t="str">
-        <v>När du har godkänts får du ett välkomstmejl. Därefter hör du bara från oss när en ny version av profiletool släpps.</v>
+        <v>UNDERKÄND</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>Close</v>
+        <v>checks</v>
       </c>
       <c r="B412" t="str">
-        <v>Stäng</v>
+        <v>kontroller</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>Privacy notice</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B413" t="str">
-        <v>Integritetsmeddelande</v>
+        <v>Genererad av iccPawgReport (iccDEV) · checklista från ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B414" t="str">
-        <v>Ange en giltig e-postadress.</v>
+        <v>ICC-profilverktyg · drivs av IccProfLib</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B415" t="str">
-        <v>För många förfrågningar. Försök igen senare.</v>
+        <v>ICC-profilverktyg</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B416" t="str">
-        <v>Kontrollera formuläret och försök igen.</v>
+        <v>Drivs av {lib}</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B417" t="str">
-        <v>Det gick inte att skicka din förfrågan. Försök igen.</v>
+        <v>Prenumerera</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B418" t="str">
-        <v>Nätverksfel. Försök igen.</v>
+        <v>Få besked om nya profiletool-versioner</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>Error:</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B419" t="str">
-        <v>Fel:</v>
+        <v>Få besked om nya versioner</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>Convert to XML</v>
+        <v>Close</v>
       </c>
       <c r="B420" t="str">
-        <v>Konvertera till XML</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>Convert to JSON</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B421" t="str">
-        <v>Konvertera till JSON</v>
+        <v>Vi mejlar dig när en ny större eller mindre version av profiletool släpps. Patchversioner hoppas över. Din adress granskas manuellt innan den läggs till.</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Convert to ICC</v>
+        <v>Email address</v>
       </c>
       <c r="B422" t="str">
-        <v>Konvertera till ICC</v>
+        <v>E-postadress</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>Converting to XML…</v>
+        <v>you@example.com</v>
       </c>
       <c r="B423" t="str">
-        <v>Konverterar till XML…</v>
+        <v>du@exempel.com</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>Converting to JSON…</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B424" t="str">
-        <v>Konverterar till JSON…</v>
+        <v>Hur kommer du att använda profiletool?</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>Converting to ICC…</v>
+        <v>(optional)</v>
       </c>
       <c r="B425" t="str">
-        <v>Konverterar till ICC…</v>
+        <v>(valfritt)</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>Load ICC profile</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B426" t="str">
-        <v>Läs in ICC-profil</v>
+        <v>t.ex. utvärdera ICC-profiler för tryckkalibrering</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B427" t="str">
-        <v>Släppzon för ICC-profilfiler</v>
+        <v>Jag godkänner att ta emot e-post om profiletool-versioner. Jag kan avsluta prenumerationen när som helst.</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>Profile ID</v>
+        <v>Cancel</v>
       </c>
       <c r="B428" t="str">
-        <v>Profil-ID</v>
+        <v>Avbryt</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>No tags found.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B429" t="str">
-        <v>Inga taggar hittades.</v>
+        <v>Prenumerera</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>Tag Name</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B430" t="str">
-        <v>Taggnamn</v>
+        <v>Tack — vi hör av oss.</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>ID</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B431" t="str">
-        <v>ID</v>
+        <v>När du har godkänts får du ett välkomstmejl. Därefter hör du bara från oss när en ny version av profiletool släpps.</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>Offset</v>
+        <v>Close</v>
       </c>
       <c r="B432" t="str">
-        <v>Offset</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Size</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B433" t="str">
-        <v>Storlek</v>
+        <v>Integritetsmeddelande</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Pad</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B434" t="str">
-        <v>Utfyllnad</v>
+        <v>Ange en giltig e-postadress.</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Bytes changed since load</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B435" t="str">
-        <v>Byte ändrade sedan inläsning</v>
+        <v>För många förfrågningar. Försök igen senare.</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Type</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B436" t="str">
-        <v>Typ</v>
+        <v>Kontrollera formuläret och försök igen.</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>Array of {type}</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B437" t="str">
-        <v>Array av {type}</v>
+        <v>Det gick inte att skicka din förfrågan. Försök igen.</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>(No content)</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B438" t="str">
-        <v>(Inget innehåll)</v>
+        <v>Nätverksfel. Försök igen.</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>bytes</v>
+        <v>Error:</v>
       </c>
       <c r="B439" t="str">
-        <v>byte</v>
+        <v>Fel:</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>Loading full description…</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B440" t="str">
-        <v>Läser in fullständig beskrivning…</v>
+        <v>Konvertera till XML</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>Could not load full description:</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B441" t="str">
-        <v>Kunde inte läsa in fullständig beskrivning:</v>
+        <v>Konvertera till JSON</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B442" t="str">
-        <v>Den här profilen kunde inte tolkas helt och får inte tillämpas. Huvudet och taggkatalogen nedan visas endast för granskning.</v>
+        <v>Konvertera till ICC</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B443" t="str">
-        <v>Tagginnehåll otillgängligt — profilen kunde inte tolkas helt.</v>
+        <v>Konverterar till XML…</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>No validation output</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B444" t="str">
-        <v>Ingen valideringsutdata</v>
+        <v>Konverterar till JSON…</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>Profile is valid</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B445" t="str">
-        <v>Profilen är giltig</v>
+        <v>Konverterar till ICC…</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B446" t="str">
-        <v>Profilen har varning(ar)</v>
+        <v>Läs in ICC-profil</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B447" t="str">
-        <v>Profilen följer inte specifikationen</v>
+        <v>Släppzon för ICC-profilfiler</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Critical validation error</v>
+        <v>Profile ID</v>
       </c>
       <c r="B448" t="str">
-        <v>Kritiskt valideringsfel</v>
+        <v>Profil-ID</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>Unknown validation status</v>
+        <v>No tags found.</v>
       </c>
       <c r="B449" t="str">
-        <v>Okänd valideringsstatus</v>
+        <v>Inga taggar hittades.</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Tag Name</v>
       </c>
       <c r="B450" t="str">
-        <v>Kritiskt — visas endast för granskning</v>
+        <v>Taggnamn</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>No warnings or errors found.</v>
+        <v>ID</v>
       </c>
       <c r="B451" t="str">
-        <v>Inga varningar eller fel hittades.</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>Valid</v>
+        <v>Offset</v>
       </c>
       <c r="B452" t="str">
-        <v>Giltig</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>Warning</v>
+        <v>Size</v>
       </c>
       <c r="B453" t="str">
-        <v>Varning</v>
+        <v>Storlek</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>Error</v>
+        <v>Pad</v>
       </c>
       <c r="B454" t="str">
-        <v>Fel</v>
+        <v>Utfyllnad</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>Unknown</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B455" t="str">
-        <v>Okänd</v>
+        <v>Byte ändrade sedan inläsning</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>Pass</v>
+        <v>Type</v>
       </c>
       <c r="B456" t="str">
-        <v>Godkänd</v>
+        <v>Typ</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>Fail</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B457" t="str">
-        <v>Underkänd</v>
+        <v>Array av {type}</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>View in context</v>
+        <v>(No content)</v>
       </c>
       <c r="B458" t="str">
-        <v>Visa i sammanhang</v>
+        <v>(Inget innehåll)</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>Validation detail</v>
+        <v>bytes</v>
       </c>
       <c r="B459" t="str">
-        <v>Valideringsdetalj</v>
+        <v>byte</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>Triggered by</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B460" t="str">
-        <v>Utlöst av</v>
+        <v>Läser in fullständig beskrivning…</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>Field</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B461" t="str">
-        <v>Fält</v>
+        <v>Kunde inte läsa in fullständig beskrivning:</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>Current value</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B462" t="str">
-        <v>Aktuellt värde</v>
+        <v>Den här profilen kunde inte tolkas helt och får inte tillämpas. Huvudet och taggkatalogen nedan visas endast för granskning.</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>Required: 0</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B463" t="str">
-        <v>Krävs: 0</v>
+        <v>Tagginnehåll otillgängligt — profilen kunde inte tolkas helt.</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>Expected: {value}</v>
+        <v>No validation output</v>
       </c>
       <c r="B464" t="str">
-        <v>Förväntat: {value}</v>
+        <v>Ingen valideringsutdata</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>Invalid</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B465" t="str">
-        <v>Ogiltigt</v>
+        <v>Profilen är giltig</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B466" t="str">
-        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
+        <v>Profilen har varning(ar)</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>Close</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B467" t="str">
-        <v>Stäng</v>
+        <v>Profilen följer inte specifikationen</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>Loading XML editor…</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B468" t="str">
-        <v>Läser in XML-redigeraren…</v>
+        <v>Kritiskt valideringsfel</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B469" t="str">
-        <v>Läser in JSON-redigeraren…</v>
+        <v>Okänd valideringsstatus</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B470" t="str">
-        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>Kritiskt — visas endast för granskning</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B471" t="str">
-        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>Inga varningar eller fel hittades.</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Valid</v>
       </c>
       <c r="B472" t="str">
-        <v>● osparade XML-ändringar</v>
+        <v>Giltig</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Warning</v>
       </c>
       <c r="B473" t="str">
-        <v>● osparade JSON-ändringar</v>
+        <v>Varning</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Error</v>
       </c>
       <c r="B474" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
+        <v>Fel</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Unknown</v>
       </c>
       <c r="B475" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
+        <v>Okänd</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>indent</v>
+        <v>Pass</v>
       </c>
       <c r="B476" t="str">
-        <v>indrag</v>
+        <v>Godkänd</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>sort keys</v>
+        <v>Fail</v>
       </c>
       <c r="B477" t="str">
-        <v>sortera nycklar</v>
+        <v>Underkänd</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B478" t="str">
+        <v>Visa i sammanhang</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B479" t="str">
+        <v>Valideringsdetalj</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B480" t="str">
+        <v>Utlöst av</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B481" t="str">
+        <v>Fält</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B482" t="str">
+        <v>Aktuellt värde</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B483" t="str">
+        <v>Krävs: 0</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B484" t="str">
+        <v>Förväntat: {value}</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B485" t="str">
+        <v>Ogiltigt</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B486" t="str">
+        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B487" t="str">
+        <v>Stäng</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B488" t="str">
+        <v>Läser in XML-redigeraren…</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B489" t="str">
+        <v>Läser in JSON-redigeraren…</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B490" t="str">
+        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B491" t="str">
+        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B492" t="str">
+        <v>● osparade XML-ändringar</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B493" t="str">
+        <v>● osparade JSON-ändringar</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B494" t="str">
+        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B495" t="str">
+        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B496" t="str">
+        <v>indrag</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B497" t="str">
+        <v>sortera nycklar</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B478" t="str">
+      <c r="B498" t="str">
         <v>Profilen skrevs från ändringarna, men omvalideringen misslyckades:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B478"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B498"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Sv.xlsx
+++ b/translations/Eng-Sv.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B498"/>
+  <dimension ref="A1:B502"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -3459,943 +3459,975 @@
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>Detecting…</v>
+        <v>Showing the SDR fallback</v>
       </c>
       <c r="B382" t="str">
-        <v>Identifierar…</v>
+        <v>Visar SDR-reserven</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>Could not detect environment.</v>
+        <v>HDR Profile in the chain</v>
       </c>
       <c r="B383" t="str">
-        <v>Kunde inte identifiera miljön.</v>
+        <v>HDR-profil i kedjan</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>HDR display</v>
+        <v>Transforms through an HDR Profile use its AToB0Tag — the baked SDR rendering required by clause 8.10.6 — because clause 8.10.1 leaves it no TRC tags. The result is that fallback, not HDR behaviour.</v>
       </c>
       <c r="B384" t="str">
-        <v>HDR-skärm</v>
+        <v>Transformationer genom en HDR-profil använder dess AToB0Tag — den fasta SDR-återgivning som klausul 8.10.6 kräver — eftersom klausul 8.10.1 inte lämnar den några TRC-taggar. Resultatet är den reserven, inte HDR-beteende.</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Wide gamut</v>
+        <v>These are HDR Profiles, which carry no TRC tags, so the gamut is built from the AToB0Tag — the baked SDR rendering clause 8.10.6 requires for consumers without HDR processing. It is not the profile’s HDR gamut, which cannot be drawn in a bounded PCS.</v>
       </c>
       <c r="B385" t="str">
-        <v>Brett färgomfång</v>
+        <v>Detta är HDR-profiler utan TRC-taggar, så färgomfånget byggs från AToB0Tag — den fasta SDR-återgivning som klausul 8.10.6 kräver för konsumenter utan HDR-bearbetning. Det är inte profilens HDR-omfång, som inte kan ritas i ett begränsat PCS.</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>HDR canvas path</v>
+        <v>Detecting…</v>
       </c>
       <c r="B386" t="str">
-        <v>HDR-canvasväg</v>
+        <v>Identifierar…</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>sRGB</v>
+        <v>Could not detect environment.</v>
       </c>
       <c r="B387" t="str">
-        <v>sRGB</v>
+        <v>Kunde inte identifiera miljön.</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>none</v>
+        <v>HDR display</v>
       </c>
       <c r="B388" t="str">
-        <v>ingen</v>
+        <v>HDR-skärm</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>yes</v>
+        <v>Wide gamut</v>
       </c>
       <c r="B389" t="str">
-        <v>ja</v>
+        <v>Brett färgomfång</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>no</v>
+        <v>HDR canvas path</v>
       </c>
       <c r="B390" t="str">
-        <v>nej</v>
+        <v>HDR-canvasväg</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>not reported</v>
+        <v>sRGB</v>
       </c>
       <c r="B391" t="str">
-        <v>ej rapporterat</v>
+        <v>sRGB</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>Format</v>
+        <v>none</v>
       </c>
       <c r="B392" t="str">
-        <v>Format</v>
+        <v>ingen</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>Inspect</v>
+        <v>yes</v>
       </c>
       <c r="B393" t="str">
-        <v>Granska</v>
+        <v>ja</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>Display</v>
+        <v>no</v>
       </c>
       <c r="B394" t="str">
-        <v>Visa</v>
+        <v>nej</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>HDR</v>
+        <v>not reported</v>
       </c>
       <c r="B395" t="str">
-        <v>HDR</v>
+        <v>ej rapporterat</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Read the embedded ICC profile — needs no codec</v>
+        <v>Format</v>
       </c>
       <c r="B396" t="str">
-        <v>Läs den inbäddade ICC-profilen — kräver ingen codec</v>
+        <v>Format</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Show the pixels</v>
+        <v>Inspect</v>
       </c>
       <c r="B397" t="str">
-        <v>Visa pixlarna</v>
+        <v>Granska</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>Render brighter-than-white</v>
+        <v>Display</v>
       </c>
       <c r="B398" t="str">
-        <v>Rendera ljusare än vitt</v>
+        <v>Visa</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>Decoded by profiletool itself, so browser-independent</v>
+        <v>HDR</v>
       </c>
       <c r="B399" t="str">
-        <v>Avkodas av profiletool själv, alltså webbläsaroberoende</v>
+        <v>HDR</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>Browsers cannot report how much HDR headroom a display has, only whether an HDR path exists.</v>
+        <v>Read the embedded ICC profile — needs no codec</v>
       </c>
       <c r="B400" t="str">
-        <v>Webbläsare kan inte rapportera hur mycket HDR-utrymme en skärm har, bara om en HDR-väg finns.</v>
+        <v>Läs den inbäddade ICC-profilen — kräver ingen codec</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>Colour primaries</v>
+        <v>Show the pixels</v>
       </c>
       <c r="B401" t="str">
-        <v>Färgprimärer</v>
+        <v>Visa pixlarna</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>Transfer characteristics</v>
+        <v>Render brighter-than-white</v>
       </c>
       <c r="B402" t="str">
-        <v>Överföringsfunktion</v>
+        <v>Rendera ljusare än vitt</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>Matrix coefficients</v>
+        <v>Decoded by profiletool itself, so browser-independent</v>
       </c>
       <c r="B403" t="str">
-        <v>Matriskoefficienter</v>
+        <v>Avkodas av profiletool själv, alltså webbläsaroberoende</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>Video full-range flag</v>
+        <v>Browsers cannot report how much HDR headroom a display has, only whether an HDR path exists.</v>
       </c>
       <c r="B404" t="str">
-        <v>Flagga för fullt videoomfång</v>
+        <v>Webbläsare kan inte rapportera hur mycket HDR-utrymme en skärm har, bara om en HDR-väg finns.</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>Full range</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B405" t="str">
-        <v>Fullt omfång</v>
+        <v>Färgprimärer</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>Narrow range</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B406" t="str">
-        <v>Begränsat omfång</v>
+        <v>Överföringsfunktion</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B407" t="str">
-        <v>inte tilldelad av ITU-T H.273</v>
+        <v>Matriskoefficienter</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B408" t="str">
-        <v>Färgprimärer 2 (Ospecificerad) hänvisar till profilen själv — primärerna hämtas från färgämnestaggarna och inte från den här taggen.</v>
+        <v>Flagga för fullt videoomfång</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Full range</v>
       </c>
       <c r="B409" t="str">
-        <v>De fyra reserverade byten i den här taggen är inte alla noll.</v>
+        <v>Fullt omfång</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>REPORT</v>
+        <v>Narrow range</v>
       </c>
       <c r="B410" t="str">
-        <v>RAPPORT</v>
+        <v>Begränsat omfång</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>FAIL</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B411" t="str">
-        <v>UNDERKÄND</v>
+        <v>inte tilldelad av ITU-T H.273</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>checks</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B412" t="str">
-        <v>kontroller</v>
+        <v>Färgprimärer 2 (Ospecificerad) hänvisar till profilen själv — primärerna hämtas från färgämnestaggarna och inte från den här taggen.</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B413" t="str">
-        <v>Genererad av iccPawgReport (iccDEV) · checklista från ICC Profile Assessment Working Group.</v>
+        <v>De fyra reserverade byten i den här taggen är inte alla noll.</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>REPORT</v>
       </c>
       <c r="B414" t="str">
-        <v>ICC-profilverktyg · drivs av IccProfLib</v>
+        <v>RAPPORT</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>ICC Profile Tool</v>
+        <v>FAIL</v>
       </c>
       <c r="B415" t="str">
-        <v>ICC-profilverktyg</v>
+        <v>UNDERKÄND</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>Powered by {lib}</v>
+        <v>checks</v>
       </c>
       <c r="B416" t="str">
-        <v>Drivs av {lib}</v>
+        <v>kontroller</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>Subscribe</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B417" t="str">
-        <v>Prenumerera</v>
+        <v>Genererad av iccPawgReport (iccDEV) · checklista från ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B418" t="str">
-        <v>Få besked om nya profiletool-versioner</v>
+        <v>ICC-profilverktyg · drivs av IccProfLib</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>Get notified about new releases</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B419" t="str">
-        <v>Få besked om nya versioner</v>
+        <v>ICC-profilverktyg</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>Close</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B420" t="str">
-        <v>Stäng</v>
+        <v>Drivs av {lib}</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B421" t="str">
-        <v>Vi mejlar dig när en ny större eller mindre version av profiletool släpps. Patchversioner hoppas över. Din adress granskas manuellt innan den läggs till.</v>
+        <v>Prenumerera</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Email address</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B422" t="str">
-        <v>E-postadress</v>
+        <v>Få besked om nya profiletool-versioner</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>you@example.com</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B423" t="str">
-        <v>du@exempel.com</v>
+        <v>Få besked om nya versioner</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Close</v>
       </c>
       <c r="B424" t="str">
-        <v>Hur kommer du att använda profiletool?</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>(optional)</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B425" t="str">
-        <v>(valfritt)</v>
+        <v>Vi mejlar dig när en ny större eller mindre version av profiletool släpps. Patchversioner hoppas över. Din adress granskas manuellt innan den läggs till.</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Email address</v>
       </c>
       <c r="B426" t="str">
-        <v>t.ex. utvärdera ICC-profiler för tryckkalibrering</v>
+        <v>E-postadress</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>you@example.com</v>
       </c>
       <c r="B427" t="str">
-        <v>Jag godkänner att ta emot e-post om profiletool-versioner. Jag kan avsluta prenumerationen när som helst.</v>
+        <v>du@exempel.com</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>Cancel</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B428" t="str">
-        <v>Avbryt</v>
+        <v>Hur kommer du att använda profiletool?</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>Subscribe</v>
+        <v>(optional)</v>
       </c>
       <c r="B429" t="str">
-        <v>Prenumerera</v>
+        <v>(valfritt)</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B430" t="str">
-        <v>Tack — vi hör av oss.</v>
+        <v>t.ex. utvärdera ICC-profiler för tryckkalibrering</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B431" t="str">
-        <v>När du har godkänts får du ett välkomstmejl. Därefter hör du bara från oss när en ny version av profiletool släpps.</v>
+        <v>Jag godkänner att ta emot e-post om profiletool-versioner. Jag kan avsluta prenumerationen när som helst.</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>Close</v>
+        <v>Cancel</v>
       </c>
       <c r="B432" t="str">
-        <v>Stäng</v>
+        <v>Avbryt</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Privacy notice</v>
+        <v>Subscribe</v>
       </c>
       <c r="B433" t="str">
-        <v>Integritetsmeddelande</v>
+        <v>Prenumerera</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B434" t="str">
-        <v>Ange en giltig e-postadress.</v>
+        <v>Tack — vi hör av oss.</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B435" t="str">
-        <v>För många förfrågningar. Försök igen senare.</v>
+        <v>När du har godkänts får du ett välkomstmejl. Därefter hör du bara från oss när en ny version av profiletool släpps.</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Close</v>
       </c>
       <c r="B436" t="str">
-        <v>Kontrollera formuläret och försök igen.</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B437" t="str">
-        <v>Det gick inte att skicka din förfrågan. Försök igen.</v>
+        <v>Integritetsmeddelande</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B438" t="str">
-        <v>Nätverksfel. Försök igen.</v>
+        <v>Ange en giltig e-postadress.</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>Error:</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B439" t="str">
-        <v>Fel:</v>
+        <v>För många förfrågningar. Försök igen senare.</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>Convert to XML</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B440" t="str">
-        <v>Konvertera till XML</v>
+        <v>Kontrollera formuläret och försök igen.</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>Convert to JSON</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B441" t="str">
-        <v>Konvertera till JSON</v>
+        <v>Det gick inte att skicka din förfrågan. Försök igen.</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>Convert to ICC</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B442" t="str">
-        <v>Konvertera till ICC</v>
+        <v>Nätverksfel. Försök igen.</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>Converting to XML…</v>
+        <v>Error:</v>
       </c>
       <c r="B443" t="str">
-        <v>Konverterar till XML…</v>
+        <v>Fel:</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>Converting to JSON…</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B444" t="str">
-        <v>Konverterar till JSON…</v>
+        <v>Konvertera till XML</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>Converting to ICC…</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B445" t="str">
-        <v>Konverterar till ICC…</v>
+        <v>Konvertera till JSON</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>Load ICC profile</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B446" t="str">
-        <v>Läs in ICC-profil</v>
+        <v>Konvertera till ICC</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B447" t="str">
-        <v>Släppzon för ICC-profilfiler</v>
+        <v>Konverterar till XML…</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Profile ID</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B448" t="str">
-        <v>Profil-ID</v>
+        <v>Konverterar till JSON…</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>No tags found.</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B449" t="str">
-        <v>Inga taggar hittades.</v>
+        <v>Konverterar till ICC…</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Tag Name</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B450" t="str">
-        <v>Taggnamn</v>
+        <v>Läs in ICC-profil</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B451" t="str">
-        <v>ID</v>
+        <v>Släppzon för ICC-profilfiler</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>Offset</v>
+        <v>Profile ID</v>
       </c>
       <c r="B452" t="str">
-        <v>Offset</v>
+        <v>Profil-ID</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>Size</v>
+        <v>No tags found.</v>
       </c>
       <c r="B453" t="str">
-        <v>Storlek</v>
+        <v>Inga taggar hittades.</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>Pad</v>
+        <v>Tag Name</v>
       </c>
       <c r="B454" t="str">
-        <v>Utfyllnad</v>
+        <v>Taggnamn</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>Bytes changed since load</v>
+        <v>ID</v>
       </c>
       <c r="B455" t="str">
-        <v>Byte ändrade sedan inläsning</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>Type</v>
+        <v>Offset</v>
       </c>
       <c r="B456" t="str">
-        <v>Typ</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>Array of {type}</v>
+        <v>Size</v>
       </c>
       <c r="B457" t="str">
-        <v>Array av {type}</v>
+        <v>Storlek</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>(No content)</v>
+        <v>Pad</v>
       </c>
       <c r="B458" t="str">
-        <v>(Inget innehåll)</v>
+        <v>Utfyllnad</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>bytes</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B459" t="str">
-        <v>byte</v>
+        <v>Byte ändrade sedan inläsning</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>Loading full description…</v>
+        <v>Type</v>
       </c>
       <c r="B460" t="str">
-        <v>Läser in fullständig beskrivning…</v>
+        <v>Typ</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>Could not load full description:</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B461" t="str">
-        <v>Kunde inte läsa in fullständig beskrivning:</v>
+        <v>Array av {type}</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>(No content)</v>
       </c>
       <c r="B462" t="str">
-        <v>Den här profilen kunde inte tolkas helt och får inte tillämpas. Huvudet och taggkatalogen nedan visas endast för granskning.</v>
+        <v>(Inget innehåll)</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>bytes</v>
       </c>
       <c r="B463" t="str">
-        <v>Tagginnehåll otillgängligt — profilen kunde inte tolkas helt.</v>
+        <v>byte</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>No validation output</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B464" t="str">
-        <v>Ingen valideringsutdata</v>
+        <v>Läser in fullständig beskrivning…</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>Profile is valid</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B465" t="str">
-        <v>Profilen är giltig</v>
+        <v>Kunde inte läsa in fullständig beskrivning:</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>Profile has warning(s)</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B466" t="str">
-        <v>Profilen har varning(ar)</v>
+        <v>Den här profilen kunde inte tolkas helt och får inte tillämpas. Huvudet och taggkatalogen nedan visas endast för granskning.</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B467" t="str">
-        <v>Profilen följer inte specifikationen</v>
+        <v>Tagginnehåll otillgängligt — profilen kunde inte tolkas helt.</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>Critical validation error</v>
+        <v>No validation output</v>
       </c>
       <c r="B468" t="str">
-        <v>Kritiskt valideringsfel</v>
+        <v>Ingen valideringsutdata</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>Unknown validation status</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B469" t="str">
-        <v>Okänd valideringsstatus</v>
+        <v>Profilen är giltig</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B470" t="str">
-        <v>Kritiskt — visas endast för granskning</v>
+        <v>Profilen har varning(ar)</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B471" t="str">
-        <v>Inga varningar eller fel hittades.</v>
+        <v>Profilen följer inte specifikationen</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>Valid</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B472" t="str">
-        <v>Giltig</v>
+        <v>Kritiskt valideringsfel</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>Warning</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B473" t="str">
-        <v>Varning</v>
+        <v>Okänd valideringsstatus</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>Error</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B474" t="str">
-        <v>Fel</v>
+        <v>Kritiskt — visas endast för granskning</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>Unknown</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B475" t="str">
-        <v>Okänd</v>
+        <v>Inga varningar eller fel hittades.</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>Pass</v>
+        <v>Valid</v>
       </c>
       <c r="B476" t="str">
-        <v>Godkänd</v>
+        <v>Giltig</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>Fail</v>
+        <v>Warning</v>
       </c>
       <c r="B477" t="str">
-        <v>Underkänd</v>
+        <v>Varning</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>View in context</v>
+        <v>Error</v>
       </c>
       <c r="B478" t="str">
-        <v>Visa i sammanhang</v>
+        <v>Fel</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>Validation detail</v>
+        <v>Unknown</v>
       </c>
       <c r="B479" t="str">
-        <v>Valideringsdetalj</v>
+        <v>Okänd</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>Triggered by</v>
+        <v>Pass</v>
       </c>
       <c r="B480" t="str">
-        <v>Utlöst av</v>
+        <v>Godkänd</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>Field</v>
+        <v>Fail</v>
       </c>
       <c r="B481" t="str">
-        <v>Fält</v>
+        <v>Underkänd</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>Current value</v>
+        <v>View in context</v>
       </c>
       <c r="B482" t="str">
-        <v>Aktuellt värde</v>
+        <v>Visa i sammanhang</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>Required: 0</v>
+        <v>Validation detail</v>
       </c>
       <c r="B483" t="str">
-        <v>Krävs: 0</v>
+        <v>Valideringsdetalj</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>Expected: {value}</v>
+        <v>Triggered by</v>
       </c>
       <c r="B484" t="str">
-        <v>Förväntat: {value}</v>
+        <v>Utlöst av</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>Invalid</v>
+        <v>Field</v>
       </c>
       <c r="B485" t="str">
-        <v>Ogiltigt</v>
+        <v>Fält</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Current value</v>
       </c>
       <c r="B486" t="str">
-        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
+        <v>Aktuellt värde</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>Close</v>
+        <v>Required: 0</v>
       </c>
       <c r="B487" t="str">
-        <v>Stäng</v>
+        <v>Krävs: 0</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>Loading XML editor…</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B488" t="str">
-        <v>Läser in XML-redigeraren…</v>
+        <v>Förväntat: {value}</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Invalid</v>
       </c>
       <c r="B489" t="str">
-        <v>Läser in JSON-redigeraren…</v>
+        <v>Ogiltigt</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B490" t="str">
-        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Close</v>
       </c>
       <c r="B491" t="str">
-        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B492" t="str">
-        <v>● osparade XML-ändringar</v>
+        <v>Läser in XML-redigeraren…</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B493" t="str">
-        <v>● osparade JSON-ändringar</v>
+        <v>Läser in JSON-redigeraren…</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B494" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
+        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B495" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
+        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>indent</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B496" t="str">
-        <v>indrag</v>
+        <v>● osparade XML-ändringar</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>sort keys</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B497" t="str">
-        <v>sortera nycklar</v>
+        <v>● osparade JSON-ändringar</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B498" t="str">
+        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B499" t="str">
+        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B500" t="str">
+        <v>indrag</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B501" t="str">
+        <v>sortera nycklar</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B498" t="str">
+      <c r="B502" t="str">
         <v>Profilen skrevs från ändringarna, men omvalideringen misslyckades:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B498"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B502"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Sv.xlsx
+++ b/translations/Eng-Sv.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B502"/>
+  <dimension ref="A1:B512"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -3643,791 +3643,871 @@
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>Colour primaries</v>
+        <v>Browser flags</v>
       </c>
       <c r="B405" t="str">
-        <v>Färgprimärer</v>
+        <v>Webbläsarflaggor</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>Transfer characteristics</v>
+        <v>on</v>
       </c>
       <c r="B406" t="str">
-        <v>Överföringsfunktion</v>
+        <v>på</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>Matrix coefficients</v>
+        <v>not enabled</v>
       </c>
       <c r="B407" t="str">
-        <v>Matriskoefficienter</v>
+        <v>inte aktiverad</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>Video full-range flag</v>
+        <v>cannot be detected here</v>
       </c>
       <c r="B408" t="str">
-        <v>Flagga för fullt videoomfång</v>
+        <v>kan inte avgöras här</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>Full range</v>
+        <v>Needed for HDR rendering in this browser: it has no WebGPU, so the HDR canvas is the only route. Profile inspection works without it.</v>
       </c>
       <c r="B409" t="str">
-        <v>Fullt omfång</v>
+        <v>Krävs för HDR-rendering i den här webbläsaren: utan WebGPU är HDR-canvas den enda vägen. Profilgranskning fungerar utan.</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>Narrow range</v>
+        <v>Optional: HDR can render through WebGPU, but this adds the HDR canvas route and lets profiletool read the screen’s real HDR headroom.</v>
       </c>
       <c r="B410" t="str">
-        <v>Begränsat omfång</v>
+        <v>Valfritt: HDR kan renderas via WebGPU, men detta lägger till HDR-canvasvägen och låter profiletool läsa skärmens verkliga HDR-utrymme.</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Web pages cannot open flag pages. Paste this into the address bar, set it to Enabled, then relaunch the browser.</v>
       </c>
       <c r="B411" t="str">
-        <v>inte tilldelad av ITU-T H.273</v>
+        <v>Webbsidor kan inte öppna flaggsidor. Klistra in detta i adressfältet, välj Enabled och starta om webbläsaren.</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Copy</v>
       </c>
       <c r="B412" t="str">
-        <v>Färgprimärer 2 (Ospecificerad) hänvisar till profilen själv — primärerna hämtas från färgämnestaggarna och inte från den här taggen.</v>
+        <v>Kopiera</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Copied</v>
       </c>
       <c r="B413" t="str">
-        <v>De fyra reserverade byten i den här taggen är inte alla noll.</v>
+        <v>Kopierat</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>REPORT</v>
+        <v>Copy failed — select the address and copy it.</v>
       </c>
       <c r="B414" t="str">
-        <v>RAPPORT</v>
+        <v>Kopiering misslyckades — markera adressen och kopiera den.</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>FAIL</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B415" t="str">
-        <v>UNDERKÄND</v>
+        <v>Färgprimärer</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>checks</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B416" t="str">
-        <v>kontroller</v>
+        <v>Överföringsfunktion</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B417" t="str">
-        <v>Genererad av iccPawgReport (iccDEV) · checklista från ICC Profile Assessment Working Group.</v>
+        <v>Matriskoefficienter</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B418" t="str">
-        <v>ICC-profilverktyg · drivs av IccProfLib</v>
+        <v>Flagga för fullt videoomfång</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Full range</v>
       </c>
       <c r="B419" t="str">
-        <v>ICC-profilverktyg</v>
+        <v>Fullt omfång</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>Powered by {lib}</v>
+        <v>Narrow range</v>
       </c>
       <c r="B420" t="str">
-        <v>Drivs av {lib}</v>
+        <v>Begränsat omfång</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>Subscribe</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B421" t="str">
-        <v>Prenumerera</v>
+        <v>inte tilldelad av ITU-T H.273</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B422" t="str">
-        <v>Få besked om nya profiletool-versioner</v>
+        <v>Färgprimärer 2 (Ospecificerad) hänvisar till profilen själv — primärerna hämtas från färgämnestaggarna och inte från den här taggen.</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>Get notified about new releases</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B423" t="str">
-        <v>Få besked om nya versioner</v>
+        <v>De fyra reserverade byten i den här taggen är inte alla noll.</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>Close</v>
+        <v>REPORT</v>
       </c>
       <c r="B424" t="str">
-        <v>Stäng</v>
+        <v>RAPPORT</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>FAIL</v>
       </c>
       <c r="B425" t="str">
-        <v>Vi mejlar dig när en ny större eller mindre version av profiletool släpps. Patchversioner hoppas över. Din adress granskas manuellt innan den läggs till.</v>
+        <v>UNDERKÄND</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>Email address</v>
+        <v>checks</v>
       </c>
       <c r="B426" t="str">
-        <v>E-postadress</v>
+        <v>kontroller</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>you@example.com</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B427" t="str">
-        <v>du@exempel.com</v>
+        <v>Genererad av iccPawgReport (iccDEV) · checklista från ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>How will you use profiletool?</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B428" t="str">
-        <v>Hur kommer du att använda profiletool?</v>
+        <v>ICC-profilverktyg · drivs av IccProfLib</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>(optional)</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B429" t="str">
-        <v>(valfritt)</v>
+        <v>ICC-profilverktyg</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B430" t="str">
-        <v>t.ex. utvärdera ICC-profiler för tryckkalibrering</v>
+        <v>Drivs av {lib}</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B431" t="str">
-        <v>Jag godkänner att ta emot e-post om profiletool-versioner. Jag kan avsluta prenumerationen när som helst.</v>
+        <v>Prenumerera</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>Cancel</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B432" t="str">
-        <v>Avbryt</v>
+        <v>Få besked om nya profiletool-versioner</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Subscribe</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B433" t="str">
-        <v>Prenumerera</v>
+        <v>Få besked om nya versioner</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Close</v>
       </c>
       <c r="B434" t="str">
-        <v>Tack — vi hör av oss.</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B435" t="str">
-        <v>När du har godkänts får du ett välkomstmejl. Därefter hör du bara från oss när en ny version av profiletool släpps.</v>
+        <v>Vi mejlar dig när en ny större eller mindre version av profiletool släpps. Patchversioner hoppas över. Din adress granskas manuellt innan den läggs till.</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Close</v>
+        <v>Email address</v>
       </c>
       <c r="B436" t="str">
-        <v>Stäng</v>
+        <v>E-postadress</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>Privacy notice</v>
+        <v>you@example.com</v>
       </c>
       <c r="B437" t="str">
-        <v>Integritetsmeddelande</v>
+        <v>du@exempel.com</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B438" t="str">
-        <v>Ange en giltig e-postadress.</v>
+        <v>Hur kommer du att använda profiletool?</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>(optional)</v>
       </c>
       <c r="B439" t="str">
-        <v>För många förfrågningar. Försök igen senare.</v>
+        <v>(valfritt)</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>Please check the form and try again.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B440" t="str">
-        <v>Kontrollera formuläret och försök igen.</v>
+        <v>t.ex. utvärdera ICC-profiler för tryckkalibrering</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B441" t="str">
-        <v>Det gick inte att skicka din förfrågan. Försök igen.</v>
+        <v>Jag godkänner att ta emot e-post om profiletool-versioner. Jag kan avsluta prenumerationen när som helst.</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Cancel</v>
       </c>
       <c r="B442" t="str">
-        <v>Nätverksfel. Försök igen.</v>
+        <v>Avbryt</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>Error:</v>
+        <v>Subscribe</v>
       </c>
       <c r="B443" t="str">
-        <v>Fel:</v>
+        <v>Prenumerera</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>Convert to XML</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B444" t="str">
-        <v>Konvertera till XML</v>
+        <v>Tack — vi hör av oss.</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>Convert to JSON</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B445" t="str">
-        <v>Konvertera till JSON</v>
+        <v>När du har godkänts får du ett välkomstmejl. Därefter hör du bara från oss när en ny version av profiletool släpps.</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>Convert to ICC</v>
+        <v>Close</v>
       </c>
       <c r="B446" t="str">
-        <v>Konvertera till ICC</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>Converting to XML…</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B447" t="str">
-        <v>Konverterar till XML…</v>
+        <v>Integritetsmeddelande</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Converting to JSON…</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B448" t="str">
-        <v>Konverterar till JSON…</v>
+        <v>Ange en giltig e-postadress.</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>Converting to ICC…</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B449" t="str">
-        <v>Konverterar till ICC…</v>
+        <v>För många förfrågningar. Försök igen senare.</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Load ICC profile</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B450" t="str">
-        <v>Läs in ICC-profil</v>
+        <v>Kontrollera formuläret och försök igen.</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B451" t="str">
-        <v>Släppzon för ICC-profilfiler</v>
+        <v>Det gick inte att skicka din förfrågan. Försök igen.</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>Profile ID</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B452" t="str">
-        <v>Profil-ID</v>
+        <v>Nätverksfel. Försök igen.</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>No tags found.</v>
+        <v>Error:</v>
       </c>
       <c r="B453" t="str">
-        <v>Inga taggar hittades.</v>
+        <v>Fel:</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>Tag Name</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B454" t="str">
-        <v>Taggnamn</v>
+        <v>Konvertera till XML</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>ID</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B455" t="str">
-        <v>ID</v>
+        <v>Konvertera till JSON</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>Offset</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B456" t="str">
-        <v>Offset</v>
+        <v>Konvertera till ICC</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>Size</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B457" t="str">
-        <v>Storlek</v>
+        <v>Konverterar till XML…</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>Pad</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B458" t="str">
-        <v>Utfyllnad</v>
+        <v>Konverterar till JSON…</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>Bytes changed since load</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B459" t="str">
-        <v>Byte ändrade sedan inläsning</v>
+        <v>Konverterar till ICC…</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>Type</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B460" t="str">
-        <v>Typ</v>
+        <v>Läs in ICC-profil</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>Array of {type}</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B461" t="str">
-        <v>Array av {type}</v>
+        <v>Släppzon för ICC-profilfiler</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>(No content)</v>
+        <v>Profile ID</v>
       </c>
       <c r="B462" t="str">
-        <v>(Inget innehåll)</v>
+        <v>Profil-ID</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>bytes</v>
+        <v>No tags found.</v>
       </c>
       <c r="B463" t="str">
-        <v>byte</v>
+        <v>Inga taggar hittades.</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>Loading full description…</v>
+        <v>Tag Name</v>
       </c>
       <c r="B464" t="str">
-        <v>Läser in fullständig beskrivning…</v>
+        <v>Taggnamn</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>Could not load full description:</v>
+        <v>ID</v>
       </c>
       <c r="B465" t="str">
-        <v>Kunde inte läsa in fullständig beskrivning:</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Offset</v>
       </c>
       <c r="B466" t="str">
-        <v>Den här profilen kunde inte tolkas helt och får inte tillämpas. Huvudet och taggkatalogen nedan visas endast för granskning.</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Size</v>
       </c>
       <c r="B467" t="str">
-        <v>Tagginnehåll otillgängligt — profilen kunde inte tolkas helt.</v>
+        <v>Storlek</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>No validation output</v>
+        <v>Pad</v>
       </c>
       <c r="B468" t="str">
-        <v>Ingen valideringsutdata</v>
+        <v>Utfyllnad</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>Profile is valid</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B469" t="str">
-        <v>Profilen är giltig</v>
+        <v>Byte ändrade sedan inläsning</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Type</v>
       </c>
       <c r="B470" t="str">
-        <v>Profilen har varning(ar)</v>
+        <v>Typ</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B471" t="str">
-        <v>Profilen följer inte specifikationen</v>
+        <v>Array av {type}</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>Critical validation error</v>
+        <v>(No content)</v>
       </c>
       <c r="B472" t="str">
-        <v>Kritiskt valideringsfel</v>
+        <v>(Inget innehåll)</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>Unknown validation status</v>
+        <v>bytes</v>
       </c>
       <c r="B473" t="str">
-        <v>Okänd valideringsstatus</v>
+        <v>byte</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B474" t="str">
-        <v>Kritiskt — visas endast för granskning</v>
+        <v>Läser in fullständig beskrivning…</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B475" t="str">
-        <v>Inga varningar eller fel hittades.</v>
+        <v>Kunde inte läsa in fullständig beskrivning:</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>Valid</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B476" t="str">
-        <v>Giltig</v>
+        <v>Den här profilen kunde inte tolkas helt och får inte tillämpas. Huvudet och taggkatalogen nedan visas endast för granskning.</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>Warning</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B477" t="str">
-        <v>Varning</v>
+        <v>Tagginnehåll otillgängligt — profilen kunde inte tolkas helt.</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>Error</v>
+        <v>No validation output</v>
       </c>
       <c r="B478" t="str">
-        <v>Fel</v>
+        <v>Ingen valideringsutdata</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>Unknown</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B479" t="str">
-        <v>Okänd</v>
+        <v>Profilen är giltig</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>Pass</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B480" t="str">
-        <v>Godkänd</v>
+        <v>Profilen har varning(ar)</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>Fail</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B481" t="str">
-        <v>Underkänd</v>
+        <v>Profilen följer inte specifikationen</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>View in context</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B482" t="str">
-        <v>Visa i sammanhang</v>
+        <v>Kritiskt valideringsfel</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>Validation detail</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B483" t="str">
-        <v>Valideringsdetalj</v>
+        <v>Okänd valideringsstatus</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>Triggered by</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B484" t="str">
-        <v>Utlöst av</v>
+        <v>Kritiskt — visas endast för granskning</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>Field</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B485" t="str">
-        <v>Fält</v>
+        <v>Inga varningar eller fel hittades.</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>Current value</v>
+        <v>Valid</v>
       </c>
       <c r="B486" t="str">
-        <v>Aktuellt värde</v>
+        <v>Giltig</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>Required: 0</v>
+        <v>Warning</v>
       </c>
       <c r="B487" t="str">
-        <v>Krävs: 0</v>
+        <v>Varning</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>Expected: {value}</v>
+        <v>Error</v>
       </c>
       <c r="B488" t="str">
-        <v>Förväntat: {value}</v>
+        <v>Fel</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>Invalid</v>
+        <v>Unknown</v>
       </c>
       <c r="B489" t="str">
-        <v>Ogiltigt</v>
+        <v>Okänd</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Pass</v>
       </c>
       <c r="B490" t="str">
-        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
+        <v>Godkänd</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>Close</v>
+        <v>Fail</v>
       </c>
       <c r="B491" t="str">
-        <v>Stäng</v>
+        <v>Underkänd</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>Loading XML editor…</v>
+        <v>View in context</v>
       </c>
       <c r="B492" t="str">
-        <v>Läser in XML-redigeraren…</v>
+        <v>Visa i sammanhang</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Validation detail</v>
       </c>
       <c r="B493" t="str">
-        <v>Läser in JSON-redigeraren…</v>
+        <v>Valideringsdetalj</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Triggered by</v>
       </c>
       <c r="B494" t="str">
-        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>Utlöst av</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Field</v>
       </c>
       <c r="B495" t="str">
-        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>Fält</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Current value</v>
       </c>
       <c r="B496" t="str">
-        <v>● osparade XML-ändringar</v>
+        <v>Aktuellt värde</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Required: 0</v>
       </c>
       <c r="B497" t="str">
-        <v>● osparade JSON-ändringar</v>
+        <v>Krävs: 0</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B498" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
+        <v>Förväntat: {value}</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Invalid</v>
       </c>
       <c r="B499" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
+        <v>Ogiltigt</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>indent</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B500" t="str">
-        <v>indrag</v>
+        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>sort keys</v>
+        <v>Close</v>
       </c>
       <c r="B501" t="str">
-        <v>sortera nycklar</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B502" t="str">
+        <v>Läser in XML-redigeraren…</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B503" t="str">
+        <v>Läser in JSON-redigeraren…</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B504" t="str">
+        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B505" t="str">
+        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B506" t="str">
+        <v>● osparade XML-ändringar</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B507" t="str">
+        <v>● osparade JSON-ändringar</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B508" t="str">
+        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B509" t="str">
+        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B510" t="str">
+        <v>indrag</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B511" t="str">
+        <v>sortera nycklar</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B502" t="str">
+      <c r="B512" t="str">
         <v>Profilen skrevs från ändringarna, men omvalideringen misslyckades:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B502"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B512"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Sv.xlsx
+++ b/translations/Eng-Sv.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B512"/>
+  <dimension ref="A1:B529"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -3635,10 +3635,10 @@
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>Browsers cannot report how much HDR headroom a display has, only whether an HDR path exists.</v>
+        <v>This browser has not reported the display’s HDR headroom, only whether an HDR path exists.</v>
       </c>
       <c r="B404" t="str">
-        <v>Webbläsare kan inte rapportera hur mycket HDR-utrymme en skärm har, bara om en HDR-väg finns.</v>
+        <v>Den här webbläsaren har inte rapporterat skärmens HDR-utrymme, bara om en HDR-väg finns.</v>
       </c>
     </row>
     <row r="405">
@@ -3723,791 +3723,927 @@
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>Colour primaries</v>
+        <v>Pixel ratio</v>
       </c>
       <c r="B415" t="str">
-        <v>Färgprimärer</v>
+        <v>Pixelförhållande</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>Transfer characteristics</v>
+        <v>Current monitor</v>
       </c>
       <c r="B416" t="str">
-        <v>Överföringsfunktion</v>
+        <v>Aktuell skärm</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>Matrix coefficients</v>
+        <v>unnamed</v>
       </c>
       <c r="B417" t="str">
-        <v>Matriskoefficienter</v>
+        <v>namnlös</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>Video full-range flag</v>
+        <v>primary</v>
       </c>
       <c r="B418" t="str">
-        <v>Flagga för fullt videoomfång</v>
+        <v>primär</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>Full range</v>
+        <v>built-in</v>
       </c>
       <c r="B419" t="str">
-        <v>Fullt omfång</v>
+        <v>inbyggd</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>Narrow range</v>
+        <v>HDR headroom</v>
       </c>
       <c r="B420" t="str">
-        <v>Begränsat omfång</v>
+        <v>HDR-utrymme</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>not exposed by this browser</v>
       </c>
       <c r="B421" t="str">
-        <v>inte tilldelad av ITU-T H.273</v>
+        <v>exponeras inte av den här webbläsaren</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Shown exactly as the browser reports it. The unit is not standardised yet; an SDR screen has been observed to report 0.</v>
       </c>
       <c r="B422" t="str">
-        <v>Färgprimärer 2 (Ospecificerad) hänvisar till profilen själv — primärerna hämtas från färgämnestaggarna och inte från den här taggen.</v>
+        <v>Visas exakt som webbläsaren rapporterar det. Enheten är ännu inte standardiserad; en SDR-skärm har rapporterat 0.</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B423" t="str">
-        <v>De fyra reserverade byten i den här taggen är inte alla noll.</v>
+        <v>HDR, färgomfång och pixelförhållande uppdateras när fönstret flyttas till en skärm där de skiljer sig.</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>REPORT</v>
+        <v>Identify displays</v>
       </c>
       <c r="B424" t="str">
-        <v>RAPPORT</v>
+        <v>Identifiera skärmar</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>FAIL</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B425" t="str">
-        <v>UNDERKÄND</v>
+        <v>Ber om tillåtelse att se vilken skärm fönstret ligger på, så att panelen även uppdateras mellan likadana skärmar och visar HDR-utrymme där webbläsaren exponerar det.</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>checks</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B426" t="str">
-        <v>kontroller</v>
+        <v>Följer vilken skärm fönstret ligger på.</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B427" t="str">
-        <v>Genererad av iccPawgReport (iccDEV) · checklista från ICC Profile Assessment Working Group.</v>
+        <v>Tillåtelse att identifiera skärmar nekades. Den kan ändras i webbplatsens inställningar.</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B428" t="str">
-        <v>ICC-profilverktyg · drivs av IccProfLib</v>
+        <v>Den här webbläsaren kan inte identifiera skärmar; bara den automatiska uppdateringen ovan gäller.</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B429" t="str">
-        <v>ICC-profilverktyg</v>
+        <v>Kunde inte identifiera skärmar.</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>Powered by {lib}</v>
+        <v>Display events</v>
       </c>
       <c r="B430" t="str">
-        <v>Drivs av {lib}</v>
+        <v>Skärmhändelser</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>Subscribe</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B431" t="str">
-        <v>Prenumerera</v>
+        <v>Inga händelser än. Dra fönstret till en annan skärm.</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B432" t="str">
-        <v>Få besked om nya profiletool-versioner</v>
+        <v>Färgprimärer</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Get notified about new releases</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B433" t="str">
-        <v>Få besked om nya versioner</v>
+        <v>Överföringsfunktion</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Close</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B434" t="str">
-        <v>Stäng</v>
+        <v>Matriskoefficienter</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B435" t="str">
-        <v>Vi mejlar dig när en ny större eller mindre version av profiletool släpps. Patchversioner hoppas över. Din adress granskas manuellt innan den läggs till.</v>
+        <v>Flagga för fullt videoomfång</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Email address</v>
+        <v>Full range</v>
       </c>
       <c r="B436" t="str">
-        <v>E-postadress</v>
+        <v>Fullt omfång</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>you@example.com</v>
+        <v>Narrow range</v>
       </c>
       <c r="B437" t="str">
-        <v>du@exempel.com</v>
+        <v>Begränsat omfång</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>How will you use profiletool?</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B438" t="str">
-        <v>Hur kommer du att använda profiletool?</v>
+        <v>inte tilldelad av ITU-T H.273</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>(optional)</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B439" t="str">
-        <v>(valfritt)</v>
+        <v>Färgprimärer 2 (Ospecificerad) hänvisar till profilen själv — primärerna hämtas från färgämnestaggarna och inte från den här taggen.</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B440" t="str">
-        <v>t.ex. utvärdera ICC-profiler för tryckkalibrering</v>
+        <v>De fyra reserverade byten i den här taggen är inte alla noll.</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>REPORT</v>
       </c>
       <c r="B441" t="str">
-        <v>Jag godkänner att ta emot e-post om profiletool-versioner. Jag kan avsluta prenumerationen när som helst.</v>
+        <v>RAPPORT</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>Cancel</v>
+        <v>FAIL</v>
       </c>
       <c r="B442" t="str">
-        <v>Avbryt</v>
+        <v>UNDERKÄND</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>Subscribe</v>
+        <v>checks</v>
       </c>
       <c r="B443" t="str">
-        <v>Prenumerera</v>
+        <v>kontroller</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B444" t="str">
-        <v>Tack — vi hör av oss.</v>
+        <v>Genererad av iccPawgReport (iccDEV) · checklista från ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B445" t="str">
-        <v>När du har godkänts får du ett välkomstmejl. Därefter hör du bara från oss när en ny version av profiletool släpps.</v>
+        <v>ICC-profilverktyg · drivs av IccProfLib</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>Close</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B446" t="str">
-        <v>Stäng</v>
+        <v>ICC-profilverktyg</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>Privacy notice</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B447" t="str">
-        <v>Integritetsmeddelande</v>
+        <v>Drivs av {lib}</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B448" t="str">
-        <v>Ange en giltig e-postadress.</v>
+        <v>Prenumerera</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B449" t="str">
-        <v>För många förfrågningar. Försök igen senare.</v>
+        <v>Få besked om nya profiletool-versioner</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B450" t="str">
-        <v>Kontrollera formuläret och försök igen.</v>
+        <v>Få besked om nya versioner</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Close</v>
       </c>
       <c r="B451" t="str">
-        <v>Det gick inte att skicka din förfrågan. Försök igen.</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>Network error. Please try again.</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B452" t="str">
-        <v>Nätverksfel. Försök igen.</v>
+        <v>Vi mejlar dig när en ny större eller mindre version av profiletool släpps. Patchversioner hoppas över. Din adress granskas manuellt innan den läggs till.</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>Error:</v>
+        <v>Email address</v>
       </c>
       <c r="B453" t="str">
-        <v>Fel:</v>
+        <v>E-postadress</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>Convert to XML</v>
+        <v>you@example.com</v>
       </c>
       <c r="B454" t="str">
-        <v>Konvertera till XML</v>
+        <v>du@exempel.com</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>Convert to JSON</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B455" t="str">
-        <v>Konvertera till JSON</v>
+        <v>Hur kommer du att använda profiletool?</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>Convert to ICC</v>
+        <v>(optional)</v>
       </c>
       <c r="B456" t="str">
-        <v>Konvertera till ICC</v>
+        <v>(valfritt)</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>Converting to XML…</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B457" t="str">
-        <v>Konverterar till XML…</v>
+        <v>t.ex. utvärdera ICC-profiler för tryckkalibrering</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>Converting to JSON…</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B458" t="str">
-        <v>Konverterar till JSON…</v>
+        <v>Jag godkänner att ta emot e-post om profiletool-versioner. Jag kan avsluta prenumerationen när som helst.</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>Converting to ICC…</v>
+        <v>Cancel</v>
       </c>
       <c r="B459" t="str">
-        <v>Konverterar till ICC…</v>
+        <v>Avbryt</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>Load ICC profile</v>
+        <v>Subscribe</v>
       </c>
       <c r="B460" t="str">
-        <v>Läs in ICC-profil</v>
+        <v>Prenumerera</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B461" t="str">
-        <v>Släppzon för ICC-profilfiler</v>
+        <v>Tack — vi hör av oss.</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>Profile ID</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B462" t="str">
-        <v>Profil-ID</v>
+        <v>När du har godkänts får du ett välkomstmejl. Därefter hör du bara från oss när en ny version av profiletool släpps.</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>No tags found.</v>
+        <v>Close</v>
       </c>
       <c r="B463" t="str">
-        <v>Inga taggar hittades.</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>Tag Name</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B464" t="str">
-        <v>Taggnamn</v>
+        <v>Integritetsmeddelande</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>ID</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B465" t="str">
-        <v>ID</v>
+        <v>Ange en giltig e-postadress.</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>Offset</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B466" t="str">
-        <v>Offset</v>
+        <v>För många förfrågningar. Försök igen senare.</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>Size</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B467" t="str">
-        <v>Storlek</v>
+        <v>Kontrollera formuläret och försök igen.</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>Pad</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B468" t="str">
-        <v>Utfyllnad</v>
+        <v>Det gick inte att skicka din förfrågan. Försök igen.</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>Bytes changed since load</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B469" t="str">
-        <v>Byte ändrade sedan inläsning</v>
+        <v>Nätverksfel. Försök igen.</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>Type</v>
+        <v>Error:</v>
       </c>
       <c r="B470" t="str">
-        <v>Typ</v>
+        <v>Fel:</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>Array of {type}</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B471" t="str">
-        <v>Array av {type}</v>
+        <v>Konvertera till XML</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>(No content)</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B472" t="str">
-        <v>(Inget innehåll)</v>
+        <v>Konvertera till JSON</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>bytes</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B473" t="str">
-        <v>byte</v>
+        <v>Konvertera till ICC</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>Loading full description…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B474" t="str">
-        <v>Läser in fullständig beskrivning…</v>
+        <v>Konverterar till XML…</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>Could not load full description:</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B475" t="str">
-        <v>Kunde inte läsa in fullständig beskrivning:</v>
+        <v>Konverterar till JSON…</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B476" t="str">
-        <v>Den här profilen kunde inte tolkas helt och får inte tillämpas. Huvudet och taggkatalogen nedan visas endast för granskning.</v>
+        <v>Konverterar till ICC…</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B477" t="str">
-        <v>Tagginnehåll otillgängligt — profilen kunde inte tolkas helt.</v>
+        <v>Läs in ICC-profil</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>No validation output</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B478" t="str">
-        <v>Ingen valideringsutdata</v>
+        <v>Släppzon för ICC-profilfiler</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>Profile is valid</v>
+        <v>Profile ID</v>
       </c>
       <c r="B479" t="str">
-        <v>Profilen är giltig</v>
+        <v>Profil-ID</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>Profile has warning(s)</v>
+        <v>No tags found.</v>
       </c>
       <c r="B480" t="str">
-        <v>Profilen har varning(ar)</v>
+        <v>Inga taggar hittades.</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Tag Name</v>
       </c>
       <c r="B481" t="str">
-        <v>Profilen följer inte specifikationen</v>
+        <v>Taggnamn</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>Critical validation error</v>
+        <v>ID</v>
       </c>
       <c r="B482" t="str">
-        <v>Kritiskt valideringsfel</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>Unknown validation status</v>
+        <v>Offset</v>
       </c>
       <c r="B483" t="str">
-        <v>Okänd valideringsstatus</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Size</v>
       </c>
       <c r="B484" t="str">
-        <v>Kritiskt — visas endast för granskning</v>
+        <v>Storlek</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Pad</v>
       </c>
       <c r="B485" t="str">
-        <v>Inga varningar eller fel hittades.</v>
+        <v>Utfyllnad</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>Valid</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B486" t="str">
-        <v>Giltig</v>
+        <v>Byte ändrade sedan inläsning</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>Warning</v>
+        <v>Type</v>
       </c>
       <c r="B487" t="str">
-        <v>Varning</v>
+        <v>Typ</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>Error</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B488" t="str">
-        <v>Fel</v>
+        <v>Array av {type}</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>Unknown</v>
+        <v>(No content)</v>
       </c>
       <c r="B489" t="str">
-        <v>Okänd</v>
+        <v>(Inget innehåll)</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>Pass</v>
+        <v>bytes</v>
       </c>
       <c r="B490" t="str">
-        <v>Godkänd</v>
+        <v>byte</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>Fail</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B491" t="str">
-        <v>Underkänd</v>
+        <v>Läser in fullständig beskrivning…</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>View in context</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B492" t="str">
-        <v>Visa i sammanhang</v>
+        <v>Kunde inte läsa in fullständig beskrivning:</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>Validation detail</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B493" t="str">
-        <v>Valideringsdetalj</v>
+        <v>Den här profilen kunde inte tolkas helt och får inte tillämpas. Huvudet och taggkatalogen nedan visas endast för granskning.</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>Triggered by</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B494" t="str">
-        <v>Utlöst av</v>
+        <v>Tagginnehåll otillgängligt — profilen kunde inte tolkas helt.</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>Field</v>
+        <v>No validation output</v>
       </c>
       <c r="B495" t="str">
-        <v>Fält</v>
+        <v>Ingen valideringsutdata</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>Current value</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B496" t="str">
-        <v>Aktuellt värde</v>
+        <v>Profilen är giltig</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>Required: 0</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B497" t="str">
-        <v>Krävs: 0</v>
+        <v>Profilen har varning(ar)</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Expected: {value}</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B498" t="str">
-        <v>Förväntat: {value}</v>
+        <v>Profilen följer inte specifikationen</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Invalid</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B499" t="str">
-        <v>Ogiltigt</v>
+        <v>Kritiskt valideringsfel</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B500" t="str">
-        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
+        <v>Okänd valideringsstatus</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>Close</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B501" t="str">
-        <v>Stäng</v>
+        <v>Kritiskt — visas endast för granskning</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>Loading XML editor…</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B502" t="str">
-        <v>Läser in XML-redigeraren…</v>
+        <v>Inga varningar eller fel hittades.</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Valid</v>
       </c>
       <c r="B503" t="str">
-        <v>Läser in JSON-redigeraren…</v>
+        <v>Giltig</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Warning</v>
       </c>
       <c r="B504" t="str">
-        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>Varning</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Error</v>
       </c>
       <c r="B505" t="str">
-        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>Fel</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Unknown</v>
       </c>
       <c r="B506" t="str">
-        <v>● osparade XML-ändringar</v>
+        <v>Okänd</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Pass</v>
       </c>
       <c r="B507" t="str">
-        <v>● osparade JSON-ändringar</v>
+        <v>Godkänd</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Fail</v>
       </c>
       <c r="B508" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
+        <v>Underkänd</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>View in context</v>
       </c>
       <c r="B509" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
+        <v>Visa i sammanhang</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>indent</v>
+        <v>Validation detail</v>
       </c>
       <c r="B510" t="str">
-        <v>indrag</v>
+        <v>Valideringsdetalj</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>sort keys</v>
+        <v>Triggered by</v>
       </c>
       <c r="B511" t="str">
-        <v>sortera nycklar</v>
+        <v>Utlöst av</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B512" t="str">
+        <v>Fält</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B513" t="str">
+        <v>Aktuellt värde</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B514" t="str">
+        <v>Krävs: 0</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B515" t="str">
+        <v>Förväntat: {value}</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B516" t="str">
+        <v>Ogiltigt</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B517" t="str">
+        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B518" t="str">
+        <v>Stäng</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B519" t="str">
+        <v>Läser in XML-redigeraren…</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B520" t="str">
+        <v>Läser in JSON-redigeraren…</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B521" t="str">
+        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B522" t="str">
+        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B523" t="str">
+        <v>● osparade XML-ändringar</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B524" t="str">
+        <v>● osparade JSON-ändringar</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B525" t="str">
+        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B526" t="str">
+        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B527" t="str">
+        <v>indrag</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B528" t="str">
+        <v>sortera nycklar</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B512" t="str">
+      <c r="B529" t="str">
         <v>Profilen skrevs från ändringarna, men omvalideringen misslyckades:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B512"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B529"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Sv.xlsx
+++ b/translations/Eng-Sv.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B529"/>
+  <dimension ref="A1:B530"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -3779,871 +3779,879 @@
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Shown exactly as the browser reports it. The unit is not standardised yet; an SDR screen has been observed to report 0.</v>
+        <v>Chromium reports this in stops: log₂ of the display’s peak brightness ÷ its SDR white level. On Windows it refreshes only when Chrome re-reads the display — the window moves to another screen, or Chrome becomes the active app again — not when brightness changes.</v>
       </c>
       <c r="B422" t="str">
-        <v>Visas exakt som webbläsaren rapporterar det. Enheten är ännu inte standardiserad; en SDR-skärm har rapporterat 0.</v>
+        <v>Chromium rapporterar detta i steg: log₂ av skärmens toppljusstyrka ÷ dess SDR-vitnivå. I Windows uppdateras det bara när Chrome läser om skärmen – fönstret flyttas till en annan skärm eller Chrome aktiveras igen – inte när ljusstyrkan ändras.</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>{stops} stops (≈{ratio}× SDR white)</v>
       </c>
       <c r="B423" t="str">
-        <v>HDR, färgomfång och pixelförhållande uppdateras när fönstret flyttas till en skärm där de skiljer sig.</v>
+        <v>{stops} steg (≈{ratio}× SDR-vitt)</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>Identify displays</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B424" t="str">
-        <v>Identifiera skärmar</v>
+        <v>HDR, färgomfång och pixelförhållande uppdateras när fönstret flyttas till en skärm där de skiljer sig.</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Identify displays</v>
       </c>
       <c r="B425" t="str">
-        <v>Ber om tillåtelse att se vilken skärm fönstret ligger på, så att panelen även uppdateras mellan likadana skärmar och visar HDR-utrymme där webbläsaren exponerar det.</v>
+        <v>Identifiera skärmar</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B426" t="str">
-        <v>Följer vilken skärm fönstret ligger på.</v>
+        <v>Ber om tillåtelse att se vilken skärm fönstret ligger på, så att panelen även uppdateras mellan likadana skärmar och visar HDR-utrymme där webbläsaren exponerar det.</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B427" t="str">
-        <v>Tillåtelse att identifiera skärmar nekades. Den kan ändras i webbplatsens inställningar.</v>
+        <v>Följer vilken skärm fönstret ligger på.</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B428" t="str">
-        <v>Den här webbläsaren kan inte identifiera skärmar; bara den automatiska uppdateringen ovan gäller.</v>
+        <v>Tillåtelse att identifiera skärmar nekades. Den kan ändras i webbplatsens inställningar.</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>Could not identify displays.</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B429" t="str">
-        <v>Kunde inte identifiera skärmar.</v>
+        <v>Den här webbläsaren kan inte identifiera skärmar; bara den automatiska uppdateringen ovan gäller.</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>Display events</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B430" t="str">
-        <v>Skärmhändelser</v>
+        <v>Kunde inte identifiera skärmar.</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Display events</v>
       </c>
       <c r="B431" t="str">
-        <v>Inga händelser än. Dra fönstret till en annan skärm.</v>
+        <v>Skärmhändelser</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>Colour primaries</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B432" t="str">
-        <v>Färgprimärer</v>
+        <v>Inga händelser än. Dra fönstret till en annan skärm.</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Transfer characteristics</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B433" t="str">
-        <v>Överföringsfunktion</v>
+        <v>Färgprimärer</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Matrix coefficients</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B434" t="str">
-        <v>Matriskoefficienter</v>
+        <v>Överföringsfunktion</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Video full-range flag</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B435" t="str">
-        <v>Flagga för fullt videoomfång</v>
+        <v>Matriskoefficienter</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Full range</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B436" t="str">
-        <v>Fullt omfång</v>
+        <v>Flagga för fullt videoomfång</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>Narrow range</v>
+        <v>Full range</v>
       </c>
       <c r="B437" t="str">
-        <v>Begränsat omfång</v>
+        <v>Fullt omfång</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Narrow range</v>
       </c>
       <c r="B438" t="str">
-        <v>inte tilldelad av ITU-T H.273</v>
+        <v>Begränsat omfång</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B439" t="str">
-        <v>Färgprimärer 2 (Ospecificerad) hänvisar till profilen själv — primärerna hämtas från färgämnestaggarna och inte från den här taggen.</v>
+        <v>inte tilldelad av ITU-T H.273</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B440" t="str">
-        <v>De fyra reserverade byten i den här taggen är inte alla noll.</v>
+        <v>Färgprimärer 2 (Ospecificerad) hänvisar till profilen själv — primärerna hämtas från färgämnestaggarna och inte från den här taggen.</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>REPORT</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B441" t="str">
-        <v>RAPPORT</v>
+        <v>De fyra reserverade byten i den här taggen är inte alla noll.</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>FAIL</v>
+        <v>REPORT</v>
       </c>
       <c r="B442" t="str">
-        <v>UNDERKÄND</v>
+        <v>RAPPORT</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>checks</v>
+        <v>FAIL</v>
       </c>
       <c r="B443" t="str">
-        <v>kontroller</v>
+        <v>UNDERKÄND</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>checks</v>
       </c>
       <c r="B444" t="str">
-        <v>Genererad av iccPawgReport (iccDEV) · checklista från ICC Profile Assessment Working Group.</v>
+        <v>kontroller</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B445" t="str">
-        <v>ICC-profilverktyg · drivs av IccProfLib</v>
+        <v>Genererad av iccPawgReport (iccDEV) · checklista från ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>ICC Profile Tool</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B446" t="str">
-        <v>ICC-profilverktyg</v>
+        <v>ICC-profilverktyg · drivs av IccProfLib</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>Powered by {lib}</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B447" t="str">
-        <v>Drivs av {lib}</v>
+        <v>ICC-profilverktyg</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Subscribe</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B448" t="str">
-        <v>Prenumerera</v>
+        <v>Drivs av {lib}</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Subscribe</v>
       </c>
       <c r="B449" t="str">
-        <v>Få besked om nya profiletool-versioner</v>
+        <v>Prenumerera</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Get notified about new releases</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B450" t="str">
-        <v>Få besked om nya versioner</v>
+        <v>Få besked om nya profiletool-versioner</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>Close</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B451" t="str">
-        <v>Stäng</v>
+        <v>Få besked om nya versioner</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Close</v>
       </c>
       <c r="B452" t="str">
-        <v>Vi mejlar dig när en ny större eller mindre version av profiletool släpps. Patchversioner hoppas över. Din adress granskas manuellt innan den läggs till.</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>Email address</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B453" t="str">
-        <v>E-postadress</v>
+        <v>Vi mejlar dig när en ny större eller mindre version av profiletool släpps. Patchversioner hoppas över. Din adress granskas manuellt innan den läggs till.</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>you@example.com</v>
+        <v>Email address</v>
       </c>
       <c r="B454" t="str">
-        <v>du@exempel.com</v>
+        <v>E-postadress</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>How will you use profiletool?</v>
+        <v>you@example.com</v>
       </c>
       <c r="B455" t="str">
-        <v>Hur kommer du att använda profiletool?</v>
+        <v>du@exempel.com</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>(optional)</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B456" t="str">
-        <v>(valfritt)</v>
+        <v>Hur kommer du att använda profiletool?</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>(optional)</v>
       </c>
       <c r="B457" t="str">
-        <v>t.ex. utvärdera ICC-profiler för tryckkalibrering</v>
+        <v>(valfritt)</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B458" t="str">
-        <v>Jag godkänner att ta emot e-post om profiletool-versioner. Jag kan avsluta prenumerationen när som helst.</v>
+        <v>t.ex. utvärdera ICC-profiler för tryckkalibrering</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>Cancel</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B459" t="str">
-        <v>Avbryt</v>
+        <v>Jag godkänner att ta emot e-post om profiletool-versioner. Jag kan avsluta prenumerationen när som helst.</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>Subscribe</v>
+        <v>Cancel</v>
       </c>
       <c r="B460" t="str">
-        <v>Prenumerera</v>
+        <v>Avbryt</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B461" t="str">
-        <v>Tack — vi hör av oss.</v>
+        <v>Prenumerera</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B462" t="str">
-        <v>När du har godkänts får du ett välkomstmejl. Därefter hör du bara från oss när en ny version av profiletool släpps.</v>
+        <v>Tack — vi hör av oss.</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>Close</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B463" t="str">
-        <v>Stäng</v>
+        <v>När du har godkänts får du ett välkomstmejl. Därefter hör du bara från oss när en ny version av profiletool släpps.</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>Privacy notice</v>
+        <v>Close</v>
       </c>
       <c r="B464" t="str">
-        <v>Integritetsmeddelande</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B465" t="str">
-        <v>Ange en giltig e-postadress.</v>
+        <v>Integritetsmeddelande</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B466" t="str">
-        <v>För många förfrågningar. Försök igen senare.</v>
+        <v>Ange en giltig e-postadress.</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B467" t="str">
-        <v>Kontrollera formuläret och försök igen.</v>
+        <v>För många förfrågningar. Försök igen senare.</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B468" t="str">
-        <v>Det gick inte att skicka din förfrågan. Försök igen.</v>
+        <v>Kontrollera formuläret och försök igen.</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B469" t="str">
-        <v>Nätverksfel. Försök igen.</v>
+        <v>Det gick inte att skicka din förfrågan. Försök igen.</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>Error:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B470" t="str">
-        <v>Fel:</v>
+        <v>Nätverksfel. Försök igen.</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>Convert to XML</v>
+        <v>Error:</v>
       </c>
       <c r="B471" t="str">
-        <v>Konvertera till XML</v>
+        <v>Fel:</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B472" t="str">
-        <v>Konvertera till JSON</v>
+        <v>Konvertera till XML</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B473" t="str">
-        <v>Konvertera till ICC</v>
+        <v>Konvertera till JSON</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B474" t="str">
-        <v>Konverterar till XML…</v>
+        <v>Konvertera till ICC</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B475" t="str">
-        <v>Konverterar till JSON…</v>
+        <v>Konverterar till XML…</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B476" t="str">
-        <v>Konverterar till ICC…</v>
+        <v>Konverterar till JSON…</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B477" t="str">
-        <v>Läs in ICC-profil</v>
+        <v>Konverterar till ICC…</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B478" t="str">
-        <v>Släppzon för ICC-profilfiler</v>
+        <v>Läs in ICC-profil</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>Profile ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B479" t="str">
-        <v>Profil-ID</v>
+        <v>Släppzon för ICC-profilfiler</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>No tags found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B480" t="str">
-        <v>Inga taggar hittades.</v>
+        <v>Profil-ID</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>Tag Name</v>
+        <v>No tags found.</v>
       </c>
       <c r="B481" t="str">
-        <v>Taggnamn</v>
+        <v>Inga taggar hittades.</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>ID</v>
+        <v>Tag Name</v>
       </c>
       <c r="B482" t="str">
-        <v>ID</v>
+        <v>Taggnamn</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
       <c r="B483" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>Size</v>
+        <v>Offset</v>
       </c>
       <c r="B484" t="str">
-        <v>Storlek</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>Pad</v>
+        <v>Size</v>
       </c>
       <c r="B485" t="str">
-        <v>Utfyllnad</v>
+        <v>Storlek</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>Bytes changed since load</v>
+        <v>Pad</v>
       </c>
       <c r="B486" t="str">
-        <v>Byte ändrade sedan inläsning</v>
+        <v>Utfyllnad</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>Type</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B487" t="str">
-        <v>Typ</v>
+        <v>Byte ändrade sedan inläsning</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>Array of {type}</v>
+        <v>Type</v>
       </c>
       <c r="B488" t="str">
-        <v>Array av {type}</v>
+        <v>Typ</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>(No content)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B489" t="str">
-        <v>(Inget innehåll)</v>
+        <v>Array av {type}</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>bytes</v>
+        <v>(No content)</v>
       </c>
       <c r="B490" t="str">
-        <v>byte</v>
+        <v>(Inget innehåll)</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>Loading full description…</v>
+        <v>bytes</v>
       </c>
       <c r="B491" t="str">
-        <v>Läser in fullständig beskrivning…</v>
+        <v>byte</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>Could not load full description:</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B492" t="str">
-        <v>Kunde inte läsa in fullständig beskrivning:</v>
+        <v>Läser in fullständig beskrivning…</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B493" t="str">
-        <v>Den här profilen kunde inte tolkas helt och får inte tillämpas. Huvudet och taggkatalogen nedan visas endast för granskning.</v>
+        <v>Kunde inte läsa in fullständig beskrivning:</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B494" t="str">
-        <v>Tagginnehåll otillgängligt — profilen kunde inte tolkas helt.</v>
+        <v>Den här profilen kunde inte tolkas helt och får inte tillämpas. Huvudet och taggkatalogen nedan visas endast för granskning.</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>No validation output</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B495" t="str">
-        <v>Ingen valideringsutdata</v>
+        <v>Tagginnehåll otillgängligt — profilen kunde inte tolkas helt.</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>Profile is valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B496" t="str">
-        <v>Profilen är giltig</v>
+        <v>Ingen valideringsutdata</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B497" t="str">
-        <v>Profilen har varning(ar)</v>
+        <v>Profilen är giltig</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B498" t="str">
-        <v>Profilen följer inte specifikationen</v>
+        <v>Profilen har varning(ar)</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B499" t="str">
-        <v>Kritiskt valideringsfel</v>
+        <v>Profilen följer inte specifikationen</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B500" t="str">
-        <v>Okänd valideringsstatus</v>
+        <v>Kritiskt valideringsfel</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B501" t="str">
-        <v>Kritiskt — visas endast för granskning</v>
+        <v>Okänd valideringsstatus</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B502" t="str">
-        <v>Inga varningar eller fel hittades.</v>
+        <v>Kritiskt — visas endast för granskning</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>Valid</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B503" t="str">
-        <v>Giltig</v>
+        <v>Inga varningar eller fel hittades.</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>Warning</v>
+        <v>Valid</v>
       </c>
       <c r="B504" t="str">
-        <v>Varning</v>
+        <v>Giltig</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>Error</v>
+        <v>Warning</v>
       </c>
       <c r="B505" t="str">
-        <v>Fel</v>
+        <v>Varning</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>Unknown</v>
+        <v>Error</v>
       </c>
       <c r="B506" t="str">
-        <v>Okänd</v>
+        <v>Fel</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>Pass</v>
+        <v>Unknown</v>
       </c>
       <c r="B507" t="str">
-        <v>Godkänd</v>
+        <v>Okänd</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="B508" t="str">
-        <v>Underkänd</v>
+        <v>Godkänd</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>View in context</v>
+        <v>Fail</v>
       </c>
       <c r="B509" t="str">
-        <v>Visa i sammanhang</v>
+        <v>Underkänd</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>Validation detail</v>
+        <v>View in context</v>
       </c>
       <c r="B510" t="str">
-        <v>Valideringsdetalj</v>
+        <v>Visa i sammanhang</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>Triggered by</v>
+        <v>Validation detail</v>
       </c>
       <c r="B511" t="str">
-        <v>Utlöst av</v>
+        <v>Valideringsdetalj</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>Field</v>
+        <v>Triggered by</v>
       </c>
       <c r="B512" t="str">
-        <v>Fält</v>
+        <v>Utlöst av</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Current value</v>
+        <v>Field</v>
       </c>
       <c r="B513" t="str">
-        <v>Aktuellt värde</v>
+        <v>Fält</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>Required: 0</v>
+        <v>Current value</v>
       </c>
       <c r="B514" t="str">
-        <v>Krävs: 0</v>
+        <v>Aktuellt värde</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Expected: {value}</v>
+        <v>Required: 0</v>
       </c>
       <c r="B515" t="str">
-        <v>Förväntat: {value}</v>
+        <v>Krävs: 0</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>Invalid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B516" t="str">
-        <v>Ogiltigt</v>
+        <v>Förväntat: {value}</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Invalid</v>
       </c>
       <c r="B517" t="str">
-        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
+        <v>Ogiltigt</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>Close</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B518" t="str">
-        <v>Stäng</v>
+        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>Loading XML editor…</v>
+        <v>Close</v>
       </c>
       <c r="B519" t="str">
-        <v>Läser in XML-redigeraren…</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B520" t="str">
-        <v>Läser in JSON-redigeraren…</v>
+        <v>Läser in XML-redigeraren…</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B521" t="str">
-        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>Läser in JSON-redigeraren…</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B522" t="str">
-        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B523" t="str">
-        <v>● osparade XML-ändringar</v>
+        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B524" t="str">
-        <v>● osparade JSON-ändringar</v>
+        <v>● osparade XML-ändringar</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B525" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
+        <v>● osparade JSON-ändringar</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B526" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
+        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B527" t="str">
-        <v>indrag</v>
+        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>sort keys</v>
+        <v>indent</v>
       </c>
       <c r="B528" t="str">
-        <v>sortera nycklar</v>
+        <v>indrag</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B529" t="str">
+        <v>sortera nycklar</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B529" t="str">
+      <c r="B530" t="str">
         <v>Profilen skrevs från ändringarna, men omvalideringen misslyckades:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B529"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B530"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Sv.xlsx
+++ b/translations/Eng-Sv.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B530"/>
+  <dimension ref="A1:B595"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -3795,863 +3795,1383 @@
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>HDR</v>
       </c>
       <c r="B424" t="str">
-        <v>HDR, färgomfång och pixelförhållande uppdateras när fönstret flyttas till en skärm där de skiljer sig.</v>
+        <v>HDR</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>Identify displays</v>
+        <v>Gain at a display headroom</v>
       </c>
       <c r="B425" t="str">
-        <v>Identifiera skärmar</v>
+        <v>Förstärkning vid ett skärmutrymme</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>View one HDR image on this display. Files the browser can decode are shown by the browser itself; OpenEXR is decoded and rendered by profiletool.</v>
       </c>
       <c r="B426" t="str">
-        <v>Ber om tillåtelse att se vilken skärm fönstret ligger på, så att panelen även uppdateras mellan likadana skärmar och visar HDR-utrymme där webbläsaren exponerar det.</v>
+        <v>Visa en HDR-bild på den här skärmen. Filer som webbläsaren kan avkoda visas av webbläsaren själv; OpenEXR avkodas och återges av profiletool.</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Drop an HDR image here, or click to choose one</v>
       </c>
       <c r="B427" t="str">
-        <v>Följer vilken skärm fönstret ligger på.</v>
+        <v>Släpp en HDR-bild här, eller klicka för att välja en</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>OpenEXR, AVIF, JPEG (including gain-map JPEG), PNG — and HEIC on Safari.</v>
       </c>
       <c r="B428" t="str">
-        <v>Tillåtelse att identifiera skärmar nekades. Den kan ändras i webbplatsens inställningar.</v>
+        <v>OpenEXR, AVIF, JPEG (även JPEG med gain map), PNG – och HEIC i Safari.</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Choose another</v>
       </c>
       <c r="B429" t="str">
-        <v>Den här webbläsaren kan inte identifiera skärmar; bara den automatiska uppdateringen ovan gäller.</v>
+        <v>Välj en annan</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>Could not identify displays.</v>
+        <v>Clear</v>
       </c>
       <c r="B430" t="str">
-        <v>Kunde inte identifiera skärmar.</v>
+        <v>Rensa</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>Display events</v>
+        <v>Embedded ICC profile</v>
       </c>
       <c r="B431" t="str">
-        <v>Skärmhändelser</v>
+        <v>Inbäddad ICC-profil</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>none — OpenEXR states colour through chromaticities</v>
       </c>
       <c r="B432" t="str">
-        <v>Inga händelser än. Dra fönstret till en annan skärm.</v>
+        <v>ingen – OpenEXR anger färg genom kromaticiteter</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Colour primaries</v>
+        <v>checking…</v>
       </c>
       <c r="B433" t="str">
-        <v>Färgprimärer</v>
+        <v>kontrollerar…</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Transfer characteristics</v>
+        <v>none</v>
       </c>
       <c r="B434" t="str">
-        <v>Överföringsfunktion</v>
+        <v>ingen</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Matrix coefficients</v>
+        <v>Open in Profile tab</v>
       </c>
       <c r="B435" t="str">
-        <v>Matriskoefficienter</v>
+        <v>Öppna på fliken Profil</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Video full-range flag</v>
+        <v>Gain map</v>
       </c>
       <c r="B436" t="str">
-        <v>Flagga för fullt videoomfång</v>
+        <v>Gain map</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>Full range</v>
+        <v>detected, not decoded</v>
       </c>
       <c r="B437" t="str">
-        <v>Fullt omfång</v>
+        <v>hittad, inte avkodad</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>Narrow range</v>
+        <v>That is not an image. Load profiles through the Profiles pane.</v>
       </c>
       <c r="B438" t="str">
-        <v>Begränsat omfång</v>
+        <v>Det är ingen bild. Läs in profiler via profilpanelen.</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Not an image format profiletool recognises.</v>
       </c>
       <c r="B439" t="str">
-        <v>inte tilldelad av ITU-T H.273</v>
+        <v>Inte ett bildformat som profiletool känner igen.</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>TIFF pixels are not shown here yet: browsers do not decode TIFF, and how HDR is encoded in a 16-bit TIFF is still undecided (Phase 4.3). Its embedded profile can be inspected.</v>
       </c>
       <c r="B440" t="str">
-        <v>Färgprimärer 2 (Ospecificerad) hänvisar till profilen själv — primärerna hämtas från färgämnestaggarna och inte från den här taggen.</v>
+        <v>TIFF-pixlar visas inte här ännu: webbläsare avkodar inte TIFF, och hur HDR kodas i en 16-bitars TIFF är ännu inte bestämt (fas 4.3). Den inbäddade profilen kan granskas.</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Cannot display this image here:</v>
       </c>
       <c r="B441" t="str">
-        <v>De fyra reserverade byten i den här taggen är inte alla noll.</v>
+        <v>Bilden kan inte visas här:</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>REPORT</v>
+        <v>Its embedded profile can still be inspected.</v>
       </c>
       <c r="B442" t="str">
-        <v>RAPPORT</v>
+        <v>Den inbäddade profilen kan ändå granskas.</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>FAIL</v>
+        <v>Shown by</v>
       </c>
       <c r="B443" t="str">
-        <v>UNDERKÄND</v>
+        <v>Visas av</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>checks</v>
+        <v>the browser</v>
       </c>
       <c r="B444" t="str">
-        <v>kontroller</v>
+        <v>webbläsaren</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>profiletool</v>
       </c>
       <c r="B445" t="str">
-        <v>Genererad av iccPawgReport (iccDEV) · checklista från ICC Profile Assessment Working Group.</v>
+        <v>profiletool</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>HDR display</v>
       </c>
       <c r="B446" t="str">
-        <v>ICC-profilverktyg · drivs av IccProfLib</v>
+        <v>HDR-skärm</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Browsers ignore HDR that is signalled only by an embedded ICC profile, so this image may look dim and flat.</v>
       </c>
       <c r="B447" t="str">
-        <v>ICC-profilverktyg</v>
+        <v>Webbläsare ignorerar HDR som bara anges av en inbäddad ICC-profil, så bilden kan se matt och platt ut.</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Powered by {lib}</v>
+        <v>This browser cannot switch an image between SDR and HDR, so it is shown as the browser renders it.</v>
       </c>
       <c r="B448" t="str">
-        <v>Drivs av {lib}</v>
+        <v>Den här webbläsaren kan inte växla en bild mellan SDR och HDR, så den visas som webbläsaren återger den.</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>Subscribe</v>
+        <v>The browser could not decode this image.</v>
       </c>
       <c r="B449" t="str">
-        <v>Prenumerera</v>
+        <v>Webbläsaren kunde inte avkoda bilden.</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Output</v>
       </c>
       <c r="B450" t="str">
-        <v>Få besked om nya profiletool-versioner</v>
+        <v>Utdata</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>Get notified about new releases</v>
+        <v>HDR canvas (float16)</v>
       </c>
       <c r="B451" t="str">
-        <v>Få besked om nya versioner</v>
+        <v>HDR-canvas (float16)</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>Close</v>
+        <v>WebGPU (extended range)</v>
       </c>
       <c r="B452" t="str">
-        <v>Stäng</v>
+        <v>WebGPU (utökat omfång)</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>SDR canvas (tone-mapped)</v>
       </c>
       <c r="B453" t="str">
-        <v>Vi mejlar dig när en ny större eller mindre version av profiletool släpps. Patchversioner hoppas över. Din adress granskas manuellt innan den läggs till.</v>
+        <v>SDR-canvas (tonmappad)</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>Email address</v>
+        <v>Size</v>
       </c>
       <c r="B454" t="str">
-        <v>E-postadress</v>
+        <v>Storlek</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>you@example.com</v>
+        <v>Brightest pixel</v>
       </c>
       <c r="B455" t="str">
-        <v>du@exempel.com</v>
+        <v>Ljusaste pixel</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>How will you use profiletool?</v>
+        <v>{n}× SDR white</v>
       </c>
       <c r="B456" t="str">
-        <v>Hur kommer du att använda profiletool?</v>
+        <v>{n}× SDR-vitt</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>(optional)</v>
+        <v>Chromaticities</v>
       </c>
       <c r="B457" t="str">
-        <v>(valfritt)</v>
+        <v>Kromaticiteter</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>not stated — Rec. 709 assumed</v>
       </c>
       <c r="B458" t="str">
-        <v>t.ex. utvärdera ICC-profiler för tryckkalibrering</v>
+        <v>inte angivna – Rec. 709 antas</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>{from} was not available here ({why}); using the next output.</v>
       </c>
       <c r="B459" t="str">
-        <v>Jag godkänner att ta emot e-post om profiletool-versioner. Jag kan avsluta prenumerationen när som helst.</v>
+        <v>{from} är inte tillgängligt här ({why}); nästa utdata används.</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>Cancel</v>
+        <v>This output cannot carry brighter-than-white values, so the tone-mapped SDR rendering is shown.</v>
       </c>
       <c r="B460" t="str">
-        <v>Avbryt</v>
+        <v>Den här utdatan kan inte bära värden ljusare än vitt, så den tonmappade SDR-återgivningen visas.</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>Subscribe</v>
+        <v>Exposure</v>
       </c>
       <c r="B461" t="str">
-        <v>Prenumerera</v>
+        <v>Exponering</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>{n} stops</v>
       </c>
       <c r="B462" t="str">
-        <v>Tack — vi hör av oss.</v>
+        <v>{n} steg</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Could not decode:</v>
       </c>
       <c r="B463" t="str">
-        <v>När du har godkänts får du ett välkomstmejl. Därefter hör du bara från oss när en ny version av profiletool släpps.</v>
+        <v>Kunde inte avkoda:</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>Close</v>
+        <v>Decoding…</v>
       </c>
       <c r="B464" t="str">
-        <v>Stäng</v>
+        <v>Avkodar…</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>Privacy notice</v>
+        <v>Dynamic range</v>
       </c>
       <c r="B465" t="str">
-        <v>Integritetsmeddelande</v>
+        <v>Dynamiskt omfång</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>This browser offers only the two ends, not a blend.</v>
       </c>
       <c r="B466" t="str">
-        <v>Ange en giltig e-postadress.</v>
+        <v>Den här webbläsaren erbjuder bara de två ändarna, ingen blandning.</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B467" t="str">
-        <v>För många förfrågningar. Försök igen senare.</v>
+        <v>IccProfLib avböjer att tillämpa den här förstärkningskurvan: {why}. En CMM faller tillbaka på nästa tonmappningsbeskrivning (avsnitt 8.10.3).</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Display headroom</v>
       </c>
       <c r="B468" t="str">
-        <v>Kontrollera formuläret och försök igen.</v>
+        <v>Skärmutrymme</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B469" t="str">
-        <v>Det gick inte att skicka din förfrågan. Försök igen.</v>
+        <v>{n} steg (≈{r}× referensvitt)</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Baseline</v>
       </c>
       <c r="B470" t="str">
-        <v>Nätverksfel. Försök igen.</v>
+        <v>Bas</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>Error:</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B471" t="str">
-        <v>Fel:</v>
+        <v>Kurvor i taggen, efter utrymme: {list} steg. Bas {b} steg, HDR-referensvitt {w} cd/m².</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>Convert to XML</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B472" t="str">
-        <v>Konvertera till XML</v>
+        <v>Det här utrymmet ligger utanför taggens kurvor, så närmaste kurva används oförändrad – biblioteket extrapolerar inte bortom dem.</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>Convert to JSON</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B473" t="str">
-        <v>Konvertera till JSON</v>
+        <v>Vissa lutningar är härledda (PCHIP) och inte lagrade i taggen. Härledningen rekonstruerar ett SMPTE-avsnitt, så betrakta de kurvornas form som preliminär.</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>Convert to ICC</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B474" t="str">
-        <v>Konvertera till ICC</v>
+        <v>Taggen begär tonmappning mot referensvitt, så dess kurvor konstrueras av biblioteket i stället för att läsas från filen (en konstruktion från ett kommittéutkast).</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>Converting to XML…</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B475" t="str">
-        <v>Konverterar till XML…</v>
+        <v>Inga alternativa bilder: taggen begär ingen tonmappning, bara en begränsning till skärmens färgvolym.</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>Converting to JSON…</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B476" t="str">
-        <v>Konverterar till JSON…</v>
+        <v>De två kurvorna som blandas vid detta utrymme blandar färgkanalerna olika, så det finns ingen enskild förstärkningskurva att rita. Tonkurvan nedan är ändå exakt.</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>Converting to ICC…</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B477" t="str">
-        <v>Konverterar till ICC…</v>
+        <v>Kurva vid {h} steg (ingen förstärkning)</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>Load ICC profile</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B478" t="str">
-        <v>Läs in ICC-profil</v>
+        <v>Kurva vid {h} steg</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B479" t="str">
-        <v>Släppzon för ICC-profilfiler</v>
+        <v>Tillämpad vid {h} steg</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>Profile ID</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B480" t="str">
-        <v>Profil-ID</v>
+        <v>Förstärkning vid detta utrymme</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>No tags found.</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B481" t="str">
-        <v>Inga taggar hittades.</v>
+        <v>Blandad indata (linjär, 1,0 = HDR-referensvitt)</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>Tag Name</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B482" t="str">
-        <v>Taggnamn</v>
+        <v>Förstärkning (log2-steg)</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>ID</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B483" t="str">
-        <v>ID</v>
+        <v>Gråskalans tonkurva vid detta utrymme</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>Offset</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B484" t="str">
-        <v>Offset</v>
+        <v>Indata (× HDR-referensvitt)</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>Size</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B485" t="str">
-        <v>Storlek</v>
+        <v>Utdata (× HDR-referensvitt)</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>Pad</v>
+        <v>No change</v>
       </c>
       <c r="B486" t="str">
-        <v>Utfyllnad</v>
+        <v>Ingen ändring</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>Bytes changed since load</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B487" t="str">
-        <v>Byte ändrade sedan inläsning</v>
+        <v>Skärmens topp vid {h} steg</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>Type</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B488" t="str">
-        <v>Typ</v>
+        <v>Utdata vid {h} steg</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>Array of {type}</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B489" t="str">
-        <v>Array av {type}</v>
+        <v>HDR, färgomfång och pixelförhållande uppdateras när fönstret flyttas till en skärm där de skiljer sig.</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>(No content)</v>
+        <v>Identify displays</v>
       </c>
       <c r="B490" t="str">
-        <v>(Inget innehåll)</v>
+        <v>Identifiera skärmar</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>bytes</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B491" t="str">
-        <v>byte</v>
+        <v>Ber om tillåtelse att se vilken skärm fönstret ligger på, så att panelen även uppdateras mellan likadana skärmar och visar HDR-utrymme där webbläsaren exponerar det.</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>Loading full description…</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B492" t="str">
-        <v>Läser in fullständig beskrivning…</v>
+        <v>Följer vilken skärm fönstret ligger på.</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>Could not load full description:</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B493" t="str">
-        <v>Kunde inte läsa in fullständig beskrivning:</v>
+        <v>Tillåtelse att identifiera skärmar nekades. Den kan ändras i webbplatsens inställningar.</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B494" t="str">
-        <v>Den här profilen kunde inte tolkas helt och får inte tillämpas. Huvudet och taggkatalogen nedan visas endast för granskning.</v>
+        <v>Den här webbläsaren kan inte identifiera skärmar; bara den automatiska uppdateringen ovan gäller.</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B495" t="str">
-        <v>Tagginnehåll otillgängligt — profilen kunde inte tolkas helt.</v>
+        <v>Kunde inte identifiera skärmar.</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>No validation output</v>
+        <v>Display events</v>
       </c>
       <c r="B496" t="str">
-        <v>Ingen valideringsutdata</v>
+        <v>Skärmhändelser</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>Profile is valid</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B497" t="str">
-        <v>Profilen är giltig</v>
+        <v>Inga händelser än. Dra fönstret till en annan skärm.</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B498" t="str">
-        <v>Profilen har varning(ar)</v>
+        <v>Färgprimärer</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B499" t="str">
-        <v>Profilen följer inte specifikationen</v>
+        <v>Överföringsfunktion</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>Critical validation error</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B500" t="str">
-        <v>Kritiskt valideringsfel</v>
+        <v>Matriskoefficienter</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>Unknown validation status</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B501" t="str">
-        <v>Okänd valideringsstatus</v>
+        <v>Flagga för fullt videoomfång</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Full range</v>
       </c>
       <c r="B502" t="str">
-        <v>Kritiskt — visas endast för granskning</v>
+        <v>Fullt omfång</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Narrow range</v>
       </c>
       <c r="B503" t="str">
-        <v>Inga varningar eller fel hittades.</v>
+        <v>Begränsat omfång</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>Valid</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B504" t="str">
-        <v>Giltig</v>
+        <v>inte tilldelad av ITU-T H.273</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>Warning</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B505" t="str">
-        <v>Varning</v>
+        <v>Färgprimärer 2 (Ospecificerad) hänvisar till profilen själv — primärerna hämtas från färgämnestaggarna och inte från den här taggen.</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>Error</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B506" t="str">
-        <v>Fel</v>
+        <v>De fyra reserverade byten i den här taggen är inte alla noll.</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>Unknown</v>
+        <v>REPORT</v>
       </c>
       <c r="B507" t="str">
-        <v>Okänd</v>
+        <v>RAPPORT</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>Pass</v>
+        <v>FAIL</v>
       </c>
       <c r="B508" t="str">
-        <v>Godkänd</v>
+        <v>UNDERKÄND</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>Fail</v>
+        <v>checks</v>
       </c>
       <c r="B509" t="str">
-        <v>Underkänd</v>
+        <v>kontroller</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>View in context</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B510" t="str">
-        <v>Visa i sammanhang</v>
+        <v>Genererad av iccPawgReport (iccDEV) · checklista från ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>Validation detail</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B511" t="str">
-        <v>Valideringsdetalj</v>
+        <v>ICC-profilverktyg · drivs av IccProfLib</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>Triggered by</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B512" t="str">
-        <v>Utlöst av</v>
+        <v>ICC-profilverktyg</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Field</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B513" t="str">
-        <v>Fält</v>
+        <v>Drivs av {lib}</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>Current value</v>
+        <v>Subscribe</v>
       </c>
       <c r="B514" t="str">
-        <v>Aktuellt värde</v>
+        <v>Prenumerera</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Required: 0</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B515" t="str">
-        <v>Krävs: 0</v>
+        <v>Få besked om nya profiletool-versioner</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>Expected: {value}</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B516" t="str">
-        <v>Förväntat: {value}</v>
+        <v>Få besked om nya versioner</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>Invalid</v>
+        <v>Close</v>
       </c>
       <c r="B517" t="str">
-        <v>Ogiltigt</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B518" t="str">
-        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
+        <v>Vi mejlar dig när en ny större eller mindre version av profiletool släpps. Patchversioner hoppas över. Din adress granskas manuellt innan den läggs till.</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>Close</v>
+        <v>Email address</v>
       </c>
       <c r="B519" t="str">
-        <v>Stäng</v>
+        <v>E-postadress</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>Loading XML editor…</v>
+        <v>you@example.com</v>
       </c>
       <c r="B520" t="str">
-        <v>Läser in XML-redigeraren…</v>
+        <v>du@exempel.com</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>Loading JSON editor…</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B521" t="str">
-        <v>Läser in JSON-redigeraren…</v>
+        <v>Hur kommer du att använda profiletool?</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>(optional)</v>
       </c>
       <c r="B522" t="str">
-        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>(valfritt)</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B523" t="str">
-        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>t.ex. utvärdera ICC-profiler för tryckkalibrering</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>● unsaved XML edits</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B524" t="str">
-        <v>● osparade XML-ändringar</v>
+        <v>Jag godkänner att ta emot e-post om profiletool-versioner. Jag kan avsluta prenumerationen när som helst.</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Cancel</v>
       </c>
       <c r="B525" t="str">
-        <v>● osparade JSON-ändringar</v>
+        <v>Avbryt</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B526" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
+        <v>Prenumerera</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B527" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
+        <v>Tack — vi hör av oss.</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>indent</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B528" t="str">
-        <v>indrag</v>
+        <v>När du har godkänts får du ett välkomstmejl. Därefter hör du bara från oss när en ny version av profiletool släpps.</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>sort keys</v>
+        <v>Close</v>
       </c>
       <c r="B529" t="str">
-        <v>sortera nycklar</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
+        <v>Privacy notice</v>
+      </c>
+      <c r="B530" t="str">
+        <v>Integritetsmeddelande</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="str">
+        <v>Please enter a valid email address.</v>
+      </c>
+      <c r="B531" t="str">
+        <v>Ange en giltig e-postadress.</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="str">
+        <v>Too many requests. Please try again later.</v>
+      </c>
+      <c r="B532" t="str">
+        <v>För många förfrågningar. Försök igen senare.</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="str">
+        <v>Please check the form and try again.</v>
+      </c>
+      <c r="B533" t="str">
+        <v>Kontrollera formuläret och försök igen.</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="str">
+        <v>Could not send your request. Please try again.</v>
+      </c>
+      <c r="B534" t="str">
+        <v>Det gick inte att skicka din förfrågan. Försök igen.</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="str">
+        <v>Network error. Please try again.</v>
+      </c>
+      <c r="B535" t="str">
+        <v>Nätverksfel. Försök igen.</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="str">
+        <v>Error:</v>
+      </c>
+      <c r="B536" t="str">
+        <v>Fel:</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="str">
+        <v>Convert to XML</v>
+      </c>
+      <c r="B537" t="str">
+        <v>Konvertera till XML</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="str">
+        <v>Convert to JSON</v>
+      </c>
+      <c r="B538" t="str">
+        <v>Konvertera till JSON</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="str">
+        <v>Convert to ICC</v>
+      </c>
+      <c r="B539" t="str">
+        <v>Konvertera till ICC</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="str">
+        <v>Converting to XML…</v>
+      </c>
+      <c r="B540" t="str">
+        <v>Konverterar till XML…</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="str">
+        <v>Converting to JSON…</v>
+      </c>
+      <c r="B541" t="str">
+        <v>Konverterar till JSON…</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="str">
+        <v>Converting to ICC…</v>
+      </c>
+      <c r="B542" t="str">
+        <v>Konverterar till ICC…</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="str">
+        <v>Load ICC profile</v>
+      </c>
+      <c r="B543" t="str">
+        <v>Läs in ICC-profil</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="str">
+        <v>Drop zone for ICC profile files</v>
+      </c>
+      <c r="B544" t="str">
+        <v>Släppzon för ICC-profilfiler</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="str">
+        <v>Profile ID</v>
+      </c>
+      <c r="B545" t="str">
+        <v>Profil-ID</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="str">
+        <v>No tags found.</v>
+      </c>
+      <c r="B546" t="str">
+        <v>Inga taggar hittades.</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="str">
+        <v>Tag Name</v>
+      </c>
+      <c r="B547" t="str">
+        <v>Taggnamn</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B548" t="str">
+        <v>ID</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="str">
+        <v>Offset</v>
+      </c>
+      <c r="B549" t="str">
+        <v>Offset</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="str">
+        <v>Size</v>
+      </c>
+      <c r="B550" t="str">
+        <v>Storlek</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="str">
+        <v>Pad</v>
+      </c>
+      <c r="B551" t="str">
+        <v>Utfyllnad</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="str">
+        <v>Bytes changed since load</v>
+      </c>
+      <c r="B552" t="str">
+        <v>Byte ändrade sedan inläsning</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="str">
+        <v>Type</v>
+      </c>
+      <c r="B553" t="str">
+        <v>Typ</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="str">
+        <v>Array of {type}</v>
+      </c>
+      <c r="B554" t="str">
+        <v>Array av {type}</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="str">
+        <v>(No content)</v>
+      </c>
+      <c r="B555" t="str">
+        <v>(Inget innehåll)</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="str">
+        <v>bytes</v>
+      </c>
+      <c r="B556" t="str">
+        <v>byte</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="str">
+        <v>Loading full description…</v>
+      </c>
+      <c r="B557" t="str">
+        <v>Läser in fullständig beskrivning…</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="str">
+        <v>Could not load full description:</v>
+      </c>
+      <c r="B558" t="str">
+        <v>Kunde inte läsa in fullständig beskrivning:</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="str">
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+      </c>
+      <c r="B559" t="str">
+        <v>Den här profilen kunde inte tolkas helt och får inte tillämpas. Huvudet och taggkatalogen nedan visas endast för granskning.</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="str">
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+      </c>
+      <c r="B560" t="str">
+        <v>Tagginnehåll otillgängligt — profilen kunde inte tolkas helt.</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="str">
+        <v>No validation output</v>
+      </c>
+      <c r="B561" t="str">
+        <v>Ingen valideringsutdata</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="str">
+        <v>Profile is valid</v>
+      </c>
+      <c r="B562" t="str">
+        <v>Profilen är giltig</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="str">
+        <v>Profile has warning(s)</v>
+      </c>
+      <c r="B563" t="str">
+        <v>Profilen har varning(ar)</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="str">
+        <v>Profile is non-compliant</v>
+      </c>
+      <c r="B564" t="str">
+        <v>Profilen följer inte specifikationen</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="str">
+        <v>Critical validation error</v>
+      </c>
+      <c r="B565" t="str">
+        <v>Kritiskt valideringsfel</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="str">
+        <v>Unknown validation status</v>
+      </c>
+      <c r="B566" t="str">
+        <v>Okänd valideringsstatus</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="str">
+        <v>Critical — shown for inspection only</v>
+      </c>
+      <c r="B567" t="str">
+        <v>Kritiskt — visas endast för granskning</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="str">
+        <v>No warnings or errors found.</v>
+      </c>
+      <c r="B568" t="str">
+        <v>Inga varningar eller fel hittades.</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="B569" t="str">
+        <v>Giltig</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="str">
+        <v>Warning</v>
+      </c>
+      <c r="B570" t="str">
+        <v>Varning</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="str">
+        <v>Error</v>
+      </c>
+      <c r="B571" t="str">
+        <v>Fel</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B572" t="str">
+        <v>Okänd</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B573" t="str">
+        <v>Godkänd</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B574" t="str">
+        <v>Underkänd</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B575" t="str">
+        <v>Visa i sammanhang</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B576" t="str">
+        <v>Valideringsdetalj</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B577" t="str">
+        <v>Utlöst av</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B578" t="str">
+        <v>Fält</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B579" t="str">
+        <v>Aktuellt värde</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B580" t="str">
+        <v>Krävs: 0</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B581" t="str">
+        <v>Förväntat: {value}</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B582" t="str">
+        <v>Ogiltigt</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B583" t="str">
+        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B584" t="str">
+        <v>Stäng</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B585" t="str">
+        <v>Läser in XML-redigeraren…</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B586" t="str">
+        <v>Läser in JSON-redigeraren…</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B587" t="str">
+        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B588" t="str">
+        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B589" t="str">
+        <v>● osparade XML-ändringar</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B590" t="str">
+        <v>● osparade JSON-ändringar</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B591" t="str">
+        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B592" t="str">
+        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B593" t="str">
+        <v>indrag</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B594" t="str">
+        <v>sortera nycklar</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B530" t="str">
+      <c r="B595" t="str">
         <v>Profilen skrevs från ändringarna, men omvalideringen misslyckades:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B530"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B595"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Sv.xlsx
+++ b/translations/Eng-Sv.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B595"/>
+  <dimension ref="A1:B612"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -3894,7 +3894,7 @@
         <v>Gain map</v>
       </c>
       <c r="B436" t="str">
-        <v>Gain map</v>
+        <v>Förstärkningskarta</v>
       </c>
     </row>
     <row r="437">
@@ -4139,1039 +4139,1175 @@
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>decoded by profiletool itself, so browser-independent</v>
       </c>
       <c r="B467" t="str">
-        <v>IccProfLib avböjer att tillämpa den här förstärkningskurvan: {why}. En CMM faller tillbaka på nästa tonmappningsbeskrivning (avsnitt 8.10.3).</v>
+        <v>avkodas av profiletool själv, så oberoende av webbläsaren</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>Display headroom</v>
+        <v>this browser decodes it</v>
       </c>
       <c r="B468" t="str">
-        <v>Skärmutrymme</v>
+        <v>den här webbläsaren avkodar det</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>this browser does not decode it</v>
       </c>
       <c r="B469" t="str">
-        <v>{n} steg (≈{r}× referensvitt)</v>
+        <v>den här webbläsaren avkodar det inte</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>Baseline</v>
+        <v>HEIC display needs Safari or another WebKit browser — Chrome and Firefox decode HEIC on no platform, macOS included</v>
       </c>
       <c r="B470" t="str">
-        <v>Bas</v>
+        <v>HEIC-visning kräver Safari eller en annan WebKit-webbläsare – Chrome och Firefox avkodar HEIC på ingen plattform, inte heller macOS</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>JPEG XL display needs Safari; other browsers have not shipped it</v>
       </c>
       <c r="B471" t="str">
-        <v>Kurvor i taggen, efter utrymme: {list} steg. Bas {b} steg, HDR-referensvitt {w} cd/m².</v>
+        <v>JPEG XL-visning kräver Safari; andra webbläsare har inte stöd än</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>deferred to a later release</v>
       </c>
       <c r="B472" t="str">
-        <v>Det här utrymmet ligger utanför taggens kurvor, så närmaste kurva används oförändrad – biblioteket extrapolerar inte bortom dem.</v>
+        <v>uppskjutet till en senare version</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>this display reports no HDR path, so HDR renders tone-mapped to SDR</v>
       </c>
       <c r="B473" t="str">
-        <v>Vissa lutningar är härledda (PCHIP) och inte lagrade i taggen. Härledningen rekonstruerar ett SMPTE-avsnitt, så betrakta de kurvornas form som preliminär.</v>
+        <v>skärmen rapporterar ingen HDR-väg, så HDR visas tonmappat som SDR</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>this browser exposes no HDR canvas path (needs float16 canvas or WebGPU)</v>
       </c>
       <c r="B474" t="str">
-        <v>Taggen begär tonmappning mot referensvitt, så dess kurvor konstrueras av biblioteket i stället för att läsas från filen (en konstruktion från ett kommittéutkast).</v>
+        <v>webbläsaren har ingen HDR-canvas (kräver float16-canvas eller WebGPU)</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>Firefox renders no HDR images and reads no gain maps; HDR content is shown as SDR</v>
       </c>
       <c r="B475" t="str">
-        <v>Inga alternativa bilder: taggen begär ingen tonmappning, bara en begränsning till skärmens färgvolym.</v>
+        <v>Firefox visar inga HDR-bilder och läser inga gain maps; HDR-innehåll visas som SDR</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>inspection needs a container parse, not a codec</v>
       </c>
       <c r="B476" t="str">
-        <v>De två kurvorna som blandas vid detta utrymme blandar färgkanalerna olika, så det finns ingen enskild förstärkningskurva att rita. Tonkurvan nedan är ändå exakt.</v>
+        <v>granskning kräver bara tolkning av behållaren, ingen codec</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>HDR display and an HDR canvas path are both available</v>
       </c>
       <c r="B477" t="str">
-        <v>Kurva vid {h} steg (ingen förstärkning)</v>
+        <v>både HDR-skärm och HDR-canvas finns</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>Curve at {h} stops</v>
+        <v>unknown format</v>
       </c>
       <c r="B478" t="str">
-        <v>Kurva vid {h} steg</v>
+        <v>okänt format</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>Applied at {h} stops</v>
+        <v>{browser} on {os}</v>
       </c>
       <c r="B479" t="str">
-        <v>Tillämpad vid {h} steg</v>
+        <v>{browser} på {os}</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>{name} · HDR display detected</v>
       </c>
       <c r="B480" t="str">
-        <v>Förstärkning vid detta utrymme</v>
+        <v>{name} · HDR-skärm hittad</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>{name} · SDR display</v>
       </c>
       <c r="B481" t="str">
-        <v>Blandad indata (linjär, 1,0 = HDR-referensvitt)</v>
+        <v>{name} · SDR-skärm</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>WebGPU applied tone mapping “{mode}”, so output is clamped to SDR</v>
       </c>
       <c r="B482" t="str">
-        <v>Förstärkning (log2-steg)</v>
+        <v>WebGPU tillämpade tonmappning ”{mode}”, så utdata begränsas till SDR</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>This browser does not report the WebGPU tone mapping it applied, so HDR output is unconfirmed</v>
       </c>
       <c r="B483" t="str">
-        <v>Gråskalans tonkurva vid detta utrymme</v>
+        <v>Webbläsaren rapporterar inte vilken WebGPU-tonmappning som tillämpades, så HDR-utdata är obekräftad</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B484" t="str">
-        <v>Indata (× HDR-referensvitt)</v>
+        <v>IccProfLib avböjer att tillämpa den här förstärkningskurvan: {why}. En CMM faller tillbaka på nästa tonmappningsbeskrivning (avsnitt 8.10.3).</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Display headroom</v>
       </c>
       <c r="B485" t="str">
-        <v>Utdata (× HDR-referensvitt)</v>
+        <v>Skärmutrymme</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>No change</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B486" t="str">
-        <v>Ingen ändring</v>
+        <v>{n} steg (≈{r}× referensvitt)</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>Baseline</v>
       </c>
       <c r="B487" t="str">
-        <v>Skärmens topp vid {h} steg</v>
+        <v>Bas</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>Output at {h} stops</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B488" t="str">
-        <v>Utdata vid {h} steg</v>
+        <v>Kurvor i taggen, efter utrymme: {list} steg. Bas {b} steg, HDR-referensvitt {w} cd/m².</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B489" t="str">
-        <v>HDR, färgomfång och pixelförhållande uppdateras när fönstret flyttas till en skärm där de skiljer sig.</v>
+        <v>Det här utrymmet ligger utanför taggens kurvor, så närmaste kurva används oförändrad – biblioteket extrapolerar inte bortom dem.</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>Identify displays</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B490" t="str">
-        <v>Identifiera skärmar</v>
+        <v>Vissa lutningar är härledda (PCHIP) och inte lagrade i taggen. Härledningen rekonstruerar ett SMPTE-avsnitt, så betrakta de kurvornas form som preliminär.</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B491" t="str">
-        <v>Ber om tillåtelse att se vilken skärm fönstret ligger på, så att panelen även uppdateras mellan likadana skärmar och visar HDR-utrymme där webbläsaren exponerar det.</v>
+        <v>Taggen begär tonmappning mot referensvitt, så dess kurvor konstrueras av biblioteket i stället för att läsas från filen (en konstruktion från ett kommittéutkast).</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B492" t="str">
-        <v>Följer vilken skärm fönstret ligger på.</v>
+        <v>Inga alternativa bilder: taggen begär ingen tonmappning, bara en begränsning till skärmens färgvolym.</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B493" t="str">
-        <v>Tillåtelse att identifiera skärmar nekades. Den kan ändras i webbplatsens inställningar.</v>
+        <v>De två kurvorna som blandas vid detta utrymme blandar färgkanalerna olika, så det finns ingen enskild förstärkningskurva att rita. Tonkurvan nedan är ändå exakt.</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B494" t="str">
-        <v>Den här webbläsaren kan inte identifiera skärmar; bara den automatiska uppdateringen ovan gäller.</v>
+        <v>Kurva vid {h} steg (ingen förstärkning)</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>Could not identify displays.</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B495" t="str">
-        <v>Kunde inte identifiera skärmar.</v>
+        <v>Kurva vid {h} steg</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>Display events</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B496" t="str">
-        <v>Skärmhändelser</v>
+        <v>Tillämpad vid {h} steg</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B497" t="str">
-        <v>Inga händelser än. Dra fönstret till en annan skärm.</v>
+        <v>Förstärkning vid detta utrymme</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Colour primaries</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B498" t="str">
-        <v>Färgprimärer</v>
+        <v>Blandad indata (linjär, 1,0 = HDR-referensvitt)</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Transfer characteristics</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B499" t="str">
-        <v>Överföringsfunktion</v>
+        <v>Förstärkning (log2-steg)</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>Matrix coefficients</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B500" t="str">
-        <v>Matriskoefficienter</v>
+        <v>Gråskalans tonkurva vid detta utrymme</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>Video full-range flag</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B501" t="str">
-        <v>Flagga för fullt videoomfång</v>
+        <v>Indata (× HDR-referensvitt)</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>Full range</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B502" t="str">
-        <v>Fullt omfång</v>
+        <v>Utdata (× HDR-referensvitt)</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>Narrow range</v>
+        <v>No change</v>
       </c>
       <c r="B503" t="str">
-        <v>Begränsat omfång</v>
+        <v>Ingen ändring</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B504" t="str">
-        <v>inte tilldelad av ITU-T H.273</v>
+        <v>Skärmens topp vid {h} steg</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B505" t="str">
-        <v>Färgprimärer 2 (Ospecificerad) hänvisar till profilen själv — primärerna hämtas från färgämnestaggarna och inte från den här taggen.</v>
+        <v>Utdata vid {h} steg</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B506" t="str">
-        <v>De fyra reserverade byten i den här taggen är inte alla noll.</v>
+        <v>HDR, färgomfång och pixelförhållande uppdateras när fönstret flyttas till en skärm där de skiljer sig.</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>REPORT</v>
+        <v>Identify displays</v>
       </c>
       <c r="B507" t="str">
-        <v>RAPPORT</v>
+        <v>Identifiera skärmar</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>FAIL</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B508" t="str">
-        <v>UNDERKÄND</v>
+        <v>Ber om tillåtelse att se vilken skärm fönstret ligger på, så att panelen även uppdateras mellan likadana skärmar och visar HDR-utrymme där webbläsaren exponerar det.</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>checks</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B509" t="str">
-        <v>kontroller</v>
+        <v>Följer vilken skärm fönstret ligger på.</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B510" t="str">
-        <v>Genererad av iccPawgReport (iccDEV) · checklista från ICC Profile Assessment Working Group.</v>
+        <v>Tillåtelse att identifiera skärmar nekades. Den kan ändras i webbplatsens inställningar.</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B511" t="str">
-        <v>ICC-profilverktyg · drivs av IccProfLib</v>
+        <v>Den här webbläsaren kan inte identifiera skärmar; bara den automatiska uppdateringen ovan gäller.</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B512" t="str">
-        <v>ICC-profilverktyg</v>
+        <v>Kunde inte identifiera skärmar.</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Powered by {lib}</v>
+        <v>Display events</v>
       </c>
       <c r="B513" t="str">
-        <v>Drivs av {lib}</v>
+        <v>Skärmhändelser</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>Subscribe</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B514" t="str">
-        <v>Prenumerera</v>
+        <v>Inga händelser än. Dra fönstret till en annan skärm.</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B515" t="str">
-        <v>Få besked om nya profiletool-versioner</v>
+        <v>Färgprimärer</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>Get notified about new releases</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B516" t="str">
-        <v>Få besked om nya versioner</v>
+        <v>Överföringsfunktion</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>Close</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B517" t="str">
-        <v>Stäng</v>
+        <v>Matriskoefficienter</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B518" t="str">
-        <v>Vi mejlar dig när en ny större eller mindre version av profiletool släpps. Patchversioner hoppas över. Din adress granskas manuellt innan den läggs till.</v>
+        <v>Flagga för fullt videoomfång</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>Email address</v>
+        <v>Full range</v>
       </c>
       <c r="B519" t="str">
-        <v>E-postadress</v>
+        <v>Fullt omfång</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>you@example.com</v>
+        <v>Narrow range</v>
       </c>
       <c r="B520" t="str">
-        <v>du@exempel.com</v>
+        <v>Begränsat omfång</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>How will you use profiletool?</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B521" t="str">
-        <v>Hur kommer du att använda profiletool?</v>
+        <v>inte tilldelad av ITU-T H.273</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>(optional)</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B522" t="str">
-        <v>(valfritt)</v>
+        <v>Färgprimärer 2 (Ospecificerad) hänvisar till profilen själv — primärerna hämtas från färgämnestaggarna och inte från den här taggen.</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B523" t="str">
-        <v>t.ex. utvärdera ICC-profiler för tryckkalibrering</v>
+        <v>De fyra reserverade byten i den här taggen är inte alla noll.</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>REPORT</v>
       </c>
       <c r="B524" t="str">
-        <v>Jag godkänner att ta emot e-post om profiletool-versioner. Jag kan avsluta prenumerationen när som helst.</v>
+        <v>RAPPORT</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>Cancel</v>
+        <v>FAIL</v>
       </c>
       <c r="B525" t="str">
-        <v>Avbryt</v>
+        <v>UNDERKÄND</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>Subscribe</v>
+        <v>checks</v>
       </c>
       <c r="B526" t="str">
-        <v>Prenumerera</v>
+        <v>kontroller</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B527" t="str">
-        <v>Tack — vi hör av oss.</v>
+        <v>Genererad av iccPawgReport (iccDEV) · checklista från ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B528" t="str">
-        <v>När du har godkänts får du ett välkomstmejl. Därefter hör du bara från oss när en ny version av profiletool släpps.</v>
+        <v>ICC-profilverktyg · drivs av IccProfLib</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>Close</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B529" t="str">
-        <v>Stäng</v>
+        <v>ICC-profilverktyg</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>Privacy notice</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B530" t="str">
-        <v>Integritetsmeddelande</v>
+        <v>Drivs av {lib}</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B531" t="str">
-        <v>Ange en giltig e-postadress.</v>
+        <v>Prenumerera</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B532" t="str">
-        <v>För många förfrågningar. Försök igen senare.</v>
+        <v>Få besked om nya profiletool-versioner</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B533" t="str">
-        <v>Kontrollera formuläret och försök igen.</v>
+        <v>Få besked om nya versioner</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Close</v>
       </c>
       <c r="B534" t="str">
-        <v>Det gick inte att skicka din förfrågan. Försök igen.</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>Network error. Please try again.</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B535" t="str">
-        <v>Nätverksfel. Försök igen.</v>
+        <v>Vi mejlar dig när en ny större eller mindre version av profiletool släpps. Patchversioner hoppas över. Din adress granskas manuellt innan den läggs till.</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>Error:</v>
+        <v>Email address</v>
       </c>
       <c r="B536" t="str">
-        <v>Fel:</v>
+        <v>E-postadress</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>Convert to XML</v>
+        <v>you@example.com</v>
       </c>
       <c r="B537" t="str">
-        <v>Konvertera till XML</v>
+        <v>du@exempel.com</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>Convert to JSON</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B538" t="str">
-        <v>Konvertera till JSON</v>
+        <v>Hur kommer du att använda profiletool?</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>Convert to ICC</v>
+        <v>(optional)</v>
       </c>
       <c r="B539" t="str">
-        <v>Konvertera till ICC</v>
+        <v>(valfritt)</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>Converting to XML…</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B540" t="str">
-        <v>Konverterar till XML…</v>
+        <v>t.ex. utvärdera ICC-profiler för tryckkalibrering</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>Converting to JSON…</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B541" t="str">
-        <v>Konverterar till JSON…</v>
+        <v>Jag godkänner att ta emot e-post om profiletool-versioner. Jag kan avsluta prenumerationen när som helst.</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>Converting to ICC…</v>
+        <v>Cancel</v>
       </c>
       <c r="B542" t="str">
-        <v>Konverterar till ICC…</v>
+        <v>Avbryt</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>Load ICC profile</v>
+        <v>Subscribe</v>
       </c>
       <c r="B543" t="str">
-        <v>Läs in ICC-profil</v>
+        <v>Prenumerera</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B544" t="str">
-        <v>Släppzon för ICC-profilfiler</v>
+        <v>Tack — vi hör av oss.</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>Profile ID</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B545" t="str">
-        <v>Profil-ID</v>
+        <v>När du har godkänts får du ett välkomstmejl. Därefter hör du bara från oss när en ny version av profiletool släpps.</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>No tags found.</v>
+        <v>Close</v>
       </c>
       <c r="B546" t="str">
-        <v>Inga taggar hittades.</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>Tag Name</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B547" t="str">
-        <v>Taggnamn</v>
+        <v>Integritetsmeddelande</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>ID</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B548" t="str">
-        <v>ID</v>
+        <v>Ange en giltig e-postadress.</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>Offset</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B549" t="str">
-        <v>Offset</v>
+        <v>För många förfrågningar. Försök igen senare.</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>Size</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B550" t="str">
-        <v>Storlek</v>
+        <v>Kontrollera formuläret och försök igen.</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>Pad</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B551" t="str">
-        <v>Utfyllnad</v>
+        <v>Det gick inte att skicka din förfrågan. Försök igen.</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>Bytes changed since load</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B552" t="str">
-        <v>Byte ändrade sedan inläsning</v>
+        <v>Nätverksfel. Försök igen.</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>Type</v>
+        <v>Error:</v>
       </c>
       <c r="B553" t="str">
-        <v>Typ</v>
+        <v>Fel:</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>Array of {type}</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B554" t="str">
-        <v>Array av {type}</v>
+        <v>Konvertera till XML</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>(No content)</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B555" t="str">
-        <v>(Inget innehåll)</v>
+        <v>Konvertera till JSON</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>bytes</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B556" t="str">
-        <v>byte</v>
+        <v>Konvertera till ICC</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Loading full description…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B557" t="str">
-        <v>Läser in fullständig beskrivning…</v>
+        <v>Konverterar till XML…</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Could not load full description:</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B558" t="str">
-        <v>Kunde inte läsa in fullständig beskrivning:</v>
+        <v>Konverterar till JSON…</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B559" t="str">
-        <v>Den här profilen kunde inte tolkas helt och får inte tillämpas. Huvudet och taggkatalogen nedan visas endast för granskning.</v>
+        <v>Konverterar till ICC…</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B560" t="str">
-        <v>Tagginnehåll otillgängligt — profilen kunde inte tolkas helt.</v>
+        <v>Läs in ICC-profil</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>No validation output</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B561" t="str">
-        <v>Ingen valideringsutdata</v>
+        <v>Släppzon för ICC-profilfiler</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Profile is valid</v>
+        <v>Profile ID</v>
       </c>
       <c r="B562" t="str">
-        <v>Profilen är giltig</v>
+        <v>Profil-ID</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>Profile has warning(s)</v>
+        <v>No tags found.</v>
       </c>
       <c r="B563" t="str">
-        <v>Profilen har varning(ar)</v>
+        <v>Inga taggar hittades.</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Tag Name</v>
       </c>
       <c r="B564" t="str">
-        <v>Profilen följer inte specifikationen</v>
+        <v>Taggnamn</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Critical validation error</v>
+        <v>ID</v>
       </c>
       <c r="B565" t="str">
-        <v>Kritiskt valideringsfel</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Unknown validation status</v>
+        <v>Offset</v>
       </c>
       <c r="B566" t="str">
-        <v>Okänd valideringsstatus</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Size</v>
       </c>
       <c r="B567" t="str">
-        <v>Kritiskt — visas endast för granskning</v>
+        <v>Storlek</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Pad</v>
       </c>
       <c r="B568" t="str">
-        <v>Inga varningar eller fel hittades.</v>
+        <v>Utfyllnad</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Valid</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B569" t="str">
-        <v>Giltig</v>
+        <v>Byte ändrade sedan inläsning</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Warning</v>
+        <v>Type</v>
       </c>
       <c r="B570" t="str">
-        <v>Varning</v>
+        <v>Typ</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Error</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B571" t="str">
-        <v>Fel</v>
+        <v>Array av {type}</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>Unknown</v>
+        <v>(No content)</v>
       </c>
       <c r="B572" t="str">
-        <v>Okänd</v>
+        <v>(Inget innehåll)</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>Pass</v>
+        <v>bytes</v>
       </c>
       <c r="B573" t="str">
-        <v>Godkänd</v>
+        <v>byte</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Fail</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B574" t="str">
-        <v>Underkänd</v>
+        <v>Läser in fullständig beskrivning…</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>View in context</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B575" t="str">
-        <v>Visa i sammanhang</v>
+        <v>Kunde inte läsa in fullständig beskrivning:</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>Validation detail</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B576" t="str">
-        <v>Valideringsdetalj</v>
+        <v>Den här profilen kunde inte tolkas helt och får inte tillämpas. Huvudet och taggkatalogen nedan visas endast för granskning.</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Triggered by</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B577" t="str">
-        <v>Utlöst av</v>
+        <v>Tagginnehåll otillgängligt — profilen kunde inte tolkas helt.</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>Field</v>
+        <v>No validation output</v>
       </c>
       <c r="B578" t="str">
-        <v>Fält</v>
+        <v>Ingen valideringsutdata</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>Current value</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B579" t="str">
-        <v>Aktuellt värde</v>
+        <v>Profilen är giltig</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>Required: 0</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B580" t="str">
-        <v>Krävs: 0</v>
+        <v>Profilen har varning(ar)</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>Expected: {value}</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B581" t="str">
-        <v>Förväntat: {value}</v>
+        <v>Profilen följer inte specifikationen</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Invalid</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B582" t="str">
-        <v>Ogiltigt</v>
+        <v>Kritiskt valideringsfel</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B583" t="str">
-        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
+        <v>Okänd valideringsstatus</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>Close</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B584" t="str">
-        <v>Stäng</v>
+        <v>Kritiskt — visas endast för granskning</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>Loading XML editor…</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B585" t="str">
-        <v>Läser in XML-redigeraren…</v>
+        <v>Inga varningar eller fel hittades.</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Valid</v>
       </c>
       <c r="B586" t="str">
-        <v>Läser in JSON-redigeraren…</v>
+        <v>Giltig</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Warning</v>
       </c>
       <c r="B587" t="str">
-        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>Varning</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Error</v>
       </c>
       <c r="B588" t="str">
-        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>Fel</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Unknown</v>
       </c>
       <c r="B589" t="str">
-        <v>● osparade XML-ändringar</v>
+        <v>Okänd</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Pass</v>
       </c>
       <c r="B590" t="str">
-        <v>● osparade JSON-ändringar</v>
+        <v>Godkänd</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Fail</v>
       </c>
       <c r="B591" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
+        <v>Underkänd</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>View in context</v>
       </c>
       <c r="B592" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
+        <v>Visa i sammanhang</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>indent</v>
+        <v>Validation detail</v>
       </c>
       <c r="B593" t="str">
-        <v>indrag</v>
+        <v>Valideringsdetalj</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>sort keys</v>
+        <v>Triggered by</v>
       </c>
       <c r="B594" t="str">
-        <v>sortera nycklar</v>
+        <v>Utlöst av</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B595" t="str">
+        <v>Fält</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B596" t="str">
+        <v>Aktuellt värde</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B597" t="str">
+        <v>Krävs: 0</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B598" t="str">
+        <v>Förväntat: {value}</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B599" t="str">
+        <v>Ogiltigt</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B600" t="str">
+        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B601" t="str">
+        <v>Stäng</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B602" t="str">
+        <v>Läser in XML-redigeraren…</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B603" t="str">
+        <v>Läser in JSON-redigeraren…</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B604" t="str">
+        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B605" t="str">
+        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B606" t="str">
+        <v>● osparade XML-ändringar</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B607" t="str">
+        <v>● osparade JSON-ändringar</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B608" t="str">
+        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B609" t="str">
+        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B610" t="str">
+        <v>indrag</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B611" t="str">
+        <v>sortera nycklar</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B595" t="str">
+      <c r="B612" t="str">
         <v>Profilen skrevs från ändringarna, men omvalideringen misslyckades:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B595"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B612"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Sv.xlsx
+++ b/translations/Eng-Sv.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B612"/>
+  <dimension ref="A1:B625"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -4275,1039 +4275,1143 @@
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>Display peak</v>
       </c>
       <c r="B484" t="str">
-        <v>IccProfLib avböjer att tillämpa den här förstärkningskurvan: {why}. En CMM faller tillbaka på nästa tonmappningsbeskrivning (avsnitt 8.10.3).</v>
+        <v>Skärmens topp</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>Display headroom</v>
+        <v>{r}× SDR white ({n} stops)</v>
       </c>
       <c r="B485" t="str">
-        <v>Skärmutrymme</v>
+        <v>{r}× SDR-vitt ({n} steg)</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>1× — SDR display</v>
       </c>
       <c r="B486" t="str">
-        <v>{n} steg (≈{r}× referensvitt)</v>
+        <v>1× – SDR-skärm</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>Baseline</v>
+        <v>not known</v>
       </c>
       <c r="B487" t="str">
-        <v>Bas</v>
+        <v>okänd</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>This display reports no HDR, so the browser shows this image in SDR at either end.</v>
       </c>
       <c r="B488" t="str">
-        <v>Kurvor i taggen, efter utrymme: {list} steg. Bas {b} steg, HDR-referensvitt {w} cd/m².</v>
+        <v>Skärmen rapporterar ingen HDR, så webbläsaren visar bilden i SDR i båda ändarna.</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>This display reports no HDR, so everything brighter than SDR white clips. Fit to display shows the tone-mapped rendering instead.</v>
       </c>
       <c r="B489" t="str">
-        <v>Det här utrymmet ligger utanför taggens kurvor, så närmaste kurva används oförändrad – biblioteket extrapolerar inte bortom dem.</v>
+        <v>Skärmen rapporterar ingen HDR, så allt ljusare än SDR-vitt klipps. ”Anpassa till skärm” visar i stället den tonmappade återgivningen.</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>This image asks for {img}× SDR white, but this display shows up to {disp}×, so brighter values clip. Fit to display rolls them off into the display’s peak instead.</v>
       </c>
       <c r="B490" t="str">
-        <v>Vissa lutningar är härledda (PCHIP) och inte lagrade i taggen. Härledningen rekonstruerar ett SMPTE-avsnitt, så betrakta de kurvornas form som preliminär.</v>
+        <v>Bilden kräver {img}× SDR-vitt, men skärmen visar bara upp till {disp}×, så ljusare värden klipps. ”Anpassa till skärm” rundar i stället av dem mot skärmens topp.</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>Fit to display</v>
       </c>
       <c r="B491" t="str">
-        <v>Taggen begär tonmappning mot referensvitt, så dess kurvor konstrueras av biblioteket i stället för att läsas från filen (en konstruktion från ett kommittéutkast).</v>
+        <v>Anpassa till skärm</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
       </c>
       <c r="B492" t="str">
-        <v>Inga alternativa bilder: taggen begär ingen tonmappning, bara en begränsning till skärmens färgvolym.</v>
+        <v>Begränsar ljusstyrkan till den topp skärmen rapporterar. I Windows kan värdet släpa efter ändringar av ljusstyrkan.</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>no limit</v>
       </c>
       <c r="B493" t="str">
-        <v>De två kurvorna som blandas vid detta utrymme blandar färgkanalerna olika, så det finns ingen enskild förstärkningskurva att rita. Tonkurvan nedan är ändå exakt.</v>
+        <v>ingen gräns</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>limit {n} stops ({r}×)</v>
       </c>
       <c r="B494" t="str">
-        <v>Kurva vid {h} steg (ingen förstärkning)</v>
+        <v>gräns {n} steg ({r}×)</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>Curve at {h} stops</v>
+        <v>SDR white</v>
       </c>
       <c r="B495" t="str">
-        <v>Kurva vid {h} steg</v>
+        <v>SDR-vitt</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
       </c>
       <c r="B496" t="str">
-        <v>Tillämpad vid {h} steg</v>
+        <v>Vanligt SDR-vitt för jämförelse. På en HDR-skärm ser HDR-högdagrar ljusare ut än detta.</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B497" t="str">
-        <v>Förstärkning vid detta utrymme</v>
+        <v>IccProfLib avböjer att tillämpa den här förstärkningskurvan: {why}. En CMM faller tillbaka på nästa tonmappningsbeskrivning (avsnitt 8.10.3).</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Display headroom</v>
       </c>
       <c r="B498" t="str">
-        <v>Blandad indata (linjär, 1,0 = HDR-referensvitt)</v>
+        <v>Skärmutrymme</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B499" t="str">
-        <v>Förstärkning (log2-steg)</v>
+        <v>{n} steg (≈{r}× referensvitt)</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>Baseline</v>
       </c>
       <c r="B500" t="str">
-        <v>Gråskalans tonkurva vid detta utrymme</v>
+        <v>Bas</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B501" t="str">
-        <v>Indata (× HDR-referensvitt)</v>
+        <v>Kurvor i taggen, efter utrymme: {list} steg. Bas {b} steg, HDR-referensvitt {w} cd/m².</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B502" t="str">
-        <v>Utdata (× HDR-referensvitt)</v>
+        <v>Det här utrymmet ligger utanför taggens kurvor, så närmaste kurva används oförändrad – biblioteket extrapolerar inte bortom dem.</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>No change</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B503" t="str">
-        <v>Ingen ändring</v>
+        <v>Vissa lutningar är härledda (PCHIP) och inte lagrade i taggen. Härledningen rekonstruerar ett SMPTE-avsnitt, så betrakta de kurvornas form som preliminär.</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B504" t="str">
-        <v>Skärmens topp vid {h} steg</v>
+        <v>Taggen begär tonmappning mot referensvitt, så dess kurvor konstrueras av biblioteket i stället för att läsas från filen (en konstruktion från ett kommittéutkast).</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>Output at {h} stops</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B505" t="str">
-        <v>Utdata vid {h} steg</v>
+        <v>Inga alternativa bilder: taggen begär ingen tonmappning, bara en begränsning till skärmens färgvolym.</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B506" t="str">
-        <v>HDR, färgomfång och pixelförhållande uppdateras när fönstret flyttas till en skärm där de skiljer sig.</v>
+        <v>De två kurvorna som blandas vid detta utrymme blandar färgkanalerna olika, så det finns ingen enskild förstärkningskurva att rita. Tonkurvan nedan är ändå exakt.</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>Identify displays</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B507" t="str">
-        <v>Identifiera skärmar</v>
+        <v>Kurva vid {h} steg (ingen förstärkning)</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B508" t="str">
-        <v>Ber om tillåtelse att se vilken skärm fönstret ligger på, så att panelen även uppdateras mellan likadana skärmar och visar HDR-utrymme där webbläsaren exponerar det.</v>
+        <v>Kurva vid {h} steg</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B509" t="str">
-        <v>Följer vilken skärm fönstret ligger på.</v>
+        <v>Tillämpad vid {h} steg</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B510" t="str">
-        <v>Tillåtelse att identifiera skärmar nekades. Den kan ändras i webbplatsens inställningar.</v>
+        <v>Förstärkning vid detta utrymme</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B511" t="str">
-        <v>Den här webbläsaren kan inte identifiera skärmar; bara den automatiska uppdateringen ovan gäller.</v>
+        <v>Blandad indata (linjär, 1,0 = HDR-referensvitt)</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>Could not identify displays.</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B512" t="str">
-        <v>Kunde inte identifiera skärmar.</v>
+        <v>Förstärkning (log2-steg)</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Display events</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B513" t="str">
-        <v>Skärmhändelser</v>
+        <v>Gråskalans tonkurva vid detta utrymme</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B514" t="str">
-        <v>Inga händelser än. Dra fönstret till en annan skärm.</v>
+        <v>Indata (× HDR-referensvitt)</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Colour primaries</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B515" t="str">
-        <v>Färgprimärer</v>
+        <v>Utdata (× HDR-referensvitt)</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>Transfer characteristics</v>
+        <v>No change</v>
       </c>
       <c r="B516" t="str">
-        <v>Överföringsfunktion</v>
+        <v>Ingen ändring</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>Matrix coefficients</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B517" t="str">
-        <v>Matriskoefficienter</v>
+        <v>Skärmens topp vid {h} steg</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>Video full-range flag</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B518" t="str">
-        <v>Flagga för fullt videoomfång</v>
+        <v>Utdata vid {h} steg</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>Full range</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B519" t="str">
-        <v>Fullt omfång</v>
+        <v>HDR, färgomfång och pixelförhållande uppdateras när fönstret flyttas till en skärm där de skiljer sig.</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>Narrow range</v>
+        <v>Identify displays</v>
       </c>
       <c r="B520" t="str">
-        <v>Begränsat omfång</v>
+        <v>Identifiera skärmar</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B521" t="str">
-        <v>inte tilldelad av ITU-T H.273</v>
+        <v>Ber om tillåtelse att se vilken skärm fönstret ligger på, så att panelen även uppdateras mellan likadana skärmar och visar HDR-utrymme där webbläsaren exponerar det.</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B522" t="str">
-        <v>Färgprimärer 2 (Ospecificerad) hänvisar till profilen själv — primärerna hämtas från färgämnestaggarna och inte från den här taggen.</v>
+        <v>Följer vilken skärm fönstret ligger på.</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B523" t="str">
-        <v>De fyra reserverade byten i den här taggen är inte alla noll.</v>
+        <v>Tillåtelse att identifiera skärmar nekades. Den kan ändras i webbplatsens inställningar.</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>REPORT</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B524" t="str">
-        <v>RAPPORT</v>
+        <v>Den här webbläsaren kan inte identifiera skärmar; bara den automatiska uppdateringen ovan gäller.</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>FAIL</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B525" t="str">
-        <v>UNDERKÄND</v>
+        <v>Kunde inte identifiera skärmar.</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>checks</v>
+        <v>Display events</v>
       </c>
       <c r="B526" t="str">
-        <v>kontroller</v>
+        <v>Skärmhändelser</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B527" t="str">
-        <v>Genererad av iccPawgReport (iccDEV) · checklista från ICC Profile Assessment Working Group.</v>
+        <v>Inga händelser än. Dra fönstret till en annan skärm.</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B528" t="str">
-        <v>ICC-profilverktyg · drivs av IccProfLib</v>
+        <v>Färgprimärer</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B529" t="str">
-        <v>ICC-profilverktyg</v>
+        <v>Överföringsfunktion</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>Powered by {lib}</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B530" t="str">
-        <v>Drivs av {lib}</v>
+        <v>Matriskoefficienter</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>Subscribe</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B531" t="str">
-        <v>Prenumerera</v>
+        <v>Flagga för fullt videoomfång</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Full range</v>
       </c>
       <c r="B532" t="str">
-        <v>Få besked om nya profiletool-versioner</v>
+        <v>Fullt omfång</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>Get notified about new releases</v>
+        <v>Narrow range</v>
       </c>
       <c r="B533" t="str">
-        <v>Få besked om nya versioner</v>
+        <v>Begränsat omfång</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>Close</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B534" t="str">
-        <v>Stäng</v>
+        <v>inte tilldelad av ITU-T H.273</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B535" t="str">
-        <v>Vi mejlar dig när en ny större eller mindre version av profiletool släpps. Patchversioner hoppas över. Din adress granskas manuellt innan den läggs till.</v>
+        <v>Färgprimärer 2 (Ospecificerad) hänvisar till profilen själv — primärerna hämtas från färgämnestaggarna och inte från den här taggen.</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>Email address</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B536" t="str">
-        <v>E-postadress</v>
+        <v>De fyra reserverade byten i den här taggen är inte alla noll.</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>you@example.com</v>
+        <v>REPORT</v>
       </c>
       <c r="B537" t="str">
-        <v>du@exempel.com</v>
+        <v>RAPPORT</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>How will you use profiletool?</v>
+        <v>FAIL</v>
       </c>
       <c r="B538" t="str">
-        <v>Hur kommer du att använda profiletool?</v>
+        <v>UNDERKÄND</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>(optional)</v>
+        <v>checks</v>
       </c>
       <c r="B539" t="str">
-        <v>(valfritt)</v>
+        <v>kontroller</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B540" t="str">
-        <v>t.ex. utvärdera ICC-profiler för tryckkalibrering</v>
+        <v>Genererad av iccPawgReport (iccDEV) · checklista från ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B541" t="str">
-        <v>Jag godkänner att ta emot e-post om profiletool-versioner. Jag kan avsluta prenumerationen när som helst.</v>
+        <v>ICC-profilverktyg · drivs av IccProfLib</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>Cancel</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B542" t="str">
-        <v>Avbryt</v>
+        <v>ICC-profilverktyg</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>Subscribe</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B543" t="str">
-        <v>Prenumerera</v>
+        <v>Drivs av {lib}</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B544" t="str">
-        <v>Tack — vi hör av oss.</v>
+        <v>Prenumerera</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B545" t="str">
-        <v>När du har godkänts får du ett välkomstmejl. Därefter hör du bara från oss när en ny version av profiletool släpps.</v>
+        <v>Få besked om nya profiletool-versioner</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>Close</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B546" t="str">
-        <v>Stäng</v>
+        <v>Få besked om nya versioner</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>Privacy notice</v>
+        <v>Close</v>
       </c>
       <c r="B547" t="str">
-        <v>Integritetsmeddelande</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B548" t="str">
-        <v>Ange en giltig e-postadress.</v>
+        <v>Vi mejlar dig när en ny större eller mindre version av profiletool släpps. Patchversioner hoppas över. Din adress granskas manuellt innan den läggs till.</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Email address</v>
       </c>
       <c r="B549" t="str">
-        <v>För många förfrågningar. Försök igen senare.</v>
+        <v>E-postadress</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>Please check the form and try again.</v>
+        <v>you@example.com</v>
       </c>
       <c r="B550" t="str">
-        <v>Kontrollera formuläret och försök igen.</v>
+        <v>du@exempel.com</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B551" t="str">
-        <v>Det gick inte att skicka din förfrågan. Försök igen.</v>
+        <v>Hur kommer du att använda profiletool?</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>Network error. Please try again.</v>
+        <v>(optional)</v>
       </c>
       <c r="B552" t="str">
-        <v>Nätverksfel. Försök igen.</v>
+        <v>(valfritt)</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>Error:</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B553" t="str">
-        <v>Fel:</v>
+        <v>t.ex. utvärdera ICC-profiler för tryckkalibrering</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>Convert to XML</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B554" t="str">
-        <v>Konvertera till XML</v>
+        <v>Jag godkänner att ta emot e-post om profiletool-versioner. Jag kan avsluta prenumerationen när som helst.</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Convert to JSON</v>
+        <v>Cancel</v>
       </c>
       <c r="B555" t="str">
-        <v>Konvertera till JSON</v>
+        <v>Avbryt</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>Convert to ICC</v>
+        <v>Subscribe</v>
       </c>
       <c r="B556" t="str">
-        <v>Konvertera till ICC</v>
+        <v>Prenumerera</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Converting to XML…</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B557" t="str">
-        <v>Konverterar till XML…</v>
+        <v>Tack — vi hör av oss.</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Converting to JSON…</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B558" t="str">
-        <v>Konverterar till JSON…</v>
+        <v>När du har godkänts får du ett välkomstmejl. Därefter hör du bara från oss när en ny version av profiletool släpps.</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Converting to ICC…</v>
+        <v>Close</v>
       </c>
       <c r="B559" t="str">
-        <v>Konverterar till ICC…</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Load ICC profile</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B560" t="str">
-        <v>Läs in ICC-profil</v>
+        <v>Integritetsmeddelande</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B561" t="str">
-        <v>Släppzon för ICC-profilfiler</v>
+        <v>Ange en giltig e-postadress.</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Profile ID</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B562" t="str">
-        <v>Profil-ID</v>
+        <v>För många förfrågningar. Försök igen senare.</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>No tags found.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B563" t="str">
-        <v>Inga taggar hittades.</v>
+        <v>Kontrollera formuläret och försök igen.</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>Tag Name</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B564" t="str">
-        <v>Taggnamn</v>
+        <v>Det gick inte att skicka din förfrågan. Försök igen.</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>ID</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B565" t="str">
-        <v>ID</v>
+        <v>Nätverksfel. Försök igen.</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Offset</v>
+        <v>Error:</v>
       </c>
       <c r="B566" t="str">
-        <v>Offset</v>
+        <v>Fel:</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Size</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B567" t="str">
-        <v>Storlek</v>
+        <v>Konvertera till XML</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Pad</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B568" t="str">
-        <v>Utfyllnad</v>
+        <v>Konvertera till JSON</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Bytes changed since load</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B569" t="str">
-        <v>Byte ändrade sedan inläsning</v>
+        <v>Konvertera till ICC</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Type</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B570" t="str">
-        <v>Typ</v>
+        <v>Konverterar till XML…</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Array of {type}</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B571" t="str">
-        <v>Array av {type}</v>
+        <v>Konverterar till JSON…</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>(No content)</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B572" t="str">
-        <v>(Inget innehåll)</v>
+        <v>Konverterar till ICC…</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>bytes</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B573" t="str">
-        <v>byte</v>
+        <v>Läs in ICC-profil</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Loading full description…</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B574" t="str">
-        <v>Läser in fullständig beskrivning…</v>
+        <v>Släppzon för ICC-profilfiler</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>Could not load full description:</v>
+        <v>Profile ID</v>
       </c>
       <c r="B575" t="str">
-        <v>Kunde inte läsa in fullständig beskrivning:</v>
+        <v>Profil-ID</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>No tags found.</v>
       </c>
       <c r="B576" t="str">
-        <v>Den här profilen kunde inte tolkas helt och får inte tillämpas. Huvudet och taggkatalogen nedan visas endast för granskning.</v>
+        <v>Inga taggar hittades.</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Tag Name</v>
       </c>
       <c r="B577" t="str">
-        <v>Tagginnehåll otillgängligt — profilen kunde inte tolkas helt.</v>
+        <v>Taggnamn</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>No validation output</v>
+        <v>ID</v>
       </c>
       <c r="B578" t="str">
-        <v>Ingen valideringsutdata</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>Profile is valid</v>
+        <v>Offset</v>
       </c>
       <c r="B579" t="str">
-        <v>Profilen är giltig</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Size</v>
       </c>
       <c r="B580" t="str">
-        <v>Profilen har varning(ar)</v>
+        <v>Storlek</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Pad</v>
       </c>
       <c r="B581" t="str">
-        <v>Profilen följer inte specifikationen</v>
+        <v>Utfyllnad</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Critical validation error</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B582" t="str">
-        <v>Kritiskt valideringsfel</v>
+        <v>Byte ändrade sedan inläsning</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>Unknown validation status</v>
+        <v>Type</v>
       </c>
       <c r="B583" t="str">
-        <v>Okänd valideringsstatus</v>
+        <v>Typ</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B584" t="str">
-        <v>Kritiskt — visas endast för granskning</v>
+        <v>Array av {type}</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>No warnings or errors found.</v>
+        <v>(No content)</v>
       </c>
       <c r="B585" t="str">
-        <v>Inga varningar eller fel hittades.</v>
+        <v>(Inget innehåll)</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>Valid</v>
+        <v>bytes</v>
       </c>
       <c r="B586" t="str">
-        <v>Giltig</v>
+        <v>byte</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>Warning</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B587" t="str">
-        <v>Varning</v>
+        <v>Läser in fullständig beskrivning…</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Error</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B588" t="str">
-        <v>Fel</v>
+        <v>Kunde inte läsa in fullständig beskrivning:</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Unknown</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B589" t="str">
-        <v>Okänd</v>
+        <v>Den här profilen kunde inte tolkas helt och får inte tillämpas. Huvudet och taggkatalogen nedan visas endast för granskning.</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Pass</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B590" t="str">
-        <v>Godkänd</v>
+        <v>Tagginnehåll otillgängligt — profilen kunde inte tolkas helt.</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Fail</v>
+        <v>No validation output</v>
       </c>
       <c r="B591" t="str">
-        <v>Underkänd</v>
+        <v>Ingen valideringsutdata</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>View in context</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B592" t="str">
-        <v>Visa i sammanhang</v>
+        <v>Profilen är giltig</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Validation detail</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B593" t="str">
-        <v>Valideringsdetalj</v>
+        <v>Profilen har varning(ar)</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Triggered by</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B594" t="str">
-        <v>Utlöst av</v>
+        <v>Profilen följer inte specifikationen</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Field</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B595" t="str">
-        <v>Fält</v>
+        <v>Kritiskt valideringsfel</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Current value</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B596" t="str">
-        <v>Aktuellt värde</v>
+        <v>Okänd valideringsstatus</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Required: 0</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B597" t="str">
-        <v>Krävs: 0</v>
+        <v>Kritiskt — visas endast för granskning</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Expected: {value}</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B598" t="str">
-        <v>Förväntat: {value}</v>
+        <v>Inga varningar eller fel hittades.</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>Invalid</v>
+        <v>Valid</v>
       </c>
       <c r="B599" t="str">
-        <v>Ogiltigt</v>
+        <v>Giltig</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Warning</v>
       </c>
       <c r="B600" t="str">
-        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
+        <v>Varning</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Close</v>
+        <v>Error</v>
       </c>
       <c r="B601" t="str">
-        <v>Stäng</v>
+        <v>Fel</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Loading XML editor…</v>
+        <v>Unknown</v>
       </c>
       <c r="B602" t="str">
-        <v>Läser in XML-redigeraren…</v>
+        <v>Okänd</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Pass</v>
       </c>
       <c r="B603" t="str">
-        <v>Läser in JSON-redigeraren…</v>
+        <v>Godkänd</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Fail</v>
       </c>
       <c r="B604" t="str">
-        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>Underkänd</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>View in context</v>
       </c>
       <c r="B605" t="str">
-        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>Visa i sammanhang</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Validation detail</v>
       </c>
       <c r="B606" t="str">
-        <v>● osparade XML-ändringar</v>
+        <v>Valideringsdetalj</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Triggered by</v>
       </c>
       <c r="B607" t="str">
-        <v>● osparade JSON-ändringar</v>
+        <v>Utlöst av</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Field</v>
       </c>
       <c r="B608" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
+        <v>Fält</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Current value</v>
       </c>
       <c r="B609" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
+        <v>Aktuellt värde</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>indent</v>
+        <v>Required: 0</v>
       </c>
       <c r="B610" t="str">
-        <v>indrag</v>
+        <v>Krävs: 0</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>sort keys</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B611" t="str">
-        <v>sortera nycklar</v>
+        <v>Förväntat: {value}</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B612" t="str">
+        <v>Ogiltigt</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B613" t="str">
+        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B614" t="str">
+        <v>Stäng</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B615" t="str">
+        <v>Läser in XML-redigeraren…</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B616" t="str">
+        <v>Läser in JSON-redigeraren…</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B617" t="str">
+        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B618" t="str">
+        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B619" t="str">
+        <v>● osparade XML-ändringar</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B620" t="str">
+        <v>● osparade JSON-ändringar</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B621" t="str">
+        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B622" t="str">
+        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B623" t="str">
+        <v>indrag</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B624" t="str">
+        <v>sortera nycklar</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B612" t="str">
+      <c r="B625" t="str">
         <v>Profilen skrevs från ändringarna, men omvalideringen misslyckades:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B612"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B625"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Sv.xlsx
+++ b/translations/Eng-Sv.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B625"/>
+  <dimension ref="A1:B627"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -4379,1039 +4379,1055 @@
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>SDR white patch</v>
       </c>
       <c r="B497" t="str">
-        <v>IccProfLib avböjer att tillämpa den här förstärkningskurvan: {why}. En CMM faller tillbaka på nästa tonmappningsbeskrivning (avsnitt 8.10.3).</v>
+        <v>SDR-vit ruta</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Display headroom</v>
+        <v>Drag to move it; double-click to put it back beside the image.</v>
       </c>
       <c r="B498" t="str">
-        <v>Skärmutrymme</v>
+        <v>Dra för att flytta den; dubbelklicka för att sätta tillbaka den bredvid bilden.</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B499" t="str">
-        <v>{n} steg (≈{r}× referensvitt)</v>
+        <v>IccProfLib avböjer att tillämpa den här förstärkningskurvan: {why}. En CMM faller tillbaka på nästa tonmappningsbeskrivning (avsnitt 8.10.3).</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>Baseline</v>
+        <v>Display headroom</v>
       </c>
       <c r="B500" t="str">
-        <v>Bas</v>
+        <v>Skärmutrymme</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B501" t="str">
-        <v>Kurvor i taggen, efter utrymme: {list} steg. Bas {b} steg, HDR-referensvitt {w} cd/m².</v>
+        <v>{n} steg (≈{r}× referensvitt)</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>Baseline</v>
       </c>
       <c r="B502" t="str">
-        <v>Det här utrymmet ligger utanför taggens kurvor, så närmaste kurva används oförändrad – biblioteket extrapolerar inte bortom dem.</v>
+        <v>Bas</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B503" t="str">
-        <v>Vissa lutningar är härledda (PCHIP) och inte lagrade i taggen. Härledningen rekonstruerar ett SMPTE-avsnitt, så betrakta de kurvornas form som preliminär.</v>
+        <v>Kurvor i taggen, efter utrymme: {list} steg. Bas {b} steg, HDR-referensvitt {w} cd/m².</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B504" t="str">
-        <v>Taggen begär tonmappning mot referensvitt, så dess kurvor konstrueras av biblioteket i stället för att läsas från filen (en konstruktion från ett kommittéutkast).</v>
+        <v>Det här utrymmet ligger utanför taggens kurvor, så närmaste kurva används oförändrad – biblioteket extrapolerar inte bortom dem.</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B505" t="str">
-        <v>Inga alternativa bilder: taggen begär ingen tonmappning, bara en begränsning till skärmens färgvolym.</v>
+        <v>Vissa lutningar är härledda (PCHIP) och inte lagrade i taggen. Härledningen rekonstruerar ett SMPTE-avsnitt, så betrakta de kurvornas form som preliminär.</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B506" t="str">
-        <v>De två kurvorna som blandas vid detta utrymme blandar färgkanalerna olika, så det finns ingen enskild förstärkningskurva att rita. Tonkurvan nedan är ändå exakt.</v>
+        <v>Taggen begär tonmappning mot referensvitt, så dess kurvor konstrueras av biblioteket i stället för att läsas från filen (en konstruktion från ett kommittéutkast).</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B507" t="str">
-        <v>Kurva vid {h} steg (ingen förstärkning)</v>
+        <v>Inga alternativa bilder: taggen begär ingen tonmappning, bara en begränsning till skärmens färgvolym.</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>Curve at {h} stops</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B508" t="str">
-        <v>Kurva vid {h} steg</v>
+        <v>De två kurvorna som blandas vid detta utrymme blandar färgkanalerna olika, så det finns ingen enskild förstärkningskurva att rita. Tonkurvan nedan är ändå exakt.</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B509" t="str">
-        <v>Tillämpad vid {h} steg</v>
+        <v>Kurva vid {h} steg (ingen förstärkning)</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B510" t="str">
-        <v>Förstärkning vid detta utrymme</v>
+        <v>Kurva vid {h} steg</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B511" t="str">
-        <v>Blandad indata (linjär, 1,0 = HDR-referensvitt)</v>
+        <v>Tillämpad vid {h} steg</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B512" t="str">
-        <v>Förstärkning (log2-steg)</v>
+        <v>Förstärkning vid detta utrymme</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B513" t="str">
-        <v>Gråskalans tonkurva vid detta utrymme</v>
+        <v>Blandad indata (linjär, 1,0 = HDR-referensvitt)</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B514" t="str">
-        <v>Indata (× HDR-referensvitt)</v>
+        <v>Förstärkning (log2-steg)</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B515" t="str">
-        <v>Utdata (× HDR-referensvitt)</v>
+        <v>Gråskalans tonkurva vid detta utrymme</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>No change</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B516" t="str">
-        <v>Ingen ändring</v>
+        <v>Indata (× HDR-referensvitt)</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B517" t="str">
-        <v>Skärmens topp vid {h} steg</v>
+        <v>Utdata (× HDR-referensvitt)</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>Output at {h} stops</v>
+        <v>No change</v>
       </c>
       <c r="B518" t="str">
-        <v>Utdata vid {h} steg</v>
+        <v>Ingen ändring</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B519" t="str">
-        <v>HDR, färgomfång och pixelförhållande uppdateras när fönstret flyttas till en skärm där de skiljer sig.</v>
+        <v>Skärmens topp vid {h} steg</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>Identify displays</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B520" t="str">
-        <v>Identifiera skärmar</v>
+        <v>Utdata vid {h} steg</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B521" t="str">
-        <v>Ber om tillåtelse att se vilken skärm fönstret ligger på, så att panelen även uppdateras mellan likadana skärmar och visar HDR-utrymme där webbläsaren exponerar det.</v>
+        <v>HDR, färgomfång och pixelförhållande uppdateras när fönstret flyttas till en skärm där de skiljer sig.</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Identify displays</v>
       </c>
       <c r="B522" t="str">
-        <v>Följer vilken skärm fönstret ligger på.</v>
+        <v>Identifiera skärmar</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B523" t="str">
-        <v>Tillåtelse att identifiera skärmar nekades. Den kan ändras i webbplatsens inställningar.</v>
+        <v>Ber om tillåtelse att se vilken skärm fönstret ligger på, så att panelen även uppdateras mellan likadana skärmar och visar HDR-utrymme där webbläsaren exponerar det.</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B524" t="str">
-        <v>Den här webbläsaren kan inte identifiera skärmar; bara den automatiska uppdateringen ovan gäller.</v>
+        <v>Följer vilken skärm fönstret ligger på.</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>Could not identify displays.</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B525" t="str">
-        <v>Kunde inte identifiera skärmar.</v>
+        <v>Tillåtelse att identifiera skärmar nekades. Den kan ändras i webbplatsens inställningar.</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>Display events</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B526" t="str">
-        <v>Skärmhändelser</v>
+        <v>Den här webbläsaren kan inte identifiera skärmar; bara den automatiska uppdateringen ovan gäller.</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B527" t="str">
-        <v>Inga händelser än. Dra fönstret till en annan skärm.</v>
+        <v>Kunde inte identifiera skärmar.</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>Colour primaries</v>
+        <v>Display events</v>
       </c>
       <c r="B528" t="str">
-        <v>Färgprimärer</v>
+        <v>Skärmhändelser</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>Transfer characteristics</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B529" t="str">
-        <v>Överföringsfunktion</v>
+        <v>Inga händelser än. Dra fönstret till en annan skärm.</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>Matrix coefficients</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B530" t="str">
-        <v>Matriskoefficienter</v>
+        <v>Färgprimärer</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>Video full-range flag</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B531" t="str">
-        <v>Flagga för fullt videoomfång</v>
+        <v>Överföringsfunktion</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Full range</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B532" t="str">
-        <v>Fullt omfång</v>
+        <v>Matriskoefficienter</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>Narrow range</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B533" t="str">
-        <v>Begränsat omfång</v>
+        <v>Flagga för fullt videoomfång</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Full range</v>
       </c>
       <c r="B534" t="str">
-        <v>inte tilldelad av ITU-T H.273</v>
+        <v>Fullt omfång</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Narrow range</v>
       </c>
       <c r="B535" t="str">
-        <v>Färgprimärer 2 (Ospecificerad) hänvisar till profilen själv — primärerna hämtas från färgämnestaggarna och inte från den här taggen.</v>
+        <v>Begränsat omfång</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B536" t="str">
-        <v>De fyra reserverade byten i den här taggen är inte alla noll.</v>
+        <v>inte tilldelad av ITU-T H.273</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>REPORT</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B537" t="str">
-        <v>RAPPORT</v>
+        <v>Färgprimärer 2 (Ospecificerad) hänvisar till profilen själv — primärerna hämtas från färgämnestaggarna och inte från den här taggen.</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>FAIL</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B538" t="str">
-        <v>UNDERKÄND</v>
+        <v>De fyra reserverade byten i den här taggen är inte alla noll.</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>checks</v>
+        <v>REPORT</v>
       </c>
       <c r="B539" t="str">
-        <v>kontroller</v>
+        <v>RAPPORT</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>FAIL</v>
       </c>
       <c r="B540" t="str">
-        <v>Genererad av iccPawgReport (iccDEV) · checklista från ICC Profile Assessment Working Group.</v>
+        <v>UNDERKÄND</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>checks</v>
       </c>
       <c r="B541" t="str">
-        <v>ICC-profilverktyg · drivs av IccProfLib</v>
+        <v>kontroller</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B542" t="str">
-        <v>ICC-profilverktyg</v>
+        <v>Genererad av iccPawgReport (iccDEV) · checklista från ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>Powered by {lib}</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B543" t="str">
-        <v>Drivs av {lib}</v>
+        <v>ICC-profilverktyg · drivs av IccProfLib</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>Subscribe</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B544" t="str">
-        <v>Prenumerera</v>
+        <v>ICC-profilverktyg</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B545" t="str">
-        <v>Få besked om nya profiletool-versioner</v>
+        <v>Drivs av {lib}</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>Get notified about new releases</v>
+        <v>Subscribe</v>
       </c>
       <c r="B546" t="str">
-        <v>Få besked om nya versioner</v>
+        <v>Prenumerera</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>Close</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B547" t="str">
-        <v>Stäng</v>
+        <v>Få besked om nya profiletool-versioner</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B548" t="str">
-        <v>Vi mejlar dig när en ny större eller mindre version av profiletool släpps. Patchversioner hoppas över. Din adress granskas manuellt innan den läggs till.</v>
+        <v>Få besked om nya versioner</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>Email address</v>
+        <v>Close</v>
       </c>
       <c r="B549" t="str">
-        <v>E-postadress</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>you@example.com</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B550" t="str">
-        <v>du@exempel.com</v>
+        <v>Vi mejlar dig när en ny större eller mindre version av profiletool släpps. Patchversioner hoppas över. Din adress granskas manuellt innan den läggs till.</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Email address</v>
       </c>
       <c r="B551" t="str">
-        <v>Hur kommer du att använda profiletool?</v>
+        <v>E-postadress</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>(optional)</v>
+        <v>you@example.com</v>
       </c>
       <c r="B552" t="str">
-        <v>(valfritt)</v>
+        <v>du@exempel.com</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B553" t="str">
-        <v>t.ex. utvärdera ICC-profiler för tryckkalibrering</v>
+        <v>Hur kommer du att använda profiletool?</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>(optional)</v>
       </c>
       <c r="B554" t="str">
-        <v>Jag godkänner att ta emot e-post om profiletool-versioner. Jag kan avsluta prenumerationen när som helst.</v>
+        <v>(valfritt)</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Cancel</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B555" t="str">
-        <v>Avbryt</v>
+        <v>t.ex. utvärdera ICC-profiler för tryckkalibrering</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>Subscribe</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B556" t="str">
-        <v>Prenumerera</v>
+        <v>Jag godkänner att ta emot e-post om profiletool-versioner. Jag kan avsluta prenumerationen när som helst.</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Cancel</v>
       </c>
       <c r="B557" t="str">
-        <v>Tack — vi hör av oss.</v>
+        <v>Avbryt</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B558" t="str">
-        <v>När du har godkänts får du ett välkomstmejl. Därefter hör du bara från oss när en ny version av profiletool släpps.</v>
+        <v>Prenumerera</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Close</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B559" t="str">
-        <v>Stäng</v>
+        <v>Tack — vi hör av oss.</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Privacy notice</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B560" t="str">
-        <v>Integritetsmeddelande</v>
+        <v>När du har godkänts får du ett välkomstmejl. Därefter hör du bara från oss när en ny version av profiletool släpps.</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Close</v>
       </c>
       <c r="B561" t="str">
-        <v>Ange en giltig e-postadress.</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B562" t="str">
-        <v>För många förfrågningar. Försök igen senare.</v>
+        <v>Integritetsmeddelande</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B563" t="str">
-        <v>Kontrollera formuläret och försök igen.</v>
+        <v>Ange en giltig e-postadress.</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B564" t="str">
-        <v>Det gick inte att skicka din förfrågan. Försök igen.</v>
+        <v>För många förfrågningar. Försök igen senare.</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B565" t="str">
-        <v>Nätverksfel. Försök igen.</v>
+        <v>Kontrollera formuläret och försök igen.</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Error:</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B566" t="str">
-        <v>Fel:</v>
+        <v>Det gick inte att skicka din förfrågan. Försök igen.</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Convert to XML</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B567" t="str">
-        <v>Konvertera till XML</v>
+        <v>Nätverksfel. Försök igen.</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Convert to JSON</v>
+        <v>Error:</v>
       </c>
       <c r="B568" t="str">
-        <v>Konvertera till JSON</v>
+        <v>Fel:</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B569" t="str">
-        <v>Konvertera till ICC</v>
+        <v>Konvertera till XML</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B570" t="str">
-        <v>Konverterar till XML…</v>
+        <v>Konvertera till JSON</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Converting to JSON…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B571" t="str">
-        <v>Konverterar till JSON…</v>
+        <v>Konvertera till ICC</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B572" t="str">
-        <v>Konverterar till ICC…</v>
+        <v>Konverterar till XML…</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B573" t="str">
-        <v>Läs in ICC-profil</v>
+        <v>Konverterar till JSON…</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B574" t="str">
-        <v>Släppzon för ICC-profilfiler</v>
+        <v>Konverterar till ICC…</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>Profile ID</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B575" t="str">
-        <v>Profil-ID</v>
+        <v>Läs in ICC-profil</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>No tags found.</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B576" t="str">
-        <v>Inga taggar hittades.</v>
+        <v>Släppzon för ICC-profilfiler</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Tag Name</v>
+        <v>Profile ID</v>
       </c>
       <c r="B577" t="str">
-        <v>Taggnamn</v>
+        <v>Profil-ID</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>ID</v>
+        <v>No tags found.</v>
       </c>
       <c r="B578" t="str">
-        <v>ID</v>
+        <v>Inga taggar hittades.</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>Offset</v>
+        <v>Tag Name</v>
       </c>
       <c r="B579" t="str">
-        <v>Offset</v>
+        <v>Taggnamn</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>Size</v>
+        <v>ID</v>
       </c>
       <c r="B580" t="str">
-        <v>Storlek</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>Pad</v>
+        <v>Offset</v>
       </c>
       <c r="B581" t="str">
-        <v>Utfyllnad</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Bytes changed since load</v>
+        <v>Size</v>
       </c>
       <c r="B582" t="str">
-        <v>Byte ändrade sedan inläsning</v>
+        <v>Storlek</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>Type</v>
+        <v>Pad</v>
       </c>
       <c r="B583" t="str">
-        <v>Typ</v>
+        <v>Utfyllnad</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>Array of {type}</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B584" t="str">
-        <v>Array av {type}</v>
+        <v>Byte ändrade sedan inläsning</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>(No content)</v>
+        <v>Type</v>
       </c>
       <c r="B585" t="str">
-        <v>(Inget innehåll)</v>
+        <v>Typ</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>bytes</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B586" t="str">
-        <v>byte</v>
+        <v>Array av {type}</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>Loading full description…</v>
+        <v>(No content)</v>
       </c>
       <c r="B587" t="str">
-        <v>Läser in fullständig beskrivning…</v>
+        <v>(Inget innehåll)</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Could not load full description:</v>
+        <v>bytes</v>
       </c>
       <c r="B588" t="str">
-        <v>Kunde inte läsa in fullständig beskrivning:</v>
+        <v>byte</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B589" t="str">
-        <v>Den här profilen kunde inte tolkas helt och får inte tillämpas. Huvudet och taggkatalogen nedan visas endast för granskning.</v>
+        <v>Läser in fullständig beskrivning…</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B590" t="str">
-        <v>Tagginnehåll otillgängligt — profilen kunde inte tolkas helt.</v>
+        <v>Kunde inte läsa in fullständig beskrivning:</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>No validation output</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B591" t="str">
-        <v>Ingen valideringsutdata</v>
+        <v>Den här profilen kunde inte tolkas helt och får inte tillämpas. Huvudet och taggkatalogen nedan visas endast för granskning.</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Profile is valid</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B592" t="str">
-        <v>Profilen är giltig</v>
+        <v>Tagginnehåll otillgängligt — profilen kunde inte tolkas helt.</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Profile has warning(s)</v>
+        <v>No validation output</v>
       </c>
       <c r="B593" t="str">
-        <v>Profilen har varning(ar)</v>
+        <v>Ingen valideringsutdata</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B594" t="str">
-        <v>Profilen följer inte specifikationen</v>
+        <v>Profilen är giltig</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Critical validation error</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B595" t="str">
-        <v>Kritiskt valideringsfel</v>
+        <v>Profilen har varning(ar)</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Unknown validation status</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B596" t="str">
-        <v>Okänd valideringsstatus</v>
+        <v>Profilen följer inte specifikationen</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B597" t="str">
-        <v>Kritiskt — visas endast för granskning</v>
+        <v>Kritiskt valideringsfel</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B598" t="str">
-        <v>Inga varningar eller fel hittades.</v>
+        <v>Okänd valideringsstatus</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>Valid</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B599" t="str">
-        <v>Giltig</v>
+        <v>Kritiskt — visas endast för granskning</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>Warning</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B600" t="str">
-        <v>Varning</v>
+        <v>Inga varningar eller fel hittades.</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Error</v>
+        <v>Valid</v>
       </c>
       <c r="B601" t="str">
-        <v>Fel</v>
+        <v>Giltig</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Unknown</v>
+        <v>Warning</v>
       </c>
       <c r="B602" t="str">
-        <v>Okänd</v>
+        <v>Varning</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Pass</v>
+        <v>Error</v>
       </c>
       <c r="B603" t="str">
-        <v>Godkänd</v>
+        <v>Fel</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>Fail</v>
+        <v>Unknown</v>
       </c>
       <c r="B604" t="str">
-        <v>Underkänd</v>
+        <v>Okänd</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>View in context</v>
+        <v>Pass</v>
       </c>
       <c r="B605" t="str">
-        <v>Visa i sammanhang</v>
+        <v>Godkänd</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Validation detail</v>
+        <v>Fail</v>
       </c>
       <c r="B606" t="str">
-        <v>Valideringsdetalj</v>
+        <v>Underkänd</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>Triggered by</v>
+        <v>View in context</v>
       </c>
       <c r="B607" t="str">
-        <v>Utlöst av</v>
+        <v>Visa i sammanhang</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Field</v>
+        <v>Validation detail</v>
       </c>
       <c r="B608" t="str">
-        <v>Fält</v>
+        <v>Valideringsdetalj</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>Current value</v>
+        <v>Triggered by</v>
       </c>
       <c r="B609" t="str">
-        <v>Aktuellt värde</v>
+        <v>Utlöst av</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>Required: 0</v>
+        <v>Field</v>
       </c>
       <c r="B610" t="str">
-        <v>Krävs: 0</v>
+        <v>Fält</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>Expected: {value}</v>
+        <v>Current value</v>
       </c>
       <c r="B611" t="str">
-        <v>Förväntat: {value}</v>
+        <v>Aktuellt värde</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>Invalid</v>
+        <v>Required: 0</v>
       </c>
       <c r="B612" t="str">
-        <v>Ogiltigt</v>
+        <v>Krävs: 0</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B613" t="str">
-        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
+        <v>Förväntat: {value}</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>Close</v>
+        <v>Invalid</v>
       </c>
       <c r="B614" t="str">
-        <v>Stäng</v>
+        <v>Ogiltigt</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>Loading XML editor…</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B615" t="str">
-        <v>Läser in XML-redigeraren…</v>
+        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Close</v>
       </c>
       <c r="B616" t="str">
-        <v>Läser in JSON-redigeraren…</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B617" t="str">
-        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>Läser in XML-redigeraren…</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B618" t="str">
-        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>Läser in JSON-redigeraren…</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B619" t="str">
-        <v>● osparade XML-ändringar</v>
+        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B620" t="str">
-        <v>● osparade JSON-ändringar</v>
+        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B621" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
+        <v>● osparade XML-ändringar</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B622" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
+        <v>● osparade JSON-ändringar</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B623" t="str">
-        <v>indrag</v>
+        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>sort keys</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B624" t="str">
-        <v>sortera nycklar</v>
+        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B625" t="str">
+        <v>indrag</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B626" t="str">
+        <v>sortera nycklar</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B625" t="str">
+      <c r="B627" t="str">
         <v>Profilen skrevs från ändringarna, men omvalideringen misslyckades:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B625"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B627"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Sv.xlsx
+++ b/translations/Eng-Sv.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B627"/>
+  <dimension ref="A1:B650"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -4395,1039 +4395,1223 @@
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>Assign profile</v>
       </c>
       <c r="B499" t="str">
-        <v>IccProfLib avböjer att tillämpa den här förstärkningskurvan: {why}. En CMM faller tillbaka på nästa tonmappningsbeskrivning (avsnitt 8.10.3).</v>
+        <v>Tilldela profil</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>Display headroom</v>
+        <v>None — use what the file signals</v>
       </c>
       <c r="B500" t="str">
-        <v>Skärmutrymme</v>
+        <v>Ingen – det filen anger</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>Embedded profile ({n} B)</v>
       </c>
       <c r="B501" t="str">
-        <v>{n} steg (≈{r}× referensvitt)</v>
+        <v>Inbäddad profil ({n} B)</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>Baseline</v>
+        <v>HDR Profiles in the pool</v>
       </c>
       <c r="B502" t="str">
-        <v>Bas</v>
+        <v>HDR-profiler i poolen</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>Profile</v>
       </c>
       <c r="B503" t="str">
-        <v>Kurvor i taggen, efter utrymme: {list} steg. Bas {b} steg, HDR-referensvitt {w} cd/m².</v>
+        <v>Profil</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>embedded profile</v>
       </c>
       <c r="B504" t="str">
-        <v>Det här utrymmet ligger utanför taggens kurvor, så närmaste kurva används oförändrad – biblioteket extrapolerar inte bortom dem.</v>
+        <v>inbäddad profil</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>Colour engine path</v>
       </c>
       <c r="B505" t="str">
-        <v>Vissa lutningar är härledda (PCHIP) och inte lagrade i taggen. Härledningen rekonstruerar ett SMPTE-avsnitt, så betrakta de kurvornas form som preliminär.</v>
+        <v>Färgmotorns väg</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>HDR path, gain curve applied</v>
       </c>
       <c r="B506" t="str">
-        <v>Taggen begär tonmappning mot referensvitt, så dess kurvor konstrueras av biblioteket i stället för att läsas från filen (en konstruktion från ett kommittéutkast).</v>
+        <v>HDR-väg, förstärkningskurva tillämpad</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>HDR path, no gain curve</v>
       </c>
       <c r="B507" t="str">
-        <v>Inga alternativa bilder: taggen begär ingen tonmappning, bara en begränsning till skärmens färgvolym.</v>
+        <v>HDR-väg, ingen förstärkningskurva</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>Baked AToB0 — not the HDR path</v>
       </c>
       <c r="B508" t="str">
-        <v>De två kurvorna som blandas vid detta utrymme blandar färgkanalerna olika, så det finns ingen enskild förstärkningskurva att rita. Tonkurvan nedan är ändå exakt.</v>
+        <v>Förberäknad AToB0 – inte HDR-vägen</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>Transfer</v>
       </c>
       <c r="B509" t="str">
-        <v>Kurva vid {h} steg (ingen förstärkning)</v>
+        <v>Överföring</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>Curve at {h} stops</v>
+        <v>HDR reference white</v>
       </c>
       <c r="B510" t="str">
-        <v>Kurva vid {h} steg</v>
+        <v>HDR-referensvitt</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Target headroom</v>
       </c>
       <c r="B511" t="str">
-        <v>Tillämpad vid {h} steg</v>
+        <v>Målutrymme</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>{r}× reference white ({n} stops)</v>
       </c>
       <c r="B512" t="str">
-        <v>Förstärkning vid detta utrymme</v>
+        <v>{r}× referensvitt ({n} steg)</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Tone mapping</v>
       </c>
       <c r="B513" t="str">
-        <v>Blandad indata (linjär, 1,0 = HDR-referensvitt)</v>
+        <v>Tonmappning</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>Auto (clause 8.10.3 ranking)</v>
       </c>
       <c r="B514" t="str">
-        <v>Förstärkning (log2-steg)</v>
+        <v>Auto (rangordning enligt 8.10.3)</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>Gain curve (HAGC)</v>
       </c>
       <c r="B515" t="str">
-        <v>Gråskalans tonkurva vid detta utrymme</v>
+        <v>Förstärkningskurva (HAGC)</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Baked SDR fallback (AToB0)</v>
       </c>
       <c r="B516" t="str">
-        <v>Indata (× HDR-referensvitt)</v>
+        <v>Förberäknad SDR-reserv (AToB0)</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Off — as a pre-amendment CMM</v>
       </c>
       <c r="B517" t="str">
-        <v>Utdata (× HDR-referensvitt)</v>
+        <v>Av – som en CMM före tillägget</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>No change</v>
+        <v>Applying the profile…</v>
       </c>
       <c r="B518" t="str">
-        <v>Ingen ändring</v>
+        <v>Tillämpar profilen…</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>OpenEXR holds linear light, so it needs a profile whose transfer is Linear (8).</v>
       </c>
       <c r="B519" t="str">
-        <v>Skärmens topp vid {h} steg</v>
+        <v>OpenEXR innehåller linjärt ljus och kräver därför en profil med överföringen Linear (8).</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>Output at {h} stops</v>
+        <v>Assigning a profile needs a 3-channel RGB image.</v>
       </c>
       <c r="B520" t="str">
-        <v>Utdata vid {h} steg</v>
+        <v>Att tilldela en profil kräver en RGB-bild med 3 kanaler.</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>To interpret its values, assign a profile above.</v>
       </c>
       <c r="B521" t="str">
-        <v>HDR, färgomfång och pixelförhållande uppdateras när fönstret flyttas till en skärm där de skiljer sig.</v>
+        <v>Tilldela en profil ovan för att tolka dess värden.</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>Identify displays</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B522" t="str">
-        <v>Identifiera skärmar</v>
+        <v>IccProfLib avböjer att tillämpa den här förstärkningskurvan: {why}. En CMM faller tillbaka på nästa tonmappningsbeskrivning (avsnitt 8.10.3).</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Display headroom</v>
       </c>
       <c r="B523" t="str">
-        <v>Ber om tillåtelse att se vilken skärm fönstret ligger på, så att panelen även uppdateras mellan likadana skärmar och visar HDR-utrymme där webbläsaren exponerar det.</v>
+        <v>Skärmutrymme</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B524" t="str">
-        <v>Följer vilken skärm fönstret ligger på.</v>
+        <v>{n} steg (≈{r}× referensvitt)</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Baseline</v>
       </c>
       <c r="B525" t="str">
-        <v>Tillåtelse att identifiera skärmar nekades. Den kan ändras i webbplatsens inställningar.</v>
+        <v>Bas</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B526" t="str">
-        <v>Den här webbläsaren kan inte identifiera skärmar; bara den automatiska uppdateringen ovan gäller.</v>
+        <v>Kurvor i taggen, efter utrymme: {list} steg. Bas {b} steg, HDR-referensvitt {w} cd/m².</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>Could not identify displays.</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B527" t="str">
-        <v>Kunde inte identifiera skärmar.</v>
+        <v>Det här utrymmet ligger utanför taggens kurvor, så närmaste kurva används oförändrad – biblioteket extrapolerar inte bortom dem.</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>Display events</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B528" t="str">
-        <v>Skärmhändelser</v>
+        <v>Vissa lutningar är härledda (PCHIP) och inte lagrade i taggen. Härledningen rekonstruerar ett SMPTE-avsnitt, så betrakta de kurvornas form som preliminär.</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B529" t="str">
-        <v>Inga händelser än. Dra fönstret till en annan skärm.</v>
+        <v>Taggen begär tonmappning mot referensvitt, så dess kurvor konstrueras av biblioteket i stället för att läsas från filen (en konstruktion från ett kommittéutkast).</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>Colour primaries</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B530" t="str">
-        <v>Färgprimärer</v>
+        <v>Inga alternativa bilder: taggen begär ingen tonmappning, bara en begränsning till skärmens färgvolym.</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>Transfer characteristics</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B531" t="str">
-        <v>Överföringsfunktion</v>
+        <v>De två kurvorna som blandas vid detta utrymme blandar färgkanalerna olika, så det finns ingen enskild förstärkningskurva att rita. Tonkurvan nedan är ändå exakt.</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Matrix coefficients</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B532" t="str">
-        <v>Matriskoefficienter</v>
+        <v>Kurva vid {h} steg (ingen förstärkning)</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>Video full-range flag</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B533" t="str">
-        <v>Flagga för fullt videoomfång</v>
+        <v>Kurva vid {h} steg</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>Full range</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B534" t="str">
-        <v>Fullt omfång</v>
+        <v>Tillämpad vid {h} steg</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>Narrow range</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B535" t="str">
-        <v>Begränsat omfång</v>
+        <v>Förstärkning vid detta utrymme</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B536" t="str">
-        <v>inte tilldelad av ITU-T H.273</v>
+        <v>Blandad indata (linjär, 1,0 = HDR-referensvitt)</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B537" t="str">
-        <v>Färgprimärer 2 (Ospecificerad) hänvisar till profilen själv — primärerna hämtas från färgämnestaggarna och inte från den här taggen.</v>
+        <v>Förstärkning (log2-steg)</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B538" t="str">
-        <v>De fyra reserverade byten i den här taggen är inte alla noll.</v>
+        <v>Gråskalans tonkurva vid detta utrymme</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>REPORT</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B539" t="str">
-        <v>RAPPORT</v>
+        <v>Indata (× HDR-referensvitt)</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>FAIL</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B540" t="str">
-        <v>UNDERKÄND</v>
+        <v>Utdata (× HDR-referensvitt)</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>checks</v>
+        <v>No change</v>
       </c>
       <c r="B541" t="str">
-        <v>kontroller</v>
+        <v>Ingen ändring</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B542" t="str">
-        <v>Genererad av iccPawgReport (iccDEV) · checklista från ICC Profile Assessment Working Group.</v>
+        <v>Skärmens topp vid {h} steg</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B543" t="str">
-        <v>ICC-profilverktyg · drivs av IccProfLib</v>
+        <v>Utdata vid {h} steg</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>ICC Profile Tool</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B544" t="str">
-        <v>ICC-profilverktyg</v>
+        <v>HDR, färgomfång och pixelförhållande uppdateras när fönstret flyttas till en skärm där de skiljer sig.</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>Powered by {lib}</v>
+        <v>Identify displays</v>
       </c>
       <c r="B545" t="str">
-        <v>Drivs av {lib}</v>
+        <v>Identifiera skärmar</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>Subscribe</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B546" t="str">
-        <v>Prenumerera</v>
+        <v>Ber om tillåtelse att se vilken skärm fönstret ligger på, så att panelen även uppdateras mellan likadana skärmar och visar HDR-utrymme där webbläsaren exponerar det.</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B547" t="str">
-        <v>Få besked om nya profiletool-versioner</v>
+        <v>Följer vilken skärm fönstret ligger på.</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>Get notified about new releases</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B548" t="str">
-        <v>Få besked om nya versioner</v>
+        <v>Tillåtelse att identifiera skärmar nekades. Den kan ändras i webbplatsens inställningar.</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>Close</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B549" t="str">
-        <v>Stäng</v>
+        <v>Den här webbläsaren kan inte identifiera skärmar; bara den automatiska uppdateringen ovan gäller.</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B550" t="str">
-        <v>Vi mejlar dig när en ny större eller mindre version av profiletool släpps. Patchversioner hoppas över. Din adress granskas manuellt innan den läggs till.</v>
+        <v>Kunde inte identifiera skärmar.</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>Email address</v>
+        <v>Display events</v>
       </c>
       <c r="B551" t="str">
-        <v>E-postadress</v>
+        <v>Skärmhändelser</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>you@example.com</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B552" t="str">
-        <v>du@exempel.com</v>
+        <v>Inga händelser än. Dra fönstret till en annan skärm.</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B553" t="str">
-        <v>Hur kommer du att använda profiletool?</v>
+        <v>Färgprimärer</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>(optional)</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B554" t="str">
-        <v>(valfritt)</v>
+        <v>Överföringsfunktion</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B555" t="str">
-        <v>t.ex. utvärdera ICC-profiler för tryckkalibrering</v>
+        <v>Matriskoefficienter</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B556" t="str">
-        <v>Jag godkänner att ta emot e-post om profiletool-versioner. Jag kan avsluta prenumerationen när som helst.</v>
+        <v>Flagga för fullt videoomfång</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Cancel</v>
+        <v>Full range</v>
       </c>
       <c r="B557" t="str">
-        <v>Avbryt</v>
+        <v>Fullt omfång</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Subscribe</v>
+        <v>Narrow range</v>
       </c>
       <c r="B558" t="str">
-        <v>Prenumerera</v>
+        <v>Begränsat omfång</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B559" t="str">
-        <v>Tack — vi hör av oss.</v>
+        <v>inte tilldelad av ITU-T H.273</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B560" t="str">
-        <v>När du har godkänts får du ett välkomstmejl. Därefter hör du bara från oss när en ny version av profiletool släpps.</v>
+        <v>Färgprimärer 2 (Ospecificerad) hänvisar till profilen själv — primärerna hämtas från färgämnestaggarna och inte från den här taggen.</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>Close</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B561" t="str">
-        <v>Stäng</v>
+        <v>De fyra reserverade byten i den här taggen är inte alla noll.</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Privacy notice</v>
+        <v>REPORT</v>
       </c>
       <c r="B562" t="str">
-        <v>Integritetsmeddelande</v>
+        <v>RAPPORT</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>FAIL</v>
       </c>
       <c r="B563" t="str">
-        <v>Ange en giltig e-postadress.</v>
+        <v>UNDERKÄND</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>checks</v>
       </c>
       <c r="B564" t="str">
-        <v>För många förfrågningar. Försök igen senare.</v>
+        <v>kontroller</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B565" t="str">
-        <v>Kontrollera formuläret och försök igen.</v>
+        <v>Genererad av iccPawgReport (iccDEV) · checklista från ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B566" t="str">
-        <v>Det gick inte att skicka din förfrågan. Försök igen.</v>
+        <v>ICC-profilverktyg · drivs av IccProfLib</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Network error. Please try again.</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B567" t="str">
-        <v>Nätverksfel. Försök igen.</v>
+        <v>ICC-profilverktyg</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Error:</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B568" t="str">
-        <v>Fel:</v>
+        <v>Drivs av {lib}</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Convert to XML</v>
+        <v>Subscribe</v>
       </c>
       <c r="B569" t="str">
-        <v>Konvertera till XML</v>
+        <v>Prenumerera</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Convert to JSON</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B570" t="str">
-        <v>Konvertera till JSON</v>
+        <v>Få besked om nya profiletool-versioner</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Convert to ICC</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B571" t="str">
-        <v>Konvertera till ICC</v>
+        <v>Få besked om nya versioner</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>Converting to XML…</v>
+        <v>Close</v>
       </c>
       <c r="B572" t="str">
-        <v>Konverterar till XML…</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>Converting to JSON…</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B573" t="str">
-        <v>Konverterar till JSON…</v>
+        <v>Vi mejlar dig när en ny större eller mindre version av profiletool släpps. Patchversioner hoppas över. Din adress granskas manuellt innan den läggs till.</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Converting to ICC…</v>
+        <v>Email address</v>
       </c>
       <c r="B574" t="str">
-        <v>Konverterar till ICC…</v>
+        <v>E-postadress</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>Load ICC profile</v>
+        <v>you@example.com</v>
       </c>
       <c r="B575" t="str">
-        <v>Läs in ICC-profil</v>
+        <v>du@exempel.com</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B576" t="str">
-        <v>Släppzon för ICC-profilfiler</v>
+        <v>Hur kommer du att använda profiletool?</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Profile ID</v>
+        <v>(optional)</v>
       </c>
       <c r="B577" t="str">
-        <v>Profil-ID</v>
+        <v>(valfritt)</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>No tags found.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B578" t="str">
-        <v>Inga taggar hittades.</v>
+        <v>t.ex. utvärdera ICC-profiler för tryckkalibrering</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>Tag Name</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B579" t="str">
-        <v>Taggnamn</v>
+        <v>Jag godkänner att ta emot e-post om profiletool-versioner. Jag kan avsluta prenumerationen när som helst.</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>ID</v>
+        <v>Cancel</v>
       </c>
       <c r="B580" t="str">
-        <v>ID</v>
+        <v>Avbryt</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>Offset</v>
+        <v>Subscribe</v>
       </c>
       <c r="B581" t="str">
-        <v>Offset</v>
+        <v>Prenumerera</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Size</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B582" t="str">
-        <v>Storlek</v>
+        <v>Tack — vi hör av oss.</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>Pad</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B583" t="str">
-        <v>Utfyllnad</v>
+        <v>När du har godkänts får du ett välkomstmejl. Därefter hör du bara från oss när en ny version av profiletool släpps.</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>Bytes changed since load</v>
+        <v>Close</v>
       </c>
       <c r="B584" t="str">
-        <v>Byte ändrade sedan inläsning</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>Type</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B585" t="str">
-        <v>Typ</v>
+        <v>Integritetsmeddelande</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>Array of {type}</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B586" t="str">
-        <v>Array av {type}</v>
+        <v>Ange en giltig e-postadress.</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>(No content)</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B587" t="str">
-        <v>(Inget innehåll)</v>
+        <v>För många förfrågningar. Försök igen senare.</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>bytes</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B588" t="str">
-        <v>byte</v>
+        <v>Kontrollera formuläret och försök igen.</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Loading full description…</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B589" t="str">
-        <v>Läser in fullständig beskrivning…</v>
+        <v>Det gick inte att skicka din förfrågan. Försök igen.</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Could not load full description:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B590" t="str">
-        <v>Kunde inte läsa in fullständig beskrivning:</v>
+        <v>Nätverksfel. Försök igen.</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Error:</v>
       </c>
       <c r="B591" t="str">
-        <v>Den här profilen kunde inte tolkas helt och får inte tillämpas. Huvudet och taggkatalogen nedan visas endast för granskning.</v>
+        <v>Fel:</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B592" t="str">
-        <v>Tagginnehåll otillgängligt — profilen kunde inte tolkas helt.</v>
+        <v>Konvertera till XML</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>No validation output</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B593" t="str">
-        <v>Ingen valideringsutdata</v>
+        <v>Konvertera till JSON</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Profile is valid</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B594" t="str">
-        <v>Profilen är giltig</v>
+        <v>Konvertera till ICC</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B595" t="str">
-        <v>Profilen har varning(ar)</v>
+        <v>Konverterar till XML…</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B596" t="str">
-        <v>Profilen följer inte specifikationen</v>
+        <v>Konverterar till JSON…</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Critical validation error</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B597" t="str">
-        <v>Kritiskt valideringsfel</v>
+        <v>Konverterar till ICC…</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Unknown validation status</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B598" t="str">
-        <v>Okänd valideringsstatus</v>
+        <v>Läs in ICC-profil</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B599" t="str">
-        <v>Kritiskt — visas endast för granskning</v>
+        <v>Släppzon för ICC-profilfiler</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B600" t="str">
-        <v>Inga varningar eller fel hittades.</v>
+        <v>Profil-ID</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Valid</v>
+        <v>No tags found.</v>
       </c>
       <c r="B601" t="str">
-        <v>Giltig</v>
+        <v>Inga taggar hittades.</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Warning</v>
+        <v>Tag Name</v>
       </c>
       <c r="B602" t="str">
-        <v>Varning</v>
+        <v>Taggnamn</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Error</v>
+        <v>ID</v>
       </c>
       <c r="B603" t="str">
-        <v>Fel</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>Unknown</v>
+        <v>Offset</v>
       </c>
       <c r="B604" t="str">
-        <v>Okänd</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>Pass</v>
+        <v>Size</v>
       </c>
       <c r="B605" t="str">
-        <v>Godkänd</v>
+        <v>Storlek</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Fail</v>
+        <v>Pad</v>
       </c>
       <c r="B606" t="str">
-        <v>Underkänd</v>
+        <v>Utfyllnad</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>View in context</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B607" t="str">
-        <v>Visa i sammanhang</v>
+        <v>Byte ändrade sedan inläsning</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Validation detail</v>
+        <v>Type</v>
       </c>
       <c r="B608" t="str">
-        <v>Valideringsdetalj</v>
+        <v>Typ</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>Triggered by</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B609" t="str">
-        <v>Utlöst av</v>
+        <v>Array av {type}</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>Field</v>
+        <v>(No content)</v>
       </c>
       <c r="B610" t="str">
-        <v>Fält</v>
+        <v>(Inget innehåll)</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>Current value</v>
+        <v>bytes</v>
       </c>
       <c r="B611" t="str">
-        <v>Aktuellt värde</v>
+        <v>byte</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>Required: 0</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B612" t="str">
-        <v>Krävs: 0</v>
+        <v>Läser in fullständig beskrivning…</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>Expected: {value}</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B613" t="str">
-        <v>Förväntat: {value}</v>
+        <v>Kunde inte läsa in fullständig beskrivning:</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>Invalid</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B614" t="str">
-        <v>Ogiltigt</v>
+        <v>Den här profilen kunde inte tolkas helt och får inte tillämpas. Huvudet och taggkatalogen nedan visas endast för granskning.</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B615" t="str">
-        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
+        <v>Tagginnehåll otillgängligt — profilen kunde inte tolkas helt.</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>Close</v>
+        <v>No validation output</v>
       </c>
       <c r="B616" t="str">
-        <v>Stäng</v>
+        <v>Ingen valideringsutdata</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>Loading XML editor…</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B617" t="str">
-        <v>Läser in XML-redigeraren…</v>
+        <v>Profilen är giltig</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B618" t="str">
-        <v>Läser in JSON-redigeraren…</v>
+        <v>Profilen har varning(ar)</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B619" t="str">
-        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>Profilen följer inte specifikationen</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B620" t="str">
-        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>Kritiskt valideringsfel</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B621" t="str">
-        <v>● osparade XML-ändringar</v>
+        <v>Okänd valideringsstatus</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B622" t="str">
-        <v>● osparade JSON-ändringar</v>
+        <v>Kritiskt — visas endast för granskning</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B623" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
+        <v>Inga varningar eller fel hittades.</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Valid</v>
       </c>
       <c r="B624" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
+        <v>Giltig</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>indent</v>
+        <v>Warning</v>
       </c>
       <c r="B625" t="str">
-        <v>indrag</v>
+        <v>Varning</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>sort keys</v>
+        <v>Error</v>
       </c>
       <c r="B626" t="str">
-        <v>sortera nycklar</v>
+        <v>Fel</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B627" t="str">
+        <v>Okänd</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B628" t="str">
+        <v>Godkänd</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B629" t="str">
+        <v>Underkänd</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B630" t="str">
+        <v>Visa i sammanhang</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B631" t="str">
+        <v>Valideringsdetalj</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B632" t="str">
+        <v>Utlöst av</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B633" t="str">
+        <v>Fält</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B634" t="str">
+        <v>Aktuellt värde</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B635" t="str">
+        <v>Krävs: 0</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B636" t="str">
+        <v>Förväntat: {value}</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B637" t="str">
+        <v>Ogiltigt</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B638" t="str">
+        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B639" t="str">
+        <v>Stäng</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B640" t="str">
+        <v>Läser in XML-redigeraren…</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B641" t="str">
+        <v>Läser in JSON-redigeraren…</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B642" t="str">
+        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B643" t="str">
+        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B644" t="str">
+        <v>● osparade XML-ändringar</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B645" t="str">
+        <v>● osparade JSON-ändringar</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B646" t="str">
+        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B647" t="str">
+        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B648" t="str">
+        <v>indrag</v>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B649" t="str">
+        <v>sortera nycklar</v>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B627" t="str">
+      <c r="B650" t="str">
         <v>Profilen skrevs från ändringarna, men omvalideringen misslyckades:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B627"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B650"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Sv.xlsx
+++ b/translations/Eng-Sv.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B650"/>
+  <dimension ref="A1:B658"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -4579,1039 +4579,1103 @@
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>HDR Profiles</v>
       </c>
       <c r="B522" t="str">
-        <v>IccProfLib avböjer att tillämpa den här förstärkningskurvan: {why}. En CMM faller tillbaka på nästa tonmappningsbeskrivning (avsnitt 8.10.3).</v>
+        <v>HDR-profiler</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>Display headroom</v>
+        <v>Linear transfer</v>
       </c>
       <c r="B523" t="str">
-        <v>Skärmutrymme</v>
+        <v>Linjär överföring</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>Non-linear transfer (PQ, HLG)</v>
       </c>
       <c r="B524" t="str">
-        <v>{n} steg (≈{r}× referensvitt)</v>
+        <v>Icke-linjär överföring (PQ, HLG)</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>Baseline</v>
+        <v>HDR Profiles — Linear transfer</v>
       </c>
       <c r="B525" t="str">
-        <v>Bas</v>
+        <v>HDR-profiler – linjär överföring</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>HDR Profiles — PQ / HLG transfer</v>
       </c>
       <c r="B526" t="str">
-        <v>Kurvor i taggen, efter utrymme: {list} steg. Bas {b} steg, HDR-referensvitt {w} cd/m².</v>
+        <v>HDR-profiler – PQ/HLG-överföring</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>OpenEXR holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
       </c>
       <c r="B527" t="str">
-        <v>Det här utrymmet ligger utanför taggens kurvor, så närmaste kurva används oförändrad – biblioteket extrapolerar inte bortom dem.</v>
+        <v>OpenEXR innehåller linjärt ljus, så bara HDR-profiler med linjär överföring kan tilldelas.</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
       </c>
       <c r="B528" t="str">
-        <v>Vissa lutningar är härledda (PCHIP) och inte lagrade i taggen. Härledningen rekonstruerar ett SMPTE-avsnitt, så betrakta de kurvornas form som preliminär.</v>
+        <v>{n} PQ/HLG-HDR-profil(er) i poolen erbjuds inte – profilpanelen listar dem under HDR-profiler › Icke-linjär överföring.</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
       </c>
       <c r="B529" t="str">
-        <v>Taggen begär tonmappning mot referensvitt, så dess kurvor konstrueras av biblioteket i stället för att läsas från filen (en konstruktion från ett kommittéutkast).</v>
+        <v>Det finns ännu ingen HDR-profil med linjär överföring i poolen; profilpanelen grupperar HDR-profiler efter överföring.</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B530" t="str">
-        <v>Inga alternativa bilder: taggen begär ingen tonmappning, bara en begränsning till skärmens färgvolym.</v>
+        <v>IccProfLib avböjer att tillämpa den här förstärkningskurvan: {why}. En CMM faller tillbaka på nästa tonmappningsbeskrivning (avsnitt 8.10.3).</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>Display headroom</v>
       </c>
       <c r="B531" t="str">
-        <v>De två kurvorna som blandas vid detta utrymme blandar färgkanalerna olika, så det finns ingen enskild förstärkningskurva att rita. Tonkurvan nedan är ändå exakt.</v>
+        <v>Skärmutrymme</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B532" t="str">
-        <v>Kurva vid {h} steg (ingen förstärkning)</v>
+        <v>{n} steg (≈{r}× referensvitt)</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>Curve at {h} stops</v>
+        <v>Baseline</v>
       </c>
       <c r="B533" t="str">
-        <v>Kurva vid {h} steg</v>
+        <v>Bas</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B534" t="str">
-        <v>Tillämpad vid {h} steg</v>
+        <v>Kurvor i taggen, efter utrymme: {list} steg. Bas {b} steg, HDR-referensvitt {w} cd/m².</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B535" t="str">
-        <v>Förstärkning vid detta utrymme</v>
+        <v>Det här utrymmet ligger utanför taggens kurvor, så närmaste kurva används oförändrad – biblioteket extrapolerar inte bortom dem.</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B536" t="str">
-        <v>Blandad indata (linjär, 1,0 = HDR-referensvitt)</v>
+        <v>Vissa lutningar är härledda (PCHIP) och inte lagrade i taggen. Härledningen rekonstruerar ett SMPTE-avsnitt, så betrakta de kurvornas form som preliminär.</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B537" t="str">
-        <v>Förstärkning (log2-steg)</v>
+        <v>Taggen begär tonmappning mot referensvitt, så dess kurvor konstrueras av biblioteket i stället för att läsas från filen (en konstruktion från ett kommittéutkast).</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B538" t="str">
-        <v>Gråskalans tonkurva vid detta utrymme</v>
+        <v>Inga alternativa bilder: taggen begär ingen tonmappning, bara en begränsning till skärmens färgvolym.</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B539" t="str">
-        <v>Indata (× HDR-referensvitt)</v>
+        <v>De två kurvorna som blandas vid detta utrymme blandar färgkanalerna olika, så det finns ingen enskild förstärkningskurva att rita. Tonkurvan nedan är ändå exakt.</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B540" t="str">
-        <v>Utdata (× HDR-referensvitt)</v>
+        <v>Kurva vid {h} steg (ingen förstärkning)</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>No change</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B541" t="str">
-        <v>Ingen ändring</v>
+        <v>Kurva vid {h} steg</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B542" t="str">
-        <v>Skärmens topp vid {h} steg</v>
+        <v>Tillämpad vid {h} steg</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>Output at {h} stops</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B543" t="str">
-        <v>Utdata vid {h} steg</v>
+        <v>Förstärkning vid detta utrymme</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B544" t="str">
-        <v>HDR, färgomfång och pixelförhållande uppdateras när fönstret flyttas till en skärm där de skiljer sig.</v>
+        <v>Blandad indata (linjär, 1,0 = HDR-referensvitt)</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>Identify displays</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B545" t="str">
-        <v>Identifiera skärmar</v>
+        <v>Förstärkning (log2-steg)</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B546" t="str">
-        <v>Ber om tillåtelse att se vilken skärm fönstret ligger på, så att panelen även uppdateras mellan likadana skärmar och visar HDR-utrymme där webbläsaren exponerar det.</v>
+        <v>Gråskalans tonkurva vid detta utrymme</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B547" t="str">
-        <v>Följer vilken skärm fönstret ligger på.</v>
+        <v>Indata (× HDR-referensvitt)</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B548" t="str">
-        <v>Tillåtelse att identifiera skärmar nekades. Den kan ändras i webbplatsens inställningar.</v>
+        <v>Utdata (× HDR-referensvitt)</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>No change</v>
       </c>
       <c r="B549" t="str">
-        <v>Den här webbläsaren kan inte identifiera skärmar; bara den automatiska uppdateringen ovan gäller.</v>
+        <v>Ingen ändring</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>Could not identify displays.</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B550" t="str">
-        <v>Kunde inte identifiera skärmar.</v>
+        <v>Skärmens topp vid {h} steg</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>Display events</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B551" t="str">
-        <v>Skärmhändelser</v>
+        <v>Utdata vid {h} steg</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B552" t="str">
-        <v>Inga händelser än. Dra fönstret till en annan skärm.</v>
+        <v>HDR, färgomfång och pixelförhållande uppdateras när fönstret flyttas till en skärm där de skiljer sig.</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>Colour primaries</v>
+        <v>Identify displays</v>
       </c>
       <c r="B553" t="str">
-        <v>Färgprimärer</v>
+        <v>Identifiera skärmar</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>Transfer characteristics</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B554" t="str">
-        <v>Överföringsfunktion</v>
+        <v>Ber om tillåtelse att se vilken skärm fönstret ligger på, så att panelen även uppdateras mellan likadana skärmar och visar HDR-utrymme där webbläsaren exponerar det.</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Matrix coefficients</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B555" t="str">
-        <v>Matriskoefficienter</v>
+        <v>Följer vilken skärm fönstret ligger på.</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>Video full-range flag</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B556" t="str">
-        <v>Flagga för fullt videoomfång</v>
+        <v>Tillåtelse att identifiera skärmar nekades. Den kan ändras i webbplatsens inställningar.</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Full range</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B557" t="str">
-        <v>Fullt omfång</v>
+        <v>Den här webbläsaren kan inte identifiera skärmar; bara den automatiska uppdateringen ovan gäller.</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Narrow range</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B558" t="str">
-        <v>Begränsat omfång</v>
+        <v>Kunde inte identifiera skärmar.</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Display events</v>
       </c>
       <c r="B559" t="str">
-        <v>inte tilldelad av ITU-T H.273</v>
+        <v>Skärmhändelser</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B560" t="str">
-        <v>Färgprimärer 2 (Ospecificerad) hänvisar till profilen själv — primärerna hämtas från färgämnestaggarna och inte från den här taggen.</v>
+        <v>Inga händelser än. Dra fönstret till en annan skärm.</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B561" t="str">
-        <v>De fyra reserverade byten i den här taggen är inte alla noll.</v>
+        <v>Färgprimärer</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>REPORT</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B562" t="str">
-        <v>RAPPORT</v>
+        <v>Överföringsfunktion</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>FAIL</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B563" t="str">
-        <v>UNDERKÄND</v>
+        <v>Matriskoefficienter</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>checks</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B564" t="str">
-        <v>kontroller</v>
+        <v>Flagga för fullt videoomfång</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Full range</v>
       </c>
       <c r="B565" t="str">
-        <v>Genererad av iccPawgReport (iccDEV) · checklista från ICC Profile Assessment Working Group.</v>
+        <v>Fullt omfång</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Narrow range</v>
       </c>
       <c r="B566" t="str">
-        <v>ICC-profilverktyg · drivs av IccProfLib</v>
+        <v>Begränsat omfång</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>ICC Profile Tool</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B567" t="str">
-        <v>ICC-profilverktyg</v>
+        <v>inte tilldelad av ITU-T H.273</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Powered by {lib}</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B568" t="str">
-        <v>Drivs av {lib}</v>
+        <v>Färgprimärer 2 (Ospecificerad) hänvisar till profilen själv — primärerna hämtas från färgämnestaggarna och inte från den här taggen.</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Subscribe</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B569" t="str">
-        <v>Prenumerera</v>
+        <v>De fyra reserverade byten i den här taggen är inte alla noll.</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>REPORT</v>
       </c>
       <c r="B570" t="str">
-        <v>Få besked om nya profiletool-versioner</v>
+        <v>RAPPORT</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Get notified about new releases</v>
+        <v>FAIL</v>
       </c>
       <c r="B571" t="str">
-        <v>Få besked om nya versioner</v>
+        <v>UNDERKÄND</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>Close</v>
+        <v>checks</v>
       </c>
       <c r="B572" t="str">
-        <v>Stäng</v>
+        <v>kontroller</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B573" t="str">
-        <v>Vi mejlar dig när en ny större eller mindre version av profiletool släpps. Patchversioner hoppas över. Din adress granskas manuellt innan den läggs till.</v>
+        <v>Genererad av iccPawgReport (iccDEV) · checklista från ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Email address</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B574" t="str">
-        <v>E-postadress</v>
+        <v>ICC-profilverktyg · drivs av IccProfLib</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>you@example.com</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B575" t="str">
-        <v>du@exempel.com</v>
+        <v>ICC-profilverktyg</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B576" t="str">
-        <v>Hur kommer du att använda profiletool?</v>
+        <v>Drivs av {lib}</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>(optional)</v>
+        <v>Subscribe</v>
       </c>
       <c r="B577" t="str">
-        <v>(valfritt)</v>
+        <v>Prenumerera</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B578" t="str">
-        <v>t.ex. utvärdera ICC-profiler för tryckkalibrering</v>
+        <v>Få besked om nya profiletool-versioner</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B579" t="str">
-        <v>Jag godkänner att ta emot e-post om profiletool-versioner. Jag kan avsluta prenumerationen när som helst.</v>
+        <v>Få besked om nya versioner</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>Cancel</v>
+        <v>Close</v>
       </c>
       <c r="B580" t="str">
-        <v>Avbryt</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>Subscribe</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B581" t="str">
-        <v>Prenumerera</v>
+        <v>Vi mejlar dig när en ny större eller mindre version av profiletool släpps. Patchversioner hoppas över. Din adress granskas manuellt innan den läggs till.</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Email address</v>
       </c>
       <c r="B582" t="str">
-        <v>Tack — vi hör av oss.</v>
+        <v>E-postadress</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>you@example.com</v>
       </c>
       <c r="B583" t="str">
-        <v>När du har godkänts får du ett välkomstmejl. Därefter hör du bara från oss när en ny version av profiletool släpps.</v>
+        <v>du@exempel.com</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>Close</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B584" t="str">
-        <v>Stäng</v>
+        <v>Hur kommer du att använda profiletool?</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>Privacy notice</v>
+        <v>(optional)</v>
       </c>
       <c r="B585" t="str">
-        <v>Integritetsmeddelande</v>
+        <v>(valfritt)</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B586" t="str">
-        <v>Ange en giltig e-postadress.</v>
+        <v>t.ex. utvärdera ICC-profiler för tryckkalibrering</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B587" t="str">
-        <v>För många förfrågningar. Försök igen senare.</v>
+        <v>Jag godkänner att ta emot e-post om profiletool-versioner. Jag kan avsluta prenumerationen när som helst.</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Cancel</v>
       </c>
       <c r="B588" t="str">
-        <v>Kontrollera formuläret och försök igen.</v>
+        <v>Avbryt</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B589" t="str">
-        <v>Det gick inte att skicka din förfrågan. Försök igen.</v>
+        <v>Prenumerera</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B590" t="str">
-        <v>Nätverksfel. Försök igen.</v>
+        <v>Tack — vi hör av oss.</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Error:</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B591" t="str">
-        <v>Fel:</v>
+        <v>När du har godkänts får du ett välkomstmejl. Därefter hör du bara från oss när en ny version av profiletool släpps.</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Convert to XML</v>
+        <v>Close</v>
       </c>
       <c r="B592" t="str">
-        <v>Konvertera till XML</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Convert to JSON</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B593" t="str">
-        <v>Konvertera till JSON</v>
+        <v>Integritetsmeddelande</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Convert to ICC</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B594" t="str">
-        <v>Konvertera till ICC</v>
+        <v>Ange en giltig e-postadress.</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Converting to XML…</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B595" t="str">
-        <v>Konverterar till XML…</v>
+        <v>För många förfrågningar. Försök igen senare.</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Converting to JSON…</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B596" t="str">
-        <v>Konverterar till JSON…</v>
+        <v>Kontrollera formuläret och försök igen.</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Converting to ICC…</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B597" t="str">
-        <v>Konverterar till ICC…</v>
+        <v>Det gick inte att skicka din förfrågan. Försök igen.</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Load ICC profile</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B598" t="str">
-        <v>Läs in ICC-profil</v>
+        <v>Nätverksfel. Försök igen.</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Error:</v>
       </c>
       <c r="B599" t="str">
-        <v>Släppzon för ICC-profilfiler</v>
+        <v>Fel:</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>Profile ID</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B600" t="str">
-        <v>Profil-ID</v>
+        <v>Konvertera till XML</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>No tags found.</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B601" t="str">
-        <v>Inga taggar hittades.</v>
+        <v>Konvertera till JSON</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Tag Name</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B602" t="str">
-        <v>Taggnamn</v>
+        <v>Konvertera till ICC</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>ID</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B603" t="str">
-        <v>ID</v>
+        <v>Konverterar till XML…</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>Offset</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B604" t="str">
-        <v>Offset</v>
+        <v>Konverterar till JSON…</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>Size</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B605" t="str">
-        <v>Storlek</v>
+        <v>Konverterar till ICC…</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Pad</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B606" t="str">
-        <v>Utfyllnad</v>
+        <v>Läs in ICC-profil</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>Bytes changed since load</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B607" t="str">
-        <v>Byte ändrade sedan inläsning</v>
+        <v>Släppzon för ICC-profilfiler</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Type</v>
+        <v>Profile ID</v>
       </c>
       <c r="B608" t="str">
-        <v>Typ</v>
+        <v>Profil-ID</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>Array of {type}</v>
+        <v>No tags found.</v>
       </c>
       <c r="B609" t="str">
-        <v>Array av {type}</v>
+        <v>Inga taggar hittades.</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>(No content)</v>
+        <v>Tag Name</v>
       </c>
       <c r="B610" t="str">
-        <v>(Inget innehåll)</v>
+        <v>Taggnamn</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>bytes</v>
+        <v>ID</v>
       </c>
       <c r="B611" t="str">
-        <v>byte</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>Loading full description…</v>
+        <v>Offset</v>
       </c>
       <c r="B612" t="str">
-        <v>Läser in fullständig beskrivning…</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>Could not load full description:</v>
+        <v>Size</v>
       </c>
       <c r="B613" t="str">
-        <v>Kunde inte läsa in fullständig beskrivning:</v>
+        <v>Storlek</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Pad</v>
       </c>
       <c r="B614" t="str">
-        <v>Den här profilen kunde inte tolkas helt och får inte tillämpas. Huvudet och taggkatalogen nedan visas endast för granskning.</v>
+        <v>Utfyllnad</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B615" t="str">
-        <v>Tagginnehåll otillgängligt — profilen kunde inte tolkas helt.</v>
+        <v>Byte ändrade sedan inläsning</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>No validation output</v>
+        <v>Type</v>
       </c>
       <c r="B616" t="str">
-        <v>Ingen valideringsutdata</v>
+        <v>Typ</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>Profile is valid</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B617" t="str">
-        <v>Profilen är giltig</v>
+        <v>Array av {type}</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>Profile has warning(s)</v>
+        <v>(No content)</v>
       </c>
       <c r="B618" t="str">
-        <v>Profilen har varning(ar)</v>
+        <v>(Inget innehåll)</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>Profile is non-compliant</v>
+        <v>bytes</v>
       </c>
       <c r="B619" t="str">
-        <v>Profilen följer inte specifikationen</v>
+        <v>byte</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>Critical validation error</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B620" t="str">
-        <v>Kritiskt valideringsfel</v>
+        <v>Läser in fullständig beskrivning…</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>Unknown validation status</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B621" t="str">
-        <v>Okänd valideringsstatus</v>
+        <v>Kunde inte läsa in fullständig beskrivning:</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B622" t="str">
-        <v>Kritiskt — visas endast för granskning</v>
+        <v>Den här profilen kunde inte tolkas helt och får inte tillämpas. Huvudet och taggkatalogen nedan visas endast för granskning.</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B623" t="str">
-        <v>Inga varningar eller fel hittades.</v>
+        <v>Tagginnehåll otillgängligt — profilen kunde inte tolkas helt.</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>Valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B624" t="str">
-        <v>Giltig</v>
+        <v>Ingen valideringsutdata</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>Warning</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B625" t="str">
-        <v>Varning</v>
+        <v>Profilen är giltig</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>Error</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B626" t="str">
-        <v>Fel</v>
+        <v>Profilen har varning(ar)</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>Unknown</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B627" t="str">
-        <v>Okänd</v>
+        <v>Profilen följer inte specifikationen</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>Pass</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B628" t="str">
-        <v>Godkänd</v>
+        <v>Kritiskt valideringsfel</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>Fail</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B629" t="str">
-        <v>Underkänd</v>
+        <v>Okänd valideringsstatus</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>View in context</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B630" t="str">
-        <v>Visa i sammanhang</v>
+        <v>Kritiskt — visas endast för granskning</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>Validation detail</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B631" t="str">
-        <v>Valideringsdetalj</v>
+        <v>Inga varningar eller fel hittades.</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>Triggered by</v>
+        <v>Valid</v>
       </c>
       <c r="B632" t="str">
-        <v>Utlöst av</v>
+        <v>Giltig</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>Field</v>
+        <v>Warning</v>
       </c>
       <c r="B633" t="str">
-        <v>Fält</v>
+        <v>Varning</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>Current value</v>
+        <v>Error</v>
       </c>
       <c r="B634" t="str">
-        <v>Aktuellt värde</v>
+        <v>Fel</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>Required: 0</v>
+        <v>Unknown</v>
       </c>
       <c r="B635" t="str">
-        <v>Krävs: 0</v>
+        <v>Okänd</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>Expected: {value}</v>
+        <v>Pass</v>
       </c>
       <c r="B636" t="str">
-        <v>Förväntat: {value}</v>
+        <v>Godkänd</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>Invalid</v>
+        <v>Fail</v>
       </c>
       <c r="B637" t="str">
-        <v>Ogiltigt</v>
+        <v>Underkänd</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>View in context</v>
       </c>
       <c r="B638" t="str">
-        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
+        <v>Visa i sammanhang</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>Close</v>
+        <v>Validation detail</v>
       </c>
       <c r="B639" t="str">
-        <v>Stäng</v>
+        <v>Valideringsdetalj</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>Loading XML editor…</v>
+        <v>Triggered by</v>
       </c>
       <c r="B640" t="str">
-        <v>Läser in XML-redigeraren…</v>
+        <v>Utlöst av</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Field</v>
       </c>
       <c r="B641" t="str">
-        <v>Läser in JSON-redigeraren…</v>
+        <v>Fält</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Current value</v>
       </c>
       <c r="B642" t="str">
-        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>Aktuellt värde</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Required: 0</v>
       </c>
       <c r="B643" t="str">
-        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>Krävs: 0</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B644" t="str">
-        <v>● osparade XML-ändringar</v>
+        <v>Förväntat: {value}</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Invalid</v>
       </c>
       <c r="B645" t="str">
-        <v>● osparade JSON-ändringar</v>
+        <v>Ogiltigt</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B646" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
+        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Close</v>
       </c>
       <c r="B647" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>indent</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B648" t="str">
-        <v>indrag</v>
+        <v>Läser in XML-redigeraren…</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>sort keys</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B649" t="str">
-        <v>sortera nycklar</v>
+        <v>Läser in JSON-redigeraren…</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B650" t="str">
+        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B651" t="str">
+        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B652" t="str">
+        <v>● osparade XML-ändringar</v>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B653" t="str">
+        <v>● osparade JSON-ändringar</v>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B654" t="str">
+        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B655" t="str">
+        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B656" t="str">
+        <v>indrag</v>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B657" t="str">
+        <v>sortera nycklar</v>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B650" t="str">
+      <c r="B658" t="str">
         <v>Profilen skrevs från ändringarna, men omvalideringen misslyckades:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B650"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B658"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Sv.xlsx
+++ b/translations/Eng-Sv.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B658"/>
+  <dimension ref="A1:B659"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -3811,10 +3811,10 @@
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>View one HDR image on this display. Files the browser can decode are shown by the browser itself; OpenEXR is decoded and rendered by profiletool.</v>
+        <v>View one HDR image on this display. Files the browser can decode are shown by the browser itself; OpenEXR and Radiance HDR are decoded and rendered by profiletool.</v>
       </c>
       <c r="B426" t="str">
-        <v>Visa en HDR-bild på den här skärmen. Filer som webbläsaren kan avkoda visas av webbläsaren själv; OpenEXR avkodas och återges av profiletool.</v>
+        <v>Visa en HDR-bild på den här skärmen. Filer som webbläsaren kan avkoda visas av webbläsaren själv; OpenEXR och Radiance HDR avkodas och återges av profiletool.</v>
       </c>
     </row>
     <row r="427">
@@ -3827,10 +3827,10 @@
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>OpenEXR, AVIF, JPEG (including gain-map JPEG), PNG — and HEIC on Safari.</v>
+        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (including gain-map JPEG), PNG — and HEIC on Safari.</v>
       </c>
       <c r="B428" t="str">
-        <v>OpenEXR, AVIF, JPEG (även JPEG med gain map), PNG – och HEIC i Safari.</v>
+        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (även JPEG med gain map), PNG – och HEIC i Safari.</v>
       </c>
     </row>
     <row r="429">
@@ -3867,1815 +3867,1823 @@
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>checking…</v>
+        <v>none — Radiance HDR states colour through its PRIMARIES header</v>
       </c>
       <c r="B433" t="str">
-        <v>kontrollerar…</v>
+        <v>ingen – Radiance HDR anger färg genom sin PRIMARIES-rubrik</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>none</v>
+        <v>checking…</v>
       </c>
       <c r="B434" t="str">
-        <v>ingen</v>
+        <v>kontrollerar…</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Open in Profile tab</v>
+        <v>none</v>
       </c>
       <c r="B435" t="str">
-        <v>Öppna på fliken Profil</v>
+        <v>ingen</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Gain map</v>
+        <v>Open in Profile tab</v>
       </c>
       <c r="B436" t="str">
-        <v>Förstärkningskarta</v>
+        <v>Öppna på fliken Profil</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>detected, not decoded</v>
+        <v>Gain map</v>
       </c>
       <c r="B437" t="str">
-        <v>hittad, inte avkodad</v>
+        <v>Förstärkningskarta</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>That is not an image. Load profiles through the Profiles pane.</v>
+        <v>detected, not decoded</v>
       </c>
       <c r="B438" t="str">
-        <v>Det är ingen bild. Läs in profiler via profilpanelen.</v>
+        <v>hittad, inte avkodad</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>Not an image format profiletool recognises.</v>
+        <v>That is not an image. Load profiles through the Profiles pane.</v>
       </c>
       <c r="B439" t="str">
-        <v>Inte ett bildformat som profiletool känner igen.</v>
+        <v>Det är ingen bild. Läs in profiler via profilpanelen.</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>TIFF pixels are not shown here yet: browsers do not decode TIFF, and how HDR is encoded in a 16-bit TIFF is still undecided (Phase 4.3). Its embedded profile can be inspected.</v>
+        <v>Not an image format profiletool recognises.</v>
       </c>
       <c r="B440" t="str">
-        <v>TIFF-pixlar visas inte här ännu: webbläsare avkodar inte TIFF, och hur HDR kodas i en 16-bitars TIFF är ännu inte bestämt (fas 4.3). Den inbäddade profilen kan granskas.</v>
+        <v>Inte ett bildformat som profiletool känner igen.</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>Cannot display this image here:</v>
+        <v>TIFF pixels are not shown here yet: browsers do not decode TIFF, and how HDR is encoded in a 16-bit TIFF is still undecided (Phase 4.3). Its embedded profile can be inspected.</v>
       </c>
       <c r="B441" t="str">
-        <v>Bilden kan inte visas här:</v>
+        <v>TIFF-pixlar visas inte här ännu: webbläsare avkodar inte TIFF, och hur HDR kodas i en 16-bitars TIFF är ännu inte bestämt (fas 4.3). Den inbäddade profilen kan granskas.</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>Its embedded profile can still be inspected.</v>
+        <v>Cannot display this image here:</v>
       </c>
       <c r="B442" t="str">
-        <v>Den inbäddade profilen kan ändå granskas.</v>
+        <v>Bilden kan inte visas här:</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>Shown by</v>
+        <v>Its embedded profile can still be inspected.</v>
       </c>
       <c r="B443" t="str">
-        <v>Visas av</v>
+        <v>Den inbäddade profilen kan ändå granskas.</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>the browser</v>
+        <v>Shown by</v>
       </c>
       <c r="B444" t="str">
-        <v>webbläsaren</v>
+        <v>Visas av</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>profiletool</v>
+        <v>the browser</v>
       </c>
       <c r="B445" t="str">
-        <v>profiletool</v>
+        <v>webbläsaren</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>HDR display</v>
+        <v>profiletool</v>
       </c>
       <c r="B446" t="str">
-        <v>HDR-skärm</v>
+        <v>profiletool</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>Browsers ignore HDR that is signalled only by an embedded ICC profile, so this image may look dim and flat.</v>
+        <v>HDR display</v>
       </c>
       <c r="B447" t="str">
-        <v>Webbläsare ignorerar HDR som bara anges av en inbäddad ICC-profil, så bilden kan se matt och platt ut.</v>
+        <v>HDR-skärm</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>This browser cannot switch an image between SDR and HDR, so it is shown as the browser renders it.</v>
+        <v>Browsers ignore HDR that is signalled only by an embedded ICC profile, so this image may look dim and flat.</v>
       </c>
       <c r="B448" t="str">
-        <v>Den här webbläsaren kan inte växla en bild mellan SDR och HDR, så den visas som webbläsaren återger den.</v>
+        <v>Webbläsare ignorerar HDR som bara anges av en inbäddad ICC-profil, så bilden kan se matt och platt ut.</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>The browser could not decode this image.</v>
+        <v>This browser cannot switch an image between SDR and HDR, so it is shown as the browser renders it.</v>
       </c>
       <c r="B449" t="str">
-        <v>Webbläsaren kunde inte avkoda bilden.</v>
+        <v>Den här webbläsaren kan inte växla en bild mellan SDR och HDR, så den visas som webbläsaren återger den.</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Output</v>
+        <v>The browser could not decode this image.</v>
       </c>
       <c r="B450" t="str">
-        <v>Utdata</v>
+        <v>Webbläsaren kunde inte avkoda bilden.</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>HDR canvas (float16)</v>
+        <v>Output</v>
       </c>
       <c r="B451" t="str">
-        <v>HDR-canvas (float16)</v>
+        <v>Utdata</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>WebGPU (extended range)</v>
+        <v>HDR canvas (float16)</v>
       </c>
       <c r="B452" t="str">
-        <v>WebGPU (utökat omfång)</v>
+        <v>HDR-canvas (float16)</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>SDR canvas (tone-mapped)</v>
+        <v>WebGPU (extended range)</v>
       </c>
       <c r="B453" t="str">
-        <v>SDR-canvas (tonmappad)</v>
+        <v>WebGPU (utökat omfång)</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>Size</v>
+        <v>SDR canvas (tone-mapped)</v>
       </c>
       <c r="B454" t="str">
-        <v>Storlek</v>
+        <v>SDR-canvas (tonmappad)</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>Brightest pixel</v>
+        <v>Size</v>
       </c>
       <c r="B455" t="str">
-        <v>Ljusaste pixel</v>
+        <v>Storlek</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>{n}× SDR white</v>
+        <v>Brightest pixel</v>
       </c>
       <c r="B456" t="str">
-        <v>{n}× SDR-vitt</v>
+        <v>Ljusaste pixel</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>Chromaticities</v>
+        <v>{n}× SDR white</v>
       </c>
       <c r="B457" t="str">
-        <v>Kromaticiteter</v>
+        <v>{n}× SDR-vitt</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>not stated — Rec. 709 assumed</v>
+        <v>Chromaticities</v>
       </c>
       <c r="B458" t="str">
-        <v>inte angivna – Rec. 709 antas</v>
+        <v>Kromaticiteter</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>{from} was not available here ({why}); using the next output.</v>
+        <v>not stated — Rec. 709 assumed</v>
       </c>
       <c r="B459" t="str">
-        <v>{from} är inte tillgängligt här ({why}); nästa utdata används.</v>
+        <v>inte angivna – Rec. 709 antas</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>This output cannot carry brighter-than-white values, so the tone-mapped SDR rendering is shown.</v>
+        <v>{from} was not available here ({why}); using the next output.</v>
       </c>
       <c r="B460" t="str">
-        <v>Den här utdatan kan inte bära värden ljusare än vitt, så den tonmappade SDR-återgivningen visas.</v>
+        <v>{from} är inte tillgängligt här ({why}); nästa utdata används.</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>Exposure</v>
+        <v>This output cannot carry brighter-than-white values, so the tone-mapped SDR rendering is shown.</v>
       </c>
       <c r="B461" t="str">
-        <v>Exponering</v>
+        <v>Den här utdatan kan inte bära värden ljusare än vitt, så den tonmappade SDR-återgivningen visas.</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>{n} stops</v>
+        <v>Exposure</v>
       </c>
       <c r="B462" t="str">
-        <v>{n} steg</v>
+        <v>Exponering</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>Could not decode:</v>
+        <v>{n} stops</v>
       </c>
       <c r="B463" t="str">
-        <v>Kunde inte avkoda:</v>
+        <v>{n} steg</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>Decoding…</v>
+        <v>Could not decode:</v>
       </c>
       <c r="B464" t="str">
-        <v>Avkodar…</v>
+        <v>Kunde inte avkoda:</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>Dynamic range</v>
+        <v>Decoding…</v>
       </c>
       <c r="B465" t="str">
-        <v>Dynamiskt omfång</v>
+        <v>Avkodar…</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>This browser offers only the two ends, not a blend.</v>
+        <v>Dynamic range</v>
       </c>
       <c r="B466" t="str">
-        <v>Den här webbläsaren erbjuder bara de två ändarna, ingen blandning.</v>
+        <v>Dynamiskt omfång</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>decoded by profiletool itself, so browser-independent</v>
+        <v>This browser offers only the two ends, not a blend.</v>
       </c>
       <c r="B467" t="str">
-        <v>avkodas av profiletool själv, så oberoende av webbläsaren</v>
+        <v>Den här webbläsaren erbjuder bara de två ändarna, ingen blandning.</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>this browser decodes it</v>
+        <v>decoded by profiletool itself, so browser-independent</v>
       </c>
       <c r="B468" t="str">
-        <v>den här webbläsaren avkodar det</v>
+        <v>avkodas av profiletool själv, så oberoende av webbläsaren</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>this browser does not decode it</v>
+        <v>this browser decodes it</v>
       </c>
       <c r="B469" t="str">
-        <v>den här webbläsaren avkodar det inte</v>
+        <v>den här webbläsaren avkodar det</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>HEIC display needs Safari or another WebKit browser — Chrome and Firefox decode HEIC on no platform, macOS included</v>
+        <v>this browser does not decode it</v>
       </c>
       <c r="B470" t="str">
-        <v>HEIC-visning kräver Safari eller en annan WebKit-webbläsare – Chrome och Firefox avkodar HEIC på ingen plattform, inte heller macOS</v>
+        <v>den här webbläsaren avkodar det inte</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>JPEG XL display needs Safari; other browsers have not shipped it</v>
+        <v>HEIC display needs Safari or another WebKit browser — Chrome and Firefox decode HEIC on no platform, macOS included</v>
       </c>
       <c r="B471" t="str">
-        <v>JPEG XL-visning kräver Safari; andra webbläsare har inte stöd än</v>
+        <v>HEIC-visning kräver Safari eller en annan WebKit-webbläsare – Chrome och Firefox avkodar HEIC på ingen plattform, inte heller macOS</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>deferred to a later release</v>
+        <v>JPEG XL display needs Safari; other browsers have not shipped it</v>
       </c>
       <c r="B472" t="str">
-        <v>uppskjutet till en senare version</v>
+        <v>JPEG XL-visning kräver Safari; andra webbläsare har inte stöd än</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>this display reports no HDR path, so HDR renders tone-mapped to SDR</v>
+        <v>deferred to a later release</v>
       </c>
       <c r="B473" t="str">
-        <v>skärmen rapporterar ingen HDR-väg, så HDR visas tonmappat som SDR</v>
+        <v>uppskjutet till en senare version</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>this browser exposes no HDR canvas path (needs float16 canvas or WebGPU)</v>
+        <v>this display reports no HDR path, so HDR renders tone-mapped to SDR</v>
       </c>
       <c r="B474" t="str">
-        <v>webbläsaren har ingen HDR-canvas (kräver float16-canvas eller WebGPU)</v>
+        <v>skärmen rapporterar ingen HDR-väg, så HDR visas tonmappat som SDR</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>Firefox renders no HDR images and reads no gain maps; HDR content is shown as SDR</v>
+        <v>this browser exposes no HDR canvas path (needs float16 canvas or WebGPU)</v>
       </c>
       <c r="B475" t="str">
-        <v>Firefox visar inga HDR-bilder och läser inga gain maps; HDR-innehåll visas som SDR</v>
+        <v>webbläsaren har ingen HDR-canvas (kräver float16-canvas eller WebGPU)</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>inspection needs a container parse, not a codec</v>
+        <v>Firefox renders no HDR images and reads no gain maps; HDR content is shown as SDR</v>
       </c>
       <c r="B476" t="str">
-        <v>granskning kräver bara tolkning av behållaren, ingen codec</v>
+        <v>Firefox visar inga HDR-bilder och läser inga gain maps; HDR-innehåll visas som SDR</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>HDR display and an HDR canvas path are both available</v>
+        <v>inspection needs a container parse, not a codec</v>
       </c>
       <c r="B477" t="str">
-        <v>både HDR-skärm och HDR-canvas finns</v>
+        <v>granskning kräver bara tolkning av behållaren, ingen codec</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>unknown format</v>
+        <v>HDR display and an HDR canvas path are both available</v>
       </c>
       <c r="B478" t="str">
-        <v>okänt format</v>
+        <v>både HDR-skärm och HDR-canvas finns</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>{browser} on {os}</v>
+        <v>unknown format</v>
       </c>
       <c r="B479" t="str">
-        <v>{browser} på {os}</v>
+        <v>okänt format</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>{name} · HDR display detected</v>
+        <v>{browser} on {os}</v>
       </c>
       <c r="B480" t="str">
-        <v>{name} · HDR-skärm hittad</v>
+        <v>{browser} på {os}</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>{name} · SDR display</v>
+        <v>{name} · HDR display detected</v>
       </c>
       <c r="B481" t="str">
-        <v>{name} · SDR-skärm</v>
+        <v>{name} · HDR-skärm hittad</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>WebGPU applied tone mapping “{mode}”, so output is clamped to SDR</v>
+        <v>{name} · SDR display</v>
       </c>
       <c r="B482" t="str">
-        <v>WebGPU tillämpade tonmappning ”{mode}”, så utdata begränsas till SDR</v>
+        <v>{name} · SDR-skärm</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>This browser does not report the WebGPU tone mapping it applied, so HDR output is unconfirmed</v>
+        <v>WebGPU applied tone mapping “{mode}”, so output is clamped to SDR</v>
       </c>
       <c r="B483" t="str">
-        <v>Webbläsaren rapporterar inte vilken WebGPU-tonmappning som tillämpades, så HDR-utdata är obekräftad</v>
+        <v>WebGPU tillämpade tonmappning ”{mode}”, så utdata begränsas till SDR</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>Display peak</v>
+        <v>This browser does not report the WebGPU tone mapping it applied, so HDR output is unconfirmed</v>
       </c>
       <c r="B484" t="str">
-        <v>Skärmens topp</v>
+        <v>Webbläsaren rapporterar inte vilken WebGPU-tonmappning som tillämpades, så HDR-utdata är obekräftad</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>{r}× SDR white ({n} stops)</v>
+        <v>Display peak</v>
       </c>
       <c r="B485" t="str">
-        <v>{r}× SDR-vitt ({n} steg)</v>
+        <v>Skärmens topp</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>1× — SDR display</v>
+        <v>{r}× SDR white ({n} stops)</v>
       </c>
       <c r="B486" t="str">
-        <v>1× – SDR-skärm</v>
+        <v>{r}× SDR-vitt ({n} steg)</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>not known</v>
+        <v>1× — SDR display</v>
       </c>
       <c r="B487" t="str">
-        <v>okänd</v>
+        <v>1× – SDR-skärm</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>This display reports no HDR, so the browser shows this image in SDR at either end.</v>
+        <v>not known</v>
       </c>
       <c r="B488" t="str">
-        <v>Skärmen rapporterar ingen HDR, så webbläsaren visar bilden i SDR i båda ändarna.</v>
+        <v>okänd</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>This display reports no HDR, so everything brighter than SDR white clips. Fit to display shows the tone-mapped rendering instead.</v>
+        <v>This display reports no HDR, so the browser shows this image in SDR at either end.</v>
       </c>
       <c r="B489" t="str">
-        <v>Skärmen rapporterar ingen HDR, så allt ljusare än SDR-vitt klipps. ”Anpassa till skärm” visar i stället den tonmappade återgivningen.</v>
+        <v>Skärmen rapporterar ingen HDR, så webbläsaren visar bilden i SDR i båda ändarna.</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>This image asks for {img}× SDR white, but this display shows up to {disp}×, so brighter values clip. Fit to display rolls them off into the display’s peak instead.</v>
+        <v>This display reports no HDR, so everything brighter than SDR white clips. Fit to display shows the tone-mapped rendering instead.</v>
       </c>
       <c r="B490" t="str">
-        <v>Bilden kräver {img}× SDR-vitt, men skärmen visar bara upp till {disp}×, så ljusare värden klipps. ”Anpassa till skärm” rundar i stället av dem mot skärmens topp.</v>
+        <v>Skärmen rapporterar ingen HDR, så allt ljusare än SDR-vitt klipps. ”Anpassa till skärm” visar i stället den tonmappade återgivningen.</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>Fit to display</v>
+        <v>This image asks for {img}× SDR white, but this display shows up to {disp}×, so brighter values clip. Fit to display rolls them off into the display’s peak instead.</v>
       </c>
       <c r="B491" t="str">
-        <v>Anpassa till skärm</v>
+        <v>Bilden kräver {img}× SDR-vitt, men skärmen visar bara upp till {disp}×, så ljusare värden klipps. ”Anpassa till skärm” rundar i stället av dem mot skärmens topp.</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
+        <v>Fit to display</v>
       </c>
       <c r="B492" t="str">
-        <v>Begränsar ljusstyrkan till den topp skärmen rapporterar. I Windows kan värdet släpa efter ändringar av ljusstyrkan.</v>
+        <v>Anpassa till skärm</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>no limit</v>
+        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
       </c>
       <c r="B493" t="str">
-        <v>ingen gräns</v>
+        <v>Begränsar ljusstyrkan till den topp skärmen rapporterar. I Windows kan värdet släpa efter ändringar av ljusstyrkan.</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>limit {n} stops ({r}×)</v>
+        <v>no limit</v>
       </c>
       <c r="B494" t="str">
-        <v>gräns {n} steg ({r}×)</v>
+        <v>ingen gräns</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>SDR white</v>
+        <v>limit {n} stops ({r}×)</v>
       </c>
       <c r="B495" t="str">
-        <v>SDR-vitt</v>
+        <v>gräns {n} steg ({r}×)</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
+        <v>SDR white</v>
       </c>
       <c r="B496" t="str">
-        <v>Vanligt SDR-vitt för jämförelse. På en HDR-skärm ser HDR-högdagrar ljusare ut än detta.</v>
+        <v>SDR-vitt</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>SDR white patch</v>
+        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
       </c>
       <c r="B497" t="str">
-        <v>SDR-vit ruta</v>
+        <v>Vanligt SDR-vitt för jämförelse. På en HDR-skärm ser HDR-högdagrar ljusare ut än detta.</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Drag to move it; double-click to put it back beside the image.</v>
+        <v>SDR white patch</v>
       </c>
       <c r="B498" t="str">
-        <v>Dra för att flytta den; dubbelklicka för att sätta tillbaka den bredvid bilden.</v>
+        <v>SDR-vit ruta</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Assign profile</v>
+        <v>Drag to move it; double-click to put it back beside the image.</v>
       </c>
       <c r="B499" t="str">
-        <v>Tilldela profil</v>
+        <v>Dra för att flytta den; dubbelklicka för att sätta tillbaka den bredvid bilden.</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>None — use what the file signals</v>
+        <v>Assign profile</v>
       </c>
       <c r="B500" t="str">
-        <v>Ingen – det filen anger</v>
+        <v>Tilldela profil</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>Embedded profile ({n} B)</v>
+        <v>None — use what the file signals</v>
       </c>
       <c r="B501" t="str">
-        <v>Inbäddad profil ({n} B)</v>
+        <v>Ingen – det filen anger</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>HDR Profiles in the pool</v>
+        <v>Embedded profile ({n} B)</v>
       </c>
       <c r="B502" t="str">
-        <v>HDR-profiler i poolen</v>
+        <v>Inbäddad profil ({n} B)</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>Profile</v>
+        <v>HDR Profiles in the pool</v>
       </c>
       <c r="B503" t="str">
-        <v>Profil</v>
+        <v>HDR-profiler i poolen</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>embedded profile</v>
+        <v>Profile</v>
       </c>
       <c r="B504" t="str">
-        <v>inbäddad profil</v>
+        <v>Profil</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>Colour engine path</v>
+        <v>embedded profile</v>
       </c>
       <c r="B505" t="str">
-        <v>Färgmotorns väg</v>
+        <v>inbäddad profil</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>HDR path, gain curve applied</v>
+        <v>Colour engine path</v>
       </c>
       <c r="B506" t="str">
-        <v>HDR-väg, förstärkningskurva tillämpad</v>
+        <v>Färgmotorns väg</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>HDR path, no gain curve</v>
+        <v>HDR path, gain curve applied</v>
       </c>
       <c r="B507" t="str">
-        <v>HDR-väg, ingen förstärkningskurva</v>
+        <v>HDR-väg, förstärkningskurva tillämpad</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>Baked AToB0 — not the HDR path</v>
+        <v>HDR path, no gain curve</v>
       </c>
       <c r="B508" t="str">
-        <v>Förberäknad AToB0 – inte HDR-vägen</v>
+        <v>HDR-väg, ingen förstärkningskurva</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>Transfer</v>
+        <v>Baked AToB0 — not the HDR path</v>
       </c>
       <c r="B509" t="str">
-        <v>Överföring</v>
+        <v>Förberäknad AToB0 – inte HDR-vägen</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>HDR reference white</v>
+        <v>Transfer</v>
       </c>
       <c r="B510" t="str">
-        <v>HDR-referensvitt</v>
+        <v>Överföring</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>Target headroom</v>
+        <v>HDR reference white</v>
       </c>
       <c r="B511" t="str">
-        <v>Målutrymme</v>
+        <v>HDR-referensvitt</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>{r}× reference white ({n} stops)</v>
+        <v>Target headroom</v>
       </c>
       <c r="B512" t="str">
-        <v>{r}× referensvitt ({n} steg)</v>
+        <v>Målutrymme</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Tone mapping</v>
+        <v>{r}× reference white ({n} stops)</v>
       </c>
       <c r="B513" t="str">
-        <v>Tonmappning</v>
+        <v>{r}× referensvitt ({n} steg)</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>Auto (clause 8.10.3 ranking)</v>
+        <v>Tone mapping</v>
       </c>
       <c r="B514" t="str">
-        <v>Auto (rangordning enligt 8.10.3)</v>
+        <v>Tonmappning</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Gain curve (HAGC)</v>
+        <v>Auto (clause 8.10.3 ranking)</v>
       </c>
       <c r="B515" t="str">
-        <v>Förstärkningskurva (HAGC)</v>
+        <v>Auto (rangordning enligt 8.10.3)</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>Baked SDR fallback (AToB0)</v>
+        <v>Gain curve (HAGC)</v>
       </c>
       <c r="B516" t="str">
-        <v>Förberäknad SDR-reserv (AToB0)</v>
+        <v>Förstärkningskurva (HAGC)</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>Off — as a pre-amendment CMM</v>
+        <v>Baked SDR fallback (AToB0)</v>
       </c>
       <c r="B517" t="str">
-        <v>Av – som en CMM före tillägget</v>
+        <v>Förberäknad SDR-reserv (AToB0)</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>Applying the profile…</v>
+        <v>Off — as a pre-amendment CMM</v>
       </c>
       <c r="B518" t="str">
-        <v>Tillämpar profilen…</v>
+        <v>Av – som en CMM före tillägget</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>OpenEXR holds linear light, so it needs a profile whose transfer is Linear (8).</v>
+        <v>Applying the profile…</v>
       </c>
       <c r="B519" t="str">
-        <v>OpenEXR innehåller linjärt ljus och kräver därför en profil med överföringen Linear (8).</v>
+        <v>Tillämpar profilen…</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>Assigning a profile needs a 3-channel RGB image.</v>
+        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
       </c>
       <c r="B520" t="str">
-        <v>Att tilldela en profil kräver en RGB-bild med 3 kanaler.</v>
+        <v>{format} innehåller linjärt ljus och kräver därför en profil med överföringen Linear (8).</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>To interpret its values, assign a profile above.</v>
+        <v>Assigning a profile needs a 3-channel RGB image.</v>
       </c>
       <c r="B521" t="str">
-        <v>Tilldela en profil ovan för att tolka dess värden.</v>
+        <v>Att tilldela en profil kräver en RGB-bild med 3 kanaler.</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>HDR Profiles</v>
+        <v>To interpret its values, assign a profile above.</v>
       </c>
       <c r="B522" t="str">
-        <v>HDR-profiler</v>
+        <v>Tilldela en profil ovan för att tolka dess värden.</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>Linear transfer</v>
+        <v>HDR Profiles</v>
       </c>
       <c r="B523" t="str">
-        <v>Linjär överföring</v>
+        <v>HDR-profiler</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>Non-linear transfer (PQ, HLG)</v>
+        <v>Linear transfer</v>
       </c>
       <c r="B524" t="str">
-        <v>Icke-linjär överföring (PQ, HLG)</v>
+        <v>Linjär överföring</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>HDR Profiles — Linear transfer</v>
+        <v>Non-linear transfer (PQ, HLG)</v>
       </c>
       <c r="B525" t="str">
-        <v>HDR-profiler – linjär överföring</v>
+        <v>Icke-linjär överföring (PQ, HLG)</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>HDR Profiles — PQ / HLG transfer</v>
+        <v>HDR Profiles — Linear transfer</v>
       </c>
       <c r="B526" t="str">
-        <v>HDR-profiler – PQ/HLG-överföring</v>
+        <v>HDR-profiler – linjär överföring</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>OpenEXR holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
+        <v>HDR Profiles — PQ / HLG transfer</v>
       </c>
       <c r="B527" t="str">
-        <v>OpenEXR innehåller linjärt ljus, så bara HDR-profiler med linjär överföring kan tilldelas.</v>
+        <v>HDR-profiler – PQ/HLG-överföring</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
+        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
       </c>
       <c r="B528" t="str">
-        <v>{n} PQ/HLG-HDR-profil(er) i poolen erbjuds inte – profilpanelen listar dem under HDR-profiler › Icke-linjär överföring.</v>
+        <v>{format} innehåller linjärt ljus, så bara HDR-profiler med linjär överföring kan tilldelas.</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
+        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
       </c>
       <c r="B529" t="str">
-        <v>Det finns ännu ingen HDR-profil med linjär överföring i poolen; profilpanelen grupperar HDR-profiler efter överföring.</v>
+        <v>{n} PQ/HLG-HDR-profil(er) i poolen erbjuds inte – profilpanelen listar dem under HDR-profiler › Icke-linjär överföring.</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
       </c>
       <c r="B530" t="str">
-        <v>IccProfLib avböjer att tillämpa den här förstärkningskurvan: {why}. En CMM faller tillbaka på nästa tonmappningsbeskrivning (avsnitt 8.10.3).</v>
+        <v>Det finns ännu ingen HDR-profil med linjär överföring i poolen; profilpanelen grupperar HDR-profiler efter överföring.</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>Display headroom</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B531" t="str">
-        <v>Skärmutrymme</v>
+        <v>IccProfLib avböjer att tillämpa den här förstärkningskurvan: {why}. En CMM faller tillbaka på nästa tonmappningsbeskrivning (avsnitt 8.10.3).</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>Display headroom</v>
       </c>
       <c r="B532" t="str">
-        <v>{n} steg (≈{r}× referensvitt)</v>
+        <v>Skärmutrymme</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>Baseline</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B533" t="str">
-        <v>Bas</v>
+        <v>{n} steg (≈{r}× referensvitt)</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>Baseline</v>
       </c>
       <c r="B534" t="str">
-        <v>Kurvor i taggen, efter utrymme: {list} steg. Bas {b} steg, HDR-referensvitt {w} cd/m².</v>
+        <v>Bas</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B535" t="str">
-        <v>Det här utrymmet ligger utanför taggens kurvor, så närmaste kurva används oförändrad – biblioteket extrapolerar inte bortom dem.</v>
+        <v>Kurvor i taggen, efter utrymme: {list} steg. Bas {b} steg, HDR-referensvitt {w} cd/m².</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B536" t="str">
-        <v>Vissa lutningar är härledda (PCHIP) och inte lagrade i taggen. Härledningen rekonstruerar ett SMPTE-avsnitt, så betrakta de kurvornas form som preliminär.</v>
+        <v>Det här utrymmet ligger utanför taggens kurvor, så närmaste kurva används oförändrad – biblioteket extrapolerar inte bortom dem.</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B537" t="str">
-        <v>Taggen begär tonmappning mot referensvitt, så dess kurvor konstrueras av biblioteket i stället för att läsas från filen (en konstruktion från ett kommittéutkast).</v>
+        <v>Vissa lutningar är härledda (PCHIP) och inte lagrade i taggen. Härledningen rekonstruerar ett SMPTE-avsnitt, så betrakta de kurvornas form som preliminär.</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B538" t="str">
-        <v>Inga alternativa bilder: taggen begär ingen tonmappning, bara en begränsning till skärmens färgvolym.</v>
+        <v>Taggen begär tonmappning mot referensvitt, så dess kurvor konstrueras av biblioteket i stället för att läsas från filen (en konstruktion från ett kommittéutkast).</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B539" t="str">
-        <v>De två kurvorna som blandas vid detta utrymme blandar färgkanalerna olika, så det finns ingen enskild förstärkningskurva att rita. Tonkurvan nedan är ändå exakt.</v>
+        <v>Inga alternativa bilder: taggen begär ingen tonmappning, bara en begränsning till skärmens färgvolym.</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B540" t="str">
-        <v>Kurva vid {h} steg (ingen förstärkning)</v>
+        <v>De två kurvorna som blandas vid detta utrymme blandar färgkanalerna olika, så det finns ingen enskild förstärkningskurva att rita. Tonkurvan nedan är ändå exakt.</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>Curve at {h} stops</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B541" t="str">
-        <v>Kurva vid {h} steg</v>
+        <v>Kurva vid {h} steg (ingen förstärkning)</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B542" t="str">
-        <v>Tillämpad vid {h} steg</v>
+        <v>Kurva vid {h} steg</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B543" t="str">
-        <v>Förstärkning vid detta utrymme</v>
+        <v>Tillämpad vid {h} steg</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B544" t="str">
-        <v>Blandad indata (linjär, 1,0 = HDR-referensvitt)</v>
+        <v>Förstärkning vid detta utrymme</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B545" t="str">
-        <v>Förstärkning (log2-steg)</v>
+        <v>Blandad indata (linjär, 1,0 = HDR-referensvitt)</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B546" t="str">
-        <v>Gråskalans tonkurva vid detta utrymme</v>
+        <v>Förstärkning (log2-steg)</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B547" t="str">
-        <v>Indata (× HDR-referensvitt)</v>
+        <v>Gråskalans tonkurva vid detta utrymme</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B548" t="str">
-        <v>Utdata (× HDR-referensvitt)</v>
+        <v>Indata (× HDR-referensvitt)</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>No change</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B549" t="str">
-        <v>Ingen ändring</v>
+        <v>Utdata (× HDR-referensvitt)</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>No change</v>
       </c>
       <c r="B550" t="str">
-        <v>Skärmens topp vid {h} steg</v>
+        <v>Ingen ändring</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>Output at {h} stops</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B551" t="str">
-        <v>Utdata vid {h} steg</v>
+        <v>Skärmens topp vid {h} steg</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B552" t="str">
-        <v>HDR, färgomfång och pixelförhållande uppdateras när fönstret flyttas till en skärm där de skiljer sig.</v>
+        <v>Utdata vid {h} steg</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>Identify displays</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B553" t="str">
-        <v>Identifiera skärmar</v>
+        <v>HDR, färgomfång och pixelförhållande uppdateras när fönstret flyttas till en skärm där de skiljer sig.</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Identify displays</v>
       </c>
       <c r="B554" t="str">
-        <v>Ber om tillåtelse att se vilken skärm fönstret ligger på, så att panelen även uppdateras mellan likadana skärmar och visar HDR-utrymme där webbläsaren exponerar det.</v>
+        <v>Identifiera skärmar</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B555" t="str">
-        <v>Följer vilken skärm fönstret ligger på.</v>
+        <v>Ber om tillåtelse att se vilken skärm fönstret ligger på, så att panelen även uppdateras mellan likadana skärmar och visar HDR-utrymme där webbläsaren exponerar det.</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B556" t="str">
-        <v>Tillåtelse att identifiera skärmar nekades. Den kan ändras i webbplatsens inställningar.</v>
+        <v>Följer vilken skärm fönstret ligger på.</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B557" t="str">
-        <v>Den här webbläsaren kan inte identifiera skärmar; bara den automatiska uppdateringen ovan gäller.</v>
+        <v>Tillåtelse att identifiera skärmar nekades. Den kan ändras i webbplatsens inställningar.</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Could not identify displays.</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B558" t="str">
-        <v>Kunde inte identifiera skärmar.</v>
+        <v>Den här webbläsaren kan inte identifiera skärmar; bara den automatiska uppdateringen ovan gäller.</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Display events</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B559" t="str">
-        <v>Skärmhändelser</v>
+        <v>Kunde inte identifiera skärmar.</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Display events</v>
       </c>
       <c r="B560" t="str">
-        <v>Inga händelser än. Dra fönstret till en annan skärm.</v>
+        <v>Skärmhändelser</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>Colour primaries</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B561" t="str">
-        <v>Färgprimärer</v>
+        <v>Inga händelser än. Dra fönstret till en annan skärm.</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Transfer characteristics</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B562" t="str">
-        <v>Överföringsfunktion</v>
+        <v>Färgprimärer</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>Matrix coefficients</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B563" t="str">
-        <v>Matriskoefficienter</v>
+        <v>Överföringsfunktion</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>Video full-range flag</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B564" t="str">
-        <v>Flagga för fullt videoomfång</v>
+        <v>Matriskoefficienter</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Full range</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B565" t="str">
-        <v>Fullt omfång</v>
+        <v>Flagga för fullt videoomfång</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Narrow range</v>
+        <v>Full range</v>
       </c>
       <c r="B566" t="str">
-        <v>Begränsat omfång</v>
+        <v>Fullt omfång</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Narrow range</v>
       </c>
       <c r="B567" t="str">
-        <v>inte tilldelad av ITU-T H.273</v>
+        <v>Begränsat omfång</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B568" t="str">
-        <v>Färgprimärer 2 (Ospecificerad) hänvisar till profilen själv — primärerna hämtas från färgämnestaggarna och inte från den här taggen.</v>
+        <v>inte tilldelad av ITU-T H.273</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B569" t="str">
-        <v>De fyra reserverade byten i den här taggen är inte alla noll.</v>
+        <v>Färgprimärer 2 (Ospecificerad) hänvisar till profilen själv — primärerna hämtas från färgämnestaggarna och inte från den här taggen.</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>REPORT</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B570" t="str">
-        <v>RAPPORT</v>
+        <v>De fyra reserverade byten i den här taggen är inte alla noll.</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>FAIL</v>
+        <v>REPORT</v>
       </c>
       <c r="B571" t="str">
-        <v>UNDERKÄND</v>
+        <v>RAPPORT</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>checks</v>
+        <v>FAIL</v>
       </c>
       <c r="B572" t="str">
-        <v>kontroller</v>
+        <v>UNDERKÄND</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>checks</v>
       </c>
       <c r="B573" t="str">
-        <v>Genererad av iccPawgReport (iccDEV) · checklista från ICC Profile Assessment Working Group.</v>
+        <v>kontroller</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B574" t="str">
-        <v>ICC-profilverktyg · drivs av IccProfLib</v>
+        <v>Genererad av iccPawgReport (iccDEV) · checklista från ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>ICC Profile Tool</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B575" t="str">
-        <v>ICC-profilverktyg</v>
+        <v>ICC-profilverktyg · drivs av IccProfLib</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>Powered by {lib}</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B576" t="str">
-        <v>Drivs av {lib}</v>
+        <v>ICC-profilverktyg</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Subscribe</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B577" t="str">
-        <v>Prenumerera</v>
+        <v>Drivs av {lib}</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Subscribe</v>
       </c>
       <c r="B578" t="str">
-        <v>Få besked om nya profiletool-versioner</v>
+        <v>Prenumerera</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>Get notified about new releases</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B579" t="str">
-        <v>Få besked om nya versioner</v>
+        <v>Få besked om nya profiletool-versioner</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>Close</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B580" t="str">
-        <v>Stäng</v>
+        <v>Få besked om nya versioner</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Close</v>
       </c>
       <c r="B581" t="str">
-        <v>Vi mejlar dig när en ny större eller mindre version av profiletool släpps. Patchversioner hoppas över. Din adress granskas manuellt innan den läggs till.</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Email address</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B582" t="str">
-        <v>E-postadress</v>
+        <v>Vi mejlar dig när en ny större eller mindre version av profiletool släpps. Patchversioner hoppas över. Din adress granskas manuellt innan den läggs till.</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>you@example.com</v>
+        <v>Email address</v>
       </c>
       <c r="B583" t="str">
-        <v>du@exempel.com</v>
+        <v>E-postadress</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>How will you use profiletool?</v>
+        <v>you@example.com</v>
       </c>
       <c r="B584" t="str">
-        <v>Hur kommer du att använda profiletool?</v>
+        <v>du@exempel.com</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>(optional)</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B585" t="str">
-        <v>(valfritt)</v>
+        <v>Hur kommer du att använda profiletool?</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>(optional)</v>
       </c>
       <c r="B586" t="str">
-        <v>t.ex. utvärdera ICC-profiler för tryckkalibrering</v>
+        <v>(valfritt)</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B587" t="str">
-        <v>Jag godkänner att ta emot e-post om profiletool-versioner. Jag kan avsluta prenumerationen när som helst.</v>
+        <v>t.ex. utvärdera ICC-profiler för tryckkalibrering</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Cancel</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B588" t="str">
-        <v>Avbryt</v>
+        <v>Jag godkänner att ta emot e-post om profiletool-versioner. Jag kan avsluta prenumerationen när som helst.</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Subscribe</v>
+        <v>Cancel</v>
       </c>
       <c r="B589" t="str">
-        <v>Prenumerera</v>
+        <v>Avbryt</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B590" t="str">
-        <v>Tack — vi hör av oss.</v>
+        <v>Prenumerera</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B591" t="str">
-        <v>När du har godkänts får du ett välkomstmejl. Därefter hör du bara från oss när en ny version av profiletool släpps.</v>
+        <v>Tack — vi hör av oss.</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Close</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B592" t="str">
-        <v>Stäng</v>
+        <v>När du har godkänts får du ett välkomstmejl. Därefter hör du bara från oss när en ny version av profiletool släpps.</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Privacy notice</v>
+        <v>Close</v>
       </c>
       <c r="B593" t="str">
-        <v>Integritetsmeddelande</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B594" t="str">
-        <v>Ange en giltig e-postadress.</v>
+        <v>Integritetsmeddelande</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B595" t="str">
-        <v>För många förfrågningar. Försök igen senare.</v>
+        <v>Ange en giltig e-postadress.</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B596" t="str">
-        <v>Kontrollera formuläret och försök igen.</v>
+        <v>För många förfrågningar. Försök igen senare.</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B597" t="str">
-        <v>Det gick inte att skicka din förfrågan. Försök igen.</v>
+        <v>Kontrollera formuläret och försök igen.</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B598" t="str">
-        <v>Nätverksfel. Försök igen.</v>
+        <v>Det gick inte att skicka din förfrågan. Försök igen.</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>Error:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B599" t="str">
-        <v>Fel:</v>
+        <v>Nätverksfel. Försök igen.</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>Convert to XML</v>
+        <v>Error:</v>
       </c>
       <c r="B600" t="str">
-        <v>Konvertera till XML</v>
+        <v>Fel:</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B601" t="str">
-        <v>Konvertera till JSON</v>
+        <v>Konvertera till XML</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B602" t="str">
-        <v>Konvertera till ICC</v>
+        <v>Konvertera till JSON</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B603" t="str">
-        <v>Konverterar till XML…</v>
+        <v>Konvertera till ICC</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B604" t="str">
-        <v>Konverterar till JSON…</v>
+        <v>Konverterar till XML…</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B605" t="str">
-        <v>Konverterar till ICC…</v>
+        <v>Konverterar till JSON…</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B606" t="str">
-        <v>Läs in ICC-profil</v>
+        <v>Konverterar till ICC…</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B607" t="str">
-        <v>Släppzon för ICC-profilfiler</v>
+        <v>Läs in ICC-profil</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Profile ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B608" t="str">
-        <v>Profil-ID</v>
+        <v>Släppzon för ICC-profilfiler</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>No tags found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B609" t="str">
-        <v>Inga taggar hittades.</v>
+        <v>Profil-ID</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>Tag Name</v>
+        <v>No tags found.</v>
       </c>
       <c r="B610" t="str">
-        <v>Taggnamn</v>
+        <v>Inga taggar hittades.</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>ID</v>
+        <v>Tag Name</v>
       </c>
       <c r="B611" t="str">
-        <v>ID</v>
+        <v>Taggnamn</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
       <c r="B612" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>Size</v>
+        <v>Offset</v>
       </c>
       <c r="B613" t="str">
-        <v>Storlek</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>Pad</v>
+        <v>Size</v>
       </c>
       <c r="B614" t="str">
-        <v>Utfyllnad</v>
+        <v>Storlek</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>Bytes changed since load</v>
+        <v>Pad</v>
       </c>
       <c r="B615" t="str">
-        <v>Byte ändrade sedan inläsning</v>
+        <v>Utfyllnad</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>Type</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B616" t="str">
-        <v>Typ</v>
+        <v>Byte ändrade sedan inläsning</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>Array of {type}</v>
+        <v>Type</v>
       </c>
       <c r="B617" t="str">
-        <v>Array av {type}</v>
+        <v>Typ</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>(No content)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B618" t="str">
-        <v>(Inget innehåll)</v>
+        <v>Array av {type}</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>bytes</v>
+        <v>(No content)</v>
       </c>
       <c r="B619" t="str">
-        <v>byte</v>
+        <v>(Inget innehåll)</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>Loading full description…</v>
+        <v>bytes</v>
       </c>
       <c r="B620" t="str">
-        <v>Läser in fullständig beskrivning…</v>
+        <v>byte</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>Could not load full description:</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B621" t="str">
-        <v>Kunde inte läsa in fullständig beskrivning:</v>
+        <v>Läser in fullständig beskrivning…</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B622" t="str">
-        <v>Den här profilen kunde inte tolkas helt och får inte tillämpas. Huvudet och taggkatalogen nedan visas endast för granskning.</v>
+        <v>Kunde inte läsa in fullständig beskrivning:</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B623" t="str">
-        <v>Tagginnehåll otillgängligt — profilen kunde inte tolkas helt.</v>
+        <v>Den här profilen kunde inte tolkas helt och får inte tillämpas. Huvudet och taggkatalogen nedan visas endast för granskning.</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>No validation output</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B624" t="str">
-        <v>Ingen valideringsutdata</v>
+        <v>Tagginnehåll otillgängligt — profilen kunde inte tolkas helt.</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>Profile is valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B625" t="str">
-        <v>Profilen är giltig</v>
+        <v>Ingen valideringsutdata</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B626" t="str">
-        <v>Profilen har varning(ar)</v>
+        <v>Profilen är giltig</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B627" t="str">
-        <v>Profilen följer inte specifikationen</v>
+        <v>Profilen har varning(ar)</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B628" t="str">
-        <v>Kritiskt valideringsfel</v>
+        <v>Profilen följer inte specifikationen</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B629" t="str">
-        <v>Okänd valideringsstatus</v>
+        <v>Kritiskt valideringsfel</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B630" t="str">
-        <v>Kritiskt — visas endast för granskning</v>
+        <v>Okänd valideringsstatus</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B631" t="str">
-        <v>Inga varningar eller fel hittades.</v>
+        <v>Kritiskt — visas endast för granskning</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>Valid</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B632" t="str">
-        <v>Giltig</v>
+        <v>Inga varningar eller fel hittades.</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>Warning</v>
+        <v>Valid</v>
       </c>
       <c r="B633" t="str">
-        <v>Varning</v>
+        <v>Giltig</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>Error</v>
+        <v>Warning</v>
       </c>
       <c r="B634" t="str">
-        <v>Fel</v>
+        <v>Varning</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>Unknown</v>
+        <v>Error</v>
       </c>
       <c r="B635" t="str">
-        <v>Okänd</v>
+        <v>Fel</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>Pass</v>
+        <v>Unknown</v>
       </c>
       <c r="B636" t="str">
-        <v>Godkänd</v>
+        <v>Okänd</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="B637" t="str">
-        <v>Underkänd</v>
+        <v>Godkänd</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>View in context</v>
+        <v>Fail</v>
       </c>
       <c r="B638" t="str">
-        <v>Visa i sammanhang</v>
+        <v>Underkänd</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>Validation detail</v>
+        <v>View in context</v>
       </c>
       <c r="B639" t="str">
-        <v>Valideringsdetalj</v>
+        <v>Visa i sammanhang</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>Triggered by</v>
+        <v>Validation detail</v>
       </c>
       <c r="B640" t="str">
-        <v>Utlöst av</v>
+        <v>Valideringsdetalj</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Field</v>
+        <v>Triggered by</v>
       </c>
       <c r="B641" t="str">
-        <v>Fält</v>
+        <v>Utlöst av</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>Current value</v>
+        <v>Field</v>
       </c>
       <c r="B642" t="str">
-        <v>Aktuellt värde</v>
+        <v>Fält</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>Required: 0</v>
+        <v>Current value</v>
       </c>
       <c r="B643" t="str">
-        <v>Krävs: 0</v>
+        <v>Aktuellt värde</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>Expected: {value}</v>
+        <v>Required: 0</v>
       </c>
       <c r="B644" t="str">
-        <v>Förväntat: {value}</v>
+        <v>Krävs: 0</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>Invalid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B645" t="str">
-        <v>Ogiltigt</v>
+        <v>Förväntat: {value}</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Invalid</v>
       </c>
       <c r="B646" t="str">
-        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
+        <v>Ogiltigt</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>Close</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B647" t="str">
-        <v>Stäng</v>
+        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>Loading XML editor…</v>
+        <v>Close</v>
       </c>
       <c r="B648" t="str">
-        <v>Läser in XML-redigeraren…</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B649" t="str">
-        <v>Läser in JSON-redigeraren…</v>
+        <v>Läser in XML-redigeraren…</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B650" t="str">
-        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>Läser in JSON-redigeraren…</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B651" t="str">
-        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B652" t="str">
-        <v>● osparade XML-ändringar</v>
+        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B653" t="str">
-        <v>● osparade JSON-ändringar</v>
+        <v>● osparade XML-ändringar</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B654" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
+        <v>● osparade JSON-ändringar</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B655" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
+        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B656" t="str">
-        <v>indrag</v>
+        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>sort keys</v>
+        <v>indent</v>
       </c>
       <c r="B657" t="str">
-        <v>sortera nycklar</v>
+        <v>indrag</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B658" t="str">
+        <v>sortera nycklar</v>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B658" t="str">
+      <c r="B659" t="str">
         <v>Profilen skrevs från ändringarna, men omvalideringen misslyckades:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B658"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B659"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Sv.xlsx
+++ b/translations/Eng-Sv.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B659"/>
+  <dimension ref="A1:B670"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -4347,1343 +4347,1431 @@
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
+        <v>Image details</v>
       </c>
       <c r="B493" t="str">
-        <v>Begränsar ljusstyrkan till den topp skärmen rapporterar. I Windows kan värdet släpa efter ändringar av ljusstyrkan.</v>
+        <v>Bilddetaljer</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>no limit</v>
+        <v>not available — the browser renders this image and cannot cap it at a set peak</v>
       </c>
       <c r="B494" t="str">
-        <v>ingen gräns</v>
+        <v>inte tillgänglig – webbläsaren återger bilden och kan inte begränsa den till en viss topp</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>limit {n} stops ({r}×)</v>
+        <v>not available — this output shows nothing above SDR white</v>
       </c>
       <c r="B495" t="str">
-        <v>gräns {n} steg ({r}×)</v>
+        <v>inte tillgänglig – den här utgången visar inget över SDR-vitt</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>SDR white</v>
+        <v>not available — this display’s peak is not known</v>
       </c>
       <c r="B496" t="str">
-        <v>SDR-vitt</v>
+        <v>inte tillgänglig – skärmens toppluminans är okänd</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
+        <v>Zoom in</v>
       </c>
       <c r="B497" t="str">
-        <v>Vanligt SDR-vitt för jämförelse. På en HDR-skärm ser HDR-högdagrar ljusare ut än detta.</v>
+        <v>Zooma in</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>SDR white patch</v>
+        <v>Zoom out</v>
       </c>
       <c r="B498" t="str">
-        <v>SDR-vit ruta</v>
+        <v>Zooma ut</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Drag to move it; double-click to put it back beside the image.</v>
+        <v>Fit image</v>
       </c>
       <c r="B499" t="str">
-        <v>Dra för att flytta den; dubbelklicka för att sätta tillbaka den bredvid bilden.</v>
+        <v>Anpassa bilden</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>Assign profile</v>
+        <v>Actual pixels (1:1)</v>
       </c>
       <c r="B500" t="str">
-        <v>Tilldela profil</v>
+        <v>Faktiska pixlar (1:1)</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>None — use what the file signals</v>
+        <v>Drag to pan · Ctrl+wheel to zoom · double-click to reset</v>
       </c>
       <c r="B501" t="str">
-        <v>Ingen – det filen anger</v>
+        <v>Dra för att panorera · Ctrl+hjul för att zooma · dubbelklicka för att återställa</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>Embedded profile ({n} B)</v>
+        <v>Drag to resize the image area; double-click to restore the default size</v>
       </c>
       <c r="B502" t="str">
-        <v>Inbäddad profil ({n} B)</v>
+        <v>Dra för att ändra bildytans storlek; dubbelklicka för standardstorlek</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>HDR Profiles in the pool</v>
+        <v>Image view</v>
       </c>
       <c r="B503" t="str">
-        <v>HDR-profiler i poolen</v>
+        <v>Bildvy</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>Profile</v>
+        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
       </c>
       <c r="B504" t="str">
-        <v>Profil</v>
+        <v>Begränsar ljusstyrkan till den topp skärmen rapporterar. I Windows kan värdet släpa efter ändringar av ljusstyrkan.</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>embedded profile</v>
+        <v>no limit</v>
       </c>
       <c r="B505" t="str">
-        <v>inbäddad profil</v>
+        <v>ingen gräns</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>Colour engine path</v>
+        <v>limit {n} stops ({r}×)</v>
       </c>
       <c r="B506" t="str">
-        <v>Färgmotorns väg</v>
+        <v>gräns {n} steg ({r}×)</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>HDR path, gain curve applied</v>
+        <v>SDR white</v>
       </c>
       <c r="B507" t="str">
-        <v>HDR-väg, förstärkningskurva tillämpad</v>
+        <v>SDR-vitt</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>HDR path, no gain curve</v>
+        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
       </c>
       <c r="B508" t="str">
-        <v>HDR-väg, ingen förstärkningskurva</v>
+        <v>Vanligt SDR-vitt för jämförelse. På en HDR-skärm ser HDR-högdagrar ljusare ut än detta.</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>Baked AToB0 — not the HDR path</v>
+        <v>SDR white patch</v>
       </c>
       <c r="B509" t="str">
-        <v>Förberäknad AToB0 – inte HDR-vägen</v>
+        <v>SDR-vit ruta</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>Transfer</v>
+        <v>Drag to move it; double-click to put it back beside the image.</v>
       </c>
       <c r="B510" t="str">
-        <v>Överföring</v>
+        <v>Dra för att flytta den; dubbelklicka för att sätta tillbaka den bredvid bilden.</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>HDR reference white</v>
+        <v>Assign profile</v>
       </c>
       <c r="B511" t="str">
-        <v>HDR-referensvitt</v>
+        <v>Tilldela profil</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>Target headroom</v>
+        <v>None — use what the file signals</v>
       </c>
       <c r="B512" t="str">
-        <v>Målutrymme</v>
+        <v>Ingen – det filen anger</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>{r}× reference white ({n} stops)</v>
+        <v>Embedded profile ({n} B)</v>
       </c>
       <c r="B513" t="str">
-        <v>{r}× referensvitt ({n} steg)</v>
+        <v>Inbäddad profil ({n} B)</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>Tone mapping</v>
+        <v>HDR Profiles in the pool</v>
       </c>
       <c r="B514" t="str">
-        <v>Tonmappning</v>
+        <v>HDR-profiler i poolen</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Auto (clause 8.10.3 ranking)</v>
+        <v>Profile</v>
       </c>
       <c r="B515" t="str">
-        <v>Auto (rangordning enligt 8.10.3)</v>
+        <v>Profil</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>Gain curve (HAGC)</v>
+        <v>embedded profile</v>
       </c>
       <c r="B516" t="str">
-        <v>Förstärkningskurva (HAGC)</v>
+        <v>inbäddad profil</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>Baked SDR fallback (AToB0)</v>
+        <v>Colour engine path</v>
       </c>
       <c r="B517" t="str">
-        <v>Förberäknad SDR-reserv (AToB0)</v>
+        <v>Färgmotorns väg</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>Off — as a pre-amendment CMM</v>
+        <v>HDR path, gain curve applied</v>
       </c>
       <c r="B518" t="str">
-        <v>Av – som en CMM före tillägget</v>
+        <v>HDR-väg, förstärkningskurva tillämpad</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>Applying the profile…</v>
+        <v>HDR path, no gain curve</v>
       </c>
       <c r="B519" t="str">
-        <v>Tillämpar profilen…</v>
+        <v>HDR-väg, ingen förstärkningskurva</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
+        <v>Baked AToB0 — not the HDR path</v>
       </c>
       <c r="B520" t="str">
-        <v>{format} innehåller linjärt ljus och kräver därför en profil med överföringen Linear (8).</v>
+        <v>Förberäknad AToB0 – inte HDR-vägen</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>Assigning a profile needs a 3-channel RGB image.</v>
+        <v>Transfer</v>
       </c>
       <c r="B521" t="str">
-        <v>Att tilldela en profil kräver en RGB-bild med 3 kanaler.</v>
+        <v>Överföring</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>To interpret its values, assign a profile above.</v>
+        <v>HDR reference white</v>
       </c>
       <c r="B522" t="str">
-        <v>Tilldela en profil ovan för att tolka dess värden.</v>
+        <v>HDR-referensvitt</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>HDR Profiles</v>
+        <v>Target headroom</v>
       </c>
       <c r="B523" t="str">
-        <v>HDR-profiler</v>
+        <v>Målutrymme</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>Linear transfer</v>
+        <v>{r}× reference white ({n} stops)</v>
       </c>
       <c r="B524" t="str">
-        <v>Linjär överföring</v>
+        <v>{r}× referensvitt ({n} steg)</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>Non-linear transfer (PQ, HLG)</v>
+        <v>Tone mapping</v>
       </c>
       <c r="B525" t="str">
-        <v>Icke-linjär överföring (PQ, HLG)</v>
+        <v>Tonmappning</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>HDR Profiles — Linear transfer</v>
+        <v>Auto (clause 8.10.3 ranking)</v>
       </c>
       <c r="B526" t="str">
-        <v>HDR-profiler – linjär överföring</v>
+        <v>Auto (rangordning enligt 8.10.3)</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>HDR Profiles — PQ / HLG transfer</v>
+        <v>Gain curve (HAGC)</v>
       </c>
       <c r="B527" t="str">
-        <v>HDR-profiler – PQ/HLG-överföring</v>
+        <v>Förstärkningskurva (HAGC)</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
+        <v>Baked SDR fallback (AToB0)</v>
       </c>
       <c r="B528" t="str">
-        <v>{format} innehåller linjärt ljus, så bara HDR-profiler med linjär överföring kan tilldelas.</v>
+        <v>Förberäknad SDR-reserv (AToB0)</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
+        <v>Off — as a pre-amendment CMM</v>
       </c>
       <c r="B529" t="str">
-        <v>{n} PQ/HLG-HDR-profil(er) i poolen erbjuds inte – profilpanelen listar dem under HDR-profiler › Icke-linjär överföring.</v>
+        <v>Av – som en CMM före tillägget</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
+        <v>Applying the profile…</v>
       </c>
       <c r="B530" t="str">
-        <v>Det finns ännu ingen HDR-profil med linjär överföring i poolen; profilpanelen grupperar HDR-profiler efter överföring.</v>
+        <v>Tillämpar profilen…</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
       </c>
       <c r="B531" t="str">
-        <v>IccProfLib avböjer att tillämpa den här förstärkningskurvan: {why}. En CMM faller tillbaka på nästa tonmappningsbeskrivning (avsnitt 8.10.3).</v>
+        <v>{format} innehåller linjärt ljus och kräver därför en profil med överföringen Linear (8).</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Display headroom</v>
+        <v>Assigning a profile needs a 3-channel RGB image.</v>
       </c>
       <c r="B532" t="str">
-        <v>Skärmutrymme</v>
+        <v>Att tilldela en profil kräver en RGB-bild med 3 kanaler.</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>To interpret its values, assign a profile above.</v>
       </c>
       <c r="B533" t="str">
-        <v>{n} steg (≈{r}× referensvitt)</v>
+        <v>Tilldela en profil ovan för att tolka dess värden.</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>Baseline</v>
+        <v>HDR Profiles</v>
       </c>
       <c r="B534" t="str">
-        <v>Bas</v>
+        <v>HDR-profiler</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>Linear transfer</v>
       </c>
       <c r="B535" t="str">
-        <v>Kurvor i taggen, efter utrymme: {list} steg. Bas {b} steg, HDR-referensvitt {w} cd/m².</v>
+        <v>Linjär överföring</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>Non-linear transfer (PQ, HLG)</v>
       </c>
       <c r="B536" t="str">
-        <v>Det här utrymmet ligger utanför taggens kurvor, så närmaste kurva används oförändrad – biblioteket extrapolerar inte bortom dem.</v>
+        <v>Icke-linjär överföring (PQ, HLG)</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>HDR Profiles — Linear transfer</v>
       </c>
       <c r="B537" t="str">
-        <v>Vissa lutningar är härledda (PCHIP) och inte lagrade i taggen. Härledningen rekonstruerar ett SMPTE-avsnitt, så betrakta de kurvornas form som preliminär.</v>
+        <v>HDR-profiler – linjär överföring</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>HDR Profiles — PQ / HLG transfer</v>
       </c>
       <c r="B538" t="str">
-        <v>Taggen begär tonmappning mot referensvitt, så dess kurvor konstrueras av biblioteket i stället för att läsas från filen (en konstruktion från ett kommittéutkast).</v>
+        <v>HDR-profiler – PQ/HLG-överföring</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
       </c>
       <c r="B539" t="str">
-        <v>Inga alternativa bilder: taggen begär ingen tonmappning, bara en begränsning till skärmens färgvolym.</v>
+        <v>{format} innehåller linjärt ljus, så bara HDR-profiler med linjär överföring kan tilldelas.</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
       </c>
       <c r="B540" t="str">
-        <v>De två kurvorna som blandas vid detta utrymme blandar färgkanalerna olika, så det finns ingen enskild förstärkningskurva att rita. Tonkurvan nedan är ändå exakt.</v>
+        <v>{n} PQ/HLG-HDR-profil(er) i poolen erbjuds inte – profilpanelen listar dem under HDR-profiler › Icke-linjär överföring.</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
       </c>
       <c r="B541" t="str">
-        <v>Kurva vid {h} steg (ingen förstärkning)</v>
+        <v>Det finns ännu ingen HDR-profil med linjär överföring i poolen; profilpanelen grupperar HDR-profiler efter överföring.</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>Curve at {h} stops</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B542" t="str">
-        <v>Kurva vid {h} steg</v>
+        <v>IccProfLib avböjer att tillämpa den här förstärkningskurvan: {why}. En CMM faller tillbaka på nästa tonmappningsbeskrivning (avsnitt 8.10.3).</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Display headroom</v>
       </c>
       <c r="B543" t="str">
-        <v>Tillämpad vid {h} steg</v>
+        <v>Skärmutrymme</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B544" t="str">
-        <v>Förstärkning vid detta utrymme</v>
+        <v>{n} steg (≈{r}× referensvitt)</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Baseline</v>
       </c>
       <c r="B545" t="str">
-        <v>Blandad indata (linjär, 1,0 = HDR-referensvitt)</v>
+        <v>Bas</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B546" t="str">
-        <v>Förstärkning (log2-steg)</v>
+        <v>Kurvor i taggen, efter utrymme: {list} steg. Bas {b} steg, HDR-referensvitt {w} cd/m².</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B547" t="str">
-        <v>Gråskalans tonkurva vid detta utrymme</v>
+        <v>Det här utrymmet ligger utanför taggens kurvor, så närmaste kurva används oförändrad – biblioteket extrapolerar inte bortom dem.</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B548" t="str">
-        <v>Indata (× HDR-referensvitt)</v>
+        <v>Vissa lutningar är härledda (PCHIP) och inte lagrade i taggen. Härledningen rekonstruerar ett SMPTE-avsnitt, så betrakta de kurvornas form som preliminär.</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B549" t="str">
-        <v>Utdata (× HDR-referensvitt)</v>
+        <v>Taggen begär tonmappning mot referensvitt, så dess kurvor konstrueras av biblioteket i stället för att läsas från filen (en konstruktion från ett kommittéutkast).</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>No change</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B550" t="str">
-        <v>Ingen ändring</v>
+        <v>Inga alternativa bilder: taggen begär ingen tonmappning, bara en begränsning till skärmens färgvolym.</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B551" t="str">
-        <v>Skärmens topp vid {h} steg</v>
+        <v>De två kurvorna som blandas vid detta utrymme blandar färgkanalerna olika, så det finns ingen enskild förstärkningskurva att rita. Tonkurvan nedan är ändå exakt.</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>Output at {h} stops</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B552" t="str">
-        <v>Utdata vid {h} steg</v>
+        <v>Kurva vid {h} steg (ingen förstärkning)</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B553" t="str">
-        <v>HDR, färgomfång och pixelförhållande uppdateras när fönstret flyttas till en skärm där de skiljer sig.</v>
+        <v>Kurva vid {h} steg</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>Identify displays</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B554" t="str">
-        <v>Identifiera skärmar</v>
+        <v>Tillämpad vid {h} steg</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B555" t="str">
-        <v>Ber om tillåtelse att se vilken skärm fönstret ligger på, så att panelen även uppdateras mellan likadana skärmar och visar HDR-utrymme där webbläsaren exponerar det.</v>
+        <v>Förstärkning vid detta utrymme</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B556" t="str">
-        <v>Följer vilken skärm fönstret ligger på.</v>
+        <v>Blandad indata (linjär, 1,0 = HDR-referensvitt)</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B557" t="str">
-        <v>Tillåtelse att identifiera skärmar nekades. Den kan ändras i webbplatsens inställningar.</v>
+        <v>Förstärkning (log2-steg)</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B558" t="str">
-        <v>Den här webbläsaren kan inte identifiera skärmar; bara den automatiska uppdateringen ovan gäller.</v>
+        <v>Gråskalans tonkurva vid detta utrymme</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Could not identify displays.</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B559" t="str">
-        <v>Kunde inte identifiera skärmar.</v>
+        <v>Indata (× HDR-referensvitt)</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Display events</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B560" t="str">
-        <v>Skärmhändelser</v>
+        <v>Utdata (× HDR-referensvitt)</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>No change</v>
       </c>
       <c r="B561" t="str">
-        <v>Inga händelser än. Dra fönstret till en annan skärm.</v>
+        <v>Ingen ändring</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Colour primaries</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B562" t="str">
-        <v>Färgprimärer</v>
+        <v>Skärmens topp vid {h} steg</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>Transfer characteristics</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B563" t="str">
-        <v>Överföringsfunktion</v>
+        <v>Utdata vid {h} steg</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>Matrix coefficients</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B564" t="str">
-        <v>Matriskoefficienter</v>
+        <v>HDR, färgomfång och pixelförhållande uppdateras när fönstret flyttas till en skärm där de skiljer sig.</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Video full-range flag</v>
+        <v>Identify displays</v>
       </c>
       <c r="B565" t="str">
-        <v>Flagga för fullt videoomfång</v>
+        <v>Identifiera skärmar</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Full range</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B566" t="str">
-        <v>Fullt omfång</v>
+        <v>Ber om tillåtelse att se vilken skärm fönstret ligger på, så att panelen även uppdateras mellan likadana skärmar och visar HDR-utrymme där webbläsaren exponerar det.</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Narrow range</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B567" t="str">
-        <v>Begränsat omfång</v>
+        <v>Följer vilken skärm fönstret ligger på.</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B568" t="str">
-        <v>inte tilldelad av ITU-T H.273</v>
+        <v>Tillåtelse att identifiera skärmar nekades. Den kan ändras i webbplatsens inställningar.</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B569" t="str">
-        <v>Färgprimärer 2 (Ospecificerad) hänvisar till profilen själv — primärerna hämtas från färgämnestaggarna och inte från den här taggen.</v>
+        <v>Den här webbläsaren kan inte identifiera skärmar; bara den automatiska uppdateringen ovan gäller.</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B570" t="str">
-        <v>De fyra reserverade byten i den här taggen är inte alla noll.</v>
+        <v>Kunde inte identifiera skärmar.</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>REPORT</v>
+        <v>Display events</v>
       </c>
       <c r="B571" t="str">
-        <v>RAPPORT</v>
+        <v>Skärmhändelser</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>FAIL</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B572" t="str">
-        <v>UNDERKÄND</v>
+        <v>Inga händelser än. Dra fönstret till en annan skärm.</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>checks</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B573" t="str">
-        <v>kontroller</v>
+        <v>Färgprimärer</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B574" t="str">
-        <v>Genererad av iccPawgReport (iccDEV) · checklista från ICC Profile Assessment Working Group.</v>
+        <v>Överföringsfunktion</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B575" t="str">
-        <v>ICC-profilverktyg · drivs av IccProfLib</v>
+        <v>Matriskoefficienter</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B576" t="str">
-        <v>ICC-profilverktyg</v>
+        <v>Flagga för fullt videoomfång</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Powered by {lib}</v>
+        <v>Full range</v>
       </c>
       <c r="B577" t="str">
-        <v>Drivs av {lib}</v>
+        <v>Fullt omfång</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>Subscribe</v>
+        <v>Narrow range</v>
       </c>
       <c r="B578" t="str">
-        <v>Prenumerera</v>
+        <v>Begränsat omfång</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B579" t="str">
-        <v>Få besked om nya profiletool-versioner</v>
+        <v>inte tilldelad av ITU-T H.273</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>Get notified about new releases</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B580" t="str">
-        <v>Få besked om nya versioner</v>
+        <v>Färgprimärer 2 (Ospecificerad) hänvisar till profilen själv — primärerna hämtas från färgämnestaggarna och inte från den här taggen.</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>Close</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B581" t="str">
-        <v>Stäng</v>
+        <v>De fyra reserverade byten i den här taggen är inte alla noll.</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>REPORT</v>
       </c>
       <c r="B582" t="str">
-        <v>Vi mejlar dig när en ny större eller mindre version av profiletool släpps. Patchversioner hoppas över. Din adress granskas manuellt innan den läggs till.</v>
+        <v>RAPPORT</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>Email address</v>
+        <v>FAIL</v>
       </c>
       <c r="B583" t="str">
-        <v>E-postadress</v>
+        <v>UNDERKÄND</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>you@example.com</v>
+        <v>checks</v>
       </c>
       <c r="B584" t="str">
-        <v>du@exempel.com</v>
+        <v>kontroller</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B585" t="str">
-        <v>Hur kommer du att använda profiletool?</v>
+        <v>Genererad av iccPawgReport (iccDEV) · checklista från ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>(optional)</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B586" t="str">
-        <v>(valfritt)</v>
+        <v>ICC-profilverktyg · drivs av IccProfLib</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B587" t="str">
-        <v>t.ex. utvärdera ICC-profiler för tryckkalibrering</v>
+        <v>ICC-profilverktyg</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B588" t="str">
-        <v>Jag godkänner att ta emot e-post om profiletool-versioner. Jag kan avsluta prenumerationen när som helst.</v>
+        <v>Drivs av {lib}</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Cancel</v>
+        <v>Subscribe</v>
       </c>
       <c r="B589" t="str">
-        <v>Avbryt</v>
+        <v>Prenumerera</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Subscribe</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B590" t="str">
-        <v>Prenumerera</v>
+        <v>Få besked om nya profiletool-versioner</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B591" t="str">
-        <v>Tack — vi hör av oss.</v>
+        <v>Få besked om nya versioner</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Close</v>
       </c>
       <c r="B592" t="str">
-        <v>När du har godkänts får du ett välkomstmejl. Därefter hör du bara från oss när en ny version av profiletool släpps.</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Close</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B593" t="str">
-        <v>Stäng</v>
+        <v>Vi mejlar dig när en ny större eller mindre version av profiletool släpps. Patchversioner hoppas över. Din adress granskas manuellt innan den läggs till.</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Privacy notice</v>
+        <v>Email address</v>
       </c>
       <c r="B594" t="str">
-        <v>Integritetsmeddelande</v>
+        <v>E-postadress</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>you@example.com</v>
       </c>
       <c r="B595" t="str">
-        <v>Ange en giltig e-postadress.</v>
+        <v>du@exempel.com</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B596" t="str">
-        <v>För många förfrågningar. Försök igen senare.</v>
+        <v>Hur kommer du att använda profiletool?</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Please check the form and try again.</v>
+        <v>(optional)</v>
       </c>
       <c r="B597" t="str">
-        <v>Kontrollera formuläret och försök igen.</v>
+        <v>(valfritt)</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B598" t="str">
-        <v>Det gick inte att skicka din förfrågan. Försök igen.</v>
+        <v>t.ex. utvärdera ICC-profiler för tryckkalibrering</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>Network error. Please try again.</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B599" t="str">
-        <v>Nätverksfel. Försök igen.</v>
+        <v>Jag godkänner att ta emot e-post om profiletool-versioner. Jag kan avsluta prenumerationen när som helst.</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>Error:</v>
+        <v>Cancel</v>
       </c>
       <c r="B600" t="str">
-        <v>Fel:</v>
+        <v>Avbryt</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Convert to XML</v>
+        <v>Subscribe</v>
       </c>
       <c r="B601" t="str">
-        <v>Konvertera till XML</v>
+        <v>Prenumerera</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Convert to JSON</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B602" t="str">
-        <v>Konvertera till JSON</v>
+        <v>Tack — vi hör av oss.</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Convert to ICC</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B603" t="str">
-        <v>Konvertera till ICC</v>
+        <v>När du har godkänts får du ett välkomstmejl. Därefter hör du bara från oss när en ny version av profiletool släpps.</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>Converting to XML…</v>
+        <v>Close</v>
       </c>
       <c r="B604" t="str">
-        <v>Konverterar till XML…</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>Converting to JSON…</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B605" t="str">
-        <v>Konverterar till JSON…</v>
+        <v>Integritetsmeddelande</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Converting to ICC…</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B606" t="str">
-        <v>Konverterar till ICC…</v>
+        <v>Ange en giltig e-postadress.</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>Load ICC profile</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B607" t="str">
-        <v>Läs in ICC-profil</v>
+        <v>För många förfrågningar. Försök igen senare.</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B608" t="str">
-        <v>Släppzon för ICC-profilfiler</v>
+        <v>Kontrollera formuläret och försök igen.</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>Profile ID</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B609" t="str">
-        <v>Profil-ID</v>
+        <v>Det gick inte att skicka din förfrågan. Försök igen.</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>No tags found.</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B610" t="str">
-        <v>Inga taggar hittades.</v>
+        <v>Nätverksfel. Försök igen.</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>Tag Name</v>
+        <v>Error:</v>
       </c>
       <c r="B611" t="str">
-        <v>Taggnamn</v>
+        <v>Fel:</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>ID</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B612" t="str">
-        <v>ID</v>
+        <v>Konvertera till XML</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>Offset</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B613" t="str">
-        <v>Offset</v>
+        <v>Konvertera till JSON</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>Size</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B614" t="str">
-        <v>Storlek</v>
+        <v>Konvertera till ICC</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>Pad</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B615" t="str">
-        <v>Utfyllnad</v>
+        <v>Konverterar till XML…</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>Bytes changed since load</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B616" t="str">
-        <v>Byte ändrade sedan inläsning</v>
+        <v>Konverterar till JSON…</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>Type</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B617" t="str">
-        <v>Typ</v>
+        <v>Konverterar till ICC…</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>Array of {type}</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B618" t="str">
-        <v>Array av {type}</v>
+        <v>Läs in ICC-profil</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>(No content)</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B619" t="str">
-        <v>(Inget innehåll)</v>
+        <v>Släppzon för ICC-profilfiler</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>bytes</v>
+        <v>Profile ID</v>
       </c>
       <c r="B620" t="str">
-        <v>byte</v>
+        <v>Profil-ID</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>Loading full description…</v>
+        <v>No tags found.</v>
       </c>
       <c r="B621" t="str">
-        <v>Läser in fullständig beskrivning…</v>
+        <v>Inga taggar hittades.</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>Could not load full description:</v>
+        <v>Tag Name</v>
       </c>
       <c r="B622" t="str">
-        <v>Kunde inte läsa in fullständig beskrivning:</v>
+        <v>Taggnamn</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>ID</v>
       </c>
       <c r="B623" t="str">
-        <v>Den här profilen kunde inte tolkas helt och får inte tillämpas. Huvudet och taggkatalogen nedan visas endast för granskning.</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Offset</v>
       </c>
       <c r="B624" t="str">
-        <v>Tagginnehåll otillgängligt — profilen kunde inte tolkas helt.</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>No validation output</v>
+        <v>Size</v>
       </c>
       <c r="B625" t="str">
-        <v>Ingen valideringsutdata</v>
+        <v>Storlek</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>Profile is valid</v>
+        <v>Pad</v>
       </c>
       <c r="B626" t="str">
-        <v>Profilen är giltig</v>
+        <v>Utfyllnad</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B627" t="str">
-        <v>Profilen har varning(ar)</v>
+        <v>Byte ändrade sedan inläsning</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Type</v>
       </c>
       <c r="B628" t="str">
-        <v>Profilen följer inte specifikationen</v>
+        <v>Typ</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>Critical validation error</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B629" t="str">
-        <v>Kritiskt valideringsfel</v>
+        <v>Array av {type}</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>Unknown validation status</v>
+        <v>(No content)</v>
       </c>
       <c r="B630" t="str">
-        <v>Okänd valideringsstatus</v>
+        <v>(Inget innehåll)</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>bytes</v>
       </c>
       <c r="B631" t="str">
-        <v>Kritiskt — visas endast för granskning</v>
+        <v>byte</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B632" t="str">
-        <v>Inga varningar eller fel hittades.</v>
+        <v>Läser in fullständig beskrivning…</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>Valid</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B633" t="str">
-        <v>Giltig</v>
+        <v>Kunde inte läsa in fullständig beskrivning:</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>Warning</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B634" t="str">
-        <v>Varning</v>
+        <v>Den här profilen kunde inte tolkas helt och får inte tillämpas. Huvudet och taggkatalogen nedan visas endast för granskning.</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>Error</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B635" t="str">
-        <v>Fel</v>
+        <v>Tagginnehåll otillgängligt — profilen kunde inte tolkas helt.</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>Unknown</v>
+        <v>No validation output</v>
       </c>
       <c r="B636" t="str">
-        <v>Okänd</v>
+        <v>Ingen valideringsutdata</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>Pass</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B637" t="str">
-        <v>Godkänd</v>
+        <v>Profilen är giltig</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>Fail</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B638" t="str">
-        <v>Underkänd</v>
+        <v>Profilen har varning(ar)</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>View in context</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B639" t="str">
-        <v>Visa i sammanhang</v>
+        <v>Profilen följer inte specifikationen</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>Validation detail</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B640" t="str">
-        <v>Valideringsdetalj</v>
+        <v>Kritiskt valideringsfel</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Triggered by</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B641" t="str">
-        <v>Utlöst av</v>
+        <v>Okänd valideringsstatus</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>Field</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B642" t="str">
-        <v>Fält</v>
+        <v>Kritiskt — visas endast för granskning</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>Current value</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B643" t="str">
-        <v>Aktuellt värde</v>
+        <v>Inga varningar eller fel hittades.</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>Required: 0</v>
+        <v>Valid</v>
       </c>
       <c r="B644" t="str">
-        <v>Krävs: 0</v>
+        <v>Giltig</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>Expected: {value}</v>
+        <v>Warning</v>
       </c>
       <c r="B645" t="str">
-        <v>Förväntat: {value}</v>
+        <v>Varning</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>Invalid</v>
+        <v>Error</v>
       </c>
       <c r="B646" t="str">
-        <v>Ogiltigt</v>
+        <v>Fel</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Unknown</v>
       </c>
       <c r="B647" t="str">
-        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
+        <v>Okänd</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>Close</v>
+        <v>Pass</v>
       </c>
       <c r="B648" t="str">
-        <v>Stäng</v>
+        <v>Godkänd</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>Loading XML editor…</v>
+        <v>Fail</v>
       </c>
       <c r="B649" t="str">
-        <v>Läser in XML-redigeraren…</v>
+        <v>Underkänd</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>Loading JSON editor…</v>
+        <v>View in context</v>
       </c>
       <c r="B650" t="str">
-        <v>Läser in JSON-redigeraren…</v>
+        <v>Visa i sammanhang</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Validation detail</v>
       </c>
       <c r="B651" t="str">
-        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>Valideringsdetalj</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Triggered by</v>
       </c>
       <c r="B652" t="str">
-        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>Utlöst av</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Field</v>
       </c>
       <c r="B653" t="str">
-        <v>● osparade XML-ändringar</v>
+        <v>Fält</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Current value</v>
       </c>
       <c r="B654" t="str">
-        <v>● osparade JSON-ändringar</v>
+        <v>Aktuellt värde</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Required: 0</v>
       </c>
       <c r="B655" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
+        <v>Krävs: 0</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B656" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
+        <v>Förväntat: {value}</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>indent</v>
+        <v>Invalid</v>
       </c>
       <c r="B657" t="str">
-        <v>indrag</v>
+        <v>Ogiltigt</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
-        <v>sort keys</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B658" t="str">
-        <v>sortera nycklar</v>
+        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B659" t="str">
+        <v>Stäng</v>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B660" t="str">
+        <v>Läser in XML-redigeraren…</v>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B661" t="str">
+        <v>Läser in JSON-redigeraren…</v>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B662" t="str">
+        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B663" t="str">
+        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B664" t="str">
+        <v>● osparade XML-ändringar</v>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B665" t="str">
+        <v>● osparade JSON-ändringar</v>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B666" t="str">
+        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B667" t="str">
+        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B668" t="str">
+        <v>indrag</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B669" t="str">
+        <v>sortera nycklar</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B659" t="str">
+      <c r="B670" t="str">
         <v>Profilen skrevs från ändringarna, men omvalideringen misslyckades:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B659"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B670"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Sv.xlsx
+++ b/translations/Eng-Sv.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B670"/>
+  <dimension ref="A1:B693"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -4771,1007 +4771,1191 @@
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>Preview through the colour engine</v>
       </c>
       <c r="B546" t="str">
-        <v>Kurvor i taggen, efter utrymme: {list} steg. Bas {b} steg, HDR-referensvitt {w} cd/m².</v>
+        <v>Förhandsvisning genom färgmotorn</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>As authored (baseline {h} stops, no gain)</v>
       </c>
       <c r="B547" t="str">
-        <v>Det här utrymmet ligger utanför taggens kurvor, så närmaste kurva används oförändrad – biblioteket extrapolerar inte bortom dem.</v>
+        <v>Som skapad (bas {h} steg, ingen förstärkning)</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>Tone-mapped for {h} stops</v>
       </c>
       <c r="B548" t="str">
-        <v>Vissa lutningar är härledda (PCHIP) och inte lagrade i taggen. Härledningen rekonstruerar ett SMPTE-avsnitt, så betrakta de kurvornas form som preliminär.</v>
+        <v>Tonmappad för {h} steg</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
       </c>
       <c r="B549" t="str">
-        <v>Taggen begär tonmappning mot referensvitt, så dess kurvor konstrueras av biblioteket i stället för att läsas från filen (en konstruktion från ett kommittéutkast).</v>
+        <v>Samma testpixlar ({transfer}-signal som stiger från vänster till höger: grått, sedan R, G, B, Y, C, M) genom IccProfLibs HDR-transform. Båda remsorna begränsas till {r}× HDR-referensvitt, som en skärm med {h} stegs headroom skulle visa dem: där den övre remsan klipps platt rullar förstärkningskurvan av högdagrarna.</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>reference white</v>
       </c>
       <c r="B550" t="str">
-        <v>Inga alternativa bilder: taggen begär ingen tonmappning, bara en begränsning till skärmens färgvolym.</v>
+        <v>referensvitt</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>display peak</v>
       </c>
       <c r="B551" t="str">
-        <v>De två kurvorna som blandas vid detta utrymme blandar färgkanalerna olika, så det finns ingen enskild förstärkningskurva att rita. Tonkurvan nedan är ändå exakt.</v>
+        <v>skärmens topp</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>Preview unavailable: {why}</v>
       </c>
       <c r="B552" t="str">
-        <v>Kurva vid {h} steg (ingen förstärkning)</v>
+        <v>Förhandsvisning inte tillgänglig: {why}</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>Curve at {h} stops</v>
+        <v>the colour engine did not take the HDR path for this profile</v>
       </c>
       <c r="B553" t="str">
-        <v>Kurva vid {h} steg</v>
+        <v>färgmotorn tog inte HDR-vägen för den här profilen</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Gain across every headroom</v>
       </c>
       <c r="B554" t="str">
-        <v>Tillämpad vid {h} steg</v>
+        <v>Förstärkning över alla headroom</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
       </c>
       <c r="B555" t="str">
-        <v>Förstärkning vid detta utrymme</v>
+        <v>Förstärkning för en grå insignal vid varje skärm-headroom: blått komprimerar, rött expanderar, vitt lämnar den oförändrad. Prickade linjer markerar kurvorna i taggen, den heldragna basen och den bärnstensfärgade reglaget; den streckade diagonalen är där insignalen når skärmens topp. Klicka för att flytta reglaget.</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Input (stops relative to HDR reference white)</v>
       </c>
       <c r="B556" t="str">
-        <v>Blandad indata (linjär, 1,0 = HDR-referensvitt)</v>
+        <v>Insignal (steg relativt HDR-referensvitt)</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>Display headroom (stops)</v>
       </c>
       <c r="B557" t="str">
-        <v>Förstärkning (log2-steg)</v>
+        <v>Skärm-headroom (steg)</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>Gain (stops)</v>
       </c>
       <c r="B558" t="str">
-        <v>Gråskalans tonkurva vid detta utrymme</v>
+        <v>Förstärkning (steg)</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Curve in the tag</v>
       </c>
       <c r="B559" t="str">
-        <v>Indata (× HDR-referensvitt)</v>
+        <v>Kurva i taggen</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Baseline</v>
       </c>
       <c r="B560" t="str">
-        <v>Utdata (× HDR-referensvitt)</v>
+        <v>Bas</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>No change</v>
+        <v>Slider</v>
       </c>
       <c r="B561" t="str">
-        <v>Ingen ändring</v>
+        <v>Reglage</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>Input = display peak</v>
       </c>
       <c r="B562" t="str">
-        <v>Skärmens topp vid {h} steg</v>
+        <v>Insignal = skärmens topp</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>Output at {h} stops</v>
+        <v>Grey tone curves by headroom</v>
       </c>
       <c r="B563" t="str">
-        <v>Utdata vid {h} steg</v>
+        <v>Grå tonkurvor per headroom</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
       </c>
       <c r="B564" t="str">
-        <v>HDR, färgomfång och pixelförhållande uppdateras när fönstret flyttas till en skärm där de skiljer sig.</v>
+        <v>Den grå tonkurvan vid varje headroom som taggen lagrar, färgad från lågt (blått) till högt (rött), med reglagets kurva i bärnsten. Båda axlarna är i steg, så diagonalen betyder ingen förändring.</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Identify displays</v>
+        <v>Output (stops relative to HDR reference white)</v>
       </c>
       <c r="B565" t="str">
-        <v>Identifiera skärmar</v>
+        <v>Utsignal (steg relativt HDR-referensvitt)</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>{h} stops</v>
       </c>
       <c r="B566" t="str">
-        <v>Ber om tillåtelse att se vilken skärm fönstret ligger på, så att panelen även uppdateras mellan likadana skärmar och visar HDR-utrymme där webbläsaren exponerar det.</v>
+        <v>{h} steg</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>{h} stops (baseline)</v>
       </c>
       <c r="B567" t="str">
-        <v>Följer vilken skärm fönstret ligger på.</v>
+        <v>{h} steg (bas)</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>At {h} stops (slider)</v>
       </c>
       <c r="B568" t="str">
-        <v>Tillåtelse att identifiera skärmar nekades. Den kan ändras i webbplatsens inställningar.</v>
+        <v>Vid {h} steg (reglage)</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B569" t="str">
-        <v>Den här webbläsaren kan inte identifiera skärmar; bara den automatiska uppdateringen ovan gäller.</v>
+        <v>Kurvor i taggen, efter utrymme: {list} steg. Bas {b} steg, HDR-referensvitt {w} cd/m².</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Could not identify displays.</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B570" t="str">
-        <v>Kunde inte identifiera skärmar.</v>
+        <v>Det här utrymmet ligger utanför taggens kurvor, så närmaste kurva används oförändrad – biblioteket extrapolerar inte bortom dem.</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Display events</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B571" t="str">
-        <v>Skärmhändelser</v>
+        <v>Vissa lutningar är härledda (PCHIP) och inte lagrade i taggen. Härledningen rekonstruerar ett SMPTE-avsnitt, så betrakta de kurvornas form som preliminär.</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B572" t="str">
-        <v>Inga händelser än. Dra fönstret till en annan skärm.</v>
+        <v>Taggen begär tonmappning mot referensvitt, så dess kurvor konstrueras av biblioteket i stället för att läsas från filen (en konstruktion från ett kommittéutkast).</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>Colour primaries</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B573" t="str">
-        <v>Färgprimärer</v>
+        <v>Inga alternativa bilder: taggen begär ingen tonmappning, bara en begränsning till skärmens färgvolym.</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Transfer characteristics</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B574" t="str">
-        <v>Överföringsfunktion</v>
+        <v>De två kurvorna som blandas vid detta utrymme blandar färgkanalerna olika, så det finns ingen enskild förstärkningskurva att rita. Tonkurvan nedan är ändå exakt.</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>Matrix coefficients</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B575" t="str">
-        <v>Matriskoefficienter</v>
+        <v>Kurva vid {h} steg (ingen förstärkning)</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>Video full-range flag</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B576" t="str">
-        <v>Flagga för fullt videoomfång</v>
+        <v>Kurva vid {h} steg</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Full range</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B577" t="str">
-        <v>Fullt omfång</v>
+        <v>Tillämpad vid {h} steg</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>Narrow range</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B578" t="str">
-        <v>Begränsat omfång</v>
+        <v>Förstärkning vid detta utrymme</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B579" t="str">
-        <v>inte tilldelad av ITU-T H.273</v>
+        <v>Blandad indata (linjär, 1,0 = HDR-referensvitt)</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B580" t="str">
-        <v>Färgprimärer 2 (Ospecificerad) hänvisar till profilen själv — primärerna hämtas från färgämnestaggarna och inte från den här taggen.</v>
+        <v>Förstärkning (log2-steg)</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B581" t="str">
-        <v>De fyra reserverade byten i den här taggen är inte alla noll.</v>
+        <v>Gråskalans tonkurva vid detta utrymme</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>REPORT</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B582" t="str">
-        <v>RAPPORT</v>
+        <v>Indata (× HDR-referensvitt)</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>FAIL</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B583" t="str">
-        <v>UNDERKÄND</v>
+        <v>Utdata (× HDR-referensvitt)</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>checks</v>
+        <v>No change</v>
       </c>
       <c r="B584" t="str">
-        <v>kontroller</v>
+        <v>Ingen ändring</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B585" t="str">
-        <v>Genererad av iccPawgReport (iccDEV) · checklista från ICC Profile Assessment Working Group.</v>
+        <v>Skärmens topp vid {h} steg</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B586" t="str">
-        <v>ICC-profilverktyg · drivs av IccProfLib</v>
+        <v>Utdata vid {h} steg</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>ICC Profile Tool</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B587" t="str">
-        <v>ICC-profilverktyg</v>
+        <v>HDR, färgomfång och pixelförhållande uppdateras när fönstret flyttas till en skärm där de skiljer sig.</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Powered by {lib}</v>
+        <v>Identify displays</v>
       </c>
       <c r="B588" t="str">
-        <v>Drivs av {lib}</v>
+        <v>Identifiera skärmar</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Subscribe</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B589" t="str">
-        <v>Prenumerera</v>
+        <v>Ber om tillåtelse att se vilken skärm fönstret ligger på, så att panelen även uppdateras mellan likadana skärmar och visar HDR-utrymme där webbläsaren exponerar det.</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B590" t="str">
-        <v>Få besked om nya profiletool-versioner</v>
+        <v>Följer vilken skärm fönstret ligger på.</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Get notified about new releases</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B591" t="str">
-        <v>Få besked om nya versioner</v>
+        <v>Tillåtelse att identifiera skärmar nekades. Den kan ändras i webbplatsens inställningar.</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Close</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B592" t="str">
-        <v>Stäng</v>
+        <v>Den här webbläsaren kan inte identifiera skärmar; bara den automatiska uppdateringen ovan gäller.</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B593" t="str">
-        <v>Vi mejlar dig när en ny större eller mindre version av profiletool släpps. Patchversioner hoppas över. Din adress granskas manuellt innan den läggs till.</v>
+        <v>Kunde inte identifiera skärmar.</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Email address</v>
+        <v>Display events</v>
       </c>
       <c r="B594" t="str">
-        <v>E-postadress</v>
+        <v>Skärmhändelser</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>you@example.com</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B595" t="str">
-        <v>du@exempel.com</v>
+        <v>Inga händelser än. Dra fönstret till en annan skärm.</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B596" t="str">
-        <v>Hur kommer du att använda profiletool?</v>
+        <v>Färgprimärer</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>(optional)</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B597" t="str">
-        <v>(valfritt)</v>
+        <v>Överföringsfunktion</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B598" t="str">
-        <v>t.ex. utvärdera ICC-profiler för tryckkalibrering</v>
+        <v>Matriskoefficienter</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B599" t="str">
-        <v>Jag godkänner att ta emot e-post om profiletool-versioner. Jag kan avsluta prenumerationen när som helst.</v>
+        <v>Flagga för fullt videoomfång</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>Cancel</v>
+        <v>Full range</v>
       </c>
       <c r="B600" t="str">
-        <v>Avbryt</v>
+        <v>Fullt omfång</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Subscribe</v>
+        <v>Narrow range</v>
       </c>
       <c r="B601" t="str">
-        <v>Prenumerera</v>
+        <v>Begränsat omfång</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B602" t="str">
-        <v>Tack — vi hör av oss.</v>
+        <v>inte tilldelad av ITU-T H.273</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B603" t="str">
-        <v>När du har godkänts får du ett välkomstmejl. Därefter hör du bara från oss när en ny version av profiletool släpps.</v>
+        <v>Färgprimärer 2 (Ospecificerad) hänvisar till profilen själv — primärerna hämtas från färgämnestaggarna och inte från den här taggen.</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>Close</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B604" t="str">
-        <v>Stäng</v>
+        <v>De fyra reserverade byten i den här taggen är inte alla noll.</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>Privacy notice</v>
+        <v>REPORT</v>
       </c>
       <c r="B605" t="str">
-        <v>Integritetsmeddelande</v>
+        <v>RAPPORT</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>FAIL</v>
       </c>
       <c r="B606" t="str">
-        <v>Ange en giltig e-postadress.</v>
+        <v>UNDERKÄND</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>checks</v>
       </c>
       <c r="B607" t="str">
-        <v>För många förfrågningar. Försök igen senare.</v>
+        <v>kontroller</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B608" t="str">
-        <v>Kontrollera formuläret och försök igen.</v>
+        <v>Genererad av iccPawgReport (iccDEV) · checklista från ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B609" t="str">
-        <v>Det gick inte att skicka din förfrågan. Försök igen.</v>
+        <v>ICC-profilverktyg · drivs av IccProfLib</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>Network error. Please try again.</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B610" t="str">
-        <v>Nätverksfel. Försök igen.</v>
+        <v>ICC-profilverktyg</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>Error:</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B611" t="str">
-        <v>Fel:</v>
+        <v>Drivs av {lib}</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>Convert to XML</v>
+        <v>Subscribe</v>
       </c>
       <c r="B612" t="str">
-        <v>Konvertera till XML</v>
+        <v>Prenumerera</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>Convert to JSON</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B613" t="str">
-        <v>Konvertera till JSON</v>
+        <v>Få besked om nya profiletool-versioner</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>Convert to ICC</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B614" t="str">
-        <v>Konvertera till ICC</v>
+        <v>Få besked om nya versioner</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>Converting to XML…</v>
+        <v>Close</v>
       </c>
       <c r="B615" t="str">
-        <v>Konverterar till XML…</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>Converting to JSON…</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B616" t="str">
-        <v>Konverterar till JSON…</v>
+        <v>Vi mejlar dig när en ny större eller mindre version av profiletool släpps. Patchversioner hoppas över. Din adress granskas manuellt innan den läggs till.</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>Converting to ICC…</v>
+        <v>Email address</v>
       </c>
       <c r="B617" t="str">
-        <v>Konverterar till ICC…</v>
+        <v>E-postadress</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>Load ICC profile</v>
+        <v>you@example.com</v>
       </c>
       <c r="B618" t="str">
-        <v>Läs in ICC-profil</v>
+        <v>du@exempel.com</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B619" t="str">
-        <v>Släppzon för ICC-profilfiler</v>
+        <v>Hur kommer du att använda profiletool?</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>Profile ID</v>
+        <v>(optional)</v>
       </c>
       <c r="B620" t="str">
-        <v>Profil-ID</v>
+        <v>(valfritt)</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>No tags found.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B621" t="str">
-        <v>Inga taggar hittades.</v>
+        <v>t.ex. utvärdera ICC-profiler för tryckkalibrering</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>Tag Name</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B622" t="str">
-        <v>Taggnamn</v>
+        <v>Jag godkänner att ta emot e-post om profiletool-versioner. Jag kan avsluta prenumerationen när som helst.</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>ID</v>
+        <v>Cancel</v>
       </c>
       <c r="B623" t="str">
-        <v>ID</v>
+        <v>Avbryt</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>Offset</v>
+        <v>Subscribe</v>
       </c>
       <c r="B624" t="str">
-        <v>Offset</v>
+        <v>Prenumerera</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>Size</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B625" t="str">
-        <v>Storlek</v>
+        <v>Tack — vi hör av oss.</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>Pad</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B626" t="str">
-        <v>Utfyllnad</v>
+        <v>När du har godkänts får du ett välkomstmejl. Därefter hör du bara från oss när en ny version av profiletool släpps.</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>Bytes changed since load</v>
+        <v>Close</v>
       </c>
       <c r="B627" t="str">
-        <v>Byte ändrade sedan inläsning</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>Type</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B628" t="str">
-        <v>Typ</v>
+        <v>Integritetsmeddelande</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>Array of {type}</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B629" t="str">
-        <v>Array av {type}</v>
+        <v>Ange en giltig e-postadress.</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>(No content)</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B630" t="str">
-        <v>(Inget innehåll)</v>
+        <v>För många förfrågningar. Försök igen senare.</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>bytes</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B631" t="str">
-        <v>byte</v>
+        <v>Kontrollera formuläret och försök igen.</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>Loading full description…</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B632" t="str">
-        <v>Läser in fullständig beskrivning…</v>
+        <v>Det gick inte att skicka din förfrågan. Försök igen.</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>Could not load full description:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B633" t="str">
-        <v>Kunde inte läsa in fullständig beskrivning:</v>
+        <v>Nätverksfel. Försök igen.</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Error:</v>
       </c>
       <c r="B634" t="str">
-        <v>Den här profilen kunde inte tolkas helt och får inte tillämpas. Huvudet och taggkatalogen nedan visas endast för granskning.</v>
+        <v>Fel:</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B635" t="str">
-        <v>Tagginnehåll otillgängligt — profilen kunde inte tolkas helt.</v>
+        <v>Konvertera till XML</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>No validation output</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B636" t="str">
-        <v>Ingen valideringsutdata</v>
+        <v>Konvertera till JSON</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>Profile is valid</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B637" t="str">
-        <v>Profilen är giltig</v>
+        <v>Konvertera till ICC</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B638" t="str">
-        <v>Profilen har varning(ar)</v>
+        <v>Konverterar till XML…</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B639" t="str">
-        <v>Profilen följer inte specifikationen</v>
+        <v>Konverterar till JSON…</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>Critical validation error</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B640" t="str">
-        <v>Kritiskt valideringsfel</v>
+        <v>Konverterar till ICC…</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Unknown validation status</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B641" t="str">
-        <v>Okänd valideringsstatus</v>
+        <v>Läs in ICC-profil</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B642" t="str">
-        <v>Kritiskt — visas endast för granskning</v>
+        <v>Släppzon för ICC-profilfiler</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B643" t="str">
-        <v>Inga varningar eller fel hittades.</v>
+        <v>Profil-ID</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>Valid</v>
+        <v>No tags found.</v>
       </c>
       <c r="B644" t="str">
-        <v>Giltig</v>
+        <v>Inga taggar hittades.</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>Warning</v>
+        <v>Tag Name</v>
       </c>
       <c r="B645" t="str">
-        <v>Varning</v>
+        <v>Taggnamn</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>Error</v>
+        <v>ID</v>
       </c>
       <c r="B646" t="str">
-        <v>Fel</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>Unknown</v>
+        <v>Offset</v>
       </c>
       <c r="B647" t="str">
-        <v>Okänd</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>Pass</v>
+        <v>Size</v>
       </c>
       <c r="B648" t="str">
-        <v>Godkänd</v>
+        <v>Storlek</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>Fail</v>
+        <v>Pad</v>
       </c>
       <c r="B649" t="str">
-        <v>Underkänd</v>
+        <v>Utfyllnad</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>View in context</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B650" t="str">
-        <v>Visa i sammanhang</v>
+        <v>Byte ändrade sedan inläsning</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>Validation detail</v>
+        <v>Type</v>
       </c>
       <c r="B651" t="str">
-        <v>Valideringsdetalj</v>
+        <v>Typ</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>Triggered by</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B652" t="str">
-        <v>Utlöst av</v>
+        <v>Array av {type}</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>Field</v>
+        <v>(No content)</v>
       </c>
       <c r="B653" t="str">
-        <v>Fält</v>
+        <v>(Inget innehåll)</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>Current value</v>
+        <v>bytes</v>
       </c>
       <c r="B654" t="str">
-        <v>Aktuellt värde</v>
+        <v>byte</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>Required: 0</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B655" t="str">
-        <v>Krävs: 0</v>
+        <v>Läser in fullständig beskrivning…</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>Expected: {value}</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B656" t="str">
-        <v>Förväntat: {value}</v>
+        <v>Kunde inte läsa in fullständig beskrivning:</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>Invalid</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B657" t="str">
-        <v>Ogiltigt</v>
+        <v>Den här profilen kunde inte tolkas helt och får inte tillämpas. Huvudet och taggkatalogen nedan visas endast för granskning.</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B658" t="str">
-        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
+        <v>Tagginnehåll otillgängligt — profilen kunde inte tolkas helt.</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="str">
-        <v>Close</v>
+        <v>No validation output</v>
       </c>
       <c r="B659" t="str">
-        <v>Stäng</v>
+        <v>Ingen valideringsutdata</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="str">
-        <v>Loading XML editor…</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B660" t="str">
-        <v>Läser in XML-redigeraren…</v>
+        <v>Profilen är giltig</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B661" t="str">
-        <v>Läser in JSON-redigeraren…</v>
+        <v>Profilen har varning(ar)</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B662" t="str">
-        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>Profilen följer inte specifikationen</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B663" t="str">
-        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>Kritiskt valideringsfel</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B664" t="str">
-        <v>● osparade XML-ändringar</v>
+        <v>Okänd valideringsstatus</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B665" t="str">
-        <v>● osparade JSON-ändringar</v>
+        <v>Kritiskt — visas endast för granskning</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B666" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
+        <v>Inga varningar eller fel hittades.</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Valid</v>
       </c>
       <c r="B667" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
+        <v>Giltig</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="str">
-        <v>indent</v>
+        <v>Warning</v>
       </c>
       <c r="B668" t="str">
-        <v>indrag</v>
+        <v>Varning</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="str">
-        <v>sort keys</v>
+        <v>Error</v>
       </c>
       <c r="B669" t="str">
-        <v>sortera nycklar</v>
+        <v>Fel</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B670" t="str">
+        <v>Okänd</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B671" t="str">
+        <v>Godkänd</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B672" t="str">
+        <v>Underkänd</v>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B673" t="str">
+        <v>Visa i sammanhang</v>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B674" t="str">
+        <v>Valideringsdetalj</v>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B675" t="str">
+        <v>Utlöst av</v>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B676" t="str">
+        <v>Fält</v>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B677" t="str">
+        <v>Aktuellt värde</v>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B678" t="str">
+        <v>Krävs: 0</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B679" t="str">
+        <v>Förväntat: {value}</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B680" t="str">
+        <v>Ogiltigt</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B681" t="str">
+        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B682" t="str">
+        <v>Stäng</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B683" t="str">
+        <v>Läser in XML-redigeraren…</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B684" t="str">
+        <v>Läser in JSON-redigeraren…</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B685" t="str">
+        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B686" t="str">
+        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B687" t="str">
+        <v>● osparade XML-ändringar</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B688" t="str">
+        <v>● osparade JSON-ändringar</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B689" t="str">
+        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B690" t="str">
+        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B691" t="str">
+        <v>indrag</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B692" t="str">
+        <v>sortera nycklar</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B670" t="str">
+      <c r="B693" t="str">
         <v>Profilen skrevs från ändringarna, men omvalideringen misslyckades:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B670"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B693"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Sv.xlsx
+++ b/translations/Eng-Sv.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B693"/>
+  <dimension ref="A1:B700"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -4587,1375 +4587,1431 @@
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>Target headroom</v>
+        <v>Linear values</v>
       </c>
       <c r="B523" t="str">
-        <v>Målutrymme</v>
+        <v>Linjära värden</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>{r}× reference white ({n} stops)</v>
+        <v>File 1.0 = HDR reference white</v>
       </c>
       <c r="B524" t="str">
-        <v>{r}× referensvitt ({n} steg)</v>
+        <v>Fil 1,0 = HDR-referensvitt</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>Tone mapping</v>
+        <v>File 1.0 = 1 cd/m² (ICC.1 clause 8.10.2 a)</v>
       </c>
       <c r="B525" t="str">
-        <v>Tonmappning</v>
+        <v>Fil 1,0 = 1 cd/m² (ICC.1 avsnitt 8.10.2 a)</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>Auto (clause 8.10.3 ranking)</v>
+        <v>OpenEXR and Radiance HDR files conventionally put SDR white at 1.0, while an ICC Linear transfer reads 1.0 as 1 cd/m². The default scales the file so its 1.0 lands on the profile’s HDR reference white.</v>
       </c>
       <c r="B526" t="str">
-        <v>Auto (rangordning enligt 8.10.3)</v>
+        <v>OpenEXR- och Radiance HDR-filer lägger enligt konvention SDR-vitt på 1,0, medan en linjär ICC-överföring läser 1,0 som 1 cd/m². Som standard skalas filen så att dess 1,0 hamnar på profilens HDR-referensvitt.</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>Gain curve (HAGC)</v>
+        <v>Input scale</v>
       </c>
       <c r="B527" t="str">
-        <v>Förstärkningskurva (HAGC)</v>
+        <v>Indataskala</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>Baked SDR fallback (AToB0)</v>
+        <v>×{w} — file 1.0 = reference white</v>
       </c>
       <c r="B528" t="str">
-        <v>Förberäknad SDR-reserv (AToB0)</v>
+        <v>×{w} – fil 1,0 = referensvitt</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>Off — as a pre-amendment CMM</v>
+        <v>none — file 1.0 = 1 cd/m²</v>
       </c>
       <c r="B529" t="str">
-        <v>Av – som en CMM före tillägget</v>
+        <v>ingen – fil 1,0 = 1 cd/m²</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>Applying the profile…</v>
+        <v>Target headroom</v>
       </c>
       <c r="B530" t="str">
-        <v>Tillämpar profilen…</v>
+        <v>Målutrymme</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
+        <v>{r}× reference white ({n} stops)</v>
       </c>
       <c r="B531" t="str">
-        <v>{format} innehåller linjärt ljus och kräver därför en profil med överföringen Linear (8).</v>
+        <v>{r}× referensvitt ({n} steg)</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Assigning a profile needs a 3-channel RGB image.</v>
+        <v>Tone mapping</v>
       </c>
       <c r="B532" t="str">
-        <v>Att tilldela en profil kräver en RGB-bild med 3 kanaler.</v>
+        <v>Tonmappning</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>To interpret its values, assign a profile above.</v>
+        <v>Auto (clause 8.10.3 ranking)</v>
       </c>
       <c r="B533" t="str">
-        <v>Tilldela en profil ovan för att tolka dess värden.</v>
+        <v>Auto (rangordning enligt 8.10.3)</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>HDR Profiles</v>
+        <v>Gain curve (HAGC)</v>
       </c>
       <c r="B534" t="str">
-        <v>HDR-profiler</v>
+        <v>Förstärkningskurva (HAGC)</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>Linear transfer</v>
+        <v>Baked SDR fallback (AToB0)</v>
       </c>
       <c r="B535" t="str">
-        <v>Linjär överföring</v>
+        <v>Förberäknad SDR-reserv (AToB0)</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>Non-linear transfer (PQ, HLG)</v>
+        <v>Off — as a pre-amendment CMM</v>
       </c>
       <c r="B536" t="str">
-        <v>Icke-linjär överföring (PQ, HLG)</v>
+        <v>Av – som en CMM före tillägget</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>HDR Profiles — Linear transfer</v>
+        <v>Applying the profile…</v>
       </c>
       <c r="B537" t="str">
-        <v>HDR-profiler – linjär överföring</v>
+        <v>Tillämpar profilen…</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>HDR Profiles — PQ / HLG transfer</v>
+        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
       </c>
       <c r="B538" t="str">
-        <v>HDR-profiler – PQ/HLG-överföring</v>
+        <v>{format} innehåller linjärt ljus och kräver därför en profil med överföringen Linear (8).</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
+        <v>Assigning a profile needs a 3-channel RGB image.</v>
       </c>
       <c r="B539" t="str">
-        <v>{format} innehåller linjärt ljus, så bara HDR-profiler med linjär överföring kan tilldelas.</v>
+        <v>Att tilldela en profil kräver en RGB-bild med 3 kanaler.</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
+        <v>To interpret its values, assign a profile above.</v>
       </c>
       <c r="B540" t="str">
-        <v>{n} PQ/HLG-HDR-profil(er) i poolen erbjuds inte – profilpanelen listar dem under HDR-profiler › Icke-linjär överföring.</v>
+        <v>Tilldela en profil ovan för att tolka dess värden.</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
+        <v>HDR Profiles</v>
       </c>
       <c r="B541" t="str">
-        <v>Det finns ännu ingen HDR-profil med linjär överföring i poolen; profilpanelen grupperar HDR-profiler efter överföring.</v>
+        <v>HDR-profiler</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>Linear transfer</v>
       </c>
       <c r="B542" t="str">
-        <v>IccProfLib avböjer att tillämpa den här förstärkningskurvan: {why}. En CMM faller tillbaka på nästa tonmappningsbeskrivning (avsnitt 8.10.3).</v>
+        <v>Linjär överföring</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>Display headroom</v>
+        <v>Non-linear transfer (PQ, HLG)</v>
       </c>
       <c r="B543" t="str">
-        <v>Skärmutrymme</v>
+        <v>Icke-linjär överföring (PQ, HLG)</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>HDR Profiles — Linear transfer</v>
       </c>
       <c r="B544" t="str">
-        <v>{n} steg (≈{r}× referensvitt)</v>
+        <v>HDR-profiler – linjär överföring</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>Baseline</v>
+        <v>HDR Profiles — PQ / HLG transfer</v>
       </c>
       <c r="B545" t="str">
-        <v>Bas</v>
+        <v>HDR-profiler – PQ/HLG-överföring</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>Preview through the colour engine</v>
+        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
       </c>
       <c r="B546" t="str">
-        <v>Förhandsvisning genom färgmotorn</v>
+        <v>{format} innehåller linjärt ljus, så bara HDR-profiler med linjär överföring kan tilldelas.</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>As authored (baseline {h} stops, no gain)</v>
+        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
       </c>
       <c r="B547" t="str">
-        <v>Som skapad (bas {h} steg, ingen förstärkning)</v>
+        <v>{n} PQ/HLG-HDR-profil(er) i poolen erbjuds inte – profilpanelen listar dem under HDR-profiler › Icke-linjär överföring.</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>Tone-mapped for {h} stops</v>
+        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
       </c>
       <c r="B548" t="str">
-        <v>Tonmappad för {h} steg</v>
+        <v>Det finns ännu ingen HDR-profil med linjär överföring i poolen; profilpanelen grupperar HDR-profiler efter överföring.</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B549" t="str">
-        <v>Samma testpixlar ({transfer}-signal som stiger från vänster till höger: grått, sedan R, G, B, Y, C, M) genom IccProfLibs HDR-transform. Båda remsorna begränsas till {r}× HDR-referensvitt, som en skärm med {h} stegs headroom skulle visa dem: där den övre remsan klipps platt rullar förstärkningskurvan av högdagrarna.</v>
+        <v>IccProfLib avböjer att tillämpa den här förstärkningskurvan: {why}. En CMM faller tillbaka på nästa tonmappningsbeskrivning (avsnitt 8.10.3).</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>reference white</v>
+        <v>Display headroom</v>
       </c>
       <c r="B550" t="str">
-        <v>referensvitt</v>
+        <v>Skärmutrymme</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>display peak</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B551" t="str">
-        <v>skärmens topp</v>
+        <v>{n} steg (≈{r}× referensvitt)</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>Preview unavailable: {why}</v>
+        <v>Baseline</v>
       </c>
       <c r="B552" t="str">
-        <v>Förhandsvisning inte tillgänglig: {why}</v>
+        <v>Bas</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>the colour engine did not take the HDR path for this profile</v>
+        <v>Preview through the colour engine</v>
       </c>
       <c r="B553" t="str">
-        <v>färgmotorn tog inte HDR-vägen för den här profilen</v>
+        <v>Förhandsvisning genom färgmotorn</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>Gain across every headroom</v>
+        <v>As authored (baseline {h} stops, no gain)</v>
       </c>
       <c r="B554" t="str">
-        <v>Förstärkning över alla headroom</v>
+        <v>Som skapad (bas {h} steg, ingen förstärkning)</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
+        <v>Tone-mapped for {h} stops</v>
       </c>
       <c r="B555" t="str">
-        <v>Förstärkning för en grå insignal vid varje skärm-headroom: blått komprimerar, rött expanderar, vitt lämnar den oförändrad. Prickade linjer markerar kurvorna i taggen, den heldragna basen och den bärnstensfärgade reglaget; den streckade diagonalen är där insignalen når skärmens topp. Klicka för att flytta reglaget.</v>
+        <v>Tonmappad för {h} steg</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>Input (stops relative to HDR reference white)</v>
+        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
       </c>
       <c r="B556" t="str">
-        <v>Insignal (steg relativt HDR-referensvitt)</v>
+        <v>Samma testpixlar ({transfer}-signal som stiger från vänster till höger: grått, sedan R, G, B, Y, C, M) genom IccProfLibs HDR-transform. Båda remsorna begränsas till {r}× HDR-referensvitt, som en skärm med {h} stegs headroom skulle visa dem: där den övre remsan klipps platt rullar förstärkningskurvan av högdagrarna.</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Display headroom (stops)</v>
+        <v>reference white</v>
       </c>
       <c r="B557" t="str">
-        <v>Skärm-headroom (steg)</v>
+        <v>referensvitt</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Gain (stops)</v>
+        <v>display peak</v>
       </c>
       <c r="B558" t="str">
-        <v>Förstärkning (steg)</v>
+        <v>skärmens topp</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Curve in the tag</v>
+        <v>Preview unavailable: {why}</v>
       </c>
       <c r="B559" t="str">
-        <v>Kurva i taggen</v>
+        <v>Förhandsvisning inte tillgänglig: {why}</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Baseline</v>
+        <v>the colour engine did not take the HDR path for this profile</v>
       </c>
       <c r="B560" t="str">
-        <v>Bas</v>
+        <v>färgmotorn tog inte HDR-vägen för den här profilen</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>Slider</v>
+        <v>Gain across every headroom</v>
       </c>
       <c r="B561" t="str">
-        <v>Reglage</v>
+        <v>Förstärkning över alla headroom</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Input = display peak</v>
+        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
       </c>
       <c r="B562" t="str">
-        <v>Insignal = skärmens topp</v>
+        <v>Förstärkning för en grå insignal vid varje skärm-headroom: blått komprimerar, rött expanderar, vitt lämnar den oförändrad. Prickade linjer markerar kurvorna i taggen, den heldragna basen och den bärnstensfärgade reglaget; den streckade diagonalen är där insignalen når skärmens topp. Klicka för att flytta reglaget.</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>Grey tone curves by headroom</v>
+        <v>Input (stops relative to HDR reference white)</v>
       </c>
       <c r="B563" t="str">
-        <v>Grå tonkurvor per headroom</v>
+        <v>Insignal (steg relativt HDR-referensvitt)</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
+        <v>Display headroom (stops)</v>
       </c>
       <c r="B564" t="str">
-        <v>Den grå tonkurvan vid varje headroom som taggen lagrar, färgad från lågt (blått) till högt (rött), med reglagets kurva i bärnsten. Båda axlarna är i steg, så diagonalen betyder ingen förändring.</v>
+        <v>Skärm-headroom (steg)</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Output (stops relative to HDR reference white)</v>
+        <v>Gain (stops)</v>
       </c>
       <c r="B565" t="str">
-        <v>Utsignal (steg relativt HDR-referensvitt)</v>
+        <v>Förstärkning (steg)</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>{h} stops</v>
+        <v>Curve in the tag</v>
       </c>
       <c r="B566" t="str">
-        <v>{h} steg</v>
+        <v>Kurva i taggen</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>{h} stops (baseline)</v>
+        <v>Baseline</v>
       </c>
       <c r="B567" t="str">
-        <v>{h} steg (bas)</v>
+        <v>Bas</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>At {h} stops (slider)</v>
+        <v>Slider</v>
       </c>
       <c r="B568" t="str">
-        <v>Vid {h} steg (reglage)</v>
+        <v>Reglage</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>Input = display peak</v>
       </c>
       <c r="B569" t="str">
-        <v>Kurvor i taggen, efter utrymme: {list} steg. Bas {b} steg, HDR-referensvitt {w} cd/m².</v>
+        <v>Insignal = skärmens topp</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>Grey tone curves by headroom</v>
       </c>
       <c r="B570" t="str">
-        <v>Det här utrymmet ligger utanför taggens kurvor, så närmaste kurva används oförändrad – biblioteket extrapolerar inte bortom dem.</v>
+        <v>Grå tonkurvor per headroom</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
       </c>
       <c r="B571" t="str">
-        <v>Vissa lutningar är härledda (PCHIP) och inte lagrade i taggen. Härledningen rekonstruerar ett SMPTE-avsnitt, så betrakta de kurvornas form som preliminär.</v>
+        <v>Den grå tonkurvan vid varje headroom som taggen lagrar, färgad från lågt (blått) till högt (rött), med reglagets kurva i bärnsten. Båda axlarna är i steg, så diagonalen betyder ingen förändring.</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>Output (stops relative to HDR reference white)</v>
       </c>
       <c r="B572" t="str">
-        <v>Taggen begär tonmappning mot referensvitt, så dess kurvor konstrueras av biblioteket i stället för att läsas från filen (en konstruktion från ett kommittéutkast).</v>
+        <v>Utsignal (steg relativt HDR-referensvitt)</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>{h} stops</v>
       </c>
       <c r="B573" t="str">
-        <v>Inga alternativa bilder: taggen begär ingen tonmappning, bara en begränsning till skärmens färgvolym.</v>
+        <v>{h} steg</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>{h} stops (baseline)</v>
       </c>
       <c r="B574" t="str">
-        <v>De två kurvorna som blandas vid detta utrymme blandar färgkanalerna olika, så det finns ingen enskild förstärkningskurva att rita. Tonkurvan nedan är ändå exakt.</v>
+        <v>{h} steg (bas)</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>At {h} stops (slider)</v>
       </c>
       <c r="B575" t="str">
-        <v>Kurva vid {h} steg (ingen förstärkning)</v>
+        <v>Vid {h} steg (reglage)</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>Curve at {h} stops</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B576" t="str">
-        <v>Kurva vid {h} steg</v>
+        <v>Kurvor i taggen, efter utrymme: {list} steg. Bas {b} steg, HDR-referensvitt {w} cd/m².</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Applied at {h} stops</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B577" t="str">
-        <v>Tillämpad vid {h} steg</v>
+        <v>Det här utrymmet ligger utanför taggens kurvor, så närmaste kurva används oförändrad – biblioteket extrapolerar inte bortom dem.</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B578" t="str">
-        <v>Förstärkning vid detta utrymme</v>
+        <v>Vissa lutningar är härledda (PCHIP) och inte lagrade i taggen. Härledningen rekonstruerar ett SMPTE-avsnitt, så betrakta de kurvornas form som preliminär.</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B579" t="str">
-        <v>Blandad indata (linjär, 1,0 = HDR-referensvitt)</v>
+        <v>Taggen begär tonmappning mot referensvitt, så dess kurvor konstrueras av biblioteket i stället för att läsas från filen (en konstruktion från ett kommittéutkast).</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B580" t="str">
-        <v>Förstärkning (log2-steg)</v>
+        <v>Inga alternativa bilder: taggen begär ingen tonmappning, bara en begränsning till skärmens färgvolym.</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B581" t="str">
-        <v>Gråskalans tonkurva vid detta utrymme</v>
+        <v>De två kurvorna som blandas vid detta utrymme blandar färgkanalerna olika, så det finns ingen enskild förstärkningskurva att rita. Tonkurvan nedan är ändå exakt.</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B582" t="str">
-        <v>Indata (× HDR-referensvitt)</v>
+        <v>Kurva vid {h} steg (ingen förstärkning)</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B583" t="str">
-        <v>Utdata (× HDR-referensvitt)</v>
+        <v>Kurva vid {h} steg</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>No change</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B584" t="str">
-        <v>Ingen ändring</v>
+        <v>Tillämpad vid {h} steg</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B585" t="str">
-        <v>Skärmens topp vid {h} steg</v>
+        <v>Förstärkning vid detta utrymme</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>Output at {h} stops</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B586" t="str">
-        <v>Utdata vid {h} steg</v>
+        <v>Blandad indata (linjär, 1,0 = HDR-referensvitt)</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B587" t="str">
-        <v>HDR, färgomfång och pixelförhållande uppdateras när fönstret flyttas till en skärm där de skiljer sig.</v>
+        <v>Förstärkning (log2-steg)</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Identify displays</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B588" t="str">
-        <v>Identifiera skärmar</v>
+        <v>Gråskalans tonkurva vid detta utrymme</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B589" t="str">
-        <v>Ber om tillåtelse att se vilken skärm fönstret ligger på, så att panelen även uppdateras mellan likadana skärmar och visar HDR-utrymme där webbläsaren exponerar det.</v>
+        <v>Indata (× HDR-referensvitt)</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B590" t="str">
-        <v>Följer vilken skärm fönstret ligger på.</v>
+        <v>Utdata (× HDR-referensvitt)</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>No change</v>
       </c>
       <c r="B591" t="str">
-        <v>Tillåtelse att identifiera skärmar nekades. Den kan ändras i webbplatsens inställningar.</v>
+        <v>Ingen ändring</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B592" t="str">
-        <v>Den här webbläsaren kan inte identifiera skärmar; bara den automatiska uppdateringen ovan gäller.</v>
+        <v>Skärmens topp vid {h} steg</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Could not identify displays.</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B593" t="str">
-        <v>Kunde inte identifiera skärmar.</v>
+        <v>Utdata vid {h} steg</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Display events</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B594" t="str">
-        <v>Skärmhändelser</v>
+        <v>HDR, färgomfång och pixelförhållande uppdateras när fönstret flyttas till en skärm där de skiljer sig.</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Identify displays</v>
       </c>
       <c r="B595" t="str">
-        <v>Inga händelser än. Dra fönstret till en annan skärm.</v>
+        <v>Identifiera skärmar</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Colour primaries</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B596" t="str">
-        <v>Färgprimärer</v>
+        <v>Ber om tillåtelse att se vilken skärm fönstret ligger på, så att panelen även uppdateras mellan likadana skärmar och visar HDR-utrymme där webbläsaren exponerar det.</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Transfer characteristics</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B597" t="str">
-        <v>Överföringsfunktion</v>
+        <v>Följer vilken skärm fönstret ligger på.</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Matrix coefficients</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B598" t="str">
-        <v>Matriskoefficienter</v>
+        <v>Tillåtelse att identifiera skärmar nekades. Den kan ändras i webbplatsens inställningar.</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>Video full-range flag</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B599" t="str">
-        <v>Flagga för fullt videoomfång</v>
+        <v>Den här webbläsaren kan inte identifiera skärmar; bara den automatiska uppdateringen ovan gäller.</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>Full range</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B600" t="str">
-        <v>Fullt omfång</v>
+        <v>Kunde inte identifiera skärmar.</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Narrow range</v>
+        <v>Display events</v>
       </c>
       <c r="B601" t="str">
-        <v>Begränsat omfång</v>
+        <v>Skärmhändelser</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B602" t="str">
-        <v>inte tilldelad av ITU-T H.273</v>
+        <v>Inga händelser än. Dra fönstret till en annan skärm.</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B603" t="str">
-        <v>Färgprimärer 2 (Ospecificerad) hänvisar till profilen själv — primärerna hämtas från färgämnestaggarna och inte från den här taggen.</v>
+        <v>Färgprimärer</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B604" t="str">
-        <v>De fyra reserverade byten i den här taggen är inte alla noll.</v>
+        <v>Överföringsfunktion</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>REPORT</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B605" t="str">
-        <v>RAPPORT</v>
+        <v>Matriskoefficienter</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>FAIL</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B606" t="str">
-        <v>UNDERKÄND</v>
+        <v>Flagga för fullt videoomfång</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>checks</v>
+        <v>Full range</v>
       </c>
       <c r="B607" t="str">
-        <v>kontroller</v>
+        <v>Fullt omfång</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Narrow range</v>
       </c>
       <c r="B608" t="str">
-        <v>Genererad av iccPawgReport (iccDEV) · checklista från ICC Profile Assessment Working Group.</v>
+        <v>Begränsat omfång</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B609" t="str">
-        <v>ICC-profilverktyg · drivs av IccProfLib</v>
+        <v>inte tilldelad av ITU-T H.273</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B610" t="str">
-        <v>ICC-profilverktyg</v>
+        <v>Färgprimärer 2 (Ospecificerad) hänvisar till profilen själv — primärerna hämtas från färgämnestaggarna och inte från den här taggen.</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>Powered by {lib}</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B611" t="str">
-        <v>Drivs av {lib}</v>
+        <v>De fyra reserverade byten i den här taggen är inte alla noll.</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>Subscribe</v>
+        <v>REPORT</v>
       </c>
       <c r="B612" t="str">
-        <v>Prenumerera</v>
+        <v>RAPPORT</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>FAIL</v>
       </c>
       <c r="B613" t="str">
-        <v>Få besked om nya profiletool-versioner</v>
+        <v>UNDERKÄND</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>Get notified about new releases</v>
+        <v>checks</v>
       </c>
       <c r="B614" t="str">
-        <v>Få besked om nya versioner</v>
+        <v>kontroller</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>Close</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B615" t="str">
-        <v>Stäng</v>
+        <v>Genererad av iccPawgReport (iccDEV) · checklista från ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B616" t="str">
-        <v>Vi mejlar dig när en ny större eller mindre version av profiletool släpps. Patchversioner hoppas över. Din adress granskas manuellt innan den läggs till.</v>
+        <v>ICC-profilverktyg · drivs av IccProfLib</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>Email address</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B617" t="str">
-        <v>E-postadress</v>
+        <v>ICC-profilverktyg</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>you@example.com</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B618" t="str">
-        <v>du@exempel.com</v>
+        <v>Drivs av {lib}</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Subscribe</v>
       </c>
       <c r="B619" t="str">
-        <v>Hur kommer du att använda profiletool?</v>
+        <v>Prenumerera</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>(optional)</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B620" t="str">
-        <v>(valfritt)</v>
+        <v>Få besked om nya profiletool-versioner</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B621" t="str">
-        <v>t.ex. utvärdera ICC-profiler för tryckkalibrering</v>
+        <v>Få besked om nya versioner</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Close</v>
       </c>
       <c r="B622" t="str">
-        <v>Jag godkänner att ta emot e-post om profiletool-versioner. Jag kan avsluta prenumerationen när som helst.</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>Cancel</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B623" t="str">
-        <v>Avbryt</v>
+        <v>Vi mejlar dig när en ny större eller mindre version av profiletool släpps. Patchversioner hoppas över. Din adress granskas manuellt innan den läggs till.</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>Subscribe</v>
+        <v>Email address</v>
       </c>
       <c r="B624" t="str">
-        <v>Prenumerera</v>
+        <v>E-postadress</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>you@example.com</v>
       </c>
       <c r="B625" t="str">
-        <v>Tack — vi hör av oss.</v>
+        <v>du@exempel.com</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B626" t="str">
-        <v>När du har godkänts får du ett välkomstmejl. Därefter hör du bara från oss när en ny version av profiletool släpps.</v>
+        <v>Hur kommer du att använda profiletool?</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>Close</v>
+        <v>(optional)</v>
       </c>
       <c r="B627" t="str">
-        <v>Stäng</v>
+        <v>(valfritt)</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>Privacy notice</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B628" t="str">
-        <v>Integritetsmeddelande</v>
+        <v>t.ex. utvärdera ICC-profiler för tryckkalibrering</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B629" t="str">
-        <v>Ange en giltig e-postadress.</v>
+        <v>Jag godkänner att ta emot e-post om profiletool-versioner. Jag kan avsluta prenumerationen när som helst.</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Cancel</v>
       </c>
       <c r="B630" t="str">
-        <v>För många förfrågningar. Försök igen senare.</v>
+        <v>Avbryt</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B631" t="str">
-        <v>Kontrollera formuläret och försök igen.</v>
+        <v>Prenumerera</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B632" t="str">
-        <v>Det gick inte att skicka din förfrågan. Försök igen.</v>
+        <v>Tack — vi hör av oss.</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B633" t="str">
-        <v>Nätverksfel. Försök igen.</v>
+        <v>När du har godkänts får du ett välkomstmejl. Därefter hör du bara från oss när en ny version av profiletool släpps.</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>Error:</v>
+        <v>Close</v>
       </c>
       <c r="B634" t="str">
-        <v>Fel:</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>Convert to XML</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B635" t="str">
-        <v>Konvertera till XML</v>
+        <v>Integritetsmeddelande</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>Convert to JSON</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B636" t="str">
-        <v>Konvertera till JSON</v>
+        <v>Ange en giltig e-postadress.</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>Convert to ICC</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B637" t="str">
-        <v>Konvertera till ICC</v>
+        <v>För många förfrågningar. Försök igen senare.</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>Converting to XML…</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B638" t="str">
-        <v>Konverterar till XML…</v>
+        <v>Kontrollera formuläret och försök igen.</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>Converting to JSON…</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B639" t="str">
-        <v>Konverterar till JSON…</v>
+        <v>Det gick inte att skicka din förfrågan. Försök igen.</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>Converting to ICC…</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B640" t="str">
-        <v>Konverterar till ICC…</v>
+        <v>Nätverksfel. Försök igen.</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Load ICC profile</v>
+        <v>Error:</v>
       </c>
       <c r="B641" t="str">
-        <v>Läs in ICC-profil</v>
+        <v>Fel:</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B642" t="str">
-        <v>Släppzon för ICC-profilfiler</v>
+        <v>Konvertera till XML</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>Profile ID</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B643" t="str">
-        <v>Profil-ID</v>
+        <v>Konvertera till JSON</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>No tags found.</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B644" t="str">
-        <v>Inga taggar hittades.</v>
+        <v>Konvertera till ICC</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>Tag Name</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B645" t="str">
-        <v>Taggnamn</v>
+        <v>Konverterar till XML…</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>ID</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B646" t="str">
-        <v>ID</v>
+        <v>Konverterar till JSON…</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>Offset</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B647" t="str">
-        <v>Offset</v>
+        <v>Konverterar till ICC…</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>Size</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B648" t="str">
-        <v>Storlek</v>
+        <v>Läs in ICC-profil</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>Pad</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B649" t="str">
-        <v>Utfyllnad</v>
+        <v>Släppzon för ICC-profilfiler</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>Bytes changed since load</v>
+        <v>Profile ID</v>
       </c>
       <c r="B650" t="str">
-        <v>Byte ändrade sedan inläsning</v>
+        <v>Profil-ID</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>Type</v>
+        <v>No tags found.</v>
       </c>
       <c r="B651" t="str">
-        <v>Typ</v>
+        <v>Inga taggar hittades.</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>Array of {type}</v>
+        <v>Tag Name</v>
       </c>
       <c r="B652" t="str">
-        <v>Array av {type}</v>
+        <v>Taggnamn</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>(No content)</v>
+        <v>ID</v>
       </c>
       <c r="B653" t="str">
-        <v>(Inget innehåll)</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>bytes</v>
+        <v>Offset</v>
       </c>
       <c r="B654" t="str">
-        <v>byte</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>Loading full description…</v>
+        <v>Size</v>
       </c>
       <c r="B655" t="str">
-        <v>Läser in fullständig beskrivning…</v>
+        <v>Storlek</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>Could not load full description:</v>
+        <v>Pad</v>
       </c>
       <c r="B656" t="str">
-        <v>Kunde inte läsa in fullständig beskrivning:</v>
+        <v>Utfyllnad</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B657" t="str">
-        <v>Den här profilen kunde inte tolkas helt och får inte tillämpas. Huvudet och taggkatalogen nedan visas endast för granskning.</v>
+        <v>Byte ändrade sedan inläsning</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Type</v>
       </c>
       <c r="B658" t="str">
-        <v>Tagginnehåll otillgängligt — profilen kunde inte tolkas helt.</v>
+        <v>Typ</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="str">
-        <v>No validation output</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B659" t="str">
-        <v>Ingen valideringsutdata</v>
+        <v>Array av {type}</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="str">
-        <v>Profile is valid</v>
+        <v>(No content)</v>
       </c>
       <c r="B660" t="str">
-        <v>Profilen är giltig</v>
+        <v>(Inget innehåll)</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="str">
-        <v>Profile has warning(s)</v>
+        <v>bytes</v>
       </c>
       <c r="B661" t="str">
-        <v>Profilen har varning(ar)</v>
+        <v>byte</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B662" t="str">
-        <v>Profilen följer inte specifikationen</v>
+        <v>Läser in fullständig beskrivning…</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="str">
-        <v>Critical validation error</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B663" t="str">
-        <v>Kritiskt valideringsfel</v>
+        <v>Kunde inte läsa in fullständig beskrivning:</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="str">
-        <v>Unknown validation status</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B664" t="str">
-        <v>Okänd valideringsstatus</v>
+        <v>Den här profilen kunde inte tolkas helt och får inte tillämpas. Huvudet och taggkatalogen nedan visas endast för granskning.</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B665" t="str">
-        <v>Kritiskt — visas endast för granskning</v>
+        <v>Tagginnehåll otillgängligt — profilen kunde inte tolkas helt.</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="str">
-        <v>No warnings or errors found.</v>
+        <v>No validation output</v>
       </c>
       <c r="B666" t="str">
-        <v>Inga varningar eller fel hittades.</v>
+        <v>Ingen valideringsutdata</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="str">
-        <v>Valid</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B667" t="str">
-        <v>Giltig</v>
+        <v>Profilen är giltig</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="str">
-        <v>Warning</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B668" t="str">
-        <v>Varning</v>
+        <v>Profilen har varning(ar)</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="str">
-        <v>Error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B669" t="str">
-        <v>Fel</v>
+        <v>Profilen följer inte specifikationen</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="str">
-        <v>Unknown</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B670" t="str">
-        <v>Okänd</v>
+        <v>Kritiskt valideringsfel</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="str">
-        <v>Pass</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B671" t="str">
-        <v>Godkänd</v>
+        <v>Okänd valideringsstatus</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="str">
-        <v>Fail</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B672" t="str">
-        <v>Underkänd</v>
+        <v>Kritiskt — visas endast för granskning</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="str">
-        <v>View in context</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B673" t="str">
-        <v>Visa i sammanhang</v>
+        <v>Inga varningar eller fel hittades.</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="str">
-        <v>Validation detail</v>
+        <v>Valid</v>
       </c>
       <c r="B674" t="str">
-        <v>Valideringsdetalj</v>
+        <v>Giltig</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="str">
-        <v>Triggered by</v>
+        <v>Warning</v>
       </c>
       <c r="B675" t="str">
-        <v>Utlöst av</v>
+        <v>Varning</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="str">
-        <v>Field</v>
+        <v>Error</v>
       </c>
       <c r="B676" t="str">
-        <v>Fält</v>
+        <v>Fel</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="str">
-        <v>Current value</v>
+        <v>Unknown</v>
       </c>
       <c r="B677" t="str">
-        <v>Aktuellt värde</v>
+        <v>Okänd</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="str">
-        <v>Required: 0</v>
+        <v>Pass</v>
       </c>
       <c r="B678" t="str">
-        <v>Krävs: 0</v>
+        <v>Godkänd</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="str">
-        <v>Expected: {value}</v>
+        <v>Fail</v>
       </c>
       <c r="B679" t="str">
-        <v>Förväntat: {value}</v>
+        <v>Underkänd</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="str">
-        <v>Invalid</v>
+        <v>View in context</v>
       </c>
       <c r="B680" t="str">
-        <v>Ogiltigt</v>
+        <v>Visa i sammanhang</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Validation detail</v>
       </c>
       <c r="B681" t="str">
-        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
+        <v>Valideringsdetalj</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="str">
-        <v>Close</v>
+        <v>Triggered by</v>
       </c>
       <c r="B682" t="str">
-        <v>Stäng</v>
+        <v>Utlöst av</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="str">
-        <v>Loading XML editor…</v>
+        <v>Field</v>
       </c>
       <c r="B683" t="str">
-        <v>Läser in XML-redigeraren…</v>
+        <v>Fält</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Current value</v>
       </c>
       <c r="B684" t="str">
-        <v>Läser in JSON-redigeraren…</v>
+        <v>Aktuellt värde</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Required: 0</v>
       </c>
       <c r="B685" t="str">
-        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>Krävs: 0</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B686" t="str">
-        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>Förväntat: {value}</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Invalid</v>
       </c>
       <c r="B687" t="str">
-        <v>● osparade XML-ändringar</v>
+        <v>Ogiltigt</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B688" t="str">
-        <v>● osparade JSON-ändringar</v>
+        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Close</v>
       </c>
       <c r="B689" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B690" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
+        <v>Läser in XML-redigeraren…</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="str">
-        <v>indent</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B691" t="str">
-        <v>indrag</v>
+        <v>Läser in JSON-redigeraren…</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="str">
-        <v>sort keys</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B692" t="str">
-        <v>sortera nycklar</v>
+        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B693" t="str">
+        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B694" t="str">
+        <v>● osparade XML-ändringar</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B695" t="str">
+        <v>● osparade JSON-ändringar</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B696" t="str">
+        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B697" t="str">
+        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B698" t="str">
+        <v>indrag</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B699" t="str">
+        <v>sortera nycklar</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B693" t="str">
+      <c r="B700" t="str">
         <v>Profilen skrevs från ändringarna, men omvalideringen misslyckades:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B693"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B700"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Sv.xlsx
+++ b/translations/Eng-Sv.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B700"/>
+  <dimension ref="A1:B705"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -4123,1895 +4123,1935 @@
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>Decoding…</v>
+        <v>This file is {size} MB; the HDR tab opens images up to {max} MB.</v>
       </c>
       <c r="B465" t="str">
-        <v>Avkodar…</v>
+        <v>Filen är {size} MB; HDR-fliken öppnar bilder upp till {max} MB.</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>Dynamic range</v>
+        <v>Could not apply the profile:</v>
       </c>
       <c r="B466" t="str">
-        <v>Dynamiskt omfång</v>
+        <v>Kunde inte tillämpa profilen:</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>This browser offers only the two ends, not a blend.</v>
+        <v>Could not draw the image:</v>
       </c>
       <c r="B467" t="str">
-        <v>Den här webbläsaren erbjuder bara de två ändarna, ingen blandning.</v>
+        <v>Kunde inte rita bilden:</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>decoded by profiletool itself, so browser-independent</v>
+        <v>(these primaries do not define a colour space — ignored, Rec. 709 used)</v>
       </c>
       <c r="B468" t="str">
-        <v>avkodas av profiletool själv, så oberoende av webbläsaren</v>
+        <v>(dessa primärfärger definierar ingen färgrymd – ignoreras, Rec. 709 används)</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>this browser decodes it</v>
+        <v>a JPEG XL profile is compressed inside the codestream, which profiletool does not decompress yet</v>
       </c>
       <c r="B469" t="str">
-        <v>den här webbläsaren avkodar det</v>
+        <v>profilen i en JPEG XL är komprimerad i kodströmmen, som profiletool ännu inte packar upp</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>this browser does not decode it</v>
+        <v>Decoding…</v>
       </c>
       <c r="B470" t="str">
-        <v>den här webbläsaren avkodar det inte</v>
+        <v>Avkodar…</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>HEIC display needs Safari or another WebKit browser — Chrome and Firefox decode HEIC on no platform, macOS included</v>
+        <v>Dynamic range</v>
       </c>
       <c r="B471" t="str">
-        <v>HEIC-visning kräver Safari eller en annan WebKit-webbläsare – Chrome och Firefox avkodar HEIC på ingen plattform, inte heller macOS</v>
+        <v>Dynamiskt omfång</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>JPEG XL display needs Safari; other browsers have not shipped it</v>
+        <v>This browser offers only the two ends, not a blend.</v>
       </c>
       <c r="B472" t="str">
-        <v>JPEG XL-visning kräver Safari; andra webbläsare har inte stöd än</v>
+        <v>Den här webbläsaren erbjuder bara de två ändarna, ingen blandning.</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>deferred to a later release</v>
+        <v>decoded by profiletool itself, so browser-independent</v>
       </c>
       <c r="B473" t="str">
-        <v>uppskjutet till en senare version</v>
+        <v>avkodas av profiletool själv, så oberoende av webbläsaren</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>this display reports no HDR path, so HDR renders tone-mapped to SDR</v>
+        <v>this browser decodes it</v>
       </c>
       <c r="B474" t="str">
-        <v>skärmen rapporterar ingen HDR-väg, så HDR visas tonmappat som SDR</v>
+        <v>den här webbläsaren avkodar det</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>this browser exposes no HDR canvas path (needs float16 canvas or WebGPU)</v>
+        <v>this browser does not decode it</v>
       </c>
       <c r="B475" t="str">
-        <v>webbläsaren har ingen HDR-canvas (kräver float16-canvas eller WebGPU)</v>
+        <v>den här webbläsaren avkodar det inte</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>Firefox renders no HDR images and reads no gain maps; HDR content is shown as SDR</v>
+        <v>HEIC display needs Safari or another WebKit browser — Chrome and Firefox decode HEIC on no platform, macOS included</v>
       </c>
       <c r="B476" t="str">
-        <v>Firefox visar inga HDR-bilder och läser inga gain maps; HDR-innehåll visas som SDR</v>
+        <v>HEIC-visning kräver Safari eller en annan WebKit-webbläsare – Chrome och Firefox avkodar HEIC på ingen plattform, inte heller macOS</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>inspection needs a container parse, not a codec</v>
+        <v>JPEG XL display needs Safari; other browsers have not shipped it</v>
       </c>
       <c r="B477" t="str">
-        <v>granskning kräver bara tolkning av behållaren, ingen codec</v>
+        <v>JPEG XL-visning kräver Safari; andra webbläsare har inte stöd än</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>HDR display and an HDR canvas path are both available</v>
+        <v>deferred to a later release</v>
       </c>
       <c r="B478" t="str">
-        <v>både HDR-skärm och HDR-canvas finns</v>
+        <v>uppskjutet till en senare version</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>unknown format</v>
+        <v>this display reports no HDR path, so HDR renders tone-mapped to SDR</v>
       </c>
       <c r="B479" t="str">
-        <v>okänt format</v>
+        <v>skärmen rapporterar ingen HDR-väg, så HDR visas tonmappat som SDR</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>{browser} on {os}</v>
+        <v>this browser exposes no HDR canvas path (needs float16 canvas or WebGPU)</v>
       </c>
       <c r="B480" t="str">
-        <v>{browser} på {os}</v>
+        <v>webbläsaren har ingen HDR-canvas (kräver float16-canvas eller WebGPU)</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>{name} · HDR display detected</v>
+        <v>Firefox renders no HDR images and reads no gain maps; HDR content is shown as SDR</v>
       </c>
       <c r="B481" t="str">
-        <v>{name} · HDR-skärm hittad</v>
+        <v>Firefox visar inga HDR-bilder och läser inga gain maps; HDR-innehåll visas som SDR</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>{name} · SDR display</v>
+        <v>inspection needs a container parse, not a codec</v>
       </c>
       <c r="B482" t="str">
-        <v>{name} · SDR-skärm</v>
+        <v>granskning kräver bara tolkning av behållaren, ingen codec</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>WebGPU applied tone mapping “{mode}”, so output is clamped to SDR</v>
+        <v>HDR display and an HDR canvas path are both available</v>
       </c>
       <c r="B483" t="str">
-        <v>WebGPU tillämpade tonmappning ”{mode}”, så utdata begränsas till SDR</v>
+        <v>både HDR-skärm och HDR-canvas finns</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>This browser does not report the WebGPU tone mapping it applied, so HDR output is unconfirmed</v>
+        <v>unknown format</v>
       </c>
       <c r="B484" t="str">
-        <v>Webbläsaren rapporterar inte vilken WebGPU-tonmappning som tillämpades, så HDR-utdata är obekräftad</v>
+        <v>okänt format</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>Display peak</v>
+        <v>{browser} on {os}</v>
       </c>
       <c r="B485" t="str">
-        <v>Skärmens topp</v>
+        <v>{browser} på {os}</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>{r}× SDR white ({n} stops)</v>
+        <v>{name} · HDR display detected</v>
       </c>
       <c r="B486" t="str">
-        <v>{r}× SDR-vitt ({n} steg)</v>
+        <v>{name} · HDR-skärm hittad</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>1× — SDR display</v>
+        <v>{name} · SDR display</v>
       </c>
       <c r="B487" t="str">
-        <v>1× – SDR-skärm</v>
+        <v>{name} · SDR-skärm</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>not known</v>
+        <v>WebGPU applied tone mapping “{mode}”, so output is clamped to SDR</v>
       </c>
       <c r="B488" t="str">
-        <v>okänd</v>
+        <v>WebGPU tillämpade tonmappning ”{mode}”, så utdata begränsas till SDR</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>This display reports no HDR, so the browser shows this image in SDR at either end.</v>
+        <v>This browser does not report the WebGPU tone mapping it applied, so HDR output is unconfirmed</v>
       </c>
       <c r="B489" t="str">
-        <v>Skärmen rapporterar ingen HDR, så webbläsaren visar bilden i SDR i båda ändarna.</v>
+        <v>Webbläsaren rapporterar inte vilken WebGPU-tonmappning som tillämpades, så HDR-utdata är obekräftad</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>This display reports no HDR, so everything brighter than SDR white clips. Fit to display shows the tone-mapped rendering instead.</v>
+        <v>Display peak</v>
       </c>
       <c r="B490" t="str">
-        <v>Skärmen rapporterar ingen HDR, så allt ljusare än SDR-vitt klipps. ”Anpassa till skärm” visar i stället den tonmappade återgivningen.</v>
+        <v>Skärmens topp</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>This image asks for {img}× SDR white, but this display shows up to {disp}×, so brighter values clip. Fit to display rolls them off into the display’s peak instead.</v>
+        <v>{r}× SDR white ({n} stops)</v>
       </c>
       <c r="B491" t="str">
-        <v>Bilden kräver {img}× SDR-vitt, men skärmen visar bara upp till {disp}×, så ljusare värden klipps. ”Anpassa till skärm” rundar i stället av dem mot skärmens topp.</v>
+        <v>{r}× SDR-vitt ({n} steg)</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>Fit to display</v>
+        <v>1× — SDR display</v>
       </c>
       <c r="B492" t="str">
-        <v>Anpassa till skärm</v>
+        <v>1× – SDR-skärm</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>Image details</v>
+        <v>not known</v>
       </c>
       <c r="B493" t="str">
-        <v>Bilddetaljer</v>
+        <v>okänd</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>not available — the browser renders this image and cannot cap it at a set peak</v>
+        <v>This display reports no HDR, so the browser shows this image in SDR at either end.</v>
       </c>
       <c r="B494" t="str">
-        <v>inte tillgänglig – webbläsaren återger bilden och kan inte begränsa den till en viss topp</v>
+        <v>Skärmen rapporterar ingen HDR, så webbläsaren visar bilden i SDR i båda ändarna.</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>not available — this output shows nothing above SDR white</v>
+        <v>This display reports no HDR, so everything brighter than SDR white clips. Fit to display shows the tone-mapped rendering instead.</v>
       </c>
       <c r="B495" t="str">
-        <v>inte tillgänglig – den här utgången visar inget över SDR-vitt</v>
+        <v>Skärmen rapporterar ingen HDR, så allt ljusare än SDR-vitt klipps. ”Anpassa till skärm” visar i stället den tonmappade återgivningen.</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>not available — this display’s peak is not known</v>
+        <v>This image asks for {img}× SDR white, but this display shows up to {disp}×, so brighter values clip. Fit to display rolls them off into the display’s peak instead.</v>
       </c>
       <c r="B496" t="str">
-        <v>inte tillgänglig – skärmens toppluminans är okänd</v>
+        <v>Bilden kräver {img}× SDR-vitt, men skärmen visar bara upp till {disp}×, så ljusare värden klipps. ”Anpassa till skärm” rundar i stället av dem mot skärmens topp.</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>Zoom in</v>
+        <v>Fit to display</v>
       </c>
       <c r="B497" t="str">
-        <v>Zooma in</v>
+        <v>Anpassa till skärm</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Zoom out</v>
+        <v>Image details</v>
       </c>
       <c r="B498" t="str">
-        <v>Zooma ut</v>
+        <v>Bilddetaljer</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Fit image</v>
+        <v>not available — the browser renders this image and cannot cap it at a set peak</v>
       </c>
       <c r="B499" t="str">
-        <v>Anpassa bilden</v>
+        <v>inte tillgänglig – webbläsaren återger bilden och kan inte begränsa den till en viss topp</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>Actual pixels (1:1)</v>
+        <v>not available — this output shows nothing above SDR white</v>
       </c>
       <c r="B500" t="str">
-        <v>Faktiska pixlar (1:1)</v>
+        <v>inte tillgänglig – den här utgången visar inget över SDR-vitt</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>Drag to pan · Ctrl+wheel to zoom · double-click to reset</v>
+        <v>not available — this display’s peak is not known</v>
       </c>
       <c r="B501" t="str">
-        <v>Dra för att panorera · Ctrl+hjul för att zooma · dubbelklicka för att återställa</v>
+        <v>inte tillgänglig – skärmens toppluminans är okänd</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>Drag to resize the image area; double-click to restore the default size</v>
+        <v>Zoom in</v>
       </c>
       <c r="B502" t="str">
-        <v>Dra för att ändra bildytans storlek; dubbelklicka för standardstorlek</v>
+        <v>Zooma in</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>Image view</v>
+        <v>Zoom out</v>
       </c>
       <c r="B503" t="str">
-        <v>Bildvy</v>
+        <v>Zooma ut</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
+        <v>Fit image</v>
       </c>
       <c r="B504" t="str">
-        <v>Begränsar ljusstyrkan till den topp skärmen rapporterar. I Windows kan värdet släpa efter ändringar av ljusstyrkan.</v>
+        <v>Anpassa bilden</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>no limit</v>
+        <v>Actual pixels (1:1)</v>
       </c>
       <c r="B505" t="str">
-        <v>ingen gräns</v>
+        <v>Faktiska pixlar (1:1)</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>limit {n} stops ({r}×)</v>
+        <v>Drag to pan · Ctrl+wheel to zoom · double-click to reset</v>
       </c>
       <c r="B506" t="str">
-        <v>gräns {n} steg ({r}×)</v>
+        <v>Dra för att panorera · Ctrl+hjul för att zooma · dubbelklicka för att återställa</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>SDR white</v>
+        <v>Drag to resize the image area; double-click to restore the default size</v>
       </c>
       <c r="B507" t="str">
-        <v>SDR-vitt</v>
+        <v>Dra för att ändra bildytans storlek; dubbelklicka för standardstorlek</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
+        <v>Image view</v>
       </c>
       <c r="B508" t="str">
-        <v>Vanligt SDR-vitt för jämförelse. På en HDR-skärm ser HDR-högdagrar ljusare ut än detta.</v>
+        <v>Bildvy</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>SDR white patch</v>
+        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
       </c>
       <c r="B509" t="str">
-        <v>SDR-vit ruta</v>
+        <v>Begränsar ljusstyrkan till den topp skärmen rapporterar. I Windows kan värdet släpa efter ändringar av ljusstyrkan.</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>Drag to move it; double-click to put it back beside the image.</v>
+        <v>no limit</v>
       </c>
       <c r="B510" t="str">
-        <v>Dra för att flytta den; dubbelklicka för att sätta tillbaka den bredvid bilden.</v>
+        <v>ingen gräns</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>Assign profile</v>
+        <v>limit {n} stops ({r}×)</v>
       </c>
       <c r="B511" t="str">
-        <v>Tilldela profil</v>
+        <v>gräns {n} steg ({r}×)</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>None — use what the file signals</v>
+        <v>SDR white</v>
       </c>
       <c r="B512" t="str">
-        <v>Ingen – det filen anger</v>
+        <v>SDR-vitt</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Embedded profile ({n} B)</v>
+        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
       </c>
       <c r="B513" t="str">
-        <v>Inbäddad profil ({n} B)</v>
+        <v>Vanligt SDR-vitt för jämförelse. På en HDR-skärm ser HDR-högdagrar ljusare ut än detta.</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>HDR Profiles in the pool</v>
+        <v>SDR white patch</v>
       </c>
       <c r="B514" t="str">
-        <v>HDR-profiler i poolen</v>
+        <v>SDR-vit ruta</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Profile</v>
+        <v>Drag to move it; double-click to put it back beside the image.</v>
       </c>
       <c r="B515" t="str">
-        <v>Profil</v>
+        <v>Dra för att flytta den; dubbelklicka för att sätta tillbaka den bredvid bilden.</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>embedded profile</v>
+        <v>Assign profile</v>
       </c>
       <c r="B516" t="str">
-        <v>inbäddad profil</v>
+        <v>Tilldela profil</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>Colour engine path</v>
+        <v>None — use what the file signals</v>
       </c>
       <c r="B517" t="str">
-        <v>Färgmotorns väg</v>
+        <v>Ingen – det filen anger</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>HDR path, gain curve applied</v>
+        <v>Embedded profile ({n} B)</v>
       </c>
       <c r="B518" t="str">
-        <v>HDR-väg, förstärkningskurva tillämpad</v>
+        <v>Inbäddad profil ({n} B)</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>HDR path, no gain curve</v>
+        <v>HDR Profiles in the pool</v>
       </c>
       <c r="B519" t="str">
-        <v>HDR-väg, ingen förstärkningskurva</v>
+        <v>HDR-profiler i poolen</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>Baked AToB0 — not the HDR path</v>
+        <v>Profile</v>
       </c>
       <c r="B520" t="str">
-        <v>Förberäknad AToB0 – inte HDR-vägen</v>
+        <v>Profil</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>Transfer</v>
+        <v>embedded profile</v>
       </c>
       <c r="B521" t="str">
-        <v>Överföring</v>
+        <v>inbäddad profil</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>HDR reference white</v>
+        <v>Colour engine path</v>
       </c>
       <c r="B522" t="str">
-        <v>HDR-referensvitt</v>
+        <v>Färgmotorns väg</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>Linear values</v>
+        <v>HDR path, gain curve applied</v>
       </c>
       <c r="B523" t="str">
-        <v>Linjära värden</v>
+        <v>HDR-väg, förstärkningskurva tillämpad</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>File 1.0 = HDR reference white</v>
+        <v>HDR path, no gain curve</v>
       </c>
       <c r="B524" t="str">
-        <v>Fil 1,0 = HDR-referensvitt</v>
+        <v>HDR-väg, ingen förstärkningskurva</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>File 1.0 = 1 cd/m² (ICC.1 clause 8.10.2 a)</v>
+        <v>Baked AToB0 — not the HDR path</v>
       </c>
       <c r="B525" t="str">
-        <v>Fil 1,0 = 1 cd/m² (ICC.1 avsnitt 8.10.2 a)</v>
+        <v>Förberäknad AToB0 – inte HDR-vägen</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>OpenEXR and Radiance HDR files conventionally put SDR white at 1.0, while an ICC Linear transfer reads 1.0 as 1 cd/m². The default scales the file so its 1.0 lands on the profile’s HDR reference white.</v>
+        <v>Transfer</v>
       </c>
       <c r="B526" t="str">
-        <v>OpenEXR- och Radiance HDR-filer lägger enligt konvention SDR-vitt på 1,0, medan en linjär ICC-överföring läser 1,0 som 1 cd/m². Som standard skalas filen så att dess 1,0 hamnar på profilens HDR-referensvitt.</v>
+        <v>Överföring</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>Input scale</v>
+        <v>HDR reference white</v>
       </c>
       <c r="B527" t="str">
-        <v>Indataskala</v>
+        <v>HDR-referensvitt</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>×{w} — file 1.0 = reference white</v>
+        <v>Linear values</v>
       </c>
       <c r="B528" t="str">
-        <v>×{w} – fil 1,0 = referensvitt</v>
+        <v>Linjära värden</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>none — file 1.0 = 1 cd/m²</v>
+        <v>File 1.0 = HDR reference white</v>
       </c>
       <c r="B529" t="str">
-        <v>ingen – fil 1,0 = 1 cd/m²</v>
+        <v>Fil 1,0 = HDR-referensvitt</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>Target headroom</v>
+        <v>File 1.0 = 1 cd/m² (ICC.1 clause 8.10.2 a)</v>
       </c>
       <c r="B530" t="str">
-        <v>Målutrymme</v>
+        <v>Fil 1,0 = 1 cd/m² (ICC.1 avsnitt 8.10.2 a)</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>{r}× reference white ({n} stops)</v>
+        <v>OpenEXR and Radiance HDR files conventionally put SDR white at 1.0, while an ICC Linear transfer reads 1.0 as 1 cd/m². The default scales the file so its 1.0 lands on the profile’s HDR reference white.</v>
       </c>
       <c r="B531" t="str">
-        <v>{r}× referensvitt ({n} steg)</v>
+        <v>OpenEXR- och Radiance HDR-filer lägger enligt konvention SDR-vitt på 1,0, medan en linjär ICC-överföring läser 1,0 som 1 cd/m². Som standard skalas filen så att dess 1,0 hamnar på profilens HDR-referensvitt.</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Tone mapping</v>
+        <v>Input scale</v>
       </c>
       <c r="B532" t="str">
-        <v>Tonmappning</v>
+        <v>Indataskala</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>Auto (clause 8.10.3 ranking)</v>
+        <v>×{w} — file 1.0 = reference white</v>
       </c>
       <c r="B533" t="str">
-        <v>Auto (rangordning enligt 8.10.3)</v>
+        <v>×{w} – fil 1,0 = referensvitt</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>Gain curve (HAGC)</v>
+        <v>none — file 1.0 = 1 cd/m²</v>
       </c>
       <c r="B534" t="str">
-        <v>Förstärkningskurva (HAGC)</v>
+        <v>ingen – fil 1,0 = 1 cd/m²</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>Baked SDR fallback (AToB0)</v>
+        <v>Target headroom</v>
       </c>
       <c r="B535" t="str">
-        <v>Förberäknad SDR-reserv (AToB0)</v>
+        <v>Målutrymme</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>Off — as a pre-amendment CMM</v>
+        <v>{r}× reference white ({n} stops)</v>
       </c>
       <c r="B536" t="str">
-        <v>Av – som en CMM före tillägget</v>
+        <v>{r}× referensvitt ({n} steg)</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>Applying the profile…</v>
+        <v>Tone mapping</v>
       </c>
       <c r="B537" t="str">
-        <v>Tillämpar profilen…</v>
+        <v>Tonmappning</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
+        <v>Auto (clause 8.10.3 ranking)</v>
       </c>
       <c r="B538" t="str">
-        <v>{format} innehåller linjärt ljus och kräver därför en profil med överföringen Linear (8).</v>
+        <v>Auto (rangordning enligt 8.10.3)</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>Assigning a profile needs a 3-channel RGB image.</v>
+        <v>Gain curve (HAGC)</v>
       </c>
       <c r="B539" t="str">
-        <v>Att tilldela en profil kräver en RGB-bild med 3 kanaler.</v>
+        <v>Förstärkningskurva (HAGC)</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>To interpret its values, assign a profile above.</v>
+        <v>Baked SDR fallback (AToB0)</v>
       </c>
       <c r="B540" t="str">
-        <v>Tilldela en profil ovan för att tolka dess värden.</v>
+        <v>Förberäknad SDR-reserv (AToB0)</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>HDR Profiles</v>
+        <v>Off — as a pre-amendment CMM</v>
       </c>
       <c r="B541" t="str">
-        <v>HDR-profiler</v>
+        <v>Av – som en CMM före tillägget</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>Linear transfer</v>
+        <v>Applying the profile…</v>
       </c>
       <c r="B542" t="str">
-        <v>Linjär överföring</v>
+        <v>Tillämpar profilen…</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>Non-linear transfer (PQ, HLG)</v>
+        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
       </c>
       <c r="B543" t="str">
-        <v>Icke-linjär överföring (PQ, HLG)</v>
+        <v>{format} innehåller linjärt ljus och kräver därför en profil med överföringen Linear (8).</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>HDR Profiles — Linear transfer</v>
+        <v>Assigning a profile needs a 3-channel RGB image.</v>
       </c>
       <c r="B544" t="str">
-        <v>HDR-profiler – linjär överföring</v>
+        <v>Att tilldela en profil kräver en RGB-bild med 3 kanaler.</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>HDR Profiles — PQ / HLG transfer</v>
+        <v>To interpret its values, assign a profile above.</v>
       </c>
       <c r="B545" t="str">
-        <v>HDR-profiler – PQ/HLG-överföring</v>
+        <v>Tilldela en profil ovan för att tolka dess värden.</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
+        <v>HDR Profiles</v>
       </c>
       <c r="B546" t="str">
-        <v>{format} innehåller linjärt ljus, så bara HDR-profiler med linjär överföring kan tilldelas.</v>
+        <v>HDR-profiler</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
+        <v>Linear transfer</v>
       </c>
       <c r="B547" t="str">
-        <v>{n} PQ/HLG-HDR-profil(er) i poolen erbjuds inte – profilpanelen listar dem under HDR-profiler › Icke-linjär överföring.</v>
+        <v>Linjär överföring</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
+        <v>Non-linear transfer (PQ, HLG)</v>
       </c>
       <c r="B548" t="str">
-        <v>Det finns ännu ingen HDR-profil med linjär överföring i poolen; profilpanelen grupperar HDR-profiler efter överföring.</v>
+        <v>Icke-linjär överföring (PQ, HLG)</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>HDR Profiles — Linear transfer</v>
       </c>
       <c r="B549" t="str">
-        <v>IccProfLib avböjer att tillämpa den här förstärkningskurvan: {why}. En CMM faller tillbaka på nästa tonmappningsbeskrivning (avsnitt 8.10.3).</v>
+        <v>HDR-profiler – linjär överföring</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>Display headroom</v>
+        <v>HDR Profiles — PQ / HLG transfer</v>
       </c>
       <c r="B550" t="str">
-        <v>Skärmutrymme</v>
+        <v>HDR-profiler – PQ/HLG-överföring</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
       </c>
       <c r="B551" t="str">
-        <v>{n} steg (≈{r}× referensvitt)</v>
+        <v>{format} innehåller linjärt ljus, så bara HDR-profiler med linjär överföring kan tilldelas.</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>Baseline</v>
+        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
       </c>
       <c r="B552" t="str">
-        <v>Bas</v>
+        <v>{n} PQ/HLG-HDR-profil(er) i poolen erbjuds inte – profilpanelen listar dem under HDR-profiler › Icke-linjär överföring.</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>Preview through the colour engine</v>
+        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
       </c>
       <c r="B553" t="str">
-        <v>Förhandsvisning genom färgmotorn</v>
+        <v>Det finns ännu ingen HDR-profil med linjär överföring i poolen; profilpanelen grupperar HDR-profiler efter överföring.</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>As authored (baseline {h} stops, no gain)</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B554" t="str">
-        <v>Som skapad (bas {h} steg, ingen förstärkning)</v>
+        <v>IccProfLib avböjer att tillämpa den här förstärkningskurvan: {why}. En CMM faller tillbaka på nästa tonmappningsbeskrivning (avsnitt 8.10.3).</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Tone-mapped for {h} stops</v>
+        <v>Display headroom</v>
       </c>
       <c r="B555" t="str">
-        <v>Tonmappad för {h} steg</v>
+        <v>Skärmutrymme</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B556" t="str">
-        <v>Samma testpixlar ({transfer}-signal som stiger från vänster till höger: grått, sedan R, G, B, Y, C, M) genom IccProfLibs HDR-transform. Båda remsorna begränsas till {r}× HDR-referensvitt, som en skärm med {h} stegs headroom skulle visa dem: där den övre remsan klipps platt rullar förstärkningskurvan av högdagrarna.</v>
+        <v>{n} steg (≈{r}× referensvitt)</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>reference white</v>
+        <v>Baseline</v>
       </c>
       <c r="B557" t="str">
-        <v>referensvitt</v>
+        <v>Bas</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>display peak</v>
+        <v>Preview through the colour engine</v>
       </c>
       <c r="B558" t="str">
-        <v>skärmens topp</v>
+        <v>Förhandsvisning genom färgmotorn</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Preview unavailable: {why}</v>
+        <v>As authored (baseline {h} stops, no gain)</v>
       </c>
       <c r="B559" t="str">
-        <v>Förhandsvisning inte tillgänglig: {why}</v>
+        <v>Som skapad (bas {h} steg, ingen förstärkning)</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>the colour engine did not take the HDR path for this profile</v>
+        <v>Tone-mapped for {h} stops</v>
       </c>
       <c r="B560" t="str">
-        <v>färgmotorn tog inte HDR-vägen för den här profilen</v>
+        <v>Tonmappad för {h} steg</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>Gain across every headroom</v>
+        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
       </c>
       <c r="B561" t="str">
-        <v>Förstärkning över alla headroom</v>
+        <v>Samma testpixlar ({transfer}-signal som stiger från vänster till höger: grått, sedan R, G, B, Y, C, M) genom IccProfLibs HDR-transform. Båda remsorna begränsas till {r}× HDR-referensvitt, som en skärm med {h} stegs headroom skulle visa dem: där den övre remsan klipps platt rullar förstärkningskurvan av högdagrarna.</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
+        <v>reference white</v>
       </c>
       <c r="B562" t="str">
-        <v>Förstärkning för en grå insignal vid varje skärm-headroom: blått komprimerar, rött expanderar, vitt lämnar den oförändrad. Prickade linjer markerar kurvorna i taggen, den heldragna basen och den bärnstensfärgade reglaget; den streckade diagonalen är där insignalen når skärmens topp. Klicka för att flytta reglaget.</v>
+        <v>referensvitt</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>Input (stops relative to HDR reference white)</v>
+        <v>display peak</v>
       </c>
       <c r="B563" t="str">
-        <v>Insignal (steg relativt HDR-referensvitt)</v>
+        <v>skärmens topp</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>Display headroom (stops)</v>
+        <v>Preview unavailable: {why}</v>
       </c>
       <c r="B564" t="str">
-        <v>Skärm-headroom (steg)</v>
+        <v>Förhandsvisning inte tillgänglig: {why}</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Gain (stops)</v>
+        <v>the colour engine did not take the HDR path for this profile</v>
       </c>
       <c r="B565" t="str">
-        <v>Förstärkning (steg)</v>
+        <v>färgmotorn tog inte HDR-vägen för den här profilen</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Curve in the tag</v>
+        <v>Gain across every headroom</v>
       </c>
       <c r="B566" t="str">
-        <v>Kurva i taggen</v>
+        <v>Förstärkning över alla headroom</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Baseline</v>
+        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
       </c>
       <c r="B567" t="str">
-        <v>Bas</v>
+        <v>Förstärkning för en grå insignal vid varje skärm-headroom: blått komprimerar, rött expanderar, vitt lämnar den oförändrad. Prickade linjer markerar kurvorna i taggen, den heldragna basen och den bärnstensfärgade reglaget; den streckade diagonalen är där insignalen når skärmens topp. Klicka för att flytta reglaget.</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Slider</v>
+        <v>Input (stops relative to HDR reference white)</v>
       </c>
       <c r="B568" t="str">
-        <v>Reglage</v>
+        <v>Insignal (steg relativt HDR-referensvitt)</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Input = display peak</v>
+        <v>Display headroom (stops)</v>
       </c>
       <c r="B569" t="str">
-        <v>Insignal = skärmens topp</v>
+        <v>Skärm-headroom (steg)</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Grey tone curves by headroom</v>
+        <v>Gain (stops)</v>
       </c>
       <c r="B570" t="str">
-        <v>Grå tonkurvor per headroom</v>
+        <v>Förstärkning (steg)</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
+        <v>Curve in the tag</v>
       </c>
       <c r="B571" t="str">
-        <v>Den grå tonkurvan vid varje headroom som taggen lagrar, färgad från lågt (blått) till högt (rött), med reglagets kurva i bärnsten. Båda axlarna är i steg, så diagonalen betyder ingen förändring.</v>
+        <v>Kurva i taggen</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>Output (stops relative to HDR reference white)</v>
+        <v>Baseline</v>
       </c>
       <c r="B572" t="str">
-        <v>Utsignal (steg relativt HDR-referensvitt)</v>
+        <v>Bas</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>{h} stops</v>
+        <v>Slider</v>
       </c>
       <c r="B573" t="str">
-        <v>{h} steg</v>
+        <v>Reglage</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>{h} stops (baseline)</v>
+        <v>Input = display peak</v>
       </c>
       <c r="B574" t="str">
-        <v>{h} steg (bas)</v>
+        <v>Insignal = skärmens topp</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>At {h} stops (slider)</v>
+        <v>Grey tone curves by headroom</v>
       </c>
       <c r="B575" t="str">
-        <v>Vid {h} steg (reglage)</v>
+        <v>Grå tonkurvor per headroom</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
       </c>
       <c r="B576" t="str">
-        <v>Kurvor i taggen, efter utrymme: {list} steg. Bas {b} steg, HDR-referensvitt {w} cd/m².</v>
+        <v>Den grå tonkurvan vid varje headroom som taggen lagrar, färgad från lågt (blått) till högt (rött), med reglagets kurva i bärnsten. Båda axlarna är i steg, så diagonalen betyder ingen förändring.</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>Output (stops relative to HDR reference white)</v>
       </c>
       <c r="B577" t="str">
-        <v>Det här utrymmet ligger utanför taggens kurvor, så närmaste kurva används oförändrad – biblioteket extrapolerar inte bortom dem.</v>
+        <v>Utsignal (steg relativt HDR-referensvitt)</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>{h} stops</v>
       </c>
       <c r="B578" t="str">
-        <v>Vissa lutningar är härledda (PCHIP) och inte lagrade i taggen. Härledningen rekonstruerar ett SMPTE-avsnitt, så betrakta de kurvornas form som preliminär.</v>
+        <v>{h} steg</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>{h} stops (baseline)</v>
       </c>
       <c r="B579" t="str">
-        <v>Taggen begär tonmappning mot referensvitt, så dess kurvor konstrueras av biblioteket i stället för att läsas från filen (en konstruktion från ett kommittéutkast).</v>
+        <v>{h} steg (bas)</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>At {h} stops (slider)</v>
       </c>
       <c r="B580" t="str">
-        <v>Inga alternativa bilder: taggen begär ingen tonmappning, bara en begränsning till skärmens färgvolym.</v>
+        <v>Vid {h} steg (reglage)</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B581" t="str">
-        <v>De två kurvorna som blandas vid detta utrymme blandar färgkanalerna olika, så det finns ingen enskild förstärkningskurva att rita. Tonkurvan nedan är ändå exakt.</v>
+        <v>Kurvor i taggen, efter utrymme: {list} steg. Bas {b} steg, HDR-referensvitt {w} cd/m².</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B582" t="str">
-        <v>Kurva vid {h} steg (ingen förstärkning)</v>
+        <v>Det här utrymmet ligger utanför taggens kurvor, så närmaste kurva används oförändrad – biblioteket extrapolerar inte bortom dem.</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>Curve at {h} stops</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B583" t="str">
-        <v>Kurva vid {h} steg</v>
+        <v>Vissa lutningar är härledda (PCHIP) och inte lagrade i taggen. Härledningen rekonstruerar ett SMPTE-avsnitt, så betrakta de kurvornas form som preliminär.</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>Applied at {h} stops</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B584" t="str">
-        <v>Tillämpad vid {h} steg</v>
+        <v>Taggen begär tonmappning mot referensvitt, så dess kurvor konstrueras av biblioteket i stället för att läsas från filen (en konstruktion från ett kommittéutkast).</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B585" t="str">
-        <v>Förstärkning vid detta utrymme</v>
+        <v>Inga alternativa bilder: taggen begär ingen tonmappning, bara en begränsning till skärmens färgvolym.</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B586" t="str">
-        <v>Blandad indata (linjär, 1,0 = HDR-referensvitt)</v>
+        <v>De två kurvorna som blandas vid detta utrymme blandar färgkanalerna olika, så det finns ingen enskild förstärkningskurva att rita. Tonkurvan nedan är ändå exakt.</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B587" t="str">
-        <v>Förstärkning (log2-steg)</v>
+        <v>Kurva vid {h} steg (ingen förstärkning)</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B588" t="str">
-        <v>Gråskalans tonkurva vid detta utrymme</v>
+        <v>Kurva vid {h} steg</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B589" t="str">
-        <v>Indata (× HDR-referensvitt)</v>
+        <v>Tillämpad vid {h} steg</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B590" t="str">
-        <v>Utdata (× HDR-referensvitt)</v>
+        <v>Förstärkning vid detta utrymme</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>No change</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B591" t="str">
-        <v>Ingen ändring</v>
+        <v>Blandad indata (linjär, 1,0 = HDR-referensvitt)</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B592" t="str">
-        <v>Skärmens topp vid {h} steg</v>
+        <v>Förstärkning (log2-steg)</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Output at {h} stops</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B593" t="str">
-        <v>Utdata vid {h} steg</v>
+        <v>Gråskalans tonkurva vid detta utrymme</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B594" t="str">
-        <v>HDR, färgomfång och pixelförhållande uppdateras när fönstret flyttas till en skärm där de skiljer sig.</v>
+        <v>Indata (× HDR-referensvitt)</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Identify displays</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B595" t="str">
-        <v>Identifiera skärmar</v>
+        <v>Utdata (× HDR-referensvitt)</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>No change</v>
       </c>
       <c r="B596" t="str">
-        <v>Ber om tillåtelse att se vilken skärm fönstret ligger på, så att panelen även uppdateras mellan likadana skärmar och visar HDR-utrymme där webbläsaren exponerar det.</v>
+        <v>Ingen ändring</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B597" t="str">
-        <v>Följer vilken skärm fönstret ligger på.</v>
+        <v>Skärmens topp vid {h} steg</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B598" t="str">
-        <v>Tillåtelse att identifiera skärmar nekades. Den kan ändras i webbplatsens inställningar.</v>
+        <v>Utdata vid {h} steg</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B599" t="str">
-        <v>Den här webbläsaren kan inte identifiera skärmar; bara den automatiska uppdateringen ovan gäller.</v>
+        <v>HDR, färgomfång och pixelförhållande uppdateras när fönstret flyttas till en skärm där de skiljer sig.</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>Could not identify displays.</v>
+        <v>Identify displays</v>
       </c>
       <c r="B600" t="str">
-        <v>Kunde inte identifiera skärmar.</v>
+        <v>Identifiera skärmar</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Display events</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B601" t="str">
-        <v>Skärmhändelser</v>
+        <v>Ber om tillåtelse att se vilken skärm fönstret ligger på, så att panelen även uppdateras mellan likadana skärmar och visar HDR-utrymme där webbläsaren exponerar det.</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B602" t="str">
-        <v>Inga händelser än. Dra fönstret till en annan skärm.</v>
+        <v>Följer vilken skärm fönstret ligger på.</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Colour primaries</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B603" t="str">
-        <v>Färgprimärer</v>
+        <v>Tillåtelse att identifiera skärmar nekades. Den kan ändras i webbplatsens inställningar.</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>Transfer characteristics</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B604" t="str">
-        <v>Överföringsfunktion</v>
+        <v>Den här webbläsaren kan inte identifiera skärmar; bara den automatiska uppdateringen ovan gäller.</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>Matrix coefficients</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B605" t="str">
-        <v>Matriskoefficienter</v>
+        <v>Kunde inte identifiera skärmar.</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Video full-range flag</v>
+        <v>Display events</v>
       </c>
       <c r="B606" t="str">
-        <v>Flagga för fullt videoomfång</v>
+        <v>Skärmhändelser</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>Full range</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B607" t="str">
-        <v>Fullt omfång</v>
+        <v>Inga händelser än. Dra fönstret till en annan skärm.</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Narrow range</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B608" t="str">
-        <v>Begränsat omfång</v>
+        <v>Färgprimärer</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B609" t="str">
-        <v>inte tilldelad av ITU-T H.273</v>
+        <v>Överföringsfunktion</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B610" t="str">
-        <v>Färgprimärer 2 (Ospecificerad) hänvisar till profilen själv — primärerna hämtas från färgämnestaggarna och inte från den här taggen.</v>
+        <v>Matriskoefficienter</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B611" t="str">
-        <v>De fyra reserverade byten i den här taggen är inte alla noll.</v>
+        <v>Flagga för fullt videoomfång</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>REPORT</v>
+        <v>Full range</v>
       </c>
       <c r="B612" t="str">
-        <v>RAPPORT</v>
+        <v>Fullt omfång</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>FAIL</v>
+        <v>Narrow range</v>
       </c>
       <c r="B613" t="str">
-        <v>UNDERKÄND</v>
+        <v>Begränsat omfång</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>checks</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B614" t="str">
-        <v>kontroller</v>
+        <v>inte tilldelad av ITU-T H.273</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B615" t="str">
-        <v>Genererad av iccPawgReport (iccDEV) · checklista från ICC Profile Assessment Working Group.</v>
+        <v>Färgprimärer 2 (Ospecificerad) hänvisar till profilen själv — primärerna hämtas från färgämnestaggarna och inte från den här taggen.</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B616" t="str">
-        <v>ICC-profilverktyg · drivs av IccProfLib</v>
+        <v>De fyra reserverade byten i den här taggen är inte alla noll.</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>ICC Profile Tool</v>
+        <v>REPORT</v>
       </c>
       <c r="B617" t="str">
-        <v>ICC-profilverktyg</v>
+        <v>RAPPORT</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>Powered by {lib}</v>
+        <v>FAIL</v>
       </c>
       <c r="B618" t="str">
-        <v>Drivs av {lib}</v>
+        <v>UNDERKÄND</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>Subscribe</v>
+        <v>checks</v>
       </c>
       <c r="B619" t="str">
-        <v>Prenumerera</v>
+        <v>kontroller</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B620" t="str">
-        <v>Få besked om nya profiletool-versioner</v>
+        <v>Genererad av iccPawgReport (iccDEV) · checklista från ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>Get notified about new releases</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B621" t="str">
-        <v>Få besked om nya versioner</v>
+        <v>ICC-profilverktyg · drivs av IccProfLib</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>Close</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B622" t="str">
-        <v>Stäng</v>
+        <v>ICC-profilverktyg</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B623" t="str">
-        <v>Vi mejlar dig när en ny större eller mindre version av profiletool släpps. Patchversioner hoppas över. Din adress granskas manuellt innan den läggs till.</v>
+        <v>Drivs av {lib}</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>Email address</v>
+        <v>Subscribe</v>
       </c>
       <c r="B624" t="str">
-        <v>E-postadress</v>
+        <v>Prenumerera</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>you@example.com</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B625" t="str">
-        <v>du@exempel.com</v>
+        <v>Få besked om nya profiletool-versioner</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B626" t="str">
-        <v>Hur kommer du att använda profiletool?</v>
+        <v>Få besked om nya versioner</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>(optional)</v>
+        <v>Close</v>
       </c>
       <c r="B627" t="str">
-        <v>(valfritt)</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B628" t="str">
-        <v>t.ex. utvärdera ICC-profiler för tryckkalibrering</v>
+        <v>Vi mejlar dig när en ny större eller mindre version av profiletool släpps. Patchversioner hoppas över. Din adress granskas manuellt innan den läggs till.</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Email address</v>
       </c>
       <c r="B629" t="str">
-        <v>Jag godkänner att ta emot e-post om profiletool-versioner. Jag kan avsluta prenumerationen när som helst.</v>
+        <v>E-postadress</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>Cancel</v>
+        <v>you@example.com</v>
       </c>
       <c r="B630" t="str">
-        <v>Avbryt</v>
+        <v>du@exempel.com</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>Subscribe</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B631" t="str">
-        <v>Prenumerera</v>
+        <v>Hur kommer du att använda profiletool?</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>(optional)</v>
       </c>
       <c r="B632" t="str">
-        <v>Tack — vi hör av oss.</v>
+        <v>(valfritt)</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B633" t="str">
-        <v>När du har godkänts får du ett välkomstmejl. Därefter hör du bara från oss när en ny version av profiletool släpps.</v>
+        <v>t.ex. utvärdera ICC-profiler för tryckkalibrering</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>Close</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B634" t="str">
-        <v>Stäng</v>
+        <v>Jag godkänner att ta emot e-post om profiletool-versioner. Jag kan avsluta prenumerationen när som helst.</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>Privacy notice</v>
+        <v>Cancel</v>
       </c>
       <c r="B635" t="str">
-        <v>Integritetsmeddelande</v>
+        <v>Avbryt</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B636" t="str">
-        <v>Ange en giltig e-postadress.</v>
+        <v>Prenumerera</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B637" t="str">
-        <v>För många förfrågningar. Försök igen senare.</v>
+        <v>Tack — vi hör av oss.</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B638" t="str">
-        <v>Kontrollera formuläret och försök igen.</v>
+        <v>När du har godkänts får du ett välkomstmejl. Därefter hör du bara från oss när en ny version av profiletool släpps.</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Close</v>
       </c>
       <c r="B639" t="str">
-        <v>Det gick inte att skicka din förfrågan. Försök igen.</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B640" t="str">
-        <v>Nätverksfel. Försök igen.</v>
+        <v>Integritetsmeddelande</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Error:</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B641" t="str">
-        <v>Fel:</v>
+        <v>Ange en giltig e-postadress.</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>Convert to XML</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B642" t="str">
-        <v>Konvertera till XML</v>
+        <v>För många förfrågningar. Försök igen senare.</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>Convert to JSON</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B643" t="str">
-        <v>Konvertera till JSON</v>
+        <v>Kontrollera formuläret och försök igen.</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>Convert to ICC</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B644" t="str">
-        <v>Konvertera till ICC</v>
+        <v>Det gick inte att skicka din förfrågan. Försök igen.</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>Converting to XML…</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B645" t="str">
-        <v>Konverterar till XML…</v>
+        <v>Nätverksfel. Försök igen.</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>Converting to JSON…</v>
+        <v>Error:</v>
       </c>
       <c r="B646" t="str">
-        <v>Konverterar till JSON…</v>
+        <v>Fel:</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>Converting to ICC…</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B647" t="str">
-        <v>Konverterar till ICC…</v>
+        <v>Konvertera till XML</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>Load ICC profile</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B648" t="str">
-        <v>Läs in ICC-profil</v>
+        <v>Konvertera till JSON</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B649" t="str">
-        <v>Släppzon för ICC-profilfiler</v>
+        <v>Konvertera till ICC</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>Profile ID</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B650" t="str">
-        <v>Profil-ID</v>
+        <v>Konverterar till XML…</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>No tags found.</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B651" t="str">
-        <v>Inga taggar hittades.</v>
+        <v>Konverterar till JSON…</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>Tag Name</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B652" t="str">
-        <v>Taggnamn</v>
+        <v>Konverterar till ICC…</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>ID</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B653" t="str">
-        <v>ID</v>
+        <v>Läs in ICC-profil</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>Offset</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B654" t="str">
-        <v>Offset</v>
+        <v>Släppzon för ICC-profilfiler</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>Size</v>
+        <v>Profile ID</v>
       </c>
       <c r="B655" t="str">
-        <v>Storlek</v>
+        <v>Profil-ID</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>Pad</v>
+        <v>No tags found.</v>
       </c>
       <c r="B656" t="str">
-        <v>Utfyllnad</v>
+        <v>Inga taggar hittades.</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>Bytes changed since load</v>
+        <v>Tag Name</v>
       </c>
       <c r="B657" t="str">
-        <v>Byte ändrade sedan inläsning</v>
+        <v>Taggnamn</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
-        <v>Type</v>
+        <v>ID</v>
       </c>
       <c r="B658" t="str">
-        <v>Typ</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="str">
-        <v>Array of {type}</v>
+        <v>Offset</v>
       </c>
       <c r="B659" t="str">
-        <v>Array av {type}</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="str">
-        <v>(No content)</v>
+        <v>Size</v>
       </c>
       <c r="B660" t="str">
-        <v>(Inget innehåll)</v>
+        <v>Storlek</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="str">
-        <v>bytes</v>
+        <v>Pad</v>
       </c>
       <c r="B661" t="str">
-        <v>byte</v>
+        <v>Utfyllnad</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="str">
-        <v>Loading full description…</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B662" t="str">
-        <v>Läser in fullständig beskrivning…</v>
+        <v>Byte ändrade sedan inläsning</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="str">
-        <v>Could not load full description:</v>
+        <v>Type</v>
       </c>
       <c r="B663" t="str">
-        <v>Kunde inte läsa in fullständig beskrivning:</v>
+        <v>Typ</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B664" t="str">
-        <v>Den här profilen kunde inte tolkas helt och får inte tillämpas. Huvudet och taggkatalogen nedan visas endast för granskning.</v>
+        <v>Array av {type}</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>(No content)</v>
       </c>
       <c r="B665" t="str">
-        <v>Tagginnehåll otillgängligt — profilen kunde inte tolkas helt.</v>
+        <v>(Inget innehåll)</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="str">
-        <v>No validation output</v>
+        <v>bytes</v>
       </c>
       <c r="B666" t="str">
-        <v>Ingen valideringsutdata</v>
+        <v>byte</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="str">
-        <v>Profile is valid</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B667" t="str">
-        <v>Profilen är giltig</v>
+        <v>Läser in fullständig beskrivning…</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B668" t="str">
-        <v>Profilen har varning(ar)</v>
+        <v>Kunde inte läsa in fullständig beskrivning:</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="str">
-        <v>Profile is non-compliant</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B669" t="str">
-        <v>Profilen följer inte specifikationen</v>
+        <v>Den här profilen kunde inte tolkas helt och får inte tillämpas. Huvudet och taggkatalogen nedan visas endast för granskning.</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="str">
-        <v>Critical validation error</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B670" t="str">
-        <v>Kritiskt valideringsfel</v>
+        <v>Tagginnehåll otillgängligt — profilen kunde inte tolkas helt.</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="str">
-        <v>Unknown validation status</v>
+        <v>No validation output</v>
       </c>
       <c r="B671" t="str">
-        <v>Okänd valideringsstatus</v>
+        <v>Ingen valideringsutdata</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B672" t="str">
-        <v>Kritiskt — visas endast för granskning</v>
+        <v>Profilen är giltig</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B673" t="str">
-        <v>Inga varningar eller fel hittades.</v>
+        <v>Profilen har varning(ar)</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="str">
-        <v>Valid</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B674" t="str">
-        <v>Giltig</v>
+        <v>Profilen följer inte specifikationen</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="str">
-        <v>Warning</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B675" t="str">
-        <v>Varning</v>
+        <v>Kritiskt valideringsfel</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="str">
-        <v>Error</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B676" t="str">
-        <v>Fel</v>
+        <v>Okänd valideringsstatus</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="str">
-        <v>Unknown</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B677" t="str">
-        <v>Okänd</v>
+        <v>Kritiskt — visas endast för granskning</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="str">
-        <v>Pass</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B678" t="str">
-        <v>Godkänd</v>
+        <v>Inga varningar eller fel hittades.</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="str">
-        <v>Fail</v>
+        <v>Valid</v>
       </c>
       <c r="B679" t="str">
-        <v>Underkänd</v>
+        <v>Giltig</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="str">
-        <v>View in context</v>
+        <v>Warning</v>
       </c>
       <c r="B680" t="str">
-        <v>Visa i sammanhang</v>
+        <v>Varning</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="str">
-        <v>Validation detail</v>
+        <v>Error</v>
       </c>
       <c r="B681" t="str">
-        <v>Valideringsdetalj</v>
+        <v>Fel</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="str">
-        <v>Triggered by</v>
+        <v>Unknown</v>
       </c>
       <c r="B682" t="str">
-        <v>Utlöst av</v>
+        <v>Okänd</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="str">
-        <v>Field</v>
+        <v>Pass</v>
       </c>
       <c r="B683" t="str">
-        <v>Fält</v>
+        <v>Godkänd</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="str">
-        <v>Current value</v>
+        <v>Fail</v>
       </c>
       <c r="B684" t="str">
-        <v>Aktuellt värde</v>
+        <v>Underkänd</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="str">
-        <v>Required: 0</v>
+        <v>View in context</v>
       </c>
       <c r="B685" t="str">
-        <v>Krävs: 0</v>
+        <v>Visa i sammanhang</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="str">
-        <v>Expected: {value}</v>
+        <v>Validation detail</v>
       </c>
       <c r="B686" t="str">
-        <v>Förväntat: {value}</v>
+        <v>Valideringsdetalj</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="str">
-        <v>Invalid</v>
+        <v>Triggered by</v>
       </c>
       <c r="B687" t="str">
-        <v>Ogiltigt</v>
+        <v>Utlöst av</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Field</v>
       </c>
       <c r="B688" t="str">
-        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
+        <v>Fält</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="str">
-        <v>Close</v>
+        <v>Current value</v>
       </c>
       <c r="B689" t="str">
-        <v>Stäng</v>
+        <v>Aktuellt värde</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="str">
-        <v>Loading XML editor…</v>
+        <v>Required: 0</v>
       </c>
       <c r="B690" t="str">
-        <v>Läser in XML-redigeraren…</v>
+        <v>Krävs: 0</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B691" t="str">
-        <v>Läser in JSON-redigeraren…</v>
+        <v>Förväntat: {value}</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Invalid</v>
       </c>
       <c r="B692" t="str">
-        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>Ogiltigt</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B693" t="str">
-        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Close</v>
       </c>
       <c r="B694" t="str">
-        <v>● osparade XML-ändringar</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B695" t="str">
-        <v>● osparade JSON-ändringar</v>
+        <v>Läser in XML-redigeraren…</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B696" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
+        <v>Läser in JSON-redigeraren…</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B697" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
+        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="str">
-        <v>indent</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B698" t="str">
-        <v>indrag</v>
+        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="str">
-        <v>sort keys</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B699" t="str">
-        <v>sortera nycklar</v>
+        <v>● osparade XML-ändringar</v>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B700" t="str">
+        <v>● osparade JSON-ändringar</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B701" t="str">
+        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B702" t="str">
+        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B703" t="str">
+        <v>indrag</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B704" t="str">
+        <v>sortera nycklar</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B700" t="str">
+      <c r="B705" t="str">
         <v>Profilen skrevs från ändringarna, men omvalideringen misslyckades:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B700"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B705"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Sv.xlsx
+++ b/translations/Eng-Sv.xlsx
@@ -3827,10 +3827,10 @@
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (including gain-map JPEG), PNG — and HEIC on Safari.</v>
+        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (including gain-map JPEG), PNG — and HEIC and JPEG XL on Safari.</v>
       </c>
       <c r="B428" t="str">
-        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (även JPEG med gain map), PNG – och HEIC i Safari.</v>
+        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (även JPEG med gain map), PNG – och HEIC och JPEG XL i Safari.</v>
       </c>
     </row>
     <row r="429">

--- a/translations/Eng-Sv.xlsx
+++ b/translations/Eng-Sv.xlsx
@@ -1221,10 +1221,10 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and downloaded.</v>
+        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and opened; nothing is downloaded until you click Save ICC profile.</v>
       </c>
       <c r="B103" t="str">
-        <v>Skapa en ICC-DeviceLink från en .cube 3D-LUT från Adobe/Resolve. Resultatet läggs till i din pool och laddas ned.</v>
+        <v>Skapa en ICC-DeviceLink från en .cube 3D-LUT från Adobe/Resolve. Resultatet läggs till i din pool och öppnas; inget laddas ned förrän du klickar på Spara ICC-profil.</v>
       </c>
     </row>
     <row r="104">

--- a/translations/Eng-Sv.xlsx
+++ b/translations/Eng-Sv.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B705"/>
+  <dimension ref="A1:B706"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -1197,4861 +1197,4869 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Sort by name</v>
+        <v>Tap to select, then tap a tab to send.</v>
       </c>
       <c r="B100" t="str">
-        <v>Sortera efter namn</v>
+        <v>Tryck för att välja, tryck sedan på en flik för att skicka.</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>A–Z</v>
+        <v>Sort by name</v>
       </c>
       <c r="B101" t="str">
-        <v>A–Z</v>
+        <v>Sortera efter namn</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>New profile from .cube</v>
+        <v>A–Z</v>
       </c>
       <c r="B102" t="str">
-        <v>Ny profil från .cube</v>
+        <v>A–Z</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and opened; nothing is downloaded until you click Save ICC profile.</v>
+        <v>New profile from .cube</v>
       </c>
       <c r="B103" t="str">
-        <v>Skapa en ICC-DeviceLink från en .cube 3D-LUT från Adobe/Resolve. Resultatet läggs till i din pool och öppnas; inget laddas ned förrän du klickar på Spara ICC-profil.</v>
+        <v>Ny profil från .cube</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Choose .cube file</v>
+        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and opened; nothing is downloaded until you click Save ICC profile.</v>
       </c>
       <c r="B104" t="str">
-        <v>Välj .cube-fil</v>
+        <v>Skapa en ICC-DeviceLink från en .cube 3D-LUT från Adobe/Resolve. Resultatet läggs till i din pool och öppnas; inget laddas ned förrän du klickar på Spara ICC-profil.</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
+        <v>Choose .cube file</v>
+      </c>
+      <c r="B105" t="str">
+        <v>Välj .cube-fil</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
         <v>or drop it here, or paste below</v>
       </c>
-      <c r="B105" t="str">
+      <c r="B106" t="str">
         <v>eller släpp den här, eller klistra in nedan</v>
       </c>
     </row>
-    <row r="106" xml:space="preserve">
-      <c r="A106" t="str" xml:space="preserve">
+    <row r="107" xml:space="preserve">
+      <c r="A107" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
-      <c r="B106" t="str" xml:space="preserve">
+      <c r="B107" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" t="str">
-        <v>Cancel</v>
-      </c>
-      <c r="B107" t="str">
-        <v>Avbryt</v>
-      </c>
-    </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Create DeviceLink</v>
+        <v>Cancel</v>
       </c>
       <c r="B108" t="str">
-        <v>Skapa DeviceLink</v>
+        <v>Avbryt</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Creating…</v>
+        <v>Create DeviceLink</v>
       </c>
       <c r="B109" t="str">
-        <v>Skapar…</v>
+        <v>Skapa DeviceLink</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Could not read that file.</v>
+        <v>Creating…</v>
       </c>
       <c r="B110" t="str">
-        <v>Det gick inte att läsa den filen.</v>
+        <v>Skapar…</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Profile</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B111" t="str">
-        <v>Profil</v>
+        <v>Det gick inte att läsa den filen.</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Compare</v>
+        <v>Profile</v>
       </c>
       <c r="B112" t="str">
-        <v>Jämför</v>
+        <v>Profil</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Combine</v>
+        <v>Compare</v>
       </c>
       <c r="B113" t="str">
-        <v>Länka</v>
+        <v>Jämför</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Spectral</v>
+        <v>Combine</v>
       </c>
       <c r="B114" t="str">
-        <v>Spektral</v>
+        <v>Länka</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Drag profiles from the pool onto this tab</v>
+        <v>Spectral</v>
       </c>
       <c r="B115" t="str">
-        <v>Dra profiler från poolen till den här fliken</v>
+        <v>Spektral</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Remove</v>
+        <v>Drag profiles from the pool onto this tab</v>
       </c>
       <c r="B116" t="str">
-        <v>Ta bort</v>
+        <v>Dra profiler från poolen till den här fliken</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>No profile selected</v>
+        <v>Remove</v>
       </c>
       <c r="B117" t="str">
-        <v>Ingen profil vald</v>
+        <v>Ta bort</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
+        <v>No profile selected</v>
       </c>
       <c r="B118" t="str">
-        <v>Dra en profil från poolen till fliken Profil för att granska den.</v>
+        <v>Ingen profil vald</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Nothing to compare yet</v>
+        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
       </c>
       <c r="B119" t="str">
-        <v>Inget att jämföra ännu</v>
+        <v>Dra en profil från poolen till fliken Profil för att granska den.</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Drag one or more profiles onto the Compare tab.</v>
+        <v>Nothing to compare yet</v>
       </c>
       <c r="B120" t="str">
-        <v>Dra en eller flera profiler till fliken Jämför.</v>
+        <v>Inget att jämföra ännu</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Gamut comparison</v>
+        <v>Drag one or more profiles onto the Compare tab.</v>
       </c>
       <c r="B121" t="str">
-        <v>Gamutjämförelse</v>
+        <v>Dra en eller flera profiler till fliken Jämför.</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
+        <v>Gamut comparison</v>
       </c>
       <c r="B122" t="str">
-        <v>Vyer för 3D-gamut och 2D-snitt kommer hit. Samlade:</v>
+        <v>Gamutjämförelse</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Rendering intent</v>
+        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
       </c>
       <c r="B123" t="str">
-        <v>Renderingsavsikt</v>
+        <v>Vyer för 3D-gamut och 2D-snitt kommer hit. Samlade:</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Shell</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B124" t="str">
-        <v>Skal</v>
+        <v>Renderingsavsikt</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Wireframe</v>
+        <v>Shell</v>
       </c>
       <c r="B125" t="str">
-        <v>Trådmodell</v>
+        <v>Skal</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Axis numbers</v>
+        <v>Wireframe</v>
       </c>
       <c r="B126" t="str">
-        <v>Axelnummer</v>
+        <v>Trådmodell</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Opacity</v>
+        <v>Axis numbers</v>
       </c>
       <c r="B127" t="str">
-        <v>Opacitet</v>
+        <v>Axelnummer</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Colour</v>
+        <v>Opacity</v>
       </c>
       <c r="B128" t="str">
-        <v>Färg</v>
+        <v>Opacitet</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Solid</v>
+        <v>Colour</v>
       </c>
       <c r="B129" t="str">
-        <v>Enfärgad</v>
+        <v>Färg</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>By value</v>
+        <v>Solid</v>
       </c>
       <c r="B130" t="str">
-        <v>Efter värde</v>
+        <v>Enfärgad</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>By hue</v>
+        <v>By value</v>
       </c>
       <c r="B131" t="str">
-        <v>Efter nyans</v>
+        <v>Efter värde</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Rotation</v>
+        <v>By hue</v>
       </c>
       <c r="B132" t="str">
-        <v>Rotation</v>
+        <v>Efter nyans</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Turntable</v>
+        <v>Rotation</v>
       </c>
       <c r="B133" t="str">
-        <v>Skivtallrik</v>
+        <v>Rotation</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Orbit</v>
+        <v>Turntable</v>
       </c>
       <c r="B134" t="str">
-        <v>Omloppsbana</v>
+        <v>Skivtallrik</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Drag speed</v>
+        <v>Orbit</v>
       </c>
       <c r="B135" t="str">
-        <v>Draghastighet</v>
+        <v>Omloppsbana</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Roll</v>
+        <v>Drag speed</v>
       </c>
       <c r="B136" t="str">
-        <v>Rullning</v>
+        <v>Draghastighet</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Roll speed</v>
+        <v>Roll</v>
       </c>
       <c r="B137" t="str">
-        <v>Rullningshastighet</v>
+        <v>Rullning</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Building gamut…</v>
+        <v>Roll speed</v>
       </c>
       <c r="B138" t="str">
-        <v>Bygger gamut…</v>
+        <v>Rullningshastighet</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>no gamut</v>
+        <v>Building gamut…</v>
       </c>
       <c r="B139" t="str">
-        <v>ingen gamut</v>
+        <v>Bygger gamut…</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Show / hide</v>
+        <v>no gamut</v>
       </c>
       <c r="B140" t="str">
-        <v>Visa/dölj</v>
+        <v>ingen gamut</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>3-D gamut shell</v>
+        <v>Show / hide</v>
       </c>
       <c r="B141" t="str">
-        <v>3D-gamutskal</v>
+        <v>Visa/dölj</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>2-D gamut slice</v>
+        <v>3-D gamut shell</v>
       </c>
       <c r="B142" t="str">
-        <v>2D-gamutsnitt</v>
+        <v>3D-gamutskal</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Plane</v>
+        <v>2-D gamut slice</v>
       </c>
       <c r="B143" t="str">
-        <v>Plan</v>
+        <v>2D-gamutsnitt</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>L*</v>
+        <v>Plane</v>
       </c>
       <c r="B144" t="str">
-        <v>L*</v>
+        <v>Plan</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>a*</v>
+        <v>L*</v>
       </c>
       <c r="B145" t="str">
-        <v>a*</v>
+        <v>L*</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>b*</v>
+        <v>a*</v>
       </c>
       <c r="B146" t="str">
-        <v>b*</v>
+        <v>a*</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
+        <v>b*</v>
       </c>
       <c r="B147" t="str">
-        <v>Ingen av de valda profilerna har en enhet→PCS-transform att härleda en gamut från.</v>
+        <v>b*</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Linking</v>
+        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
       </c>
       <c r="B148" t="str">
-        <v>Länkning</v>
+        <v>Ingen av de valda profilerna har en enhet→PCS-transform att härleda en gamut från.</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
+        <v>Linking</v>
       </c>
       <c r="B149" t="str">
-        <v>DeviceLink-produktion och transformer över flera profiler kommer i en senare fas.</v>
+        <v>Länkning</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>More link makers (DeviceLink, …) arrive here.</v>
+        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
       </c>
       <c r="B150" t="str">
-        <v>Fler länkverktyg (DeviceLink, …) kommer hit.</v>
+        <v>DeviceLink-produktion och transformer över flera profiler kommer i en senare fas.</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Observer Change</v>
+        <v>More link makers (DeviceLink, …) arrive here.</v>
       </c>
       <c r="B151" t="str">
-        <v>V4-skärmskapare</v>
+        <v>Fler länkverktyg (DeviceLink, …) kommer hit.</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
+        <v>Observer Change</v>
       </c>
       <c r="B152" t="str">
-        <v>Dra en V5 RGB-skärm och en V5-observatörsprofil hit för att skapa en V4-skärmprofil.</v>
+        <v>V4-skärmskapare</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>V5 RGB display</v>
+        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
       </c>
       <c r="B153" t="str">
-        <v>V5 RGB-skärm</v>
+        <v>Dra en V5 RGB-skärm och en V5-observatörsprofil hit för att skapa en V4-skärmprofil.</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>drop a display profile</v>
+        <v>V5 RGB display</v>
       </c>
       <c r="B154" t="str">
-        <v>släpp en skärmprofil</v>
+        <v>V5 RGB-skärm</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>V5 observer (PCC)</v>
+        <v>drop a display profile</v>
       </c>
       <c r="B155" t="str">
-        <v>V5-observatör (PCC)</v>
+        <v>släpp en skärmprofil</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>drop an observer profile</v>
+        <v>V5 observer (PCC)</v>
       </c>
       <c r="B156" t="str">
-        <v>släpp en observatörsprofil</v>
+        <v>V5-observatör (PCC)</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
+        <v>drop an observer profile</v>
       </c>
       <c r="B157" t="str">
-        <v>En profil som varken är en V5 RGB-skärm eller en observatör ignorerades.</v>
+        <v>släpp en observatörsprofil</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Make V4 Display Profile</v>
+        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
       </c>
       <c r="B158" t="str">
-        <v>Skapa V4-skärmprofil</v>
+        <v>En profil som varken är en V5 RGB-skärm eller en observatör ignorerades.</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Profile name</v>
+        <v>Make V4 Display Profile</v>
       </c>
       <c r="B159" t="str">
-        <v>Profilnamn</v>
+        <v>Skapa V4-skärmprofil</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Create</v>
+        <v>Profile name</v>
       </c>
       <c r="B160" t="str">
-        <v>Skapa</v>
+        <v>Profilnamn</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Making…</v>
+        <v>Create</v>
       </c>
       <c r="B161" t="str">
-        <v>Skapar…</v>
+        <v>Skapa</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Making…</v>
       </c>
       <c r="B162" t="str">
-        <v>”{name}” skapad — tillagd i poolen och den här fliken.</v>
+        <v>Skapar…</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Link Pipeline</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B163" t="str">
-        <v>Länkpipeline</v>
+        <v>”{name}” skapad — tillagd i poolen och den här fliken.</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
+        <v>Link Pipeline</v>
       </c>
       <c r="B164" t="str">
-        <v>Bygg en kedja av profiler och skapa sedan en DeviceLink, transformera en bild eller transformera ett färgdataset genom den.</v>
+        <v>Länkpipeline</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Done</v>
+        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
       </c>
       <c r="B165" t="str">
-        <v>Klar</v>
+        <v>Bygg en kedja av profiler och skapa sedan en DeviceLink, transformera en bild eller transformera ett färgdataset genom den.</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
+        <v>Done</v>
       </c>
       <c r="B166" t="str">
-        <v>Släpp en bild att transformera (TIFF/PNG/JPEG)</v>
+        <v>Klar</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Checking image…</v>
+        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
       </c>
       <c r="B167" t="str">
-        <v>Kontrollerar bild…</v>
+        <v>Släpp en bild att transformera (TIFF/PNG/JPEG)</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Not a supported image (TIFF, PNG or JPEG).</v>
+        <v>Checking image…</v>
       </c>
       <c r="B168" t="str">
-        <v>Bildtypen stöds inte (TIFF, PNG eller JPEG).</v>
+        <v>Kontrollerar bild…</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Image too large ({mp} MP; limit {max} MP).</v>
+        <v>Not a supported image (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B169" t="str">
-        <v>Bilden är för stor ({mp} MP; gräns {max} MP).</v>
+        <v>Bildtypen stöds inte (TIFF, PNG eller JPEG).</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Transform Image</v>
+        <v>Image too large ({mp} MP; limit {max} MP).</v>
       </c>
       <c r="B170" t="str">
-        <v>Transformera bild</v>
+        <v>Bilden är för stor ({mp} MP; gräns {max} MP).</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Transforming…</v>
+        <v>Transform Image</v>
       </c>
       <c r="B171" t="str">
-        <v>Transformerar…</v>
+        <v>Transformera bild</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Drop profiles to start the chain</v>
+        <v>Transforming…</v>
       </c>
       <c r="B172" t="str">
-        <v>Släpp profiler för att starta kedjan</v>
+        <v>Transformerar…</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>removed</v>
+        <v>Drop profiles to start the chain</v>
       </c>
       <c r="B173" t="str">
-        <v>borttagen</v>
+        <v>Släpp profiler för att starta kedjan</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Move earlier</v>
+        <v>removed</v>
       </c>
       <c r="B174" t="str">
-        <v>Flytta tidigare</v>
+        <v>borttagen</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Move later</v>
+        <v>Move earlier</v>
       </c>
       <c r="B175" t="str">
-        <v>Flytta senare</v>
+        <v>Flytta tidigare</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Move up</v>
+        <v>Move later</v>
       </c>
       <c r="B176" t="str">
-        <v>Flytta upp</v>
+        <v>Flytta senare</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Move down</v>
+        <v>Move up</v>
       </c>
       <c r="B177" t="str">
-        <v>Flytta ner</v>
+        <v>Flytta upp</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Rendering intent (all)</v>
+        <v>Move down</v>
       </c>
       <c r="B178" t="str">
-        <v>Återgivningsalternativ (alla)</v>
+        <v>Flytta ner</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Rendering intent for this transform</v>
+        <v>Rendering intent (all)</v>
       </c>
       <c r="B179" t="str">
-        <v>Återgivningsalternativ för denna transformering</v>
+        <v>Återgivningsalternativ (alla)</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Transforms use different rendering intents</v>
+        <v>Rendering intent for this transform</v>
       </c>
       <c r="B180" t="str">
-        <v>Transformeringarna använder olika återgivningsalternativ</v>
+        <v>Återgivningsalternativ för denna transformering</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
+        <v>Transforms use different rendering intents</v>
       </c>
       <c r="B181" t="str">
-        <v>Vänd kedjeriktning (vänder den första transformeringen, vilket sprider sig genom kedjan)</v>
+        <v>Transformeringarna använder olika återgivningsalternativ</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>A chained profile was removed from the pool — remove it to continue.</v>
+        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
       </c>
       <c r="B182" t="str">
-        <v>En profil i kedjan togs bort från poolen — ta bort den för att fortsätta.</v>
+        <v>Vänd kedjeriktning (vänder den första transformeringen, vilket sprider sig genom kedjan)</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Chain</v>
+        <v>A chained profile was removed from the pool — remove it to continue.</v>
       </c>
       <c r="B183" t="str">
-        <v>Kedja</v>
+        <v>En profil i kedjan togs bort från poolen — ta bort den för att fortsätta.</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>The chain could not be analysed.</v>
+        <v>Chain</v>
       </c>
       <c r="B184" t="str">
-        <v>Kedjan kunde inte analyseras.</v>
+        <v>Kedja</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Checking chain…</v>
+        <v>The chain could not be analysed.</v>
       </c>
       <c r="B185" t="str">
-        <v>Kontrollerar kedja…</v>
+        <v>Kedjan kunde inte analyseras.</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>The chain does not connect ({detail}).</v>
+        <v>Checking chain…</v>
       </c>
       <c r="B186" t="str">
-        <v>Kedjan hänger inte ihop ({detail}).</v>
+        <v>Kontrollerar kedja…</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
+        <v>The chain does not connect ({detail}).</v>
       </c>
       <c r="B187" t="str">
-        <v>Profil {n} hänger inte ihop med föregående steg ({detail}).</v>
+        <v>Kedjan hänger inte ihop ({detail}).</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Fix the chain before processing images</v>
+        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
       </c>
       <c r="B188" t="str">
-        <v>Åtgärda kedjan innan bilder bearbetas</v>
+        <v>Profil {n} hänger inte ihop med föregående steg ({detail}).</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Clear</v>
+        <v>Fix the chain before processing images</v>
       </c>
       <c r="B189" t="str">
-        <v>Rensa</v>
+        <v>Åtgärda kedjan innan bilder bearbetas</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Make DeviceLink</v>
+        <v>Clear</v>
       </c>
       <c r="B190" t="str">
-        <v>Skapa DeviceLink</v>
+        <v>Rensa</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>DeviceLink name</v>
+        <v>Make DeviceLink</v>
       </c>
       <c r="B191" t="str">
-        <v>DeviceLink-namn</v>
+        <v>Skapa DeviceLink</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Making…</v>
+        <v>DeviceLink name</v>
       </c>
       <c r="B192" t="str">
-        <v>Skapar…</v>
+        <v>DeviceLink-namn</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Making…</v>
       </c>
       <c r="B193" t="str">
-        <v>Skapade ”{name}” — tillagd i poolen och denna flik.</v>
+        <v>Skapar…</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B194" t="str">
-        <v>Släpp {src}-bilder för att konvertera till {dst} — resultaten laddas ner, inget sparas.</v>
+        <v>Skapade ”{name}” — tillagd i poolen och denna flik.</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Build a chain to process images</v>
+        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
       </c>
       <c r="B195" t="str">
-        <v>Bygg en kedja för att bearbeta bilder</v>
+        <v>Släpp {src}-bilder för att konvertera till {dst} — resultaten laddas ner, inget sparas.</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>This chain does not start and end in an image colour space</v>
+        <v>Build a chain to process images</v>
       </c>
       <c r="B196" t="str">
-        <v>Denna kedja börjar och slutar inte i en bildfärgrymd</v>
+        <v>Bygg en kedja för att bearbeta bilder</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Saved the transformed image.</v>
+        <v>This chain does not start and end in an image colour space</v>
       </c>
       <c r="B197" t="str">
-        <v>Sparade den transformerade bilden.</v>
+        <v>Denna kedja börjar och slutar inte i en bildfärgrymd</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
+        <v>Saved the transformed image.</v>
       </c>
       <c r="B198" t="str">
-        <v>Släpp ett färgdataset (CGATS/CSV/CxF/JSON)</v>
+        <v>Sparade den transformerade bilden.</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Could not read that file.</v>
+        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
       </c>
       <c r="B199" t="str">
-        <v>Kunde inte läsa filen.</v>
+        <v>Släpp ett färgdataset (CGATS/CSV/CxF/JSON)</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Data file too large.</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B200" t="str">
-        <v>Datafilen är för stor.</v>
+        <v>Kunde inte läsa filen.</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Transform Data</v>
+        <v>Data file too large.</v>
       </c>
       <c r="B201" t="str">
-        <v>Transformera data</v>
+        <v>Datafilen är för stor.</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Transforming…</v>
+        <v>Transform Data</v>
       </c>
       <c r="B202" t="str">
-        <v>Transformerar…</v>
+        <v>Transformera data</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Prefer</v>
+        <v>Transforming…</v>
       </c>
       <c r="B203" t="str">
-        <v>Föredra</v>
+        <v>Transformerar…</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Observer</v>
+        <v>Prefer</v>
       </c>
       <c r="B204" t="str">
-        <v>Observatör</v>
+        <v>Föredra</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>Illuminant</v>
+        <v>Observer</v>
       </c>
       <c r="B205" t="str">
-        <v>Ljuskälla</v>
+        <v>Observatör</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>Condition</v>
+        <v>Illuminant</v>
       </c>
       <c r="B206" t="str">
-        <v>Villkor</v>
+        <v>Ljuskälla</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Filter {n} duplicate(s)</v>
+        <v>Condition</v>
       </c>
       <c r="B207" t="str">
-        <v>Filtrera {n} dubblett(er)</v>
+        <v>Villkor</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>median</v>
+        <v>Filter {n} duplicate(s)</v>
       </c>
       <c r="B208" t="str">
-        <v>median</v>
+        <v>Filtrera {n} dubblett(er)</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>mean</v>
+        <v>median</v>
       </c>
       <c r="B209" t="str">
-        <v>medelvärde</v>
+        <v>median</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>patches</v>
+        <v>mean</v>
       </c>
       <c r="B210" t="str">
-        <v>patchar</v>
+        <v>medelvärde</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>{n} duplicates</v>
+        <v>patches</v>
       </c>
       <c r="B211" t="str">
-        <v>{n} dubbletter</v>
+        <v>patchar</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Transform result</v>
+        <v>{n} duplicates</v>
       </c>
       <c r="B212" t="str">
-        <v>Transformeringsresultat</v>
+        <v>{n} dubbletter</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>{src} → {dst} · {n} patches</v>
+        <v>Transform result</v>
       </c>
       <c r="B213" t="str">
-        <v>{src} → {dst} · {n} patchar</v>
+        <v>Transformeringsresultat</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Showing first {shown} of {total} — Save writes them all.</v>
+        <v>{src} → {dst} · {n} patches</v>
       </c>
       <c r="B214" t="str">
-        <v>Visar de första {shown} av {total} — Spara skriver alla.</v>
+        <v>{src} → {dst} · {n} patchar</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>Save as</v>
+        <v>Showing first {shown} of {total} — Save writes them all.</v>
       </c>
       <c r="B215" t="str">
-        <v>Spara som</v>
+        <v>Visar de första {shown} av {total} — Spara skriver alla.</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>Save</v>
+        <v>Save as</v>
       </c>
       <c r="B216" t="str">
-        <v>Spara</v>
+        <v>Spara som</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>Invert Transform</v>
+        <v>Save</v>
       </c>
       <c r="B217" t="str">
-        <v>Invertera transformering</v>
+        <v>Spara</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>Inverting…</v>
+        <v>Invert Transform</v>
       </c>
       <c r="B218" t="str">
-        <v>Inverterar…</v>
+        <v>Invertera transformering</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>Invert</v>
+        <v>Inverting…</v>
       </c>
       <c r="B219" t="str">
-        <v>Invertera</v>
+        <v>Inverterar…</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>last stage</v>
+        <v>Invert</v>
       </c>
       <c r="B220" t="str">
-        <v>sista steget</v>
+        <v>Invertera</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>first stage</v>
+        <v>last stage</v>
       </c>
       <c r="B221" t="str">
-        <v>första steget</v>
+        <v>sista steget</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>Data in {in} → search {out}</v>
+        <v>first stage</v>
       </c>
       <c r="B222" t="str">
-        <v>Data i {in} → sök {out}</v>
+        <v>första steget</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>Invert needs a 2–3 profile chain</v>
+        <v>Data in {in} → search {out}</v>
       </c>
       <c r="B223" t="str">
-        <v>Invertering kräver en kedja med 2–3 profiler</v>
+        <v>Data i {in} → sök {out}</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
+        <v>Invert needs a 2–3 profile chain</v>
       </c>
       <c r="B224" t="str">
-        <v>Datasetet måste vara {in}; den omvända sökningen ger {out} plus en inverterbarhetskostnad per patch.</v>
+        <v>Invertering kräver en kedja med 2–3 profiler</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>ΔE cost</v>
+        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
       </c>
       <c r="B225" t="str">
-        <v>ΔE-kostnad</v>
+        <v>Datasetet måste vara {in}; den omvända sökningen ger {out} plus en inverterbarhetskostnad per patch.</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>This image has an embedded ICC profile.</v>
+        <v>ΔE cost</v>
       </c>
       <c r="B226" t="str">
-        <v>Denna bild har en inbäddad ICC-profil.</v>
+        <v>ΔE-kostnad</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>Extract &amp; add to chain</v>
+        <v>This image has an embedded ICC profile.</v>
       </c>
       <c r="B227" t="str">
-        <v>Extrahera och lägg till i kedjan</v>
+        <v>Denna bild har en inbäddad ICC-profil.</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>Extracting…</v>
+        <v>Extract &amp; add to chain</v>
       </c>
       <c r="B228" t="str">
-        <v>Extraherar…</v>
+        <v>Extrahera och lägg till i kedjan</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>Dismiss</v>
+        <v>Extracting…</v>
       </c>
       <c r="B229" t="str">
-        <v>Avfärda</v>
+        <v>Extraherar…</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
+        <v>Dismiss</v>
       </c>
       <c r="B230" t="str">
-        <v>Extraherade den inbäddade profilen — tillagd i poolen och placerad först i kedjan.</v>
+        <v>Avfärda</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>Image output options</v>
+        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
       </c>
       <c r="B231" t="str">
-        <v>Alternativ för bildutdata</v>
+        <v>Extraherade den inbäddade profilen — tillagd i poolen och placerad först i kedjan.</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>Encoding</v>
+        <v>Image output options</v>
       </c>
       <c r="B232" t="str">
-        <v>Kodning</v>
+        <v>Alternativ för bildutdata</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>Same as source</v>
+        <v>Encoding</v>
       </c>
       <c r="B233" t="str">
-        <v>Samma som källan</v>
+        <v>Kodning</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>8-bit</v>
+        <v>Same as source</v>
       </c>
       <c r="B234" t="str">
-        <v>8-bitars</v>
+        <v>Samma som källan</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>16-bit</v>
+        <v>8-bit</v>
       </c>
       <c r="B235" t="str">
-        <v>16-bitars</v>
+        <v>8-bitars</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>Float (32-bit)</v>
+        <v>16-bit</v>
       </c>
       <c r="B236" t="str">
-        <v>Flyttal (32-bitars)</v>
+        <v>16-bitars</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>Compression</v>
+        <v>Float (32-bit)</v>
       </c>
       <c r="B237" t="str">
-        <v>Komprimering</v>
+        <v>Flyttal (32-bitars)</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>None</v>
+        <v>Compression</v>
       </c>
       <c r="B238" t="str">
-        <v>Ingen</v>
+        <v>Komprimering</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>Planar</v>
+        <v>None</v>
       </c>
       <c r="B239" t="str">
-        <v>Planformat</v>
+        <v>Ingen</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>Composite</v>
+        <v>Planar</v>
       </c>
       <c r="B240" t="str">
-        <v>Sammansatt</v>
+        <v>Planformat</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>Separated</v>
+        <v>Composite</v>
       </c>
       <c r="B241" t="str">
-        <v>Separerad</v>
+        <v>Sammansatt</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>CMM interpolation</v>
+        <v>Separated</v>
       </c>
       <c r="B242" t="str">
-        <v>CMM-interpolation</v>
+        <v>Separerad</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>Tetrahedral</v>
+        <v>CMM interpolation</v>
       </c>
       <c r="B243" t="str">
-        <v>Tetraedrisk</v>
+        <v>CMM-interpolation</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>Linear</v>
+        <v>Tetrahedral</v>
       </c>
       <c r="B244" t="str">
-        <v>Linjär</v>
+        <v>Tetraedrisk</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>Embed ICC</v>
+        <v>Linear</v>
       </c>
       <c r="B245" t="str">
-        <v>Bädda in ICC</v>
+        <v>Linjär</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
+        <v>Embed ICC</v>
       </c>
       <c r="B246" t="str">
-        <v>Kodning, komprimering och planformat formar den sparade TIFF-filen. RGB/Gray-utdata förblir PNG om inte ett TIFF-specifikt alternativ (flyttal, LZW/ZIP, separerad) väljs.</v>
+        <v>Bädda in ICC</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>Assemble spectral TIFF</v>
+        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
       </c>
       <c r="B247" t="str">
-        <v>Montera spektral-TIFF</v>
+        <v>Kodning, komprimering och planformat formar den sparade TIFF-filen. RGB/Gray-utdata förblir PNG om inte ett TIFF-specifikt alternativ (flyttal, LZW/ZIP, separerad) väljs.</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
+        <v>Assemble spectral TIFF</v>
       </c>
       <c r="B248" t="str">
-        <v>Släpp enkanaliga spektralbilder i kanalordning och montera dem till en flerkanalig TIFF.</v>
+        <v>Montera spektral-TIFF</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>Drop spectral images here (or click to choose)</v>
+        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
       </c>
       <c r="B249" t="str">
-        <v>Släpp spektralbilder här (eller klicka för att välja)</v>
+        <v>Släpp enkanaliga spektralbilder i kanalordning och montera dem till en flerkanalig TIFF.</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>ch</v>
+        <v>Drop spectral images here (or click to choose)</v>
       </c>
       <c r="B250" t="str">
-        <v>ch</v>
+        <v>Släpp spektralbilder här (eller klicka för att välja)</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>Assemble &amp; Save</v>
+        <v>ch</v>
       </c>
       <c r="B251" t="str">
-        <v>Montera och spara</v>
+        <v>ch</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>Assembling…</v>
+        <v>Assemble &amp; Save</v>
       </c>
       <c r="B252" t="str">
-        <v>Monterar…</v>
+        <v>Montera och spara</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>Assembled {n} channels.</v>
+        <v>Assembling…</v>
       </c>
       <c r="B253" t="str">
-        <v>Monterade {n} kanaler.</v>
+        <v>Monterar…</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>None of those look like images (TIFF, PNG or JPEG).</v>
+        <v>Assembled {n} channels.</v>
       </c>
       <c r="B254" t="str">
-        <v>Inga av dessa ser ut som bilder (TIFF, PNG eller JPEG).</v>
+        <v>Monterade {n} kanaler.</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>Cancel</v>
+        <v>None of those look like images (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B255" t="str">
-        <v>Avbryt</v>
+        <v>Inga av dessa ser ut som bilder (TIFF, PNG eller JPEG).</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>{n} file(s) not loaded</v>
+        <v>Cancel</v>
       </c>
       <c r="B256" t="str">
-        <v>{n} fil(er) inte inlästa</v>
+        <v>Avbryt</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>These files are not ICC profiles, so they were not added to the pool:</v>
+        <v>{n} file(s) not loaded</v>
       </c>
       <c r="B257" t="str">
-        <v>De här filerna är inte ICC-profiler och lades därför inte till i poolen:</v>
+        <v>{n} fil(er) inte inlästa</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>OK</v>
+        <v>These files are not ICC profiles, so they were not added to the pool:</v>
       </c>
       <c r="B258" t="str">
-        <v>OK</v>
+        <v>De här filerna är inte ICC-profiler och lades därför inte till i poolen:</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>OK</v>
       </c>
       <c r="B259" t="str">
-        <v>Släpp en ICC-profil här</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>or</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B260" t="str">
-        <v>eller</v>
+        <v>Släpp en ICC-profil här</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>Choose file</v>
+        <v>or</v>
       </c>
       <c r="B261" t="str">
-        <v>Välj fil</v>
+        <v>eller</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>.icc and .icm files</v>
+        <v>Choose file</v>
       </c>
       <c r="B262" t="str">
-        <v>.icc- och .icm-filer</v>
+        <v>Välj fil</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>Header</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B263" t="str">
-        <v>Rubrik</v>
+        <v>.icc- och .icm-filer</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>Tags</v>
+        <v>Header</v>
       </c>
       <c r="B264" t="str">
-        <v>Taggar</v>
+        <v>Rubrik</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>Validation</v>
+        <v>Tags</v>
       </c>
       <c r="B265" t="str">
-        <v>Validering</v>
+        <v>Taggar</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>Analysis</v>
+        <v>Validation</v>
       </c>
       <c r="B266" t="str">
-        <v>Analys</v>
+        <v>Validering</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>Analysis</v>
       </c>
       <c r="B267" t="str">
-        <v>Bläckning av neutralaxeln</v>
+        <v>Analys</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B268" t="str">
-        <v>Färgmängd längs neutralaxeln (a*=b*=0) när ljusheten går från vitt (L*=100) till svart (L*=0).</v>
+        <v>Bläckning av neutralaxeln</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B269" t="str">
-        <v>Bläckning av neutralaxeln är endast tillgänglig för utdataprofiler (skrivare).</v>
+        <v>Färgmängd längs neutralaxeln (a*=b*=0) när ljusheten går från vitt (L*=100) till svart (L*=0).</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B270" t="str">
-        <v>Den här profilen har ingen B2A-tabell (PCS→enhet) att sampla.</v>
+        <v>Bläckning av neutralaxeln är endast tillgänglig för utdataprofiler (skrivare).</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>Rendering intent</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B271" t="str">
-        <v>Renderingsavsikt</v>
+        <v>Den här profilen har ingen B2A-tabell (PCS→enhet) att sampla.</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>% ink</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B272" t="str">
-        <v>% färg</v>
+        <v>Renderingsavsikt</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>L* out (tone)</v>
+        <v>% ink</v>
       </c>
       <c r="B273" t="str">
-        <v>L* ut (ton)</v>
+        <v>% färg</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>Δa*b*</v>
+        <v>L* out (tone)</v>
       </c>
       <c r="B274" t="str">
-        <v>Δa*b*</v>
+        <v>L* ut (ton)</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>Extrema Colorimetry</v>
+        <v>Δa*b*</v>
       </c>
       <c r="B275" t="str">
-        <v>Kolorimetri för ytterlägen</v>
+        <v>Δa*b*</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>The ends of the profile’s reproduction range: substrate white, the darkest black it will print, the ink that black costs, and where each hue reaches its most saturated point.</v>
+        <v>Extrema Colorimetry</v>
       </c>
       <c r="B276" t="str">
-        <v>Ytterlägena i profilens återgivningsomfång: substratets vithet, det mörkaste svart den trycker, bläcket som det svarta kostar och var varje nyans når sin mest mättade punkt.</v>
+        <v>Kolorimetri för ytterlägen</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>White point is the colour of zero colorant — bare substrate. Black point is found by pushing PCS black (L*=0, a*=b*=0) through the selected B2A table to get the inking the profile chooses for black, then reading that inking back through A2B1. Total area coverage (TAC) is the sum of that inking. Absolute colorimetry shows the substrate’s own colour; relative re-references it to a perfect white.</v>
+        <v>The ends of the profile’s reproduction range: substrate white, the darkest black it will print, the ink that black costs, and where each hue reaches its most saturated point.</v>
       </c>
       <c r="B277" t="str">
-        <v>Vitpunkten är färgen vid noll färgmedel — det bara substratet. Svartpunkten tas fram genom att föra PCS-svart (L*=0, a*=b*=0) genom den valda B2A-tabellen för att få den färgmängd profilen väljer för svart, och sedan läsa tillbaka den färgmängden via A2B1. Den totala färgmängden (TAC) är summan av den färgmängden. Absolut kolorimetri visar substratets egen färg; relativ refererar om den till ett perfekt vitt.</v>
+        <v>Ytterlägena i profilens återgivningsomfång: substratets vithet, det mörkaste svart den trycker, bläcket som det svarta kostar och var varje nyans når sin mest mättade punkt.</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>Relative</v>
+        <v>White point is the colour of zero colorant — bare substrate. Black point is found by pushing PCS black (L*=0, a*=b*=0) through the selected B2A table to get the inking the profile chooses for black, then reading that inking back through A2B1. Total area coverage (TAC) is the sum of that inking. Absolute colorimetry shows the substrate’s own colour; relative re-references it to a perfect white.</v>
       </c>
       <c r="B278" t="str">
-        <v>Relativ</v>
+        <v>Vitpunkten är färgen vid noll färgmedel — det bara substratet. Svartpunkten tas fram genom att föra PCS-svart (L*=0, a*=b*=0) genom den valda B2A-tabellen för att få den färgmängd profilen väljer för svart, och sedan läsa tillbaka den färgmängden via A2B1. Den totala färgmängden (TAC) är summan av den färgmängden. Absolut kolorimetri visar substratets egen färg; relativ refererar om den till ett perfekt vitt.</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>Absolute</v>
+        <v>Relative</v>
       </c>
       <c r="B279" t="str">
-        <v>Absolut</v>
+        <v>Relativ</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>White point</v>
+        <v>Absolute</v>
       </c>
       <c r="B280" t="str">
-        <v>Vitpunkt</v>
+        <v>Absolut</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>Black point</v>
+        <v>White point</v>
       </c>
       <c r="B281" t="str">
-        <v>Svartpunkt</v>
+        <v>Vitpunkt</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>Inking at black point</v>
+        <v>Black point</v>
       </c>
       <c r="B282" t="str">
-        <v>Färgmängd vid svartpunkten</v>
+        <v>Svartpunkt</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>TAC</v>
+        <v>Inking at black point</v>
       </c>
       <c r="B283" t="str">
-        <v>TAC</v>
+        <v>Färgmängd vid svartpunkten</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>This profile has no media white point tag, so absolute colorimetry is unavailable.</v>
+        <v>TAC</v>
       </c>
       <c r="B284" t="str">
-        <v>Den här profilen saknar tagg för mediets vitpunkt, så absolut kolorimetri är inte tillgänglig.</v>
+        <v>TAC</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>Extrema colorimetry is only available for output (printer) profiles — it assumes zero colorant means bare substrate.</v>
+        <v>This profile has no media white point tag, so absolute colorimetry is unavailable.</v>
       </c>
       <c r="B285" t="str">
-        <v>Kolorimetri för ytterlägen är endast tillgänglig för utdataprofiler (skrivare) — den förutsätter att noll färgmedel betyder bart substrat.</v>
+        <v>Den här profilen saknar tagg för mediets vitpunkt, så absolut kolorimetri är inte tillgänglig.</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>Full tone vs maximum chroma</v>
+        <v>Extrema colorimetry is only available for output (printer) profiles — it assumes zero colorant means bare substrate.</v>
       </c>
       <c r="B286" t="str">
-        <v>Fullton mot maximal kroma</v>
+        <v>Kolorimetri för ytterlägen är endast tillgänglig för utdataprofiler (skrivare) — den förutsätter att noll färgmedel betyder bart substrat.</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>Where each ink corner lands, and the most chromatic point on the way there. Measured through A2B1, so these rows do not change with the rendering intent above. On a well-behaved profile the two rows match; if maximum chroma arrives before full tone, the extra ink past that point is only darkening.</v>
+        <v>Full tone vs maximum chroma</v>
       </c>
       <c r="B287" t="str">
-        <v>Var varje bläckhörn hamnar, och den mest kromatiska punkten på vägen dit. Mätt via A2B1, så dessa rader ändras inte med renderingsavsikten ovan. I en välartad profil sammanfaller de två raderna; om maximal kroma nås före fullton gör bläcket efter den punkten bara mörkare.</v>
+        <v>Fullton mot maximal kroma</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>Hue</v>
+        <v>Where each ink corner lands, and the most chromatic point on the way there. Measured through A2B1, so these rows do not change with the rendering intent above. On a well-behaved profile the two rows match; if maximum chroma arrives before full tone, the extra ink past that point is only darkening.</v>
       </c>
       <c r="B288" t="str">
-        <v>Nyans</v>
+        <v>Var varje bläckhörn hamnar, och den mest kromatiska punkten på vägen dit. Mätt via A2B1, så dessa rader ändras inte med renderingsavsikten ovan. I en välartad profil sammanfaller de två raderna; om maximal kroma nås före fullton gör bläcket efter den punkten bara mörkare.</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>Full tone</v>
+        <v>Hue</v>
       </c>
       <c r="B289" t="str">
-        <v>Fullton</v>
+        <v>Nyans</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>Max C*</v>
+        <v>Full tone</v>
       </c>
       <c r="B290" t="str">
-        <v>Max C*</v>
+        <v>Fullton</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>At ink</v>
+        <v>Max C*</v>
       </c>
       <c r="B291" t="str">
-        <v>Vid färgmängd</v>
+        <v>Max C*</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>Maximum chroma is reached before full tone — ink past this point only darkens.</v>
+        <v>At ink</v>
       </c>
       <c r="B292" t="str">
-        <v>Maximal kroma nås före fullton — bläck efter denna punkt gör bara mörkare.</v>
+        <v>Vid färgmängd</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>Ink Usage in Shadows</v>
+        <v>Maximum chroma is reached before full tone — ink past this point only darkens.</v>
       </c>
       <c r="B293" t="str">
-        <v>Bläckförbrukning i skuggor</v>
+        <v>Maximal kroma nås före fullton — bläck efter denna punkt gör bara mörkare.</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>Four straight paths across the a*b* plane at one constant, deliberately dark lightness, run through the selected B2A table. Every sample shares the same L*, so any abrupt step or reversal in a colorant comes from hue and chroma handling alone — the signature of a shadow gamut-mapping artefact.</v>
+        <v>Ink Usage in Shadows</v>
       </c>
       <c r="B294" t="str">
-        <v>Fyra raka banor genom a*b*-planet vid en konstant, medvetet mörk ljushet, förda genom den valda B2A-tabellen. Alla sampel har samma L*, så varje abrupt steg eller omkastning i ett färgmedel kommer enbart från hanteringen av nyans och kroma — signaturen för en gamutmappningsartefakt i skuggorna.</v>
+        <v>Bläckförbrukning i skuggor</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>Ink usage in shadows is only available for output (printer) profiles.</v>
+        <v>Four straight paths across the a*b* plane at one constant, deliberately dark lightness, run through the selected B2A table. Every sample shares the same L*, so any abrupt step or reversal in a colorant comes from hue and chroma handling alone — the signature of a shadow gamut-mapping artefact.</v>
       </c>
       <c r="B295" t="str">
-        <v>Bläckförbrukning i skuggor är endast tillgänglig för utdataprofiler (skrivare).</v>
+        <v>Fyra raka banor genom a*b*-planet vid en konstant, medvetet mörk ljushet, förda genom den valda B2A-tabellen. Alla sampel har samma L*, så varje abrupt steg eller omkastning i ett färgmedel kommer enbart från hanteringen av nyans och kroma — signaturen för en gamutmappningsartefakt i skuggorna.</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>Constant L* plane</v>
+        <v>Ink usage in shadows is only available for output (printer) profiles.</v>
       </c>
       <c r="B296" t="str">
-        <v>Plan med konstant L*</v>
+        <v>Bläckförbrukning i skuggor är endast tillgänglig för utdataprofiler (skrivare).</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>black-point compensated from</v>
+        <v>Constant L* plane</v>
       </c>
       <c r="B297" t="str">
-        <v>svartpunktskompenserad från</v>
+        <v>Plan med konstant L*</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>Position along path</v>
+        <v>black-point compensated from</v>
       </c>
       <c r="B298" t="str">
-        <v>Position längs banan</v>
+        <v>svartpunktskompenserad från</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>Path</v>
+        <v>Position along path</v>
       </c>
       <c r="B299" t="str">
-        <v>Bana</v>
+        <v>Position längs banan</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Primary-Inking Paths through Neutral</v>
+        <v>Path</v>
       </c>
       <c r="B300" t="str">
-        <v>Primärbläckvägar genom neutralt</v>
+        <v>Bana</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Three in-gamut paths — Cyan→Red, Magenta→Green, Yellow→Blue — each routed through the neutral axis at the midpoint lightness of its endpoints, run through the selected B2A table. Every sample is inside the gamut, so unlike the shadow paths any abrupt step or reversal in a colorant is a CLUT-smoothness defect rather than a gamut-mapping artefact.</v>
+        <v>Primary-Inking Paths through Neutral</v>
       </c>
       <c r="B301" t="str">
-        <v>Tre vägar inom färgomfånget — cyan→röd, magenta→grön, gul→blå — var och en genom neutralaxeln vid mittljusheten för sina ändpunkter, genom den valda B2A-tabellen. Varje sampel ligger inom omfånget, så till skillnad från skuggvägarna är varje plötsligt steg eller omkastning i ett färgämne ett CLUT-jämnhetsfel snarare än en omfångsmappningsartefakt.</v>
+        <v>Primärbläckvägar genom neutralt</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Primary-inking paths are only available for output (printer) profiles.</v>
+        <v>Three in-gamut paths — Cyan→Red, Magenta→Green, Yellow→Blue — each routed through the neutral axis at the midpoint lightness of its endpoints, run through the selected B2A table. Every sample is inside the gamut, so unlike the shadow paths any abrupt step or reversal in a colorant is a CLUT-smoothness defect rather than a gamut-mapping artefact.</v>
       </c>
       <c r="B302" t="str">
-        <v>Primärbläckvägar är endast tillgängliga för utdataprofiler (skrivare).</v>
+        <v>Tre vägar inom färgomfånget — cyan→röd, magenta→grön, gul→blå — var och en genom neutralaxeln vid mittljusheten för sina ändpunkter, genom den valda B2A-tabellen. Varje sampel ligger inom omfånget, så till skillnad från skuggvägarna är varje plötsligt steg eller omkastning i ett färgämne ett CLUT-jämnhetsfel snarare än en omfångsmappningsartefakt.</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Position along path (neutral at midpoint)</v>
+        <v>Primary-inking paths are only available for output (printer) profiles.</v>
       </c>
       <c r="B303" t="str">
-        <v>Position längs vägen (neutralt i mitten)</v>
+        <v>Primärbläckvägar är endast tillgängliga för utdataprofiler (skrivare).</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Black-point compensated for this intent.</v>
+        <v>Position along path (neutral at midpoint)</v>
       </c>
       <c r="B304" t="str">
-        <v>Svartpunktskompensation tillämpad för denna återgivning.</v>
+        <v>Position längs vägen (neutralt i mitten)</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Ink Usage Statistics</v>
+        <v>Black-point compensated for this intent.</v>
       </c>
       <c r="B305" t="str">
-        <v>Statistik för färgförbrukning</v>
+        <v>Svartpunktskompensation tillämpad för denna återgivning.</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>How much of each colorant the profile lays down, as a sum and as a share of the total — the ink-consumption signature of the separation.</v>
+        <v>Ink Usage Statistics</v>
       </c>
       <c r="B306" t="str">
-        <v>Hur mycket av varje färgämne profilen lägger på, som summa och som andel av totalen — separationens signatur för färgförbrukning.</v>
+        <v>Statistik för färgförbrukning</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>Ink usage statistics are only available for output (printer) profiles.</v>
+        <v>How much of each colorant the profile lays down, as a sum and as a share of the total — the ink-consumption signature of the separation.</v>
       </c>
       <c r="B307" t="str">
-        <v>Statistik för färgförbrukning är endast tillgänglig för utdataprofiler (skrivare).</v>
+        <v>Hur mycket av varje färgämne profilen lägger på, som summa och som andel av totalen — separationens signatur för färgförbrukning.</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Neutral axis</v>
+        <v>Ink usage statistics are only available for output (printer) profiles.</v>
       </c>
       <c r="B308" t="str">
-        <v>Neutralaxel</v>
+        <v>Statistik för färgförbrukning är endast tillgänglig för utdataprofiler (skrivare).</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>Mean coverage</v>
+        <v>Neutral axis</v>
       </c>
       <c r="B309" t="str">
-        <v>Medeltäckning</v>
+        <v>Neutralaxel</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>Share of ink</v>
+        <v>Mean coverage</v>
       </c>
       <c r="B310" t="str">
-        <v>Färgandel</v>
+        <v>Medeltäckning</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>Share of ink is the neutral-build fingerprint — each colorant’s fraction of the total ink laid down, independent of the sample count.</v>
+        <v>Share of ink</v>
       </c>
       <c r="B311" t="str">
-        <v>Färgandelen är fingeravtrycket för neutraluppbyggnaden — varje färgämnes andel av den totala pålagda färgen, oberoende av antalet sampel.</v>
+        <v>Färgandel</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>On &amp; in-gamut points</v>
+        <v>Share of ink is the neutral-build fingerprint — each colorant’s fraction of the total ink laid down, independent of the sample count.</v>
       </c>
       <c r="B312" t="str">
-        <v>Punkter inom omfånget</v>
+        <v>Färgandelen är fingeravtrycket för neutraluppbyggnaden — varje färgämnes andel av den totala pålagda färgen, oberoende av antalet sampel.</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>Ink usage across all in-gamut colours needs the B2A-direction gamut boundary, which is not yet built — pending.</v>
+        <v>On &amp; in-gamut points</v>
       </c>
       <c r="B313" t="str">
-        <v>Färgförbrukning över alla färger i omfånget kräver B2A-omfångsgränsen, som ännu inte är byggd — kommer senare.</v>
+        <v>Punkter inom omfånget</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>No colorant data to summarize.</v>
+        <v>Ink usage across all in-gamut colours needs the B2A-direction gamut boundary, which is not yet built — pending.</v>
       </c>
       <c r="B314" t="str">
-        <v>Inga färgämnesdata att sammanfatta.</v>
+        <v>Färgförbrukning över alla färger i omfånget kräver B2A-omfångsgränsen, som ännu inte är byggd — kommer senare.</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>Select a B2A (PCS→device) table below to also see a grayscale ink-coverage image for each colorant.</v>
+        <v>No colorant data to summarize.</v>
       </c>
       <c r="B315" t="str">
-        <v>Välj en B2A-tabell (PCS→enhet) nedan för att även visa en gråskalebild av färgtäckningen för varje färgämne.</v>
+        <v>Inga färgämnesdata att sammanfatta.</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>Ink coverage of each colorant across the same lattice (darker = more ink).</v>
+        <v>Select a B2A (PCS→device) table below to also see a grayscale ink-coverage image for each colorant.</v>
       </c>
       <c r="B316" t="str">
-        <v>Färgtäckning för varje färgämne över samma gitter (mörkare = mer färg).</v>
+        <v>Välj en B2A-tabell (PCS→enhet) nedan för att även visa en gråskalebild av färgtäckningen för varje färgämne.</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>Cyan</v>
+        <v>Ink coverage of each colorant across the same lattice (darker = more ink).</v>
       </c>
       <c r="B317" t="str">
-        <v>Cyan</v>
+        <v>Färgtäckning för varje färgämne över samma gitter (mörkare = mer färg).</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>Magenta</v>
+        <v>Cyan</v>
       </c>
       <c r="B318" t="str">
-        <v>Magenta</v>
+        <v>Cyan</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>Yellow</v>
+        <v>Magenta</v>
       </c>
       <c r="B319" t="str">
-        <v>Gul</v>
+        <v>Magenta</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>Red</v>
+        <v>Yellow</v>
       </c>
       <c r="B320" t="str">
-        <v>Röd</v>
+        <v>Gul</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>Green</v>
+        <v>Red</v>
       </c>
       <c r="B321" t="str">
-        <v>Grön</v>
+        <v>Röd</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>Blue</v>
+        <v>Green</v>
       </c>
       <c r="B322" t="str">
-        <v>Blå</v>
+        <v>Grön</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>Black</v>
+        <v>Blue</v>
       </c>
       <c r="B323" t="str">
-        <v>Svart</v>
+        <v>Blå</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>Perceptual</v>
+        <v>Black</v>
       </c>
       <c r="B324" t="str">
-        <v>Perceptuell</v>
+        <v>Svart</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Perceptual</v>
       </c>
       <c r="B325" t="str">
-        <v>Relativ kolorimetrisk</v>
+        <v>Perceptuell</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>Saturation</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B326" t="str">
-        <v>Mättnad</v>
+        <v>Relativ kolorimetrisk</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>Saturation</v>
       </c>
       <c r="B327" t="str">
-        <v>Absolut kolorimetrisk</v>
+        <v>Mättnad</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>Profile Statistics</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B328" t="str">
-        <v>Profilstatistik</v>
+        <v>Absolut kolorimetrisk</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B329" t="str">
-        <v>Profilövergripande mått per renderingsavsikt: gamutvolymen som omsluts av enhet→PCS-transformen (ΔE*ab³) och B2A-rundturens noggrannhet — ΔE*ab för en Lab → enhet → Lab-rundtur genom profilen.</v>
+        <v>Profilstatistik</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B330" t="str">
-        <v>Inga enhet↔PCS-CLUT:ar i den här profilen — profilstatistiken gäller inte (t.ex. en matris/TRC-skärmprofil).</v>
+        <v>Profilövergripande mått per renderingsavsikt: gamutvolymen som omsluts av enhet→PCS-transformen (ΔE*ab³) och B2A-rundturens noggrannhet — ΔE*ab för en Lab → enhet → Lab-rundtur genom profilen.</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>Rendering intent</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B331" t="str">
-        <v>Renderingsavsikt</v>
+        <v>Inga enhet↔PCS-CLUT:ar i den här profilen — profilstatistiken gäller inte (t.ex. en matris/TRC-skärmprofil).</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B332" t="str">
-        <v>Gamutvolym (ΔE³)</v>
+        <v>Renderingsavsikt</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>Round-trip ΔE</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B333" t="str">
-        <v>Rundtur-ΔE</v>
+        <v>Gamutvolym (ΔE³)</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B334" t="str">
-        <v>Gamytens gräns kollapsade eller var mestadels odefinierad, så denna gamutvolym är otillförlitlig.</v>
+        <v>Rundtur-ΔE</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>mean</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B335" t="str">
-        <v>medel</v>
+        <v>Gamytens gräns kollapsade eller var mestadels odefinierad, så denna gamutvolym är otillförlitlig.</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>P90</v>
+        <v>mean</v>
       </c>
       <c r="B336" t="str">
-        <v>P90</v>
+        <v>medel</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>max</v>
+        <v>P90</v>
       </c>
       <c r="B337" t="str">
-        <v>max</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>Analysing…</v>
+        <v>max</v>
       </c>
       <c r="B338" t="str">
-        <v>Analyserar…</v>
+        <v>max</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>Analysis</v>
+        <v>Analysing…</v>
       </c>
       <c r="B339" t="str">
-        <v>Analys</v>
+        <v>Analyserar…</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Analysis</v>
       </c>
       <c r="B340" t="str">
-        <v>Kvalitetsanalyser för hela profilen, härledda från enhet→PCS-transformen.</v>
+        <v>Analys</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>Plot</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B341" t="str">
-        <v>Diagram</v>
+        <v>Kvalitetsanalyser för hela profilen, härledda från enhet→PCS-transformen.</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>Raw Output</v>
+        <v>Plot</v>
       </c>
       <c r="B342" t="str">
-        <v>Rådata</v>
+        <v>Diagram</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>XML</v>
+        <v>Raw Output</v>
       </c>
       <c r="B343" t="str">
-        <v>XML</v>
+        <v>Rådata</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
       <c r="B344" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>Curves</v>
+        <v>JSON</v>
       </c>
       <c r="B345" t="str">
-        <v>Kurvor</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>Input curves</v>
+        <v>Curves</v>
       </c>
       <c r="B346" t="str">
-        <v>Ingångskurvor</v>
+        <v>Kurvor</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>Output curves</v>
+        <v>Input curves</v>
       </c>
       <c r="B347" t="str">
-        <v>Utgångskurvor</v>
+        <v>Ingångskurvor</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>CLUT image</v>
+        <v>Output curves</v>
       </c>
       <c r="B348" t="str">
-        <v>CLUT-bild</v>
+        <v>Utgångskurvor</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>Gamut image</v>
+        <v>CLUT image</v>
       </c>
       <c r="B349" t="str">
-        <v>Gamut-bild</v>
+        <v>CLUT-bild</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>Chromaticity</v>
+        <v>Gamut image</v>
       </c>
       <c r="B350" t="str">
-        <v>Kromaticitet</v>
+        <v>Gamut-bild</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>Scatter plot</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B351" t="str">
-        <v>Spridningsdiagram</v>
+        <v>Kromaticitet</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>Tone response curve</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B352" t="str">
-        <v>Tonkurva</v>
+        <v>Spridningsdiagram</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>Curve table</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B353" t="str">
-        <v>Kurvtabell</v>
+        <v>Tonkurva</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>Tables</v>
+        <v>Curve table</v>
       </c>
       <c r="B354" t="str">
-        <v>Tabeller</v>
+        <v>Kurvtabell</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>Data</v>
+        <v>Tables</v>
       </c>
       <c r="B355" t="str">
-        <v>Data</v>
+        <v>Tabeller</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>Evaluate</v>
+        <v>Data</v>
       </c>
       <c r="B356" t="str">
-        <v>Utvärdera</v>
+        <v>Data</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>Loading…</v>
+        <v>Evaluate</v>
       </c>
       <c r="B357" t="str">
-        <v>Läser in…</v>
+        <v>Utvärdera</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>Input</v>
+        <v>Loading…</v>
       </c>
       <c r="B358" t="str">
-        <v>Ingång</v>
+        <v>Läser in…</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>Output</v>
+        <v>Input</v>
       </c>
       <c r="B359" t="str">
-        <v>Utgång</v>
+        <v>Ingång</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>Floating point</v>
+        <v>Output</v>
       </c>
       <c r="B360" t="str">
-        <v>Flyttal</v>
+        <v>Utgång</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>Grid point</v>
+        <v>Floating point</v>
       </c>
       <c r="B361" t="str">
-        <v>Rutnätspunkt</v>
+        <v>Flyttal</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>Normalized</v>
+        <v>Grid point</v>
       </c>
       <c r="B362" t="str">
-        <v>Normaliserad</v>
+        <v>Rutnätspunkt</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>Human</v>
+        <v>Normalized</v>
       </c>
       <c r="B363" t="str">
-        <v>Läsbar</v>
+        <v>Normaliserad</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>Device → PCS</v>
+        <v>Human</v>
       </c>
       <c r="B364" t="str">
-        <v>Enhet → PCS</v>
+        <v>Läsbar</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>PCS → Device</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B365" t="str">
-        <v>PCS → Enhet</v>
+        <v>Enhet → PCS</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>No CLUT grid</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B366" t="str">
-        <v>Inget CLUT-rutnät</v>
+        <v>PCS → Enhet</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>Loading…</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B367" t="str">
-        <v>Läser in…</v>
+        <v>Inget CLUT-rutnät</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Loading…</v>
       </c>
       <c r="B368" t="str">
-        <v>Neutral = inom gamut · röd = utanför gamut</v>
+        <v>Läser in…</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B369" t="str">
-        <v>Ogiltig profil-URL:</v>
+        <v>Neutral = inom gamut · röd = utanför gamut</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B370" t="str">
-        <v>Det gick inte att hämta profilen från</v>
+        <v>Ogiltig profil-URL:</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B371" t="str">
-        <v>Läsa in en ICC-profil från denna externa webbplats?</v>
+        <v>Det gick inte att hämta profilen från</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B372" t="str">
-        <v>Laddar Profile Assessment WG-rapport…</v>
+        <v>Läsa in en ICC-profil från denna externa webbplats?</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B373" t="str">
-        <v>Kör Profile Assessment WG-kontroller…</v>
+        <v>Laddar Profile Assessment WG-rapport…</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B374" t="str">
-        <v>Profile Assessment WG-rapport</v>
+        <v>Kör Profile Assessment WG-kontroller…</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>Security</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B375" t="str">
-        <v>Säkerhet</v>
+        <v>Profile Assessment WG-rapport</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>Conformance</v>
+        <v>Security</v>
       </c>
       <c r="B376" t="str">
-        <v>Överensstämmelse</v>
+        <v>Säkerhet</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>Quality</v>
+        <v>Conformance</v>
       </c>
       <c r="B377" t="str">
-        <v>Kvalitet</v>
+        <v>Överensstämmelse</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>HDR</v>
+        <v>Quality</v>
       </c>
       <c r="B378" t="str">
-        <v>HDR</v>
+        <v>Kvalitet</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>Code points</v>
+        <v>HDR</v>
       </c>
       <c r="B379" t="str">
-        <v>Kodpunkter</v>
+        <v>HDR</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>Gain curve</v>
+        <v>Code points</v>
       </c>
       <c r="B380" t="str">
-        <v>Förstärkningskurva</v>
+        <v>Kodpunkter</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Environment</v>
+        <v>Gain curve</v>
       </c>
       <c r="B381" t="str">
-        <v>Miljö</v>
+        <v>Förstärkningskurva</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>Showing the SDR fallback</v>
+        <v>Environment</v>
       </c>
       <c r="B382" t="str">
-        <v>Visar SDR-reserven</v>
+        <v>Miljö</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>HDR Profile in the chain</v>
+        <v>Showing the SDR fallback</v>
       </c>
       <c r="B383" t="str">
-        <v>HDR-profil i kedjan</v>
+        <v>Visar SDR-reserven</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>Transforms through an HDR Profile use its AToB0Tag — the baked SDR rendering required by clause 8.10.6 — because clause 8.10.1 leaves it no TRC tags. The result is that fallback, not HDR behaviour.</v>
+        <v>HDR Profile in the chain</v>
       </c>
       <c r="B384" t="str">
-        <v>Transformationer genom en HDR-profil använder dess AToB0Tag — den fasta SDR-återgivning som klausul 8.10.6 kräver — eftersom klausul 8.10.1 inte lämnar den några TRC-taggar. Resultatet är den reserven, inte HDR-beteende.</v>
+        <v>HDR-profil i kedjan</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>These are HDR Profiles, which carry no TRC tags, so the gamut is built from the AToB0Tag — the baked SDR rendering clause 8.10.6 requires for consumers without HDR processing. It is not the profile’s HDR gamut, which cannot be drawn in a bounded PCS.</v>
+        <v>Transforms through an HDR Profile use its AToB0Tag — the baked SDR rendering required by clause 8.10.6 — because clause 8.10.1 leaves it no TRC tags. The result is that fallback, not HDR behaviour.</v>
       </c>
       <c r="B385" t="str">
-        <v>Detta är HDR-profiler utan TRC-taggar, så färgomfånget byggs från AToB0Tag — den fasta SDR-återgivning som klausul 8.10.6 kräver för konsumenter utan HDR-bearbetning. Det är inte profilens HDR-omfång, som inte kan ritas i ett begränsat PCS.</v>
+        <v>Transformationer genom en HDR-profil använder dess AToB0Tag — den fasta SDR-återgivning som klausul 8.10.6 kräver — eftersom klausul 8.10.1 inte lämnar den några TRC-taggar. Resultatet är den reserven, inte HDR-beteende.</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>Detecting…</v>
+        <v>These are HDR Profiles, which carry no TRC tags, so the gamut is built from the AToB0Tag — the baked SDR rendering clause 8.10.6 requires for consumers without HDR processing. It is not the profile’s HDR gamut, which cannot be drawn in a bounded PCS.</v>
       </c>
       <c r="B386" t="str">
-        <v>Identifierar…</v>
+        <v>Detta är HDR-profiler utan TRC-taggar, så färgomfånget byggs från AToB0Tag — den fasta SDR-återgivning som klausul 8.10.6 kräver för konsumenter utan HDR-bearbetning. Det är inte profilens HDR-omfång, som inte kan ritas i ett begränsat PCS.</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>Could not detect environment.</v>
+        <v>Detecting…</v>
       </c>
       <c r="B387" t="str">
-        <v>Kunde inte identifiera miljön.</v>
+        <v>Identifierar…</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>HDR display</v>
+        <v>Could not detect environment.</v>
       </c>
       <c r="B388" t="str">
-        <v>HDR-skärm</v>
+        <v>Kunde inte identifiera miljön.</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>Wide gamut</v>
+        <v>HDR display</v>
       </c>
       <c r="B389" t="str">
-        <v>Brett färgomfång</v>
+        <v>HDR-skärm</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>HDR canvas path</v>
+        <v>Wide gamut</v>
       </c>
       <c r="B390" t="str">
-        <v>HDR-canvasväg</v>
+        <v>Brett färgomfång</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>sRGB</v>
+        <v>HDR canvas path</v>
       </c>
       <c r="B391" t="str">
-        <v>sRGB</v>
+        <v>HDR-canvasväg</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>none</v>
+        <v>sRGB</v>
       </c>
       <c r="B392" t="str">
-        <v>ingen</v>
+        <v>sRGB</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>yes</v>
+        <v>none</v>
       </c>
       <c r="B393" t="str">
-        <v>ja</v>
+        <v>ingen</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>no</v>
+        <v>yes</v>
       </c>
       <c r="B394" t="str">
-        <v>nej</v>
+        <v>ja</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>not reported</v>
+        <v>no</v>
       </c>
       <c r="B395" t="str">
-        <v>ej rapporterat</v>
+        <v>nej</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Format</v>
+        <v>not reported</v>
       </c>
       <c r="B396" t="str">
-        <v>Format</v>
+        <v>ej rapporterat</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Inspect</v>
+        <v>Format</v>
       </c>
       <c r="B397" t="str">
-        <v>Granska</v>
+        <v>Format</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>Display</v>
+        <v>Inspect</v>
       </c>
       <c r="B398" t="str">
-        <v>Visa</v>
+        <v>Granska</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>HDR</v>
+        <v>Display</v>
       </c>
       <c r="B399" t="str">
-        <v>HDR</v>
+        <v>Visa</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>Read the embedded ICC profile — needs no codec</v>
+        <v>HDR</v>
       </c>
       <c r="B400" t="str">
-        <v>Läs den inbäddade ICC-profilen — kräver ingen codec</v>
+        <v>HDR</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>Show the pixels</v>
+        <v>Read the embedded ICC profile — needs no codec</v>
       </c>
       <c r="B401" t="str">
-        <v>Visa pixlarna</v>
+        <v>Läs den inbäddade ICC-profilen — kräver ingen codec</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>Render brighter-than-white</v>
+        <v>Show the pixels</v>
       </c>
       <c r="B402" t="str">
-        <v>Rendera ljusare än vitt</v>
+        <v>Visa pixlarna</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>Decoded by profiletool itself, so browser-independent</v>
+        <v>Render brighter-than-white</v>
       </c>
       <c r="B403" t="str">
-        <v>Avkodas av profiletool själv, alltså webbläsaroberoende</v>
+        <v>Rendera ljusare än vitt</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>This browser has not reported the display’s HDR headroom, only whether an HDR path exists.</v>
+        <v>Decoded by profiletool itself, so browser-independent</v>
       </c>
       <c r="B404" t="str">
-        <v>Den här webbläsaren har inte rapporterat skärmens HDR-utrymme, bara om en HDR-väg finns.</v>
+        <v>Avkodas av profiletool själv, alltså webbläsaroberoende</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>Browser flags</v>
+        <v>This browser has not reported the display’s HDR headroom, only whether an HDR path exists.</v>
       </c>
       <c r="B405" t="str">
-        <v>Webbläsarflaggor</v>
+        <v>Den här webbläsaren har inte rapporterat skärmens HDR-utrymme, bara om en HDR-väg finns.</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>on</v>
+        <v>Browser flags</v>
       </c>
       <c r="B406" t="str">
-        <v>på</v>
+        <v>Webbläsarflaggor</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>not enabled</v>
+        <v>on</v>
       </c>
       <c r="B407" t="str">
-        <v>inte aktiverad</v>
+        <v>på</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>cannot be detected here</v>
+        <v>not enabled</v>
       </c>
       <c r="B408" t="str">
-        <v>kan inte avgöras här</v>
+        <v>inte aktiverad</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>Needed for HDR rendering in this browser: it has no WebGPU, so the HDR canvas is the only route. Profile inspection works without it.</v>
+        <v>cannot be detected here</v>
       </c>
       <c r="B409" t="str">
-        <v>Krävs för HDR-rendering i den här webbläsaren: utan WebGPU är HDR-canvas den enda vägen. Profilgranskning fungerar utan.</v>
+        <v>kan inte avgöras här</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>Optional: HDR can render through WebGPU, but this adds the HDR canvas route and lets profiletool read the screen’s real HDR headroom.</v>
+        <v>Needed for HDR rendering in this browser: it has no WebGPU, so the HDR canvas is the only route. Profile inspection works without it.</v>
       </c>
       <c r="B410" t="str">
-        <v>Valfritt: HDR kan renderas via WebGPU, men detta lägger till HDR-canvasvägen och låter profiletool läsa skärmens verkliga HDR-utrymme.</v>
+        <v>Krävs för HDR-rendering i den här webbläsaren: utan WebGPU är HDR-canvas den enda vägen. Profilgranskning fungerar utan.</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>Web pages cannot open flag pages. Paste this into the address bar, set it to Enabled, then relaunch the browser.</v>
+        <v>Optional: HDR can render through WebGPU, but this adds the HDR canvas route and lets profiletool read the screen’s real HDR headroom.</v>
       </c>
       <c r="B411" t="str">
-        <v>Webbsidor kan inte öppna flaggsidor. Klistra in detta i adressfältet, välj Enabled och starta om webbläsaren.</v>
+        <v>Valfritt: HDR kan renderas via WebGPU, men detta lägger till HDR-canvasvägen och låter profiletool läsa skärmens verkliga HDR-utrymme.</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>Copy</v>
+        <v>Web pages cannot open flag pages. Paste this into the address bar, set it to Enabled, then relaunch the browser.</v>
       </c>
       <c r="B412" t="str">
-        <v>Kopiera</v>
+        <v>Webbsidor kan inte öppna flaggsidor. Klistra in detta i adressfältet, välj Enabled och starta om webbläsaren.</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>Copied</v>
+        <v>Copy</v>
       </c>
       <c r="B413" t="str">
-        <v>Kopierat</v>
+        <v>Kopiera</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>Copy failed — select the address and copy it.</v>
+        <v>Copied</v>
       </c>
       <c r="B414" t="str">
-        <v>Kopiering misslyckades — markera adressen och kopiera den.</v>
+        <v>Kopierat</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>Pixel ratio</v>
+        <v>Copy failed — select the address and copy it.</v>
       </c>
       <c r="B415" t="str">
-        <v>Pixelförhållande</v>
+        <v>Kopiering misslyckades — markera adressen och kopiera den.</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>Current monitor</v>
+        <v>Pixel ratio</v>
       </c>
       <c r="B416" t="str">
-        <v>Aktuell skärm</v>
+        <v>Pixelförhållande</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>unnamed</v>
+        <v>Current monitor</v>
       </c>
       <c r="B417" t="str">
-        <v>namnlös</v>
+        <v>Aktuell skärm</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>primary</v>
+        <v>unnamed</v>
       </c>
       <c r="B418" t="str">
-        <v>primär</v>
+        <v>namnlös</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>built-in</v>
+        <v>primary</v>
       </c>
       <c r="B419" t="str">
-        <v>inbyggd</v>
+        <v>primär</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>HDR headroom</v>
+        <v>built-in</v>
       </c>
       <c r="B420" t="str">
-        <v>HDR-utrymme</v>
+        <v>inbyggd</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>not exposed by this browser</v>
+        <v>HDR headroom</v>
       </c>
       <c r="B421" t="str">
-        <v>exponeras inte av den här webbläsaren</v>
+        <v>HDR-utrymme</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Chromium reports this in stops: log₂ of the display’s peak brightness ÷ its SDR white level. On Windows it refreshes only when Chrome re-reads the display — the window moves to another screen, or Chrome becomes the active app again — not when brightness changes.</v>
+        <v>not exposed by this browser</v>
       </c>
       <c r="B422" t="str">
-        <v>Chromium rapporterar detta i steg: log₂ av skärmens toppljusstyrka ÷ dess SDR-vitnivå. I Windows uppdateras det bara när Chrome läser om skärmen – fönstret flyttas till en annan skärm eller Chrome aktiveras igen – inte när ljusstyrkan ändras.</v>
+        <v>exponeras inte av den här webbläsaren</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>{stops} stops (≈{ratio}× SDR white)</v>
+        <v>Chromium reports this in stops: log₂ of the display’s peak brightness ÷ its SDR white level. On Windows it refreshes only when Chrome re-reads the display — the window moves to another screen, or Chrome becomes the active app again — not when brightness changes.</v>
       </c>
       <c r="B423" t="str">
-        <v>{stops} steg (≈{ratio}× SDR-vitt)</v>
+        <v>Chromium rapporterar detta i steg: log₂ av skärmens toppljusstyrka ÷ dess SDR-vitnivå. I Windows uppdateras det bara när Chrome läser om skärmen – fönstret flyttas till en annan skärm eller Chrome aktiveras igen – inte när ljusstyrkan ändras.</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>HDR</v>
+        <v>{stops} stops (≈{ratio}× SDR white)</v>
       </c>
       <c r="B424" t="str">
-        <v>HDR</v>
+        <v>{stops} steg (≈{ratio}× SDR-vitt)</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>Gain at a display headroom</v>
+        <v>HDR</v>
       </c>
       <c r="B425" t="str">
-        <v>Förstärkning vid ett skärmutrymme</v>
+        <v>HDR</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>View one HDR image on this display. Files the browser can decode are shown by the browser itself; OpenEXR and Radiance HDR are decoded and rendered by profiletool.</v>
+        <v>Gain at a display headroom</v>
       </c>
       <c r="B426" t="str">
-        <v>Visa en HDR-bild på den här skärmen. Filer som webbläsaren kan avkoda visas av webbläsaren själv; OpenEXR och Radiance HDR avkodas och återges av profiletool.</v>
+        <v>Förstärkning vid ett skärmutrymme</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>Drop an HDR image here, or click to choose one</v>
+        <v>View one HDR image on this display. Files the browser can decode are shown by the browser itself; OpenEXR and Radiance HDR are decoded and rendered by profiletool.</v>
       </c>
       <c r="B427" t="str">
-        <v>Släpp en HDR-bild här, eller klicka för att välja en</v>
+        <v>Visa en HDR-bild på den här skärmen. Filer som webbläsaren kan avkoda visas av webbläsaren själv; OpenEXR och Radiance HDR avkodas och återges av profiletool.</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (including gain-map JPEG), PNG — and HEIC and JPEG XL on Safari.</v>
+        <v>Drop an HDR image here, or click to choose one</v>
       </c>
       <c r="B428" t="str">
-        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (även JPEG med gain map), PNG – och HEIC och JPEG XL i Safari.</v>
+        <v>Släpp en HDR-bild här, eller klicka för att välja en</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>Choose another</v>
+        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (including gain-map JPEG), PNG — and HEIC and JPEG XL on Safari.</v>
       </c>
       <c r="B429" t="str">
-        <v>Välj en annan</v>
+        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (även JPEG med gain map), PNG – och HEIC och JPEG XL i Safari.</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>Clear</v>
+        <v>Choose another</v>
       </c>
       <c r="B430" t="str">
-        <v>Rensa</v>
+        <v>Välj en annan</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>Embedded ICC profile</v>
+        <v>Clear</v>
       </c>
       <c r="B431" t="str">
-        <v>Inbäddad ICC-profil</v>
+        <v>Rensa</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>none — OpenEXR states colour through chromaticities</v>
+        <v>Embedded ICC profile</v>
       </c>
       <c r="B432" t="str">
-        <v>ingen – OpenEXR anger färg genom kromaticiteter</v>
+        <v>Inbäddad ICC-profil</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>none — Radiance HDR states colour through its PRIMARIES header</v>
+        <v>none — OpenEXR states colour through chromaticities</v>
       </c>
       <c r="B433" t="str">
-        <v>ingen – Radiance HDR anger färg genom sin PRIMARIES-rubrik</v>
+        <v>ingen – OpenEXR anger färg genom kromaticiteter</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>checking…</v>
+        <v>none — Radiance HDR states colour through its PRIMARIES header</v>
       </c>
       <c r="B434" t="str">
-        <v>kontrollerar…</v>
+        <v>ingen – Radiance HDR anger färg genom sin PRIMARIES-rubrik</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>none</v>
+        <v>checking…</v>
       </c>
       <c r="B435" t="str">
-        <v>ingen</v>
+        <v>kontrollerar…</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Open in Profile tab</v>
+        <v>none</v>
       </c>
       <c r="B436" t="str">
-        <v>Öppna på fliken Profil</v>
+        <v>ingen</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>Gain map</v>
+        <v>Open in Profile tab</v>
       </c>
       <c r="B437" t="str">
-        <v>Förstärkningskarta</v>
+        <v>Öppna på fliken Profil</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>detected, not decoded</v>
+        <v>Gain map</v>
       </c>
       <c r="B438" t="str">
-        <v>hittad, inte avkodad</v>
+        <v>Förstärkningskarta</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>That is not an image. Load profiles through the Profiles pane.</v>
+        <v>detected, not decoded</v>
       </c>
       <c r="B439" t="str">
-        <v>Det är ingen bild. Läs in profiler via profilpanelen.</v>
+        <v>hittad, inte avkodad</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>Not an image format profiletool recognises.</v>
+        <v>That is not an image. Load profiles through the Profiles pane.</v>
       </c>
       <c r="B440" t="str">
-        <v>Inte ett bildformat som profiletool känner igen.</v>
+        <v>Det är ingen bild. Läs in profiler via profilpanelen.</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>TIFF pixels are not shown here yet: browsers do not decode TIFF, and how HDR is encoded in a 16-bit TIFF is still undecided (Phase 4.3). Its embedded profile can be inspected.</v>
+        <v>Not an image format profiletool recognises.</v>
       </c>
       <c r="B441" t="str">
-        <v>TIFF-pixlar visas inte här ännu: webbläsare avkodar inte TIFF, och hur HDR kodas i en 16-bitars TIFF är ännu inte bestämt (fas 4.3). Den inbäddade profilen kan granskas.</v>
+        <v>Inte ett bildformat som profiletool känner igen.</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>Cannot display this image here:</v>
+        <v>TIFF pixels are not shown here yet: browsers do not decode TIFF, and how HDR is encoded in a 16-bit TIFF is still undecided (Phase 4.3). Its embedded profile can be inspected.</v>
       </c>
       <c r="B442" t="str">
-        <v>Bilden kan inte visas här:</v>
+        <v>TIFF-pixlar visas inte här ännu: webbläsare avkodar inte TIFF, och hur HDR kodas i en 16-bitars TIFF är ännu inte bestämt (fas 4.3). Den inbäddade profilen kan granskas.</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>Its embedded profile can still be inspected.</v>
+        <v>Cannot display this image here:</v>
       </c>
       <c r="B443" t="str">
-        <v>Den inbäddade profilen kan ändå granskas.</v>
+        <v>Bilden kan inte visas här:</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>Shown by</v>
+        <v>Its embedded profile can still be inspected.</v>
       </c>
       <c r="B444" t="str">
-        <v>Visas av</v>
+        <v>Den inbäddade profilen kan ändå granskas.</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>the browser</v>
+        <v>Shown by</v>
       </c>
       <c r="B445" t="str">
-        <v>webbläsaren</v>
+        <v>Visas av</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>profiletool</v>
+        <v>the browser</v>
       </c>
       <c r="B446" t="str">
-        <v>profiletool</v>
+        <v>webbläsaren</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>HDR display</v>
+        <v>profiletool</v>
       </c>
       <c r="B447" t="str">
-        <v>HDR-skärm</v>
+        <v>profiletool</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Browsers ignore HDR that is signalled only by an embedded ICC profile, so this image may look dim and flat.</v>
+        <v>HDR display</v>
       </c>
       <c r="B448" t="str">
-        <v>Webbläsare ignorerar HDR som bara anges av en inbäddad ICC-profil, så bilden kan se matt och platt ut.</v>
+        <v>HDR-skärm</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>This browser cannot switch an image between SDR and HDR, so it is shown as the browser renders it.</v>
+        <v>Browsers ignore HDR that is signalled only by an embedded ICC profile, so this image may look dim and flat.</v>
       </c>
       <c r="B449" t="str">
-        <v>Den här webbläsaren kan inte växla en bild mellan SDR och HDR, så den visas som webbläsaren återger den.</v>
+        <v>Webbläsare ignorerar HDR som bara anges av en inbäddad ICC-profil, så bilden kan se matt och platt ut.</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>The browser could not decode this image.</v>
+        <v>This browser cannot switch an image between SDR and HDR, so it is shown as the browser renders it.</v>
       </c>
       <c r="B450" t="str">
-        <v>Webbläsaren kunde inte avkoda bilden.</v>
+        <v>Den här webbläsaren kan inte växla en bild mellan SDR och HDR, så den visas som webbläsaren återger den.</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>Output</v>
+        <v>The browser could not decode this image.</v>
       </c>
       <c r="B451" t="str">
-        <v>Utdata</v>
+        <v>Webbläsaren kunde inte avkoda bilden.</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>HDR canvas (float16)</v>
+        <v>Output</v>
       </c>
       <c r="B452" t="str">
-        <v>HDR-canvas (float16)</v>
+        <v>Utdata</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>WebGPU (extended range)</v>
+        <v>HDR canvas (float16)</v>
       </c>
       <c r="B453" t="str">
-        <v>WebGPU (utökat omfång)</v>
+        <v>HDR-canvas (float16)</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>SDR canvas (tone-mapped)</v>
+        <v>WebGPU (extended range)</v>
       </c>
       <c r="B454" t="str">
-        <v>SDR-canvas (tonmappad)</v>
+        <v>WebGPU (utökat omfång)</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>Size</v>
+        <v>SDR canvas (tone-mapped)</v>
       </c>
       <c r="B455" t="str">
-        <v>Storlek</v>
+        <v>SDR-canvas (tonmappad)</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>Brightest pixel</v>
+        <v>Size</v>
       </c>
       <c r="B456" t="str">
-        <v>Ljusaste pixel</v>
+        <v>Storlek</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>{n}× SDR white</v>
+        <v>Brightest pixel</v>
       </c>
       <c r="B457" t="str">
-        <v>{n}× SDR-vitt</v>
+        <v>Ljusaste pixel</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>Chromaticities</v>
+        <v>{n}× SDR white</v>
       </c>
       <c r="B458" t="str">
-        <v>Kromaticiteter</v>
+        <v>{n}× SDR-vitt</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>not stated — Rec. 709 assumed</v>
+        <v>Chromaticities</v>
       </c>
       <c r="B459" t="str">
-        <v>inte angivna – Rec. 709 antas</v>
+        <v>Kromaticiteter</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>{from} was not available here ({why}); using the next output.</v>
+        <v>not stated — Rec. 709 assumed</v>
       </c>
       <c r="B460" t="str">
-        <v>{from} är inte tillgängligt här ({why}); nästa utdata används.</v>
+        <v>inte angivna – Rec. 709 antas</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>This output cannot carry brighter-than-white values, so the tone-mapped SDR rendering is shown.</v>
+        <v>{from} was not available here ({why}); using the next output.</v>
       </c>
       <c r="B461" t="str">
-        <v>Den här utdatan kan inte bära värden ljusare än vitt, så den tonmappade SDR-återgivningen visas.</v>
+        <v>{from} är inte tillgängligt här ({why}); nästa utdata används.</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>Exposure</v>
+        <v>This output cannot carry brighter-than-white values, so the tone-mapped SDR rendering is shown.</v>
       </c>
       <c r="B462" t="str">
-        <v>Exponering</v>
+        <v>Den här utdatan kan inte bära värden ljusare än vitt, så den tonmappade SDR-återgivningen visas.</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>{n} stops</v>
+        <v>Exposure</v>
       </c>
       <c r="B463" t="str">
-        <v>{n} steg</v>
+        <v>Exponering</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>Could not decode:</v>
+        <v>{n} stops</v>
       </c>
       <c r="B464" t="str">
-        <v>Kunde inte avkoda:</v>
+        <v>{n} steg</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>This file is {size} MB; the HDR tab opens images up to {max} MB.</v>
+        <v>Could not decode:</v>
       </c>
       <c r="B465" t="str">
-        <v>Filen är {size} MB; HDR-fliken öppnar bilder upp till {max} MB.</v>
+        <v>Kunde inte avkoda:</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>Could not apply the profile:</v>
+        <v>This file is {size} MB; the HDR tab opens images up to {max} MB.</v>
       </c>
       <c r="B466" t="str">
-        <v>Kunde inte tillämpa profilen:</v>
+        <v>Filen är {size} MB; HDR-fliken öppnar bilder upp till {max} MB.</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>Could not draw the image:</v>
+        <v>Could not apply the profile:</v>
       </c>
       <c r="B467" t="str">
-        <v>Kunde inte rita bilden:</v>
+        <v>Kunde inte tillämpa profilen:</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>(these primaries do not define a colour space — ignored, Rec. 709 used)</v>
+        <v>Could not draw the image:</v>
       </c>
       <c r="B468" t="str">
-        <v>(dessa primärfärger definierar ingen färgrymd – ignoreras, Rec. 709 används)</v>
+        <v>Kunde inte rita bilden:</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>a JPEG XL profile is compressed inside the codestream, which profiletool does not decompress yet</v>
+        <v>(these primaries do not define a colour space — ignored, Rec. 709 used)</v>
       </c>
       <c r="B469" t="str">
-        <v>profilen i en JPEG XL är komprimerad i kodströmmen, som profiletool ännu inte packar upp</v>
+        <v>(dessa primärfärger definierar ingen färgrymd – ignoreras, Rec. 709 används)</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>Decoding…</v>
+        <v>a JPEG XL profile is compressed inside the codestream, which profiletool does not decompress yet</v>
       </c>
       <c r="B470" t="str">
-        <v>Avkodar…</v>
+        <v>profilen i en JPEG XL är komprimerad i kodströmmen, som profiletool ännu inte packar upp</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>Dynamic range</v>
+        <v>Decoding…</v>
       </c>
       <c r="B471" t="str">
-        <v>Dynamiskt omfång</v>
+        <v>Avkodar…</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>This browser offers only the two ends, not a blend.</v>
+        <v>Dynamic range</v>
       </c>
       <c r="B472" t="str">
-        <v>Den här webbläsaren erbjuder bara de två ändarna, ingen blandning.</v>
+        <v>Dynamiskt omfång</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>decoded by profiletool itself, so browser-independent</v>
+        <v>This browser offers only the two ends, not a blend.</v>
       </c>
       <c r="B473" t="str">
-        <v>avkodas av profiletool själv, så oberoende av webbläsaren</v>
+        <v>Den här webbläsaren erbjuder bara de två ändarna, ingen blandning.</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>this browser decodes it</v>
+        <v>decoded by profiletool itself, so browser-independent</v>
       </c>
       <c r="B474" t="str">
-        <v>den här webbläsaren avkodar det</v>
+        <v>avkodas av profiletool själv, så oberoende av webbläsaren</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>this browser does not decode it</v>
+        <v>this browser decodes it</v>
       </c>
       <c r="B475" t="str">
-        <v>den här webbläsaren avkodar det inte</v>
+        <v>den här webbläsaren avkodar det</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>HEIC display needs Safari or another WebKit browser — Chrome and Firefox decode HEIC on no platform, macOS included</v>
+        <v>this browser does not decode it</v>
       </c>
       <c r="B476" t="str">
-        <v>HEIC-visning kräver Safari eller en annan WebKit-webbläsare – Chrome och Firefox avkodar HEIC på ingen plattform, inte heller macOS</v>
+        <v>den här webbläsaren avkodar det inte</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>JPEG XL display needs Safari; other browsers have not shipped it</v>
+        <v>HEIC display needs Safari or another WebKit browser — Chrome and Firefox decode HEIC on no platform, macOS included</v>
       </c>
       <c r="B477" t="str">
-        <v>JPEG XL-visning kräver Safari; andra webbläsare har inte stöd än</v>
+        <v>HEIC-visning kräver Safari eller en annan WebKit-webbläsare – Chrome och Firefox avkodar HEIC på ingen plattform, inte heller macOS</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>deferred to a later release</v>
+        <v>JPEG XL display needs Safari; other browsers have not shipped it</v>
       </c>
       <c r="B478" t="str">
-        <v>uppskjutet till en senare version</v>
+        <v>JPEG XL-visning kräver Safari; andra webbläsare har inte stöd än</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>this display reports no HDR path, so HDR renders tone-mapped to SDR</v>
+        <v>deferred to a later release</v>
       </c>
       <c r="B479" t="str">
-        <v>skärmen rapporterar ingen HDR-väg, så HDR visas tonmappat som SDR</v>
+        <v>uppskjutet till en senare version</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>this browser exposes no HDR canvas path (needs float16 canvas or WebGPU)</v>
+        <v>this display reports no HDR path, so HDR renders tone-mapped to SDR</v>
       </c>
       <c r="B480" t="str">
-        <v>webbläsaren har ingen HDR-canvas (kräver float16-canvas eller WebGPU)</v>
+        <v>skärmen rapporterar ingen HDR-väg, så HDR visas tonmappat som SDR</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>Firefox renders no HDR images and reads no gain maps; HDR content is shown as SDR</v>
+        <v>this browser exposes no HDR canvas path (needs float16 canvas or WebGPU)</v>
       </c>
       <c r="B481" t="str">
-        <v>Firefox visar inga HDR-bilder och läser inga gain maps; HDR-innehåll visas som SDR</v>
+        <v>webbläsaren har ingen HDR-canvas (kräver float16-canvas eller WebGPU)</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>inspection needs a container parse, not a codec</v>
+        <v>Firefox renders no HDR images and reads no gain maps; HDR content is shown as SDR</v>
       </c>
       <c r="B482" t="str">
-        <v>granskning kräver bara tolkning av behållaren, ingen codec</v>
+        <v>Firefox visar inga HDR-bilder och läser inga gain maps; HDR-innehåll visas som SDR</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>HDR display and an HDR canvas path are both available</v>
+        <v>inspection needs a container parse, not a codec</v>
       </c>
       <c r="B483" t="str">
-        <v>både HDR-skärm och HDR-canvas finns</v>
+        <v>granskning kräver bara tolkning av behållaren, ingen codec</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>unknown format</v>
+        <v>HDR display and an HDR canvas path are both available</v>
       </c>
       <c r="B484" t="str">
-        <v>okänt format</v>
+        <v>både HDR-skärm och HDR-canvas finns</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>{browser} on {os}</v>
+        <v>unknown format</v>
       </c>
       <c r="B485" t="str">
-        <v>{browser} på {os}</v>
+        <v>okänt format</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>{name} · HDR display detected</v>
+        <v>{browser} on {os}</v>
       </c>
       <c r="B486" t="str">
-        <v>{name} · HDR-skärm hittad</v>
+        <v>{browser} på {os}</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>{name} · SDR display</v>
+        <v>{name} · HDR display detected</v>
       </c>
       <c r="B487" t="str">
-        <v>{name} · SDR-skärm</v>
+        <v>{name} · HDR-skärm hittad</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>WebGPU applied tone mapping “{mode}”, so output is clamped to SDR</v>
+        <v>{name} · SDR display</v>
       </c>
       <c r="B488" t="str">
-        <v>WebGPU tillämpade tonmappning ”{mode}”, så utdata begränsas till SDR</v>
+        <v>{name} · SDR-skärm</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>This browser does not report the WebGPU tone mapping it applied, so HDR output is unconfirmed</v>
+        <v>WebGPU applied tone mapping “{mode}”, so output is clamped to SDR</v>
       </c>
       <c r="B489" t="str">
-        <v>Webbläsaren rapporterar inte vilken WebGPU-tonmappning som tillämpades, så HDR-utdata är obekräftad</v>
+        <v>WebGPU tillämpade tonmappning ”{mode}”, så utdata begränsas till SDR</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>Display peak</v>
+        <v>This browser does not report the WebGPU tone mapping it applied, so HDR output is unconfirmed</v>
       </c>
       <c r="B490" t="str">
-        <v>Skärmens topp</v>
+        <v>Webbläsaren rapporterar inte vilken WebGPU-tonmappning som tillämpades, så HDR-utdata är obekräftad</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>{r}× SDR white ({n} stops)</v>
+        <v>Display peak</v>
       </c>
       <c r="B491" t="str">
-        <v>{r}× SDR-vitt ({n} steg)</v>
+        <v>Skärmens topp</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>1× — SDR display</v>
+        <v>{r}× SDR white ({n} stops)</v>
       </c>
       <c r="B492" t="str">
-        <v>1× – SDR-skärm</v>
+        <v>{r}× SDR-vitt ({n} steg)</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>not known</v>
+        <v>1× — SDR display</v>
       </c>
       <c r="B493" t="str">
-        <v>okänd</v>
+        <v>1× – SDR-skärm</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>This display reports no HDR, so the browser shows this image in SDR at either end.</v>
+        <v>not known</v>
       </c>
       <c r="B494" t="str">
-        <v>Skärmen rapporterar ingen HDR, så webbläsaren visar bilden i SDR i båda ändarna.</v>
+        <v>okänd</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>This display reports no HDR, so everything brighter than SDR white clips. Fit to display shows the tone-mapped rendering instead.</v>
+        <v>This display reports no HDR, so the browser shows this image in SDR at either end.</v>
       </c>
       <c r="B495" t="str">
-        <v>Skärmen rapporterar ingen HDR, så allt ljusare än SDR-vitt klipps. ”Anpassa till skärm” visar i stället den tonmappade återgivningen.</v>
+        <v>Skärmen rapporterar ingen HDR, så webbläsaren visar bilden i SDR i båda ändarna.</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>This image asks for {img}× SDR white, but this display shows up to {disp}×, so brighter values clip. Fit to display rolls them off into the display’s peak instead.</v>
+        <v>This display reports no HDR, so everything brighter than SDR white clips. Fit to display shows the tone-mapped rendering instead.</v>
       </c>
       <c r="B496" t="str">
-        <v>Bilden kräver {img}× SDR-vitt, men skärmen visar bara upp till {disp}×, så ljusare värden klipps. ”Anpassa till skärm” rundar i stället av dem mot skärmens topp.</v>
+        <v>Skärmen rapporterar ingen HDR, så allt ljusare än SDR-vitt klipps. ”Anpassa till skärm” visar i stället den tonmappade återgivningen.</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>Fit to display</v>
+        <v>This image asks for {img}× SDR white, but this display shows up to {disp}×, so brighter values clip. Fit to display rolls them off into the display’s peak instead.</v>
       </c>
       <c r="B497" t="str">
-        <v>Anpassa till skärm</v>
+        <v>Bilden kräver {img}× SDR-vitt, men skärmen visar bara upp till {disp}×, så ljusare värden klipps. ”Anpassa till skärm” rundar i stället av dem mot skärmens topp.</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Image details</v>
+        <v>Fit to display</v>
       </c>
       <c r="B498" t="str">
-        <v>Bilddetaljer</v>
+        <v>Anpassa till skärm</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>not available — the browser renders this image and cannot cap it at a set peak</v>
+        <v>Image details</v>
       </c>
       <c r="B499" t="str">
-        <v>inte tillgänglig – webbläsaren återger bilden och kan inte begränsa den till en viss topp</v>
+        <v>Bilddetaljer</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>not available — this output shows nothing above SDR white</v>
+        <v>not available — the browser renders this image and cannot cap it at a set peak</v>
       </c>
       <c r="B500" t="str">
-        <v>inte tillgänglig – den här utgången visar inget över SDR-vitt</v>
+        <v>inte tillgänglig – webbläsaren återger bilden och kan inte begränsa den till en viss topp</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>not available — this display’s peak is not known</v>
+        <v>not available — this output shows nothing above SDR white</v>
       </c>
       <c r="B501" t="str">
-        <v>inte tillgänglig – skärmens toppluminans är okänd</v>
+        <v>inte tillgänglig – den här utgången visar inget över SDR-vitt</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>Zoom in</v>
+        <v>not available — this display’s peak is not known</v>
       </c>
       <c r="B502" t="str">
-        <v>Zooma in</v>
+        <v>inte tillgänglig – skärmens toppluminans är okänd</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>Zoom out</v>
+        <v>Zoom in</v>
       </c>
       <c r="B503" t="str">
-        <v>Zooma ut</v>
+        <v>Zooma in</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>Fit image</v>
+        <v>Zoom out</v>
       </c>
       <c r="B504" t="str">
-        <v>Anpassa bilden</v>
+        <v>Zooma ut</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>Actual pixels (1:1)</v>
+        <v>Fit image</v>
       </c>
       <c r="B505" t="str">
-        <v>Faktiska pixlar (1:1)</v>
+        <v>Anpassa bilden</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>Drag to pan · Ctrl+wheel to zoom · double-click to reset</v>
+        <v>Actual pixels (1:1)</v>
       </c>
       <c r="B506" t="str">
-        <v>Dra för att panorera · Ctrl+hjul för att zooma · dubbelklicka för att återställa</v>
+        <v>Faktiska pixlar (1:1)</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>Drag to resize the image area; double-click to restore the default size</v>
+        <v>Drag to pan · Ctrl+wheel to zoom · double-click to reset</v>
       </c>
       <c r="B507" t="str">
-        <v>Dra för att ändra bildytans storlek; dubbelklicka för standardstorlek</v>
+        <v>Dra för att panorera · Ctrl+hjul för att zooma · dubbelklicka för att återställa</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>Image view</v>
+        <v>Drag to resize the image area; double-click to restore the default size</v>
       </c>
       <c r="B508" t="str">
-        <v>Bildvy</v>
+        <v>Dra för att ändra bildytans storlek; dubbelklicka för standardstorlek</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
+        <v>Image view</v>
       </c>
       <c r="B509" t="str">
-        <v>Begränsar ljusstyrkan till den topp skärmen rapporterar. I Windows kan värdet släpa efter ändringar av ljusstyrkan.</v>
+        <v>Bildvy</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>no limit</v>
+        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
       </c>
       <c r="B510" t="str">
-        <v>ingen gräns</v>
+        <v>Begränsar ljusstyrkan till den topp skärmen rapporterar. I Windows kan värdet släpa efter ändringar av ljusstyrkan.</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>limit {n} stops ({r}×)</v>
+        <v>no limit</v>
       </c>
       <c r="B511" t="str">
-        <v>gräns {n} steg ({r}×)</v>
+        <v>ingen gräns</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>SDR white</v>
+        <v>limit {n} stops ({r}×)</v>
       </c>
       <c r="B512" t="str">
-        <v>SDR-vitt</v>
+        <v>gräns {n} steg ({r}×)</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
+        <v>SDR white</v>
       </c>
       <c r="B513" t="str">
-        <v>Vanligt SDR-vitt för jämförelse. På en HDR-skärm ser HDR-högdagrar ljusare ut än detta.</v>
+        <v>SDR-vitt</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>SDR white patch</v>
+        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
       </c>
       <c r="B514" t="str">
-        <v>SDR-vit ruta</v>
+        <v>Vanligt SDR-vitt för jämförelse. På en HDR-skärm ser HDR-högdagrar ljusare ut än detta.</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Drag to move it; double-click to put it back beside the image.</v>
+        <v>SDR white patch</v>
       </c>
       <c r="B515" t="str">
-        <v>Dra för att flytta den; dubbelklicka för att sätta tillbaka den bredvid bilden.</v>
+        <v>SDR-vit ruta</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>Assign profile</v>
+        <v>Drag to move it; double-click to put it back beside the image.</v>
       </c>
       <c r="B516" t="str">
-        <v>Tilldela profil</v>
+        <v>Dra för att flytta den; dubbelklicka för att sätta tillbaka den bredvid bilden.</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>None — use what the file signals</v>
+        <v>Assign profile</v>
       </c>
       <c r="B517" t="str">
-        <v>Ingen – det filen anger</v>
+        <v>Tilldela profil</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>Embedded profile ({n} B)</v>
+        <v>None — use what the file signals</v>
       </c>
       <c r="B518" t="str">
-        <v>Inbäddad profil ({n} B)</v>
+        <v>Ingen – det filen anger</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>HDR Profiles in the pool</v>
+        <v>Embedded profile ({n} B)</v>
       </c>
       <c r="B519" t="str">
-        <v>HDR-profiler i poolen</v>
+        <v>Inbäddad profil ({n} B)</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>Profile</v>
+        <v>HDR Profiles in the pool</v>
       </c>
       <c r="B520" t="str">
-        <v>Profil</v>
+        <v>HDR-profiler i poolen</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>embedded profile</v>
+        <v>Profile</v>
       </c>
       <c r="B521" t="str">
-        <v>inbäddad profil</v>
+        <v>Profil</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>Colour engine path</v>
+        <v>embedded profile</v>
       </c>
       <c r="B522" t="str">
-        <v>Färgmotorns väg</v>
+        <v>inbäddad profil</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>HDR path, gain curve applied</v>
+        <v>Colour engine path</v>
       </c>
       <c r="B523" t="str">
-        <v>HDR-väg, förstärkningskurva tillämpad</v>
+        <v>Färgmotorns väg</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>HDR path, no gain curve</v>
+        <v>HDR path, gain curve applied</v>
       </c>
       <c r="B524" t="str">
-        <v>HDR-väg, ingen förstärkningskurva</v>
+        <v>HDR-väg, förstärkningskurva tillämpad</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>Baked AToB0 — not the HDR path</v>
+        <v>HDR path, no gain curve</v>
       </c>
       <c r="B525" t="str">
-        <v>Förberäknad AToB0 – inte HDR-vägen</v>
+        <v>HDR-väg, ingen förstärkningskurva</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>Transfer</v>
+        <v>Baked AToB0 — not the HDR path</v>
       </c>
       <c r="B526" t="str">
-        <v>Överföring</v>
+        <v>Förberäknad AToB0 – inte HDR-vägen</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>HDR reference white</v>
+        <v>Transfer</v>
       </c>
       <c r="B527" t="str">
-        <v>HDR-referensvitt</v>
+        <v>Överföring</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>Linear values</v>
+        <v>HDR reference white</v>
       </c>
       <c r="B528" t="str">
-        <v>Linjära värden</v>
+        <v>HDR-referensvitt</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>File 1.0 = HDR reference white</v>
+        <v>Linear values</v>
       </c>
       <c r="B529" t="str">
-        <v>Fil 1,0 = HDR-referensvitt</v>
+        <v>Linjära värden</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>File 1.0 = 1 cd/m² (ICC.1 clause 8.10.2 a)</v>
+        <v>File 1.0 = HDR reference white</v>
       </c>
       <c r="B530" t="str">
-        <v>Fil 1,0 = 1 cd/m² (ICC.1 avsnitt 8.10.2 a)</v>
+        <v>Fil 1,0 = HDR-referensvitt</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>OpenEXR and Radiance HDR files conventionally put SDR white at 1.0, while an ICC Linear transfer reads 1.0 as 1 cd/m². The default scales the file so its 1.0 lands on the profile’s HDR reference white.</v>
+        <v>File 1.0 = 1 cd/m² (ICC.1 clause 8.10.2 a)</v>
       </c>
       <c r="B531" t="str">
-        <v>OpenEXR- och Radiance HDR-filer lägger enligt konvention SDR-vitt på 1,0, medan en linjär ICC-överföring läser 1,0 som 1 cd/m². Som standard skalas filen så att dess 1,0 hamnar på profilens HDR-referensvitt.</v>
+        <v>Fil 1,0 = 1 cd/m² (ICC.1 avsnitt 8.10.2 a)</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Input scale</v>
+        <v>OpenEXR and Radiance HDR files conventionally put SDR white at 1.0, while an ICC Linear transfer reads 1.0 as 1 cd/m². The default scales the file so its 1.0 lands on the profile’s HDR reference white.</v>
       </c>
       <c r="B532" t="str">
-        <v>Indataskala</v>
+        <v>OpenEXR- och Radiance HDR-filer lägger enligt konvention SDR-vitt på 1,0, medan en linjär ICC-överföring läser 1,0 som 1 cd/m². Som standard skalas filen så att dess 1,0 hamnar på profilens HDR-referensvitt.</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>×{w} — file 1.0 = reference white</v>
+        <v>Input scale</v>
       </c>
       <c r="B533" t="str">
-        <v>×{w} – fil 1,0 = referensvitt</v>
+        <v>Indataskala</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>none — file 1.0 = 1 cd/m²</v>
+        <v>×{w} — file 1.0 = reference white</v>
       </c>
       <c r="B534" t="str">
-        <v>ingen – fil 1,0 = 1 cd/m²</v>
+        <v>×{w} – fil 1,0 = referensvitt</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>Target headroom</v>
+        <v>none — file 1.0 = 1 cd/m²</v>
       </c>
       <c r="B535" t="str">
-        <v>Målutrymme</v>
+        <v>ingen – fil 1,0 = 1 cd/m²</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>{r}× reference white ({n} stops)</v>
+        <v>Target headroom</v>
       </c>
       <c r="B536" t="str">
-        <v>{r}× referensvitt ({n} steg)</v>
+        <v>Målutrymme</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>Tone mapping</v>
+        <v>{r}× reference white ({n} stops)</v>
       </c>
       <c r="B537" t="str">
-        <v>Tonmappning</v>
+        <v>{r}× referensvitt ({n} steg)</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>Auto (clause 8.10.3 ranking)</v>
+        <v>Tone mapping</v>
       </c>
       <c r="B538" t="str">
-        <v>Auto (rangordning enligt 8.10.3)</v>
+        <v>Tonmappning</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>Gain curve (HAGC)</v>
+        <v>Auto (clause 8.10.3 ranking)</v>
       </c>
       <c r="B539" t="str">
-        <v>Förstärkningskurva (HAGC)</v>
+        <v>Auto (rangordning enligt 8.10.3)</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>Baked SDR fallback (AToB0)</v>
+        <v>Gain curve (HAGC)</v>
       </c>
       <c r="B540" t="str">
-        <v>Förberäknad SDR-reserv (AToB0)</v>
+        <v>Förstärkningskurva (HAGC)</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>Off — as a pre-amendment CMM</v>
+        <v>Baked SDR fallback (AToB0)</v>
       </c>
       <c r="B541" t="str">
-        <v>Av – som en CMM före tillägget</v>
+        <v>Förberäknad SDR-reserv (AToB0)</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>Applying the profile…</v>
+        <v>Off — as a pre-amendment CMM</v>
       </c>
       <c r="B542" t="str">
-        <v>Tillämpar profilen…</v>
+        <v>Av – som en CMM före tillägget</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
+        <v>Applying the profile…</v>
       </c>
       <c r="B543" t="str">
-        <v>{format} innehåller linjärt ljus och kräver därför en profil med överföringen Linear (8).</v>
+        <v>Tillämpar profilen…</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>Assigning a profile needs a 3-channel RGB image.</v>
+        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
       </c>
       <c r="B544" t="str">
-        <v>Att tilldela en profil kräver en RGB-bild med 3 kanaler.</v>
+        <v>{format} innehåller linjärt ljus och kräver därför en profil med överföringen Linear (8).</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>To interpret its values, assign a profile above.</v>
+        <v>Assigning a profile needs a 3-channel RGB image.</v>
       </c>
       <c r="B545" t="str">
-        <v>Tilldela en profil ovan för att tolka dess värden.</v>
+        <v>Att tilldela en profil kräver en RGB-bild med 3 kanaler.</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>HDR Profiles</v>
+        <v>To interpret its values, assign a profile above.</v>
       </c>
       <c r="B546" t="str">
-        <v>HDR-profiler</v>
+        <v>Tilldela en profil ovan för att tolka dess värden.</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>Linear transfer</v>
+        <v>HDR Profiles</v>
       </c>
       <c r="B547" t="str">
-        <v>Linjär överföring</v>
+        <v>HDR-profiler</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>Non-linear transfer (PQ, HLG)</v>
+        <v>Linear transfer</v>
       </c>
       <c r="B548" t="str">
-        <v>Icke-linjär överföring (PQ, HLG)</v>
+        <v>Linjär överföring</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>HDR Profiles — Linear transfer</v>
+        <v>Non-linear transfer (PQ, HLG)</v>
       </c>
       <c r="B549" t="str">
-        <v>HDR-profiler – linjär överföring</v>
+        <v>Icke-linjär överföring (PQ, HLG)</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>HDR Profiles — PQ / HLG transfer</v>
+        <v>HDR Profiles — Linear transfer</v>
       </c>
       <c r="B550" t="str">
-        <v>HDR-profiler – PQ/HLG-överföring</v>
+        <v>HDR-profiler – linjär överföring</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
+        <v>HDR Profiles — PQ / HLG transfer</v>
       </c>
       <c r="B551" t="str">
-        <v>{format} innehåller linjärt ljus, så bara HDR-profiler med linjär överföring kan tilldelas.</v>
+        <v>HDR-profiler – PQ/HLG-överföring</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
+        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
       </c>
       <c r="B552" t="str">
-        <v>{n} PQ/HLG-HDR-profil(er) i poolen erbjuds inte – profilpanelen listar dem under HDR-profiler › Icke-linjär överföring.</v>
+        <v>{format} innehåller linjärt ljus, så bara HDR-profiler med linjär överföring kan tilldelas.</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
+        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
       </c>
       <c r="B553" t="str">
-        <v>Det finns ännu ingen HDR-profil med linjär överföring i poolen; profilpanelen grupperar HDR-profiler efter överföring.</v>
+        <v>{n} PQ/HLG-HDR-profil(er) i poolen erbjuds inte – profilpanelen listar dem under HDR-profiler › Icke-linjär överföring.</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
       </c>
       <c r="B554" t="str">
-        <v>IccProfLib avböjer att tillämpa den här förstärkningskurvan: {why}. En CMM faller tillbaka på nästa tonmappningsbeskrivning (avsnitt 8.10.3).</v>
+        <v>Det finns ännu ingen HDR-profil med linjär överföring i poolen; profilpanelen grupperar HDR-profiler efter överföring.</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Display headroom</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B555" t="str">
-        <v>Skärmutrymme</v>
+        <v>IccProfLib avböjer att tillämpa den här förstärkningskurvan: {why}. En CMM faller tillbaka på nästa tonmappningsbeskrivning (avsnitt 8.10.3).</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>Display headroom</v>
       </c>
       <c r="B556" t="str">
-        <v>{n} steg (≈{r}× referensvitt)</v>
+        <v>Skärmutrymme</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Baseline</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B557" t="str">
-        <v>Bas</v>
+        <v>{n} steg (≈{r}× referensvitt)</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Preview through the colour engine</v>
+        <v>Baseline</v>
       </c>
       <c r="B558" t="str">
-        <v>Förhandsvisning genom färgmotorn</v>
+        <v>Bas</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>As authored (baseline {h} stops, no gain)</v>
+        <v>Preview through the colour engine</v>
       </c>
       <c r="B559" t="str">
-        <v>Som skapad (bas {h} steg, ingen förstärkning)</v>
+        <v>Förhandsvisning genom färgmotorn</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Tone-mapped for {h} stops</v>
+        <v>As authored (baseline {h} stops, no gain)</v>
       </c>
       <c r="B560" t="str">
-        <v>Tonmappad för {h} steg</v>
+        <v>Som skapad (bas {h} steg, ingen förstärkning)</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
+        <v>Tone-mapped for {h} stops</v>
       </c>
       <c r="B561" t="str">
-        <v>Samma testpixlar ({transfer}-signal som stiger från vänster till höger: grått, sedan R, G, B, Y, C, M) genom IccProfLibs HDR-transform. Båda remsorna begränsas till {r}× HDR-referensvitt, som en skärm med {h} stegs headroom skulle visa dem: där den övre remsan klipps platt rullar förstärkningskurvan av högdagrarna.</v>
+        <v>Tonmappad för {h} steg</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>reference white</v>
+        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
       </c>
       <c r="B562" t="str">
-        <v>referensvitt</v>
+        <v>Samma testpixlar ({transfer}-signal som stiger från vänster till höger: grått, sedan R, G, B, Y, C, M) genom IccProfLibs HDR-transform. Båda remsorna begränsas till {r}× HDR-referensvitt, som en skärm med {h} stegs headroom skulle visa dem: där den övre remsan klipps platt rullar förstärkningskurvan av högdagrarna.</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>display peak</v>
+        <v>reference white</v>
       </c>
       <c r="B563" t="str">
-        <v>skärmens topp</v>
+        <v>referensvitt</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>Preview unavailable: {why}</v>
+        <v>display peak</v>
       </c>
       <c r="B564" t="str">
-        <v>Förhandsvisning inte tillgänglig: {why}</v>
+        <v>skärmens topp</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>the colour engine did not take the HDR path for this profile</v>
+        <v>Preview unavailable: {why}</v>
       </c>
       <c r="B565" t="str">
-        <v>färgmotorn tog inte HDR-vägen för den här profilen</v>
+        <v>Förhandsvisning inte tillgänglig: {why}</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Gain across every headroom</v>
+        <v>the colour engine did not take the HDR path for this profile</v>
       </c>
       <c r="B566" t="str">
-        <v>Förstärkning över alla headroom</v>
+        <v>färgmotorn tog inte HDR-vägen för den här profilen</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
+        <v>Gain across every headroom</v>
       </c>
       <c r="B567" t="str">
-        <v>Förstärkning för en grå insignal vid varje skärm-headroom: blått komprimerar, rött expanderar, vitt lämnar den oförändrad. Prickade linjer markerar kurvorna i taggen, den heldragna basen och den bärnstensfärgade reglaget; den streckade diagonalen är där insignalen når skärmens topp. Klicka för att flytta reglaget.</v>
+        <v>Förstärkning över alla headroom</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Input (stops relative to HDR reference white)</v>
+        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
       </c>
       <c r="B568" t="str">
-        <v>Insignal (steg relativt HDR-referensvitt)</v>
+        <v>Förstärkning för en grå insignal vid varje skärm-headroom: blått komprimerar, rött expanderar, vitt lämnar den oförändrad. Prickade linjer markerar kurvorna i taggen, den heldragna basen och den bärnstensfärgade reglaget; den streckade diagonalen är där insignalen når skärmens topp. Klicka för att flytta reglaget.</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Display headroom (stops)</v>
+        <v>Input (stops relative to HDR reference white)</v>
       </c>
       <c r="B569" t="str">
-        <v>Skärm-headroom (steg)</v>
+        <v>Insignal (steg relativt HDR-referensvitt)</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Gain (stops)</v>
+        <v>Display headroom (stops)</v>
       </c>
       <c r="B570" t="str">
-        <v>Förstärkning (steg)</v>
+        <v>Skärm-headroom (steg)</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Curve in the tag</v>
+        <v>Gain (stops)</v>
       </c>
       <c r="B571" t="str">
-        <v>Kurva i taggen</v>
+        <v>Förstärkning (steg)</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>Baseline</v>
+        <v>Curve in the tag</v>
       </c>
       <c r="B572" t="str">
-        <v>Bas</v>
+        <v>Kurva i taggen</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>Slider</v>
+        <v>Baseline</v>
       </c>
       <c r="B573" t="str">
-        <v>Reglage</v>
+        <v>Bas</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Input = display peak</v>
+        <v>Slider</v>
       </c>
       <c r="B574" t="str">
-        <v>Insignal = skärmens topp</v>
+        <v>Reglage</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>Grey tone curves by headroom</v>
+        <v>Input = display peak</v>
       </c>
       <c r="B575" t="str">
-        <v>Grå tonkurvor per headroom</v>
+        <v>Insignal = skärmens topp</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
+        <v>Grey tone curves by headroom</v>
       </c>
       <c r="B576" t="str">
-        <v>Den grå tonkurvan vid varje headroom som taggen lagrar, färgad från lågt (blått) till högt (rött), med reglagets kurva i bärnsten. Båda axlarna är i steg, så diagonalen betyder ingen förändring.</v>
+        <v>Grå tonkurvor per headroom</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Output (stops relative to HDR reference white)</v>
+        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
       </c>
       <c r="B577" t="str">
-        <v>Utsignal (steg relativt HDR-referensvitt)</v>
+        <v>Den grå tonkurvan vid varje headroom som taggen lagrar, färgad från lågt (blått) till högt (rött), med reglagets kurva i bärnsten. Båda axlarna är i steg, så diagonalen betyder ingen förändring.</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>{h} stops</v>
+        <v>Output (stops relative to HDR reference white)</v>
       </c>
       <c r="B578" t="str">
-        <v>{h} steg</v>
+        <v>Utsignal (steg relativt HDR-referensvitt)</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>{h} stops (baseline)</v>
+        <v>{h} stops</v>
       </c>
       <c r="B579" t="str">
-        <v>{h} steg (bas)</v>
+        <v>{h} steg</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>At {h} stops (slider)</v>
+        <v>{h} stops (baseline)</v>
       </c>
       <c r="B580" t="str">
-        <v>Vid {h} steg (reglage)</v>
+        <v>{h} steg (bas)</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>At {h} stops (slider)</v>
       </c>
       <c r="B581" t="str">
-        <v>Kurvor i taggen, efter utrymme: {list} steg. Bas {b} steg, HDR-referensvitt {w} cd/m².</v>
+        <v>Vid {h} steg (reglage)</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B582" t="str">
-        <v>Det här utrymmet ligger utanför taggens kurvor, så närmaste kurva används oförändrad – biblioteket extrapolerar inte bortom dem.</v>
+        <v>Kurvor i taggen, efter utrymme: {list} steg. Bas {b} steg, HDR-referensvitt {w} cd/m².</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B583" t="str">
-        <v>Vissa lutningar är härledda (PCHIP) och inte lagrade i taggen. Härledningen rekonstruerar ett SMPTE-avsnitt, så betrakta de kurvornas form som preliminär.</v>
+        <v>Det här utrymmet ligger utanför taggens kurvor, så närmaste kurva används oförändrad – biblioteket extrapolerar inte bortom dem.</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B584" t="str">
-        <v>Taggen begär tonmappning mot referensvitt, så dess kurvor konstrueras av biblioteket i stället för att läsas från filen (en konstruktion från ett kommittéutkast).</v>
+        <v>Vissa lutningar är härledda (PCHIP) och inte lagrade i taggen. Härledningen rekonstruerar ett SMPTE-avsnitt, så betrakta de kurvornas form som preliminär.</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B585" t="str">
-        <v>Inga alternativa bilder: taggen begär ingen tonmappning, bara en begränsning till skärmens färgvolym.</v>
+        <v>Taggen begär tonmappning mot referensvitt, så dess kurvor konstrueras av biblioteket i stället för att läsas från filen (en konstruktion från ett kommittéutkast).</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B586" t="str">
-        <v>De två kurvorna som blandas vid detta utrymme blandar färgkanalerna olika, så det finns ingen enskild förstärkningskurva att rita. Tonkurvan nedan är ändå exakt.</v>
+        <v>Inga alternativa bilder: taggen begär ingen tonmappning, bara en begränsning till skärmens färgvolym.</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B587" t="str">
-        <v>Kurva vid {h} steg (ingen förstärkning)</v>
+        <v>De två kurvorna som blandas vid detta utrymme blandar färgkanalerna olika, så det finns ingen enskild förstärkningskurva att rita. Tonkurvan nedan är ändå exakt.</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Curve at {h} stops</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B588" t="str">
-        <v>Kurva vid {h} steg</v>
+        <v>Kurva vid {h} steg (ingen förstärkning)</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B589" t="str">
-        <v>Tillämpad vid {h} steg</v>
+        <v>Kurva vid {h} steg</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B590" t="str">
-        <v>Förstärkning vid detta utrymme</v>
+        <v>Tillämpad vid {h} steg</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B591" t="str">
-        <v>Blandad indata (linjär, 1,0 = HDR-referensvitt)</v>
+        <v>Förstärkning vid detta utrymme</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B592" t="str">
-        <v>Förstärkning (log2-steg)</v>
+        <v>Blandad indata (linjär, 1,0 = HDR-referensvitt)</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B593" t="str">
-        <v>Gråskalans tonkurva vid detta utrymme</v>
+        <v>Förstärkning (log2-steg)</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B594" t="str">
-        <v>Indata (× HDR-referensvitt)</v>
+        <v>Gråskalans tonkurva vid detta utrymme</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B595" t="str">
-        <v>Utdata (× HDR-referensvitt)</v>
+        <v>Indata (× HDR-referensvitt)</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>No change</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B596" t="str">
-        <v>Ingen ändring</v>
+        <v>Utdata (× HDR-referensvitt)</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>No change</v>
       </c>
       <c r="B597" t="str">
-        <v>Skärmens topp vid {h} steg</v>
+        <v>Ingen ändring</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Output at {h} stops</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B598" t="str">
-        <v>Utdata vid {h} steg</v>
+        <v>Skärmens topp vid {h} steg</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B599" t="str">
-        <v>HDR, färgomfång och pixelförhållande uppdateras när fönstret flyttas till en skärm där de skiljer sig.</v>
+        <v>Utdata vid {h} steg</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>Identify displays</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B600" t="str">
-        <v>Identifiera skärmar</v>
+        <v>HDR, färgomfång och pixelförhållande uppdateras när fönstret flyttas till en skärm där de skiljer sig.</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Identify displays</v>
       </c>
       <c r="B601" t="str">
-        <v>Ber om tillåtelse att se vilken skärm fönstret ligger på, så att panelen även uppdateras mellan likadana skärmar och visar HDR-utrymme där webbläsaren exponerar det.</v>
+        <v>Identifiera skärmar</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B602" t="str">
-        <v>Följer vilken skärm fönstret ligger på.</v>
+        <v>Ber om tillåtelse att se vilken skärm fönstret ligger på, så att panelen även uppdateras mellan likadana skärmar och visar HDR-utrymme där webbläsaren exponerar det.</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B603" t="str">
-        <v>Tillåtelse att identifiera skärmar nekades. Den kan ändras i webbplatsens inställningar.</v>
+        <v>Följer vilken skärm fönstret ligger på.</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B604" t="str">
-        <v>Den här webbläsaren kan inte identifiera skärmar; bara den automatiska uppdateringen ovan gäller.</v>
+        <v>Tillåtelse att identifiera skärmar nekades. Den kan ändras i webbplatsens inställningar.</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>Could not identify displays.</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B605" t="str">
-        <v>Kunde inte identifiera skärmar.</v>
+        <v>Den här webbläsaren kan inte identifiera skärmar; bara den automatiska uppdateringen ovan gäller.</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Display events</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B606" t="str">
-        <v>Skärmhändelser</v>
+        <v>Kunde inte identifiera skärmar.</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Display events</v>
       </c>
       <c r="B607" t="str">
-        <v>Inga händelser än. Dra fönstret till en annan skärm.</v>
+        <v>Skärmhändelser</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Colour primaries</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B608" t="str">
-        <v>Färgprimärer</v>
+        <v>Inga händelser än. Dra fönstret till en annan skärm.</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>Transfer characteristics</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B609" t="str">
-        <v>Överföringsfunktion</v>
+        <v>Färgprimärer</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>Matrix coefficients</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B610" t="str">
-        <v>Matriskoefficienter</v>
+        <v>Överföringsfunktion</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>Video full-range flag</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B611" t="str">
-        <v>Flagga för fullt videoomfång</v>
+        <v>Matriskoefficienter</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>Full range</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B612" t="str">
-        <v>Fullt omfång</v>
+        <v>Flagga för fullt videoomfång</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>Narrow range</v>
+        <v>Full range</v>
       </c>
       <c r="B613" t="str">
-        <v>Begränsat omfång</v>
+        <v>Fullt omfång</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Narrow range</v>
       </c>
       <c r="B614" t="str">
-        <v>inte tilldelad av ITU-T H.273</v>
+        <v>Begränsat omfång</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B615" t="str">
-        <v>Färgprimärer 2 (Ospecificerad) hänvisar till profilen själv — primärerna hämtas från färgämnestaggarna och inte från den här taggen.</v>
+        <v>inte tilldelad av ITU-T H.273</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B616" t="str">
-        <v>De fyra reserverade byten i den här taggen är inte alla noll.</v>
+        <v>Färgprimärer 2 (Ospecificerad) hänvisar till profilen själv — primärerna hämtas från färgämnestaggarna och inte från den här taggen.</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>REPORT</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B617" t="str">
-        <v>RAPPORT</v>
+        <v>De fyra reserverade byten i den här taggen är inte alla noll.</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>FAIL</v>
+        <v>REPORT</v>
       </c>
       <c r="B618" t="str">
-        <v>UNDERKÄND</v>
+        <v>RAPPORT</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>checks</v>
+        <v>FAIL</v>
       </c>
       <c r="B619" t="str">
-        <v>kontroller</v>
+        <v>UNDERKÄND</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>checks</v>
       </c>
       <c r="B620" t="str">
-        <v>Genererad av iccPawgReport (iccDEV) · checklista från ICC Profile Assessment Working Group.</v>
+        <v>kontroller</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B621" t="str">
-        <v>ICC-profilverktyg · drivs av IccProfLib</v>
+        <v>Genererad av iccPawgReport (iccDEV) · checklista från ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>ICC Profile Tool</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B622" t="str">
-        <v>ICC-profilverktyg</v>
+        <v>ICC-profilverktyg · drivs av IccProfLib</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>Powered by {lib}</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B623" t="str">
-        <v>Drivs av {lib}</v>
+        <v>ICC-profilverktyg</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>Subscribe</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B624" t="str">
-        <v>Prenumerera</v>
+        <v>Drivs av {lib}</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Subscribe</v>
       </c>
       <c r="B625" t="str">
-        <v>Få besked om nya profiletool-versioner</v>
+        <v>Prenumerera</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>Get notified about new releases</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B626" t="str">
-        <v>Få besked om nya versioner</v>
+        <v>Få besked om nya profiletool-versioner</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>Close</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B627" t="str">
-        <v>Stäng</v>
+        <v>Få besked om nya versioner</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Close</v>
       </c>
       <c r="B628" t="str">
-        <v>Vi mejlar dig när en ny större eller mindre version av profiletool släpps. Patchversioner hoppas över. Din adress granskas manuellt innan den läggs till.</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>Email address</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B629" t="str">
-        <v>E-postadress</v>
+        <v>Vi mejlar dig när en ny större eller mindre version av profiletool släpps. Patchversioner hoppas över. Din adress granskas manuellt innan den läggs till.</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>you@example.com</v>
+        <v>Email address</v>
       </c>
       <c r="B630" t="str">
-        <v>du@exempel.com</v>
+        <v>E-postadress</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>How will you use profiletool?</v>
+        <v>you@example.com</v>
       </c>
       <c r="B631" t="str">
-        <v>Hur kommer du att använda profiletool?</v>
+        <v>du@exempel.com</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>(optional)</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B632" t="str">
-        <v>(valfritt)</v>
+        <v>Hur kommer du att använda profiletool?</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>(optional)</v>
       </c>
       <c r="B633" t="str">
-        <v>t.ex. utvärdera ICC-profiler för tryckkalibrering</v>
+        <v>(valfritt)</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B634" t="str">
-        <v>Jag godkänner att ta emot e-post om profiletool-versioner. Jag kan avsluta prenumerationen när som helst.</v>
+        <v>t.ex. utvärdera ICC-profiler för tryckkalibrering</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>Cancel</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B635" t="str">
-        <v>Avbryt</v>
+        <v>Jag godkänner att ta emot e-post om profiletool-versioner. Jag kan avsluta prenumerationen när som helst.</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>Subscribe</v>
+        <v>Cancel</v>
       </c>
       <c r="B636" t="str">
-        <v>Prenumerera</v>
+        <v>Avbryt</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B637" t="str">
-        <v>Tack — vi hör av oss.</v>
+        <v>Prenumerera</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B638" t="str">
-        <v>När du har godkänts får du ett välkomstmejl. Därefter hör du bara från oss när en ny version av profiletool släpps.</v>
+        <v>Tack — vi hör av oss.</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>Close</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B639" t="str">
-        <v>Stäng</v>
+        <v>När du har godkänts får du ett välkomstmejl. Därefter hör du bara från oss när en ny version av profiletool släpps.</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>Privacy notice</v>
+        <v>Close</v>
       </c>
       <c r="B640" t="str">
-        <v>Integritetsmeddelande</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B641" t="str">
-        <v>Ange en giltig e-postadress.</v>
+        <v>Integritetsmeddelande</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B642" t="str">
-        <v>För många förfrågningar. Försök igen senare.</v>
+        <v>Ange en giltig e-postadress.</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B643" t="str">
-        <v>Kontrollera formuläret och försök igen.</v>
+        <v>För många förfrågningar. Försök igen senare.</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B644" t="str">
-        <v>Det gick inte att skicka din förfrågan. Försök igen.</v>
+        <v>Kontrollera formuläret och försök igen.</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B645" t="str">
-        <v>Nätverksfel. Försök igen.</v>
+        <v>Det gick inte att skicka din förfrågan. Försök igen.</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>Error:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B646" t="str">
-        <v>Fel:</v>
+        <v>Nätverksfel. Försök igen.</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>Convert to XML</v>
+        <v>Error:</v>
       </c>
       <c r="B647" t="str">
-        <v>Konvertera till XML</v>
+        <v>Fel:</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B648" t="str">
-        <v>Konvertera till JSON</v>
+        <v>Konvertera till XML</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B649" t="str">
-        <v>Konvertera till ICC</v>
+        <v>Konvertera till JSON</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B650" t="str">
-        <v>Konverterar till XML…</v>
+        <v>Konvertera till ICC</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B651" t="str">
-        <v>Konverterar till JSON…</v>
+        <v>Konverterar till XML…</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B652" t="str">
-        <v>Konverterar till ICC…</v>
+        <v>Konverterar till JSON…</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B653" t="str">
-        <v>Läs in ICC-profil</v>
+        <v>Konverterar till ICC…</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B654" t="str">
-        <v>Släppzon för ICC-profilfiler</v>
+        <v>Läs in ICC-profil</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>Profile ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B655" t="str">
-        <v>Profil-ID</v>
+        <v>Släppzon för ICC-profilfiler</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>No tags found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B656" t="str">
-        <v>Inga taggar hittades.</v>
+        <v>Profil-ID</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>Tag Name</v>
+        <v>No tags found.</v>
       </c>
       <c r="B657" t="str">
-        <v>Taggnamn</v>
+        <v>Inga taggar hittades.</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
-        <v>ID</v>
+        <v>Tag Name</v>
       </c>
       <c r="B658" t="str">
-        <v>ID</v>
+        <v>Taggnamn</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
       <c r="B659" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="str">
-        <v>Size</v>
+        <v>Offset</v>
       </c>
       <c r="B660" t="str">
-        <v>Storlek</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="str">
-        <v>Pad</v>
+        <v>Size</v>
       </c>
       <c r="B661" t="str">
-        <v>Utfyllnad</v>
+        <v>Storlek</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="str">
-        <v>Bytes changed since load</v>
+        <v>Pad</v>
       </c>
       <c r="B662" t="str">
-        <v>Byte ändrade sedan inläsning</v>
+        <v>Utfyllnad</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="str">
-        <v>Type</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B663" t="str">
-        <v>Typ</v>
+        <v>Byte ändrade sedan inläsning</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="str">
-        <v>Array of {type}</v>
+        <v>Type</v>
       </c>
       <c r="B664" t="str">
-        <v>Array av {type}</v>
+        <v>Typ</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="str">
-        <v>(No content)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B665" t="str">
-        <v>(Inget innehåll)</v>
+        <v>Array av {type}</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="str">
-        <v>bytes</v>
+        <v>(No content)</v>
       </c>
       <c r="B666" t="str">
-        <v>byte</v>
+        <v>(Inget innehåll)</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="str">
-        <v>Loading full description…</v>
+        <v>bytes</v>
       </c>
       <c r="B667" t="str">
-        <v>Läser in fullständig beskrivning…</v>
+        <v>byte</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="str">
-        <v>Could not load full description:</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B668" t="str">
-        <v>Kunde inte läsa in fullständig beskrivning:</v>
+        <v>Läser in fullständig beskrivning…</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B669" t="str">
-        <v>Den här profilen kunde inte tolkas helt och får inte tillämpas. Huvudet och taggkatalogen nedan visas endast för granskning.</v>
+        <v>Kunde inte läsa in fullständig beskrivning:</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B670" t="str">
-        <v>Tagginnehåll otillgängligt — profilen kunde inte tolkas helt.</v>
+        <v>Den här profilen kunde inte tolkas helt och får inte tillämpas. Huvudet och taggkatalogen nedan visas endast för granskning.</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="str">
-        <v>No validation output</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B671" t="str">
-        <v>Ingen valideringsutdata</v>
+        <v>Tagginnehåll otillgängligt — profilen kunde inte tolkas helt.</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="str">
-        <v>Profile is valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B672" t="str">
-        <v>Profilen är giltig</v>
+        <v>Ingen valideringsutdata</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B673" t="str">
-        <v>Profilen har varning(ar)</v>
+        <v>Profilen är giltig</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B674" t="str">
-        <v>Profilen följer inte specifikationen</v>
+        <v>Profilen har varning(ar)</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B675" t="str">
-        <v>Kritiskt valideringsfel</v>
+        <v>Profilen följer inte specifikationen</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B676" t="str">
-        <v>Okänd valideringsstatus</v>
+        <v>Kritiskt valideringsfel</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B677" t="str">
-        <v>Kritiskt — visas endast för granskning</v>
+        <v>Okänd valideringsstatus</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B678" t="str">
-        <v>Inga varningar eller fel hittades.</v>
+        <v>Kritiskt — visas endast för granskning</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="str">
-        <v>Valid</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B679" t="str">
-        <v>Giltig</v>
+        <v>Inga varningar eller fel hittades.</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="str">
-        <v>Warning</v>
+        <v>Valid</v>
       </c>
       <c r="B680" t="str">
-        <v>Varning</v>
+        <v>Giltig</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="str">
-        <v>Error</v>
+        <v>Warning</v>
       </c>
       <c r="B681" t="str">
-        <v>Fel</v>
+        <v>Varning</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="str">
-        <v>Unknown</v>
+        <v>Error</v>
       </c>
       <c r="B682" t="str">
-        <v>Okänd</v>
+        <v>Fel</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="str">
-        <v>Pass</v>
+        <v>Unknown</v>
       </c>
       <c r="B683" t="str">
-        <v>Godkänd</v>
+        <v>Okänd</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="B684" t="str">
-        <v>Underkänd</v>
+        <v>Godkänd</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="str">
-        <v>View in context</v>
+        <v>Fail</v>
       </c>
       <c r="B685" t="str">
-        <v>Visa i sammanhang</v>
+        <v>Underkänd</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="str">
-        <v>Validation detail</v>
+        <v>View in context</v>
       </c>
       <c r="B686" t="str">
-        <v>Valideringsdetalj</v>
+        <v>Visa i sammanhang</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="str">
-        <v>Triggered by</v>
+        <v>Validation detail</v>
       </c>
       <c r="B687" t="str">
-        <v>Utlöst av</v>
+        <v>Valideringsdetalj</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="str">
-        <v>Field</v>
+        <v>Triggered by</v>
       </c>
       <c r="B688" t="str">
-        <v>Fält</v>
+        <v>Utlöst av</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="str">
-        <v>Current value</v>
+        <v>Field</v>
       </c>
       <c r="B689" t="str">
-        <v>Aktuellt värde</v>
+        <v>Fält</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="str">
-        <v>Required: 0</v>
+        <v>Current value</v>
       </c>
       <c r="B690" t="str">
-        <v>Krävs: 0</v>
+        <v>Aktuellt värde</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="str">
-        <v>Expected: {value}</v>
+        <v>Required: 0</v>
       </c>
       <c r="B691" t="str">
-        <v>Förväntat: {value}</v>
+        <v>Krävs: 0</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="str">
-        <v>Invalid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B692" t="str">
-        <v>Ogiltigt</v>
+        <v>Förväntat: {value}</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Invalid</v>
       </c>
       <c r="B693" t="str">
-        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
+        <v>Ogiltigt</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="str">
-        <v>Close</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B694" t="str">
-        <v>Stäng</v>
+        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="str">
-        <v>Loading XML editor…</v>
+        <v>Close</v>
       </c>
       <c r="B695" t="str">
-        <v>Läser in XML-redigeraren…</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B696" t="str">
-        <v>Läser in JSON-redigeraren…</v>
+        <v>Läser in XML-redigeraren…</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B697" t="str">
-        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>Läser in JSON-redigeraren…</v>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B698" t="str">
-        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B699" t="str">
-        <v>● osparade XML-ändringar</v>
+        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B700" t="str">
-        <v>● osparade JSON-ändringar</v>
+        <v>● osparade XML-ändringar</v>
       </c>
     </row>
     <row r="701">
       <c r="A701" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B701" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
+        <v>● osparade JSON-ändringar</v>
       </c>
     </row>
     <row r="702">
       <c r="A702" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B702" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
+        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
       </c>
     </row>
     <row r="703">
       <c r="A703" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B703" t="str">
-        <v>indrag</v>
+        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="str">
-        <v>sort keys</v>
+        <v>indent</v>
       </c>
       <c r="B704" t="str">
-        <v>sortera nycklar</v>
+        <v>indrag</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B705" t="str">
+        <v>sortera nycklar</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B705" t="str">
+      <c r="B706" t="str">
         <v>Profilen skrevs från ändringarna, men omvalideringen misslyckades:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B705"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B706"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Sv.xlsx
+++ b/translations/Eng-Sv.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B466"/>
+  <dimension ref="A1:B467"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -1197,2949 +1197,2957 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Sort by name</v>
+        <v>Tap to select, then tap a tab to send.</v>
       </c>
       <c r="B100" t="str">
-        <v>Sortera efter namn</v>
+        <v>Tryck för att välja, tryck sedan på en flik för att skicka.</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>A–Z</v>
+        <v>Sort by name</v>
       </c>
       <c r="B101" t="str">
-        <v>A–Z</v>
+        <v>Sortera efter namn</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>New profile from .cube</v>
+        <v>A–Z</v>
       </c>
       <c r="B102" t="str">
-        <v>Ny profil från .cube</v>
+        <v>A–Z</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and opened; nothing is downloaded until you click Save ICC profile.</v>
+        <v>New profile from .cube</v>
       </c>
       <c r="B103" t="str">
-        <v>Skapa en ICC-DeviceLink från en .cube 3D-LUT från Adobe/Resolve. Resultatet läggs till i din pool och öppnas; inget laddas ned förrän du klickar på Spara ICC-profil.</v>
+        <v>Ny profil från .cube</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Choose .cube file</v>
+        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and opened; nothing is downloaded until you click Save ICC profile.</v>
       </c>
       <c r="B104" t="str">
-        <v>Välj .cube-fil</v>
+        <v>Skapa en ICC-DeviceLink från en .cube 3D-LUT från Adobe/Resolve. Resultatet läggs till i din pool och öppnas; inget laddas ned förrän du klickar på Spara ICC-profil.</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
+        <v>Choose .cube file</v>
+      </c>
+      <c r="B105" t="str">
+        <v>Välj .cube-fil</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
         <v>or drop it here, or paste below</v>
       </c>
-      <c r="B105" t="str">
+      <c r="B106" t="str">
         <v>eller släpp den här, eller klistra in nedan</v>
       </c>
     </row>
-    <row r="106" xml:space="preserve">
-      <c r="A106" t="str" xml:space="preserve">
+    <row r="107" xml:space="preserve">
+      <c r="A107" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
-      <c r="B106" t="str" xml:space="preserve">
+      <c r="B107" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" t="str">
-        <v>Cancel</v>
-      </c>
-      <c r="B107" t="str">
-        <v>Avbryt</v>
-      </c>
-    </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Create DeviceLink</v>
+        <v>Cancel</v>
       </c>
       <c r="B108" t="str">
-        <v>Skapa DeviceLink</v>
+        <v>Avbryt</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Creating…</v>
+        <v>Create DeviceLink</v>
       </c>
       <c r="B109" t="str">
-        <v>Skapar…</v>
+        <v>Skapa DeviceLink</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Could not read that file.</v>
+        <v>Creating…</v>
       </c>
       <c r="B110" t="str">
-        <v>Det gick inte att läsa den filen.</v>
+        <v>Skapar…</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Profile</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B111" t="str">
-        <v>Profil</v>
+        <v>Det gick inte att läsa den filen.</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Compare</v>
+        <v>Profile</v>
       </c>
       <c r="B112" t="str">
-        <v>Jämför</v>
+        <v>Profil</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Combine</v>
+        <v>Compare</v>
       </c>
       <c r="B113" t="str">
-        <v>Länka</v>
+        <v>Jämför</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Spectral</v>
+        <v>Combine</v>
       </c>
       <c r="B114" t="str">
-        <v>Spektral</v>
+        <v>Länka</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Drag profiles from the pool onto this tab</v>
+        <v>Spectral</v>
       </c>
       <c r="B115" t="str">
-        <v>Dra profiler från poolen till den här fliken</v>
+        <v>Spektral</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Remove</v>
+        <v>Drag profiles from the pool onto this tab</v>
       </c>
       <c r="B116" t="str">
-        <v>Ta bort</v>
+        <v>Dra profiler från poolen till den här fliken</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>No profile selected</v>
+        <v>Remove</v>
       </c>
       <c r="B117" t="str">
-        <v>Ingen profil vald</v>
+        <v>Ta bort</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
+        <v>No profile selected</v>
       </c>
       <c r="B118" t="str">
-        <v>Dra en profil från poolen till fliken Profil för att granska den.</v>
+        <v>Ingen profil vald</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Nothing to compare yet</v>
+        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
       </c>
       <c r="B119" t="str">
-        <v>Inget att jämföra ännu</v>
+        <v>Dra en profil från poolen till fliken Profil för att granska den.</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Drag one or more profiles onto the Compare tab.</v>
+        <v>Nothing to compare yet</v>
       </c>
       <c r="B120" t="str">
-        <v>Dra en eller flera profiler till fliken Jämför.</v>
+        <v>Inget att jämföra ännu</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Gamut comparison</v>
+        <v>Drag one or more profiles onto the Compare tab.</v>
       </c>
       <c r="B121" t="str">
-        <v>Gamutjämförelse</v>
+        <v>Dra en eller flera profiler till fliken Jämför.</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
+        <v>Gamut comparison</v>
       </c>
       <c r="B122" t="str">
-        <v>Vyer för 3D-gamut och 2D-snitt kommer hit. Samlade:</v>
+        <v>Gamutjämförelse</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Rendering intent</v>
+        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
       </c>
       <c r="B123" t="str">
-        <v>Renderingsavsikt</v>
+        <v>Vyer för 3D-gamut och 2D-snitt kommer hit. Samlade:</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Shell</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B124" t="str">
-        <v>Skal</v>
+        <v>Renderingsavsikt</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Wireframe</v>
+        <v>Shell</v>
       </c>
       <c r="B125" t="str">
-        <v>Trådmodell</v>
+        <v>Skal</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Axis numbers</v>
+        <v>Wireframe</v>
       </c>
       <c r="B126" t="str">
-        <v>Axelnummer</v>
+        <v>Trådmodell</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Opacity</v>
+        <v>Axis numbers</v>
       </c>
       <c r="B127" t="str">
-        <v>Opacitet</v>
+        <v>Axelnummer</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Colour</v>
+        <v>Opacity</v>
       </c>
       <c r="B128" t="str">
-        <v>Färg</v>
+        <v>Opacitet</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Solid</v>
+        <v>Colour</v>
       </c>
       <c r="B129" t="str">
-        <v>Enfärgad</v>
+        <v>Färg</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>By value</v>
+        <v>Solid</v>
       </c>
       <c r="B130" t="str">
-        <v>Efter värde</v>
+        <v>Enfärgad</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>By hue</v>
+        <v>By value</v>
       </c>
       <c r="B131" t="str">
-        <v>Efter nyans</v>
+        <v>Efter värde</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Rotation</v>
+        <v>By hue</v>
       </c>
       <c r="B132" t="str">
-        <v>Rotation</v>
+        <v>Efter nyans</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Turntable</v>
+        <v>Rotation</v>
       </c>
       <c r="B133" t="str">
-        <v>Skivtallrik</v>
+        <v>Rotation</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Orbit</v>
+        <v>Turntable</v>
       </c>
       <c r="B134" t="str">
-        <v>Omloppsbana</v>
+        <v>Skivtallrik</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Drag speed</v>
+        <v>Orbit</v>
       </c>
       <c r="B135" t="str">
-        <v>Draghastighet</v>
+        <v>Omloppsbana</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Roll</v>
+        <v>Drag speed</v>
       </c>
       <c r="B136" t="str">
-        <v>Rullning</v>
+        <v>Draghastighet</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Roll speed</v>
+        <v>Roll</v>
       </c>
       <c r="B137" t="str">
-        <v>Rullningshastighet</v>
+        <v>Rullning</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Building gamut…</v>
+        <v>Roll speed</v>
       </c>
       <c r="B138" t="str">
-        <v>Bygger gamut…</v>
+        <v>Rullningshastighet</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>no gamut</v>
+        <v>Building gamut…</v>
       </c>
       <c r="B139" t="str">
-        <v>ingen gamut</v>
+        <v>Bygger gamut…</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Show / hide</v>
+        <v>no gamut</v>
       </c>
       <c r="B140" t="str">
-        <v>Visa/dölj</v>
+        <v>ingen gamut</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>3-D gamut shell</v>
+        <v>Show / hide</v>
       </c>
       <c r="B141" t="str">
-        <v>3D-gamutskal</v>
+        <v>Visa/dölj</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>2-D gamut slice</v>
+        <v>3-D gamut shell</v>
       </c>
       <c r="B142" t="str">
-        <v>2D-gamutsnitt</v>
+        <v>3D-gamutskal</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Plane</v>
+        <v>2-D gamut slice</v>
       </c>
       <c r="B143" t="str">
-        <v>Plan</v>
+        <v>2D-gamutsnitt</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>L*</v>
+        <v>Plane</v>
       </c>
       <c r="B144" t="str">
-        <v>L*</v>
+        <v>Plan</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>a*</v>
+        <v>L*</v>
       </c>
       <c r="B145" t="str">
-        <v>a*</v>
+        <v>L*</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>b*</v>
+        <v>a*</v>
       </c>
       <c r="B146" t="str">
-        <v>b*</v>
+        <v>a*</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
+        <v>b*</v>
       </c>
       <c r="B147" t="str">
-        <v>Ingen av de valda profilerna har en enhet→PCS-transform att härleda en gamut från.</v>
+        <v>b*</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Linking</v>
+        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
       </c>
       <c r="B148" t="str">
-        <v>Länkning</v>
+        <v>Ingen av de valda profilerna har en enhet→PCS-transform att härleda en gamut från.</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
+        <v>Linking</v>
       </c>
       <c r="B149" t="str">
-        <v>DeviceLink-produktion och transformer över flera profiler kommer i en senare fas.</v>
+        <v>Länkning</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>More link makers (DeviceLink, …) arrive here.</v>
+        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
       </c>
       <c r="B150" t="str">
-        <v>Fler länkverktyg (DeviceLink, …) kommer hit.</v>
+        <v>DeviceLink-produktion och transformer över flera profiler kommer i en senare fas.</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Observer Change</v>
+        <v>More link makers (DeviceLink, …) arrive here.</v>
       </c>
       <c r="B151" t="str">
-        <v>V4-skärmskapare</v>
+        <v>Fler länkverktyg (DeviceLink, …) kommer hit.</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
+        <v>Observer Change</v>
       </c>
       <c r="B152" t="str">
-        <v>Dra en V5 RGB-skärm och en V5-observatörsprofil hit för att skapa en V4-skärmprofil.</v>
+        <v>V4-skärmskapare</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>V5 RGB display</v>
+        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
       </c>
       <c r="B153" t="str">
-        <v>V5 RGB-skärm</v>
+        <v>Dra en V5 RGB-skärm och en V5-observatörsprofil hit för att skapa en V4-skärmprofil.</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>drop a display profile</v>
+        <v>V5 RGB display</v>
       </c>
       <c r="B154" t="str">
-        <v>släpp en skärmprofil</v>
+        <v>V5 RGB-skärm</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>V5 observer (PCC)</v>
+        <v>drop a display profile</v>
       </c>
       <c r="B155" t="str">
-        <v>V5-observatör (PCC)</v>
+        <v>släpp en skärmprofil</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>drop an observer profile</v>
+        <v>V5 observer (PCC)</v>
       </c>
       <c r="B156" t="str">
-        <v>släpp en observatörsprofil</v>
+        <v>V5-observatör (PCC)</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
+        <v>drop an observer profile</v>
       </c>
       <c r="B157" t="str">
-        <v>En profil som varken är en V5 RGB-skärm eller en observatör ignorerades.</v>
+        <v>släpp en observatörsprofil</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Make V4 Display Profile</v>
+        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
       </c>
       <c r="B158" t="str">
-        <v>Skapa V4-skärmprofil</v>
+        <v>En profil som varken är en V5 RGB-skärm eller en observatör ignorerades.</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Profile name</v>
+        <v>Make V4 Display Profile</v>
       </c>
       <c r="B159" t="str">
-        <v>Profilnamn</v>
+        <v>Skapa V4-skärmprofil</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Create</v>
+        <v>Profile name</v>
       </c>
       <c r="B160" t="str">
-        <v>Skapa</v>
+        <v>Profilnamn</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Making…</v>
+        <v>Create</v>
       </c>
       <c r="B161" t="str">
-        <v>Skapar…</v>
+        <v>Skapa</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Making…</v>
       </c>
       <c r="B162" t="str">
-        <v>”{name}” skapad — tillagd i poolen och den här fliken.</v>
+        <v>Skapar…</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Link Pipeline</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B163" t="str">
-        <v>Länkpipeline</v>
+        <v>”{name}” skapad — tillagd i poolen och den här fliken.</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
+        <v>Link Pipeline</v>
       </c>
       <c r="B164" t="str">
-        <v>Bygg en kedja av profiler och skapa sedan en DeviceLink, transformera en bild eller transformera ett färgdataset genom den.</v>
+        <v>Länkpipeline</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Done</v>
+        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
       </c>
       <c r="B165" t="str">
-        <v>Klar</v>
+        <v>Bygg en kedja av profiler och skapa sedan en DeviceLink, transformera en bild eller transformera ett färgdataset genom den.</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
+        <v>Done</v>
       </c>
       <c r="B166" t="str">
-        <v>Släpp en bild att transformera (TIFF/PNG/JPEG)</v>
+        <v>Klar</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Checking image…</v>
+        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
       </c>
       <c r="B167" t="str">
-        <v>Kontrollerar bild…</v>
+        <v>Släpp en bild att transformera (TIFF/PNG/JPEG)</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Not a supported image (TIFF, PNG or JPEG).</v>
+        <v>Checking image…</v>
       </c>
       <c r="B168" t="str">
-        <v>Bildtypen stöds inte (TIFF, PNG eller JPEG).</v>
+        <v>Kontrollerar bild…</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Image too large ({mp} MP; limit {max} MP).</v>
+        <v>Not a supported image (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B169" t="str">
-        <v>Bilden är för stor ({mp} MP; gräns {max} MP).</v>
+        <v>Bildtypen stöds inte (TIFF, PNG eller JPEG).</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Transform Image</v>
+        <v>Image too large ({mp} MP; limit {max} MP).</v>
       </c>
       <c r="B170" t="str">
-        <v>Transformera bild</v>
+        <v>Bilden är för stor ({mp} MP; gräns {max} MP).</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Transforming…</v>
+        <v>Transform Image</v>
       </c>
       <c r="B171" t="str">
-        <v>Transformerar…</v>
+        <v>Transformera bild</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Drop profiles to start the chain</v>
+        <v>Transforming…</v>
       </c>
       <c r="B172" t="str">
-        <v>Släpp profiler för att starta kedjan</v>
+        <v>Transformerar…</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>removed</v>
+        <v>Drop profiles to start the chain</v>
       </c>
       <c r="B173" t="str">
-        <v>borttagen</v>
+        <v>Släpp profiler för att starta kedjan</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Move earlier</v>
+        <v>removed</v>
       </c>
       <c r="B174" t="str">
-        <v>Flytta tidigare</v>
+        <v>borttagen</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Move later</v>
+        <v>Move earlier</v>
       </c>
       <c r="B175" t="str">
-        <v>Flytta senare</v>
+        <v>Flytta tidigare</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Move up</v>
+        <v>Move later</v>
       </c>
       <c r="B176" t="str">
-        <v>Flytta upp</v>
+        <v>Flytta senare</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Move down</v>
+        <v>Move up</v>
       </c>
       <c r="B177" t="str">
-        <v>Flytta ner</v>
+        <v>Flytta upp</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Rendering intent (all)</v>
+        <v>Move down</v>
       </c>
       <c r="B178" t="str">
-        <v>Återgivningsalternativ (alla)</v>
+        <v>Flytta ner</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Rendering intent for this transform</v>
+        <v>Rendering intent (all)</v>
       </c>
       <c r="B179" t="str">
-        <v>Återgivningsalternativ för denna transformering</v>
+        <v>Återgivningsalternativ (alla)</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Transforms use different rendering intents</v>
+        <v>Rendering intent for this transform</v>
       </c>
       <c r="B180" t="str">
-        <v>Transformeringarna använder olika återgivningsalternativ</v>
+        <v>Återgivningsalternativ för denna transformering</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
+        <v>Transforms use different rendering intents</v>
       </c>
       <c r="B181" t="str">
-        <v>Vänd kedjeriktning (vänder den första transformeringen, vilket sprider sig genom kedjan)</v>
+        <v>Transformeringarna använder olika återgivningsalternativ</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>A chained profile was removed from the pool — remove it to continue.</v>
+        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
       </c>
       <c r="B182" t="str">
-        <v>En profil i kedjan togs bort från poolen — ta bort den för att fortsätta.</v>
+        <v>Vänd kedjeriktning (vänder den första transformeringen, vilket sprider sig genom kedjan)</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Chain</v>
+        <v>A chained profile was removed from the pool — remove it to continue.</v>
       </c>
       <c r="B183" t="str">
-        <v>Kedja</v>
+        <v>En profil i kedjan togs bort från poolen — ta bort den för att fortsätta.</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>The chain could not be analysed.</v>
+        <v>Chain</v>
       </c>
       <c r="B184" t="str">
-        <v>Kedjan kunde inte analyseras.</v>
+        <v>Kedja</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Checking chain…</v>
+        <v>The chain could not be analysed.</v>
       </c>
       <c r="B185" t="str">
-        <v>Kontrollerar kedja…</v>
+        <v>Kedjan kunde inte analyseras.</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>The chain does not connect ({detail}).</v>
+        <v>Checking chain…</v>
       </c>
       <c r="B186" t="str">
-        <v>Kedjan hänger inte ihop ({detail}).</v>
+        <v>Kontrollerar kedja…</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
+        <v>The chain does not connect ({detail}).</v>
       </c>
       <c r="B187" t="str">
-        <v>Profil {n} hänger inte ihop med föregående steg ({detail}).</v>
+        <v>Kedjan hänger inte ihop ({detail}).</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Fix the chain before processing images</v>
+        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
       </c>
       <c r="B188" t="str">
-        <v>Åtgärda kedjan innan bilder bearbetas</v>
+        <v>Profil {n} hänger inte ihop med föregående steg ({detail}).</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Clear</v>
+        <v>Fix the chain before processing images</v>
       </c>
       <c r="B189" t="str">
-        <v>Rensa</v>
+        <v>Åtgärda kedjan innan bilder bearbetas</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Make DeviceLink</v>
+        <v>Clear</v>
       </c>
       <c r="B190" t="str">
-        <v>Skapa DeviceLink</v>
+        <v>Rensa</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>DeviceLink name</v>
+        <v>Make DeviceLink</v>
       </c>
       <c r="B191" t="str">
-        <v>DeviceLink-namn</v>
+        <v>Skapa DeviceLink</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Making…</v>
+        <v>DeviceLink name</v>
       </c>
       <c r="B192" t="str">
-        <v>Skapar…</v>
+        <v>DeviceLink-namn</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Making…</v>
       </c>
       <c r="B193" t="str">
-        <v>Skapade ”{name}” — tillagd i poolen och denna flik.</v>
+        <v>Skapar…</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B194" t="str">
-        <v>Släpp {src}-bilder för att konvertera till {dst} — resultaten laddas ner, inget sparas.</v>
+        <v>Skapade ”{name}” — tillagd i poolen och denna flik.</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Build a chain to process images</v>
+        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
       </c>
       <c r="B195" t="str">
-        <v>Bygg en kedja för att bearbeta bilder</v>
+        <v>Släpp {src}-bilder för att konvertera till {dst} — resultaten laddas ner, inget sparas.</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>This chain does not start and end in an image colour space</v>
+        <v>Build a chain to process images</v>
       </c>
       <c r="B196" t="str">
-        <v>Denna kedja börjar och slutar inte i en bildfärgrymd</v>
+        <v>Bygg en kedja för att bearbeta bilder</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Saved the transformed image.</v>
+        <v>This chain does not start and end in an image colour space</v>
       </c>
       <c r="B197" t="str">
-        <v>Sparade den transformerade bilden.</v>
+        <v>Denna kedja börjar och slutar inte i en bildfärgrymd</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
+        <v>Saved the transformed image.</v>
       </c>
       <c r="B198" t="str">
-        <v>Släpp ett färgdataset (CGATS/CSV/CxF/JSON)</v>
+        <v>Sparade den transformerade bilden.</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Could not read that file.</v>
+        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
       </c>
       <c r="B199" t="str">
-        <v>Kunde inte läsa filen.</v>
+        <v>Släpp ett färgdataset (CGATS/CSV/CxF/JSON)</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Data file too large.</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B200" t="str">
-        <v>Datafilen är för stor.</v>
+        <v>Kunde inte läsa filen.</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Transform Data</v>
+        <v>Data file too large.</v>
       </c>
       <c r="B201" t="str">
-        <v>Transformera data</v>
+        <v>Datafilen är för stor.</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Transforming…</v>
+        <v>Transform Data</v>
       </c>
       <c r="B202" t="str">
-        <v>Transformerar…</v>
+        <v>Transformera data</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Prefer</v>
+        <v>Transforming…</v>
       </c>
       <c r="B203" t="str">
-        <v>Föredra</v>
+        <v>Transformerar…</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Observer</v>
+        <v>Prefer</v>
       </c>
       <c r="B204" t="str">
-        <v>Observatör</v>
+        <v>Föredra</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>Illuminant</v>
+        <v>Observer</v>
       </c>
       <c r="B205" t="str">
-        <v>Ljuskälla</v>
+        <v>Observatör</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>Condition</v>
+        <v>Illuminant</v>
       </c>
       <c r="B206" t="str">
-        <v>Villkor</v>
+        <v>Ljuskälla</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Filter {n} duplicate(s)</v>
+        <v>Condition</v>
       </c>
       <c r="B207" t="str">
-        <v>Filtrera {n} dubblett(er)</v>
+        <v>Villkor</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>median</v>
+        <v>Filter {n} duplicate(s)</v>
       </c>
       <c r="B208" t="str">
-        <v>median</v>
+        <v>Filtrera {n} dubblett(er)</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>mean</v>
+        <v>median</v>
       </c>
       <c r="B209" t="str">
-        <v>medelvärde</v>
+        <v>median</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>patches</v>
+        <v>mean</v>
       </c>
       <c r="B210" t="str">
-        <v>patchar</v>
+        <v>medelvärde</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>{n} duplicates</v>
+        <v>patches</v>
       </c>
       <c r="B211" t="str">
-        <v>{n} dubbletter</v>
+        <v>patchar</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Transform result</v>
+        <v>{n} duplicates</v>
       </c>
       <c r="B212" t="str">
-        <v>Transformeringsresultat</v>
+        <v>{n} dubbletter</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>{src} → {dst} · {n} patches</v>
+        <v>Transform result</v>
       </c>
       <c r="B213" t="str">
-        <v>{src} → {dst} · {n} patchar</v>
+        <v>Transformeringsresultat</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Showing first {shown} of {total} — Save writes them all.</v>
+        <v>{src} → {dst} · {n} patches</v>
       </c>
       <c r="B214" t="str">
-        <v>Visar de första {shown} av {total} — Spara skriver alla.</v>
+        <v>{src} → {dst} · {n} patchar</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>Save as</v>
+        <v>Showing first {shown} of {total} — Save writes them all.</v>
       </c>
       <c r="B215" t="str">
-        <v>Spara som</v>
+        <v>Visar de första {shown} av {total} — Spara skriver alla.</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>Save</v>
+        <v>Save as</v>
       </c>
       <c r="B216" t="str">
-        <v>Spara</v>
+        <v>Spara som</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>Invert Transform</v>
+        <v>Save</v>
       </c>
       <c r="B217" t="str">
-        <v>Invertera transformering</v>
+        <v>Spara</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>Inverting…</v>
+        <v>Invert Transform</v>
       </c>
       <c r="B218" t="str">
-        <v>Inverterar…</v>
+        <v>Invertera transformering</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>Invert</v>
+        <v>Inverting…</v>
       </c>
       <c r="B219" t="str">
-        <v>Invertera</v>
+        <v>Inverterar…</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>last stage</v>
+        <v>Invert</v>
       </c>
       <c r="B220" t="str">
-        <v>sista steget</v>
+        <v>Invertera</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>first stage</v>
+        <v>last stage</v>
       </c>
       <c r="B221" t="str">
-        <v>första steget</v>
+        <v>sista steget</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>Data in {in} → search {out}</v>
+        <v>first stage</v>
       </c>
       <c r="B222" t="str">
-        <v>Data i {in} → sök {out}</v>
+        <v>första steget</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>Invert needs a 2–3 profile chain</v>
+        <v>Data in {in} → search {out}</v>
       </c>
       <c r="B223" t="str">
-        <v>Invertering kräver en kedja med 2–3 profiler</v>
+        <v>Data i {in} → sök {out}</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
+        <v>Invert needs a 2–3 profile chain</v>
       </c>
       <c r="B224" t="str">
-        <v>Datasetet måste vara {in}; den omvända sökningen ger {out} plus en inverterbarhetskostnad per patch.</v>
+        <v>Invertering kräver en kedja med 2–3 profiler</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>ΔE cost</v>
+        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
       </c>
       <c r="B225" t="str">
-        <v>ΔE-kostnad</v>
+        <v>Datasetet måste vara {in}; den omvända sökningen ger {out} plus en inverterbarhetskostnad per patch.</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>This image has an embedded ICC profile.</v>
+        <v>ΔE cost</v>
       </c>
       <c r="B226" t="str">
-        <v>Denna bild har en inbäddad ICC-profil.</v>
+        <v>ΔE-kostnad</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>Extract &amp; add to chain</v>
+        <v>This image has an embedded ICC profile.</v>
       </c>
       <c r="B227" t="str">
-        <v>Extrahera och lägg till i kedjan</v>
+        <v>Denna bild har en inbäddad ICC-profil.</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>Extracting…</v>
+        <v>Extract &amp; add to chain</v>
       </c>
       <c r="B228" t="str">
-        <v>Extraherar…</v>
+        <v>Extrahera och lägg till i kedjan</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>Dismiss</v>
+        <v>Extracting…</v>
       </c>
       <c r="B229" t="str">
-        <v>Avfärda</v>
+        <v>Extraherar…</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
+        <v>Dismiss</v>
       </c>
       <c r="B230" t="str">
-        <v>Extraherade den inbäddade profilen — tillagd i poolen och placerad först i kedjan.</v>
+        <v>Avfärda</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>Image output options</v>
+        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
       </c>
       <c r="B231" t="str">
-        <v>Alternativ för bildutdata</v>
+        <v>Extraherade den inbäddade profilen — tillagd i poolen och placerad först i kedjan.</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>Encoding</v>
+        <v>Image output options</v>
       </c>
       <c r="B232" t="str">
-        <v>Kodning</v>
+        <v>Alternativ för bildutdata</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>Same as source</v>
+        <v>Encoding</v>
       </c>
       <c r="B233" t="str">
-        <v>Samma som källan</v>
+        <v>Kodning</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>8-bit</v>
+        <v>Same as source</v>
       </c>
       <c r="B234" t="str">
-        <v>8-bitars</v>
+        <v>Samma som källan</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>16-bit</v>
+        <v>8-bit</v>
       </c>
       <c r="B235" t="str">
-        <v>16-bitars</v>
+        <v>8-bitars</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>Float (32-bit)</v>
+        <v>16-bit</v>
       </c>
       <c r="B236" t="str">
-        <v>Flyttal (32-bitars)</v>
+        <v>16-bitars</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>Compression</v>
+        <v>Float (32-bit)</v>
       </c>
       <c r="B237" t="str">
-        <v>Komprimering</v>
+        <v>Flyttal (32-bitars)</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>None</v>
+        <v>Compression</v>
       </c>
       <c r="B238" t="str">
-        <v>Ingen</v>
+        <v>Komprimering</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>Planar</v>
+        <v>None</v>
       </c>
       <c r="B239" t="str">
-        <v>Planformat</v>
+        <v>Ingen</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>Composite</v>
+        <v>Planar</v>
       </c>
       <c r="B240" t="str">
-        <v>Sammansatt</v>
+        <v>Planformat</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>Separated</v>
+        <v>Composite</v>
       </c>
       <c r="B241" t="str">
-        <v>Separerad</v>
+        <v>Sammansatt</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>CMM interpolation</v>
+        <v>Separated</v>
       </c>
       <c r="B242" t="str">
-        <v>CMM-interpolation</v>
+        <v>Separerad</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>Tetrahedral</v>
+        <v>CMM interpolation</v>
       </c>
       <c r="B243" t="str">
-        <v>Tetraedrisk</v>
+        <v>CMM-interpolation</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>Linear</v>
+        <v>Tetrahedral</v>
       </c>
       <c r="B244" t="str">
-        <v>Linjär</v>
+        <v>Tetraedrisk</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>Embed ICC</v>
+        <v>Linear</v>
       </c>
       <c r="B245" t="str">
-        <v>Bädda in ICC</v>
+        <v>Linjär</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
+        <v>Embed ICC</v>
       </c>
       <c r="B246" t="str">
-        <v>Kodning, komprimering och planformat formar den sparade TIFF-filen. RGB/Gray-utdata förblir PNG om inte ett TIFF-specifikt alternativ (flyttal, LZW/ZIP, separerad) väljs.</v>
+        <v>Bädda in ICC</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>Assemble spectral TIFF</v>
+        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
       </c>
       <c r="B247" t="str">
-        <v>Montera spektral-TIFF</v>
+        <v>Kodning, komprimering och planformat formar den sparade TIFF-filen. RGB/Gray-utdata förblir PNG om inte ett TIFF-specifikt alternativ (flyttal, LZW/ZIP, separerad) väljs.</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
+        <v>Assemble spectral TIFF</v>
       </c>
       <c r="B248" t="str">
-        <v>Släpp enkanaliga spektralbilder i kanalordning och montera dem till en flerkanalig TIFF.</v>
+        <v>Montera spektral-TIFF</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>Drop spectral images here (or click to choose)</v>
+        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
       </c>
       <c r="B249" t="str">
-        <v>Släpp spektralbilder här (eller klicka för att välja)</v>
+        <v>Släpp enkanaliga spektralbilder i kanalordning och montera dem till en flerkanalig TIFF.</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>ch</v>
+        <v>Drop spectral images here (or click to choose)</v>
       </c>
       <c r="B250" t="str">
-        <v>ch</v>
+        <v>Släpp spektralbilder här (eller klicka för att välja)</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>Assemble &amp; Save</v>
+        <v>ch</v>
       </c>
       <c r="B251" t="str">
-        <v>Montera och spara</v>
+        <v>ch</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>Assembling…</v>
+        <v>Assemble &amp; Save</v>
       </c>
       <c r="B252" t="str">
-        <v>Monterar…</v>
+        <v>Montera och spara</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>Assembled {n} channels.</v>
+        <v>Assembling…</v>
       </c>
       <c r="B253" t="str">
-        <v>Monterade {n} kanaler.</v>
+        <v>Monterar…</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>None of those look like images (TIFF, PNG or JPEG).</v>
+        <v>Assembled {n} channels.</v>
       </c>
       <c r="B254" t="str">
-        <v>Inga av dessa ser ut som bilder (TIFF, PNG eller JPEG).</v>
+        <v>Monterade {n} kanaler.</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>Cancel</v>
+        <v>None of those look like images (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B255" t="str">
-        <v>Avbryt</v>
+        <v>Inga av dessa ser ut som bilder (TIFF, PNG eller JPEG).</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>{n} file(s) not loaded</v>
+        <v>Cancel</v>
       </c>
       <c r="B256" t="str">
-        <v>{n} fil(er) inte inlästa</v>
+        <v>Avbryt</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>These files are not ICC profiles, so they were not added to the pool:</v>
+        <v>{n} file(s) not loaded</v>
       </c>
       <c r="B257" t="str">
-        <v>De här filerna är inte ICC-profiler och lades därför inte till i poolen:</v>
+        <v>{n} fil(er) inte inlästa</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>OK</v>
+        <v>These files are not ICC profiles, so they were not added to the pool:</v>
       </c>
       <c r="B258" t="str">
-        <v>OK</v>
+        <v>De här filerna är inte ICC-profiler och lades därför inte till i poolen:</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>OK</v>
       </c>
       <c r="B259" t="str">
-        <v>Släpp en ICC-profil här</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>or</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B260" t="str">
-        <v>eller</v>
+        <v>Släpp en ICC-profil här</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>Choose file</v>
+        <v>or</v>
       </c>
       <c r="B261" t="str">
-        <v>Välj fil</v>
+        <v>eller</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>.icc and .icm files</v>
+        <v>Choose file</v>
       </c>
       <c r="B262" t="str">
-        <v>.icc- och .icm-filer</v>
+        <v>Välj fil</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>Header</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B263" t="str">
-        <v>Rubrik</v>
+        <v>.icc- och .icm-filer</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>Tags</v>
+        <v>Header</v>
       </c>
       <c r="B264" t="str">
-        <v>Taggar</v>
+        <v>Rubrik</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>Validation</v>
+        <v>Tags</v>
       </c>
       <c r="B265" t="str">
-        <v>Validering</v>
+        <v>Taggar</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>Analysis</v>
+        <v>Validation</v>
       </c>
       <c r="B266" t="str">
-        <v>Analys</v>
+        <v>Validering</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>Analysis</v>
       </c>
       <c r="B267" t="str">
-        <v>Bläckning av neutralaxeln</v>
+        <v>Analys</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B268" t="str">
-        <v>Färgmängd längs neutralaxeln (a*=b*=0) när ljusheten går från vitt (L*=100) till svart (L*=0).</v>
+        <v>Bläckning av neutralaxeln</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B269" t="str">
-        <v>Bläckning av neutralaxeln är endast tillgänglig för utdataprofiler (skrivare).</v>
+        <v>Färgmängd längs neutralaxeln (a*=b*=0) när ljusheten går från vitt (L*=100) till svart (L*=0).</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B270" t="str">
-        <v>Den här profilen har ingen B2A-tabell (PCS→enhet) att sampla.</v>
+        <v>Bläckning av neutralaxeln är endast tillgänglig för utdataprofiler (skrivare).</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>Rendering intent</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B271" t="str">
-        <v>Renderingsavsikt</v>
+        <v>Den här profilen har ingen B2A-tabell (PCS→enhet) att sampla.</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>% ink</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B272" t="str">
-        <v>% färg</v>
+        <v>Renderingsavsikt</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>L* out (tone)</v>
+        <v>% ink</v>
       </c>
       <c r="B273" t="str">
-        <v>L* ut (ton)</v>
+        <v>% färg</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>Δa*b*</v>
+        <v>L* out (tone)</v>
       </c>
       <c r="B274" t="str">
-        <v>Δa*b*</v>
+        <v>L* ut (ton)</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>Extrema Colorimetry</v>
+        <v>Δa*b*</v>
       </c>
       <c r="B275" t="str">
-        <v>Kolorimetri för ytterlägen</v>
+        <v>Δa*b*</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>The ends of the profile’s reproduction range: substrate white, the darkest black it will print, the ink that black costs, and where each hue reaches its most saturated point.</v>
+        <v>Extrema Colorimetry</v>
       </c>
       <c r="B276" t="str">
-        <v>Ytterlägena i profilens återgivningsomfång: substratets vithet, det mörkaste svart den trycker, bläcket som det svarta kostar och var varje nyans når sin mest mättade punkt.</v>
+        <v>Kolorimetri för ytterlägen</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>White point is the colour of zero colorant — bare substrate. Black point is found by pushing PCS black (L*=0, a*=b*=0) through the selected B2A table to get the inking the profile chooses for black, then reading that inking back through A2B1. Total area coverage (TAC) is the sum of that inking. Absolute colorimetry shows the substrate’s own colour; relative re-references it to a perfect white.</v>
+        <v>The ends of the profile’s reproduction range: substrate white, the darkest black it will print, the ink that black costs, and where each hue reaches its most saturated point.</v>
       </c>
       <c r="B277" t="str">
-        <v>Vitpunkten är färgen vid noll färgmedel — det bara substratet. Svartpunkten tas fram genom att föra PCS-svart (L*=0, a*=b*=0) genom den valda B2A-tabellen för att få den färgmängd profilen väljer för svart, och sedan läsa tillbaka den färgmängden via A2B1. Den totala färgmängden (TAC) är summan av den färgmängden. Absolut kolorimetri visar substratets egen färg; relativ refererar om den till ett perfekt vitt.</v>
+        <v>Ytterlägena i profilens återgivningsomfång: substratets vithet, det mörkaste svart den trycker, bläcket som det svarta kostar och var varje nyans når sin mest mättade punkt.</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>Relative</v>
+        <v>White point is the colour of zero colorant — bare substrate. Black point is found by pushing PCS black (L*=0, a*=b*=0) through the selected B2A table to get the inking the profile chooses for black, then reading that inking back through A2B1. Total area coverage (TAC) is the sum of that inking. Absolute colorimetry shows the substrate’s own colour; relative re-references it to a perfect white.</v>
       </c>
       <c r="B278" t="str">
-        <v>Relativ</v>
+        <v>Vitpunkten är färgen vid noll färgmedel — det bara substratet. Svartpunkten tas fram genom att föra PCS-svart (L*=0, a*=b*=0) genom den valda B2A-tabellen för att få den färgmängd profilen väljer för svart, och sedan läsa tillbaka den färgmängden via A2B1. Den totala färgmängden (TAC) är summan av den färgmängden. Absolut kolorimetri visar substratets egen färg; relativ refererar om den till ett perfekt vitt.</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>Absolute</v>
+        <v>Relative</v>
       </c>
       <c r="B279" t="str">
-        <v>Absolut</v>
+        <v>Relativ</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>White point</v>
+        <v>Absolute</v>
       </c>
       <c r="B280" t="str">
-        <v>Vitpunkt</v>
+        <v>Absolut</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>Black point</v>
+        <v>White point</v>
       </c>
       <c r="B281" t="str">
-        <v>Svartpunkt</v>
+        <v>Vitpunkt</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>Inking at black point</v>
+        <v>Black point</v>
       </c>
       <c r="B282" t="str">
-        <v>Färgmängd vid svartpunkten</v>
+        <v>Svartpunkt</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>TAC</v>
+        <v>Inking at black point</v>
       </c>
       <c r="B283" t="str">
-        <v>TAC</v>
+        <v>Färgmängd vid svartpunkten</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>This profile has no media white point tag, so absolute colorimetry is unavailable.</v>
+        <v>TAC</v>
       </c>
       <c r="B284" t="str">
-        <v>Den här profilen saknar tagg för mediets vitpunkt, så absolut kolorimetri är inte tillgänglig.</v>
+        <v>TAC</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>Extrema colorimetry is only available for output (printer) profiles — it assumes zero colorant means bare substrate.</v>
+        <v>This profile has no media white point tag, so absolute colorimetry is unavailable.</v>
       </c>
       <c r="B285" t="str">
-        <v>Kolorimetri för ytterlägen är endast tillgänglig för utdataprofiler (skrivare) — den förutsätter att noll färgmedel betyder bart substrat.</v>
+        <v>Den här profilen saknar tagg för mediets vitpunkt, så absolut kolorimetri är inte tillgänglig.</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>Full tone vs maximum chroma</v>
+        <v>Extrema colorimetry is only available for output (printer) profiles — it assumes zero colorant means bare substrate.</v>
       </c>
       <c r="B286" t="str">
-        <v>Fullton mot maximal kroma</v>
+        <v>Kolorimetri för ytterlägen är endast tillgänglig för utdataprofiler (skrivare) — den förutsätter att noll färgmedel betyder bart substrat.</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>Where each ink corner lands, and the most chromatic point on the way there. Measured through A2B1, so these rows do not change with the rendering intent above. On a well-behaved profile the two rows match; if maximum chroma arrives before full tone, the extra ink past that point is only darkening.</v>
+        <v>Full tone vs maximum chroma</v>
       </c>
       <c r="B287" t="str">
-        <v>Var varje bläckhörn hamnar, och den mest kromatiska punkten på vägen dit. Mätt via A2B1, så dessa rader ändras inte med renderingsavsikten ovan. I en välartad profil sammanfaller de två raderna; om maximal kroma nås före fullton gör bläcket efter den punkten bara mörkare.</v>
+        <v>Fullton mot maximal kroma</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>Hue</v>
+        <v>Where each ink corner lands, and the most chromatic point on the way there. Measured through A2B1, so these rows do not change with the rendering intent above. On a well-behaved profile the two rows match; if maximum chroma arrives before full tone, the extra ink past that point is only darkening.</v>
       </c>
       <c r="B288" t="str">
-        <v>Nyans</v>
+        <v>Var varje bläckhörn hamnar, och den mest kromatiska punkten på vägen dit. Mätt via A2B1, så dessa rader ändras inte med renderingsavsikten ovan. I en välartad profil sammanfaller de två raderna; om maximal kroma nås före fullton gör bläcket efter den punkten bara mörkare.</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>Full tone</v>
+        <v>Hue</v>
       </c>
       <c r="B289" t="str">
-        <v>Fullton</v>
+        <v>Nyans</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>Max C*</v>
+        <v>Full tone</v>
       </c>
       <c r="B290" t="str">
-        <v>Max C*</v>
+        <v>Fullton</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>At ink</v>
+        <v>Max C*</v>
       </c>
       <c r="B291" t="str">
-        <v>Vid färgmängd</v>
+        <v>Max C*</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>Maximum chroma is reached before full tone — ink past this point only darkens.</v>
+        <v>At ink</v>
       </c>
       <c r="B292" t="str">
-        <v>Maximal kroma nås före fullton — bläck efter denna punkt gör bara mörkare.</v>
+        <v>Vid färgmängd</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>Ink Usage in Shadows</v>
+        <v>Maximum chroma is reached before full tone — ink past this point only darkens.</v>
       </c>
       <c r="B293" t="str">
-        <v>Bläckförbrukning i skuggor</v>
+        <v>Maximal kroma nås före fullton — bläck efter denna punkt gör bara mörkare.</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>Four straight paths across the a*b* plane at one constant, deliberately dark lightness, run through the selected B2A table. Every sample shares the same L*, so any abrupt step or reversal in a colorant comes from hue and chroma handling alone — the signature of a shadow gamut-mapping artefact.</v>
+        <v>Ink Usage in Shadows</v>
       </c>
       <c r="B294" t="str">
-        <v>Fyra raka banor genom a*b*-planet vid en konstant, medvetet mörk ljushet, förda genom den valda B2A-tabellen. Alla sampel har samma L*, så varje abrupt steg eller omkastning i ett färgmedel kommer enbart från hanteringen av nyans och kroma — signaturen för en gamutmappningsartefakt i skuggorna.</v>
+        <v>Bläckförbrukning i skuggor</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>Ink usage in shadows is only available for output (printer) profiles.</v>
+        <v>Four straight paths across the a*b* plane at one constant, deliberately dark lightness, run through the selected B2A table. Every sample shares the same L*, so any abrupt step or reversal in a colorant comes from hue and chroma handling alone — the signature of a shadow gamut-mapping artefact.</v>
       </c>
       <c r="B295" t="str">
-        <v>Bläckförbrukning i skuggor är endast tillgänglig för utdataprofiler (skrivare).</v>
+        <v>Fyra raka banor genom a*b*-planet vid en konstant, medvetet mörk ljushet, förda genom den valda B2A-tabellen. Alla sampel har samma L*, så varje abrupt steg eller omkastning i ett färgmedel kommer enbart från hanteringen av nyans och kroma — signaturen för en gamutmappningsartefakt i skuggorna.</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>Constant L* plane</v>
+        <v>Ink usage in shadows is only available for output (printer) profiles.</v>
       </c>
       <c r="B296" t="str">
-        <v>Plan med konstant L*</v>
+        <v>Bläckförbrukning i skuggor är endast tillgänglig för utdataprofiler (skrivare).</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>black-point compensated from</v>
+        <v>Constant L* plane</v>
       </c>
       <c r="B297" t="str">
-        <v>svartpunktskompenserad från</v>
+        <v>Plan med konstant L*</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>Position along path</v>
+        <v>black-point compensated from</v>
       </c>
       <c r="B298" t="str">
-        <v>Position längs banan</v>
+        <v>svartpunktskompenserad från</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>Path</v>
+        <v>Position along path</v>
       </c>
       <c r="B299" t="str">
-        <v>Bana</v>
+        <v>Position längs banan</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Primary-Inking Paths through Neutral</v>
+        <v>Path</v>
       </c>
       <c r="B300" t="str">
-        <v>Primärbläckvägar genom neutralt</v>
+        <v>Bana</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Three in-gamut paths — Cyan→Red, Magenta→Green, Yellow→Blue — each routed through the neutral axis at the midpoint lightness of its endpoints, run through the selected B2A table. Every sample is inside the gamut, so unlike the shadow paths any abrupt step or reversal in a colorant is a CLUT-smoothness defect rather than a gamut-mapping artefact.</v>
+        <v>Primary-Inking Paths through Neutral</v>
       </c>
       <c r="B301" t="str">
-        <v>Tre vägar inom färgomfånget — cyan→röd, magenta→grön, gul→blå — var och en genom neutralaxeln vid mittljusheten för sina ändpunkter, genom den valda B2A-tabellen. Varje sampel ligger inom omfånget, så till skillnad från skuggvägarna är varje plötsligt steg eller omkastning i ett färgämne ett CLUT-jämnhetsfel snarare än en omfångsmappningsartefakt.</v>
+        <v>Primärbläckvägar genom neutralt</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Primary-inking paths are only available for output (printer) profiles.</v>
+        <v>Three in-gamut paths — Cyan→Red, Magenta→Green, Yellow→Blue — each routed through the neutral axis at the midpoint lightness of its endpoints, run through the selected B2A table. Every sample is inside the gamut, so unlike the shadow paths any abrupt step or reversal in a colorant is a CLUT-smoothness defect rather than a gamut-mapping artefact.</v>
       </c>
       <c r="B302" t="str">
-        <v>Primärbläckvägar är endast tillgängliga för utdataprofiler (skrivare).</v>
+        <v>Tre vägar inom färgomfånget — cyan→röd, magenta→grön, gul→blå — var och en genom neutralaxeln vid mittljusheten för sina ändpunkter, genom den valda B2A-tabellen. Varje sampel ligger inom omfånget, så till skillnad från skuggvägarna är varje plötsligt steg eller omkastning i ett färgämne ett CLUT-jämnhetsfel snarare än en omfångsmappningsartefakt.</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Position along path (neutral at midpoint)</v>
+        <v>Primary-inking paths are only available for output (printer) profiles.</v>
       </c>
       <c r="B303" t="str">
-        <v>Position längs vägen (neutralt i mitten)</v>
+        <v>Primärbläckvägar är endast tillgängliga för utdataprofiler (skrivare).</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Black-point compensated for this intent.</v>
+        <v>Position along path (neutral at midpoint)</v>
       </c>
       <c r="B304" t="str">
-        <v>Svartpunktskompensation tillämpad för denna återgivning.</v>
+        <v>Position längs vägen (neutralt i mitten)</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Ink Usage Statistics</v>
+        <v>Black-point compensated for this intent.</v>
       </c>
       <c r="B305" t="str">
-        <v>Statistik för färgförbrukning</v>
+        <v>Svartpunktskompensation tillämpad för denna återgivning.</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>How much of each colorant the profile lays down, as a sum and as a share of the total — the ink-consumption signature of the separation.</v>
+        <v>Ink Usage Statistics</v>
       </c>
       <c r="B306" t="str">
-        <v>Hur mycket av varje färgämne profilen lägger på, som summa och som andel av totalen — separationens signatur för färgförbrukning.</v>
+        <v>Statistik för färgförbrukning</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>Ink usage statistics are only available for output (printer) profiles.</v>
+        <v>How much of each colorant the profile lays down, as a sum and as a share of the total — the ink-consumption signature of the separation.</v>
       </c>
       <c r="B307" t="str">
-        <v>Statistik för färgförbrukning är endast tillgänglig för utdataprofiler (skrivare).</v>
+        <v>Hur mycket av varje färgämne profilen lägger på, som summa och som andel av totalen — separationens signatur för färgförbrukning.</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Neutral axis</v>
+        <v>Ink usage statistics are only available for output (printer) profiles.</v>
       </c>
       <c r="B308" t="str">
-        <v>Neutralaxel</v>
+        <v>Statistik för färgförbrukning är endast tillgänglig för utdataprofiler (skrivare).</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>Mean coverage</v>
+        <v>Neutral axis</v>
       </c>
       <c r="B309" t="str">
-        <v>Medeltäckning</v>
+        <v>Neutralaxel</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>Share of ink</v>
+        <v>Mean coverage</v>
       </c>
       <c r="B310" t="str">
-        <v>Färgandel</v>
+        <v>Medeltäckning</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>Share of ink is the neutral-build fingerprint — each colorant’s fraction of the total ink laid down, independent of the sample count.</v>
+        <v>Share of ink</v>
       </c>
       <c r="B311" t="str">
-        <v>Färgandelen är fingeravtrycket för neutraluppbyggnaden — varje färgämnes andel av den totala pålagda färgen, oberoende av antalet sampel.</v>
+        <v>Färgandel</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>On &amp; in-gamut points</v>
+        <v>Share of ink is the neutral-build fingerprint — each colorant’s fraction of the total ink laid down, independent of the sample count.</v>
       </c>
       <c r="B312" t="str">
-        <v>Punkter inom omfånget</v>
+        <v>Färgandelen är fingeravtrycket för neutraluppbyggnaden — varje färgämnes andel av den totala pålagda färgen, oberoende av antalet sampel.</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>Ink usage across all in-gamut colours needs the B2A-direction gamut boundary, which is not yet built — pending.</v>
+        <v>On &amp; in-gamut points</v>
       </c>
       <c r="B313" t="str">
-        <v>Färgförbrukning över alla färger i omfånget kräver B2A-omfångsgränsen, som ännu inte är byggd — kommer senare.</v>
+        <v>Punkter inom omfånget</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>No colorant data to summarize.</v>
+        <v>Ink usage across all in-gamut colours needs the B2A-direction gamut boundary, which is not yet built — pending.</v>
       </c>
       <c r="B314" t="str">
-        <v>Inga färgämnesdata att sammanfatta.</v>
+        <v>Färgförbrukning över alla färger i omfånget kräver B2A-omfångsgränsen, som ännu inte är byggd — kommer senare.</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>Select a B2A (PCS→device) table below to also see a grayscale ink-coverage image for each colorant.</v>
+        <v>No colorant data to summarize.</v>
       </c>
       <c r="B315" t="str">
-        <v>Välj en B2A-tabell (PCS→enhet) nedan för att även visa en gråskalebild av färgtäckningen för varje färgämne.</v>
+        <v>Inga färgämnesdata att sammanfatta.</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>Ink coverage of each colorant across the same lattice (darker = more ink).</v>
+        <v>Select a B2A (PCS→device) table below to also see a grayscale ink-coverage image for each colorant.</v>
       </c>
       <c r="B316" t="str">
-        <v>Färgtäckning för varje färgämne över samma gitter (mörkare = mer färg).</v>
+        <v>Välj en B2A-tabell (PCS→enhet) nedan för att även visa en gråskalebild av färgtäckningen för varje färgämne.</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>Cyan</v>
+        <v>Ink coverage of each colorant across the same lattice (darker = more ink).</v>
       </c>
       <c r="B317" t="str">
-        <v>Cyan</v>
+        <v>Färgtäckning för varje färgämne över samma gitter (mörkare = mer färg).</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>Magenta</v>
+        <v>Cyan</v>
       </c>
       <c r="B318" t="str">
-        <v>Magenta</v>
+        <v>Cyan</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>Yellow</v>
+        <v>Magenta</v>
       </c>
       <c r="B319" t="str">
-        <v>Gul</v>
+        <v>Magenta</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>Red</v>
+        <v>Yellow</v>
       </c>
       <c r="B320" t="str">
-        <v>Röd</v>
+        <v>Gul</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>Green</v>
+        <v>Red</v>
       </c>
       <c r="B321" t="str">
-        <v>Grön</v>
+        <v>Röd</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>Blue</v>
+        <v>Green</v>
       </c>
       <c r="B322" t="str">
-        <v>Blå</v>
+        <v>Grön</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>Black</v>
+        <v>Blue</v>
       </c>
       <c r="B323" t="str">
-        <v>Svart</v>
+        <v>Blå</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>Perceptual</v>
+        <v>Black</v>
       </c>
       <c r="B324" t="str">
-        <v>Perceptuell</v>
+        <v>Svart</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Perceptual</v>
       </c>
       <c r="B325" t="str">
-        <v>Relativ kolorimetrisk</v>
+        <v>Perceptuell</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>Saturation</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B326" t="str">
-        <v>Mättnad</v>
+        <v>Relativ kolorimetrisk</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>Saturation</v>
       </c>
       <c r="B327" t="str">
-        <v>Absolut kolorimetrisk</v>
+        <v>Mättnad</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>Profile Statistics</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B328" t="str">
-        <v>Profilstatistik</v>
+        <v>Absolut kolorimetrisk</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B329" t="str">
-        <v>Profilövergripande mått per renderingsavsikt: gamutvolymen som omsluts av enhet→PCS-transformen (ΔE*ab³) och B2A-rundturens noggrannhet — ΔE*ab för en Lab → enhet → Lab-rundtur genom profilen.</v>
+        <v>Profilstatistik</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B330" t="str">
-        <v>Inga enhet↔PCS-CLUT:ar i den här profilen — profilstatistiken gäller inte (t.ex. en matris/TRC-skärmprofil).</v>
+        <v>Profilövergripande mått per renderingsavsikt: gamutvolymen som omsluts av enhet→PCS-transformen (ΔE*ab³) och B2A-rundturens noggrannhet — ΔE*ab för en Lab → enhet → Lab-rundtur genom profilen.</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>Rendering intent</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B331" t="str">
-        <v>Renderingsavsikt</v>
+        <v>Inga enhet↔PCS-CLUT:ar i den här profilen — profilstatistiken gäller inte (t.ex. en matris/TRC-skärmprofil).</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B332" t="str">
-        <v>Gamutvolym (ΔE³)</v>
+        <v>Renderingsavsikt</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>Round-trip ΔE</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B333" t="str">
-        <v>Rundtur-ΔE</v>
+        <v>Gamutvolym (ΔE³)</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B334" t="str">
-        <v>Gamytens gräns kollapsade eller var mestadels odefinierad, så denna gamutvolym är otillförlitlig.</v>
+        <v>Rundtur-ΔE</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>mean</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B335" t="str">
-        <v>medel</v>
+        <v>Gamytens gräns kollapsade eller var mestadels odefinierad, så denna gamutvolym är otillförlitlig.</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>P90</v>
+        <v>mean</v>
       </c>
       <c r="B336" t="str">
-        <v>P90</v>
+        <v>medel</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>max</v>
+        <v>P90</v>
       </c>
       <c r="B337" t="str">
-        <v>max</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>Analysing…</v>
+        <v>max</v>
       </c>
       <c r="B338" t="str">
-        <v>Analyserar…</v>
+        <v>max</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>Analysis</v>
+        <v>Analysing…</v>
       </c>
       <c r="B339" t="str">
-        <v>Analys</v>
+        <v>Analyserar…</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Analysis</v>
       </c>
       <c r="B340" t="str">
-        <v>Kvalitetsanalyser för hela profilen, härledda från enhet→PCS-transformen.</v>
+        <v>Analys</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>Plot</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B341" t="str">
-        <v>Diagram</v>
+        <v>Kvalitetsanalyser för hela profilen, härledda från enhet→PCS-transformen.</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>Raw Output</v>
+        <v>Plot</v>
       </c>
       <c r="B342" t="str">
-        <v>Rådata</v>
+        <v>Diagram</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>XML</v>
+        <v>Raw Output</v>
       </c>
       <c r="B343" t="str">
-        <v>XML</v>
+        <v>Rådata</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
       <c r="B344" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>Curves</v>
+        <v>JSON</v>
       </c>
       <c r="B345" t="str">
-        <v>Kurvor</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>Input curves</v>
+        <v>Curves</v>
       </c>
       <c r="B346" t="str">
-        <v>Ingångskurvor</v>
+        <v>Kurvor</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>Output curves</v>
+        <v>Input curves</v>
       </c>
       <c r="B347" t="str">
-        <v>Utgångskurvor</v>
+        <v>Ingångskurvor</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>CLUT image</v>
+        <v>Output curves</v>
       </c>
       <c r="B348" t="str">
-        <v>CLUT-bild</v>
+        <v>Utgångskurvor</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>Gamut image</v>
+        <v>CLUT image</v>
       </c>
       <c r="B349" t="str">
-        <v>Gamut-bild</v>
+        <v>CLUT-bild</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>Chromaticity</v>
+        <v>Gamut image</v>
       </c>
       <c r="B350" t="str">
-        <v>Kromaticitet</v>
+        <v>Gamut-bild</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>Scatter plot</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B351" t="str">
-        <v>Spridningsdiagram</v>
+        <v>Kromaticitet</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>Tone response curve</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B352" t="str">
-        <v>Tonkurva</v>
+        <v>Spridningsdiagram</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>Curve table</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B353" t="str">
-        <v>Kurvtabell</v>
+        <v>Tonkurva</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>Tables</v>
+        <v>Curve table</v>
       </c>
       <c r="B354" t="str">
-        <v>Tabeller</v>
+        <v>Kurvtabell</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>Data</v>
+        <v>Tables</v>
       </c>
       <c r="B355" t="str">
-        <v>Data</v>
+        <v>Tabeller</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>Evaluate</v>
+        <v>Data</v>
       </c>
       <c r="B356" t="str">
-        <v>Utvärdera</v>
+        <v>Data</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>Loading…</v>
+        <v>Evaluate</v>
       </c>
       <c r="B357" t="str">
-        <v>Läser in…</v>
+        <v>Utvärdera</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>Input</v>
+        <v>Loading…</v>
       </c>
       <c r="B358" t="str">
-        <v>Ingång</v>
+        <v>Läser in…</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>Output</v>
+        <v>Input</v>
       </c>
       <c r="B359" t="str">
-        <v>Utgång</v>
+        <v>Ingång</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>Floating point</v>
+        <v>Output</v>
       </c>
       <c r="B360" t="str">
-        <v>Flyttal</v>
+        <v>Utgång</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>Grid point</v>
+        <v>Floating point</v>
       </c>
       <c r="B361" t="str">
-        <v>Rutnätspunkt</v>
+        <v>Flyttal</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>Normalized</v>
+        <v>Grid point</v>
       </c>
       <c r="B362" t="str">
-        <v>Normaliserad</v>
+        <v>Rutnätspunkt</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>Human</v>
+        <v>Normalized</v>
       </c>
       <c r="B363" t="str">
-        <v>Läsbar</v>
+        <v>Normaliserad</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>Device → PCS</v>
+        <v>Human</v>
       </c>
       <c r="B364" t="str">
-        <v>Enhet → PCS</v>
+        <v>Läsbar</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>PCS → Device</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B365" t="str">
-        <v>PCS → Enhet</v>
+        <v>Enhet → PCS</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>No CLUT grid</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B366" t="str">
-        <v>Inget CLUT-rutnät</v>
+        <v>PCS → Enhet</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>Loading…</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B367" t="str">
-        <v>Läser in…</v>
+        <v>Inget CLUT-rutnät</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Loading…</v>
       </c>
       <c r="B368" t="str">
-        <v>Neutral = inom gamut · röd = utanför gamut</v>
+        <v>Läser in…</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B369" t="str">
-        <v>Ogiltig profil-URL:</v>
+        <v>Neutral = inom gamut · röd = utanför gamut</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B370" t="str">
-        <v>Det gick inte att hämta profilen från</v>
+        <v>Ogiltig profil-URL:</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B371" t="str">
-        <v>Läsa in en ICC-profil från denna externa webbplats?</v>
+        <v>Det gick inte att hämta profilen från</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B372" t="str">
-        <v>Laddar Profile Assessment WG-rapport…</v>
+        <v>Läsa in en ICC-profil från denna externa webbplats?</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B373" t="str">
-        <v>Kör Profile Assessment WG-kontroller…</v>
+        <v>Laddar Profile Assessment WG-rapport…</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B374" t="str">
-        <v>Profile Assessment WG-rapport</v>
+        <v>Kör Profile Assessment WG-kontroller…</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>Security</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B375" t="str">
-        <v>Säkerhet</v>
+        <v>Profile Assessment WG-rapport</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>Conformance</v>
+        <v>Security</v>
       </c>
       <c r="B376" t="str">
-        <v>Överensstämmelse</v>
+        <v>Säkerhet</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>Quality</v>
+        <v>Conformance</v>
       </c>
       <c r="B377" t="str">
-        <v>Kvalitet</v>
+        <v>Överensstämmelse</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>REPORT</v>
+        <v>Quality</v>
       </c>
       <c r="B378" t="str">
-        <v>RAPPORT</v>
+        <v>Kvalitet</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>FAIL</v>
+        <v>REPORT</v>
       </c>
       <c r="B379" t="str">
-        <v>UNDERKÄND</v>
+        <v>RAPPORT</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>checks</v>
+        <v>FAIL</v>
       </c>
       <c r="B380" t="str">
-        <v>kontroller</v>
+        <v>UNDERKÄND</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>checks</v>
       </c>
       <c r="B381" t="str">
-        <v>Genererad av iccPawgReport (iccDEV) · checklista från ICC Profile Assessment Working Group.</v>
+        <v>kontroller</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B382" t="str">
-        <v>ICC-profilverktyg · drivs av IccProfLib</v>
+        <v>Genererad av iccPawgReport (iccDEV) · checklista från ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>ICC Profile Tool</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B383" t="str">
-        <v>ICC-profilverktyg</v>
+        <v>ICC-profilverktyg · drivs av IccProfLib</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>Powered by {lib}</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B384" t="str">
-        <v>Drivs av {lib}</v>
+        <v>ICC-profilverktyg</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Subscribe</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B385" t="str">
-        <v>Prenumerera</v>
+        <v>Drivs av {lib}</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Subscribe</v>
       </c>
       <c r="B386" t="str">
-        <v>Få besked om nya profiletool-versioner</v>
+        <v>Prenumerera</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>Get notified about new releases</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B387" t="str">
-        <v>Få besked om nya versioner</v>
+        <v>Få besked om nya profiletool-versioner</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Close</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B388" t="str">
-        <v>Stäng</v>
+        <v>Få besked om nya versioner</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Close</v>
       </c>
       <c r="B389" t="str">
-        <v>Vi mejlar dig när en ny större eller mindre version av profiletool släpps. Patchversioner hoppas över. Din adress granskas manuellt innan den läggs till.</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>Email address</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B390" t="str">
-        <v>E-postadress</v>
+        <v>Vi mejlar dig när en ny större eller mindre version av profiletool släpps. Patchversioner hoppas över. Din adress granskas manuellt innan den läggs till.</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>you@example.com</v>
+        <v>Email address</v>
       </c>
       <c r="B391" t="str">
-        <v>du@exempel.com</v>
+        <v>E-postadress</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>How will you use profiletool?</v>
+        <v>you@example.com</v>
       </c>
       <c r="B392" t="str">
-        <v>Hur kommer du att använda profiletool?</v>
+        <v>du@exempel.com</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>(optional)</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B393" t="str">
-        <v>(valfritt)</v>
+        <v>Hur kommer du att använda profiletool?</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>(optional)</v>
       </c>
       <c r="B394" t="str">
-        <v>t.ex. utvärdera ICC-profiler för tryckkalibrering</v>
+        <v>(valfritt)</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B395" t="str">
-        <v>Jag godkänner att ta emot e-post om profiletool-versioner. Jag kan avsluta prenumerationen när som helst.</v>
+        <v>t.ex. utvärdera ICC-profiler för tryckkalibrering</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Cancel</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B396" t="str">
-        <v>Avbryt</v>
+        <v>Jag godkänner att ta emot e-post om profiletool-versioner. Jag kan avsluta prenumerationen när som helst.</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Subscribe</v>
+        <v>Cancel</v>
       </c>
       <c r="B397" t="str">
-        <v>Prenumerera</v>
+        <v>Avbryt</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B398" t="str">
-        <v>Tack — vi hör av oss.</v>
+        <v>Prenumerera</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B399" t="str">
-        <v>När du har godkänts får du ett välkomstmejl. Därefter hör du bara från oss när en ny version av profiletool släpps.</v>
+        <v>Tack — vi hör av oss.</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>Close</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B400" t="str">
-        <v>Stäng</v>
+        <v>När du har godkänts får du ett välkomstmejl. Därefter hör du bara från oss när en ny version av profiletool släpps.</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>Privacy notice</v>
+        <v>Close</v>
       </c>
       <c r="B401" t="str">
-        <v>Integritetsmeddelande</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B402" t="str">
-        <v>Ange en giltig e-postadress.</v>
+        <v>Integritetsmeddelande</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B403" t="str">
-        <v>För många förfrågningar. Försök igen senare.</v>
+        <v>Ange en giltig e-postadress.</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B404" t="str">
-        <v>Kontrollera formuläret och försök igen.</v>
+        <v>För många förfrågningar. Försök igen senare.</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B405" t="str">
-        <v>Det gick inte att skicka din förfrågan. Försök igen.</v>
+        <v>Kontrollera formuläret och försök igen.</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B406" t="str">
-        <v>Nätverksfel. Försök igen.</v>
+        <v>Det gick inte att skicka din förfrågan. Försök igen.</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>Error:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B407" t="str">
-        <v>Fel:</v>
+        <v>Nätverksfel. Försök igen.</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>Convert to XML</v>
+        <v>Error:</v>
       </c>
       <c r="B408" t="str">
-        <v>Konvertera till XML</v>
+        <v>Fel:</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B409" t="str">
-        <v>Konvertera till JSON</v>
+        <v>Konvertera till XML</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B410" t="str">
-        <v>Konvertera till ICC</v>
+        <v>Konvertera till JSON</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B411" t="str">
-        <v>Konverterar till XML…</v>
+        <v>Konvertera till ICC</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B412" t="str">
-        <v>Konverterar till JSON…</v>
+        <v>Konverterar till XML…</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B413" t="str">
-        <v>Konverterar till ICC…</v>
+        <v>Konverterar till JSON…</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B414" t="str">
-        <v>Läs in ICC-profil</v>
+        <v>Konverterar till ICC…</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B415" t="str">
-        <v>Släppzon för ICC-profilfiler</v>
+        <v>Läs in ICC-profil</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>Profile ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B416" t="str">
-        <v>Profil-ID</v>
+        <v>Släppzon för ICC-profilfiler</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>No tags found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B417" t="str">
-        <v>Inga taggar hittades.</v>
+        <v>Profil-ID</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>Tag Name</v>
+        <v>No tags found.</v>
       </c>
       <c r="B418" t="str">
-        <v>Taggnamn</v>
+        <v>Inga taggar hittades.</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>ID</v>
+        <v>Tag Name</v>
       </c>
       <c r="B419" t="str">
-        <v>ID</v>
+        <v>Taggnamn</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
       <c r="B420" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>Size</v>
+        <v>Offset</v>
       </c>
       <c r="B421" t="str">
-        <v>Storlek</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Pad</v>
+        <v>Size</v>
       </c>
       <c r="B422" t="str">
-        <v>Utfyllnad</v>
+        <v>Storlek</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>Bytes changed since load</v>
+        <v>Pad</v>
       </c>
       <c r="B423" t="str">
-        <v>Byte ändrade sedan inläsning</v>
+        <v>Utfyllnad</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>Type</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B424" t="str">
-        <v>Typ</v>
+        <v>Byte ändrade sedan inläsning</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>Array of {type}</v>
+        <v>Type</v>
       </c>
       <c r="B425" t="str">
-        <v>Array av {type}</v>
+        <v>Typ</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>(No content)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B426" t="str">
-        <v>(Inget innehåll)</v>
+        <v>Array av {type}</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>bytes</v>
+        <v>(No content)</v>
       </c>
       <c r="B427" t="str">
-        <v>byte</v>
+        <v>(Inget innehåll)</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>Loading full description…</v>
+        <v>bytes</v>
       </c>
       <c r="B428" t="str">
-        <v>Läser in fullständig beskrivning…</v>
+        <v>byte</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>Could not load full description:</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B429" t="str">
-        <v>Kunde inte läsa in fullständig beskrivning:</v>
+        <v>Läser in fullständig beskrivning…</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B430" t="str">
-        <v>Den här profilen kunde inte tolkas helt och får inte tillämpas. Huvudet och taggkatalogen nedan visas endast för granskning.</v>
+        <v>Kunde inte läsa in fullständig beskrivning:</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B431" t="str">
-        <v>Tagginnehåll otillgängligt — profilen kunde inte tolkas helt.</v>
+        <v>Den här profilen kunde inte tolkas helt och får inte tillämpas. Huvudet och taggkatalogen nedan visas endast för granskning.</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>No validation output</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B432" t="str">
-        <v>Ingen valideringsutdata</v>
+        <v>Tagginnehåll otillgängligt — profilen kunde inte tolkas helt.</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Profile is valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B433" t="str">
-        <v>Profilen är giltig</v>
+        <v>Ingen valideringsutdata</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B434" t="str">
-        <v>Profilen har varning(ar)</v>
+        <v>Profilen är giltig</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B435" t="str">
-        <v>Profilen följer inte specifikationen</v>
+        <v>Profilen har varning(ar)</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B436" t="str">
-        <v>Kritiskt valideringsfel</v>
+        <v>Profilen följer inte specifikationen</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B437" t="str">
-        <v>Okänd valideringsstatus</v>
+        <v>Kritiskt valideringsfel</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B438" t="str">
-        <v>Kritiskt — visas endast för granskning</v>
+        <v>Okänd valideringsstatus</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B439" t="str">
-        <v>Inga varningar eller fel hittades.</v>
+        <v>Kritiskt — visas endast för granskning</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>Valid</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B440" t="str">
-        <v>Giltig</v>
+        <v>Inga varningar eller fel hittades.</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>Warning</v>
+        <v>Valid</v>
       </c>
       <c r="B441" t="str">
-        <v>Varning</v>
+        <v>Giltig</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>Error</v>
+        <v>Warning</v>
       </c>
       <c r="B442" t="str">
-        <v>Fel</v>
+        <v>Varning</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>Unknown</v>
+        <v>Error</v>
       </c>
       <c r="B443" t="str">
-        <v>Okänd</v>
+        <v>Fel</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>Pass</v>
+        <v>Unknown</v>
       </c>
       <c r="B444" t="str">
-        <v>Godkänd</v>
+        <v>Okänd</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="B445" t="str">
-        <v>Underkänd</v>
+        <v>Godkänd</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>View in context</v>
+        <v>Fail</v>
       </c>
       <c r="B446" t="str">
-        <v>Visa i sammanhang</v>
+        <v>Underkänd</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>Validation detail</v>
+        <v>View in context</v>
       </c>
       <c r="B447" t="str">
-        <v>Valideringsdetalj</v>
+        <v>Visa i sammanhang</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Triggered by</v>
+        <v>Validation detail</v>
       </c>
       <c r="B448" t="str">
-        <v>Utlöst av</v>
+        <v>Valideringsdetalj</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>Field</v>
+        <v>Triggered by</v>
       </c>
       <c r="B449" t="str">
-        <v>Fält</v>
+        <v>Utlöst av</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Current value</v>
+        <v>Field</v>
       </c>
       <c r="B450" t="str">
-        <v>Aktuellt värde</v>
+        <v>Fält</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>Required: 0</v>
+        <v>Current value</v>
       </c>
       <c r="B451" t="str">
-        <v>Krävs: 0</v>
+        <v>Aktuellt värde</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>Expected: {value}</v>
+        <v>Required: 0</v>
       </c>
       <c r="B452" t="str">
-        <v>Förväntat: {value}</v>
+        <v>Krävs: 0</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>Invalid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B453" t="str">
-        <v>Ogiltigt</v>
+        <v>Förväntat: {value}</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Invalid</v>
       </c>
       <c r="B454" t="str">
-        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
+        <v>Ogiltigt</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>Close</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B455" t="str">
-        <v>Stäng</v>
+        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>Loading XML editor…</v>
+        <v>Close</v>
       </c>
       <c r="B456" t="str">
-        <v>Läser in XML-redigeraren…</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B457" t="str">
-        <v>Läser in JSON-redigeraren…</v>
+        <v>Läser in XML-redigeraren…</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B458" t="str">
-        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>Läser in JSON-redigeraren…</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B459" t="str">
-        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B460" t="str">
-        <v>● osparade XML-ändringar</v>
+        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B461" t="str">
-        <v>● osparade JSON-ändringar</v>
+        <v>● osparade XML-ändringar</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B462" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
+        <v>● osparade JSON-ändringar</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B463" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
+        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B464" t="str">
-        <v>indrag</v>
+        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>sort keys</v>
+        <v>indent</v>
       </c>
       <c r="B465" t="str">
-        <v>sortera nycklar</v>
+        <v>indrag</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B466" t="str">
+        <v>sortera nycklar</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B466" t="str">
+      <c r="B467" t="str">
         <v>Profilen skrevs från ändringarna, men omvalideringen misslyckades:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B466"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B467"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Sv.xlsx
+++ b/translations/Eng-Sv.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B706"/>
+  <dimension ref="A1:B707"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -3475,26 +3475,26 @@
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>HDR Profile in the chain</v>
+        <v>HDR ColorSpace Profile in the chain</v>
       </c>
       <c r="B384" t="str">
-        <v>HDR-profil i kedjan</v>
+        <v>HDR ColorSpace-profil i kedjan</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Transforms through an HDR Profile use its AToB0Tag — the baked SDR rendering required by clause 8.10.6 — because clause 8.10.1 leaves it no TRC tags. The result is that fallback, not HDR behaviour.</v>
+        <v>Transforms through an HDR ColorSpace Profile use its AToB0Tag — the baked SDR rendering required by clause 8.7.1.5 — because a ColorSpace profile has no TRC tags. The result is that fallback, not HDR behaviour.</v>
       </c>
       <c r="B385" t="str">
-        <v>Transformationer genom en HDR-profil använder dess AToB0Tag — den fasta SDR-återgivning som klausul 8.10.6 kräver — eftersom klausul 8.10.1 inte lämnar den några TRC-taggar. Resultatet är den reserven, inte HDR-beteende.</v>
+        <v>Transformationer genom en HDR ColorSpace-profil använder dess AToB0Tag — den fasta SDR-återgivning som klausul 8.7.1.5 kräver — eftersom en ColorSpace-profil inte har några TRC-taggar. Resultatet är den reserven, inte HDR-beteende.</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>These are HDR Profiles, which carry no TRC tags, so the gamut is built from the AToB0Tag — the baked SDR rendering clause 8.10.6 requires for consumers without HDR processing. It is not the profile’s HDR gamut, which cannot be drawn in a bounded PCS.</v>
+        <v>These are HDR ColorSpace Profiles, which carry no TRC tags, so the gamut is built from the AToB0Tag — the baked SDR rendering clause 8.7.1.5 requires for consumers without HDR processing. It is not the profile’s HDR gamut, which cannot be drawn in a bounded PCS.</v>
       </c>
       <c r="B386" t="str">
-        <v>Detta är HDR-profiler utan TRC-taggar, så färgomfånget byggs från AToB0Tag — den fasta SDR-återgivning som klausul 8.10.6 kräver för konsumenter utan HDR-bearbetning. Det är inte profilens HDR-omfång, som inte kan ritas i ett begränsat PCS.</v>
+        <v>Detta är HDR ColorSpace-profiler utan TRC-taggar, så färgomfånget byggs från AToB0Tag — den fasta SDR-återgivning som klausul 8.7.1.5 kräver för konsumenter utan HDR-bearbetning. Det är inte profilens HDR-omfång, som inte kan ritas i ett begränsat PCS.</v>
       </c>
     </row>
     <row r="387">
@@ -4651,10 +4651,10 @@
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>File 1.0 = 1 cd/m² (ICC.1 clause 8.10.2 a)</v>
+        <v>File 1.0 = 1 cd/m² (ICC.1 clause 8.7.1.2 a)</v>
       </c>
       <c r="B531" t="str">
-        <v>Fil 1,0 = 1 cd/m² (ICC.1 avsnitt 8.10.2 a)</v>
+        <v>Fil 1,0 = 1 cd/m² (ICC.1 avsnitt 8.7.1.2 a)</v>
       </c>
     </row>
     <row r="532">
@@ -4715,10 +4715,10 @@
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>Auto (clause 8.10.3 ranking)</v>
+        <v>Auto (clause 8.7.1.3 ranking)</v>
       </c>
       <c r="B539" t="str">
-        <v>Auto (rangordning enligt 8.10.3)</v>
+        <v>Auto (rangordning enligt 8.7.1.3)</v>
       </c>
     </row>
     <row r="540">
@@ -4779,10 +4779,10 @@
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>HDR Profiles</v>
+        <v>HDR ColorSpace Profiles</v>
       </c>
       <c r="B547" t="str">
-        <v>HDR-profiler</v>
+        <v>HDR ColorSpace-profiler</v>
       </c>
     </row>
     <row r="548">
@@ -4803,1263 +4803,1271 @@
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>HDR Profiles — Linear transfer</v>
+        <v>HDR ColorSpace Profiles — Linear transfer</v>
       </c>
       <c r="B550" t="str">
-        <v>HDR-profiler – linjär överföring</v>
+        <v>HDR ColorSpace-profiler – linjär överföring</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>HDR Profiles — PQ / HLG transfer</v>
+        <v>HDR ColorSpace Profiles — PQ / HLG transfer</v>
       </c>
       <c r="B551" t="str">
-        <v>HDR-profiler – PQ/HLG-överföring</v>
+        <v>HDR ColorSpace-profiler – PQ/HLG-överföring</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
+        <v>{format} holds linear light, so only HDR ColorSpace Profiles with a Linear transfer can be assigned.</v>
       </c>
       <c r="B552" t="str">
-        <v>{format} innehåller linjärt ljus, så bara HDR-profiler med linjär överföring kan tilldelas.</v>
+        <v>{format} innehåller linjärt ljus, så bara HDR ColorSpace-profiler med linjär överföring kan tilldelas.</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
+        <v>{n} PQ/HLG HDR ColorSpace Profile(s) in the pool are not offered — the Profiles pane lists them under HDR ColorSpace Profiles › Non-linear transfer.</v>
       </c>
       <c r="B553" t="str">
-        <v>{n} PQ/HLG-HDR-profil(er) i poolen erbjuds inte – profilpanelen listar dem under HDR-profiler › Icke-linjär överföring.</v>
+        <v>{n} PQ/HLG-HDR ColorSpace-profil(er) i poolen erbjuds inte – profilpanelen listar dem under HDR ColorSpace-profiler › Icke-linjär överföring.</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
+        <v>There is no Linear-transfer HDR ColorSpace Profile in the pool yet; the Profiles pane groups HDR ColorSpace Profiles by transfer.</v>
       </c>
       <c r="B554" t="str">
-        <v>Det finns ännu ingen HDR-profil med linjär överföring i poolen; profilpanelen grupperar HDR-profiler efter överföring.</v>
+        <v>Det finns ännu ingen HDR ColorSpace-profil med linjär överföring i poolen; profilpanelen grupperar HDR ColorSpace-profiler efter överföring.</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>Unspecified primaries: no HDR path in this build</v>
       </c>
       <c r="B555" t="str">
-        <v>IccProfLib avböjer att tillämpa den här förstärkningskurvan: {why}. En CMM faller tillbaka på nästa tonmappningsbeskrivning (avsnitt 8.10.3).</v>
+        <v>Ospecificerade primärfärger: ingen HDR-väg i den här versionen</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>Display headroom</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.7.1.3).</v>
       </c>
       <c r="B556" t="str">
-        <v>Skärmutrymme</v>
+        <v>IccProfLib avböjer att tillämpa den här förstärkningskurvan: {why}. En CMM faller tillbaka på nästa tonmappningsbeskrivning (avsnitt 8.7.1.3).</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>Display headroom</v>
       </c>
       <c r="B557" t="str">
-        <v>{n} steg (≈{r}× referensvitt)</v>
+        <v>Skärmutrymme</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Baseline</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B558" t="str">
-        <v>Bas</v>
+        <v>{n} steg (≈{r}× referensvitt)</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Preview through the colour engine</v>
+        <v>Baseline</v>
       </c>
       <c r="B559" t="str">
-        <v>Förhandsvisning genom färgmotorn</v>
+        <v>Bas</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>As authored (baseline {h} stops, no gain)</v>
+        <v>Preview through the colour engine</v>
       </c>
       <c r="B560" t="str">
-        <v>Som skapad (bas {h} steg, ingen förstärkning)</v>
+        <v>Förhandsvisning genom färgmotorn</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>Tone-mapped for {h} stops</v>
+        <v>As authored (baseline {h} stops, no gain)</v>
       </c>
       <c r="B561" t="str">
-        <v>Tonmappad för {h} steg</v>
+        <v>Som skapad (bas {h} steg, ingen förstärkning)</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
+        <v>Tone-mapped for {h} stops</v>
       </c>
       <c r="B562" t="str">
-        <v>Samma testpixlar ({transfer}-signal som stiger från vänster till höger: grått, sedan R, G, B, Y, C, M) genom IccProfLibs HDR-transform. Båda remsorna begränsas till {r}× HDR-referensvitt, som en skärm med {h} stegs headroom skulle visa dem: där den övre remsan klipps platt rullar förstärkningskurvan av högdagrarna.</v>
+        <v>Tonmappad för {h} steg</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>reference white</v>
+        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
       </c>
       <c r="B563" t="str">
-        <v>referensvitt</v>
+        <v>Samma testpixlar ({transfer}-signal som stiger från vänster till höger: grått, sedan R, G, B, Y, C, M) genom IccProfLibs HDR-transform. Båda remsorna begränsas till {r}× HDR-referensvitt, som en skärm med {h} stegs headroom skulle visa dem: där den övre remsan klipps platt rullar förstärkningskurvan av högdagrarna.</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>display peak</v>
+        <v>reference white</v>
       </c>
       <c r="B564" t="str">
-        <v>skärmens topp</v>
+        <v>referensvitt</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Preview unavailable: {why}</v>
+        <v>display peak</v>
       </c>
       <c r="B565" t="str">
-        <v>Förhandsvisning inte tillgänglig: {why}</v>
+        <v>skärmens topp</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>the colour engine did not take the HDR path for this profile</v>
+        <v>Preview unavailable: {why}</v>
       </c>
       <c r="B566" t="str">
-        <v>färgmotorn tog inte HDR-vägen för den här profilen</v>
+        <v>Förhandsvisning inte tillgänglig: {why}</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Gain across every headroom</v>
+        <v>the colour engine did not take the HDR path for this profile</v>
       </c>
       <c r="B567" t="str">
-        <v>Förstärkning över alla headroom</v>
+        <v>färgmotorn tog inte HDR-vägen för den här profilen</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
+        <v>Gain across every headroom</v>
       </c>
       <c r="B568" t="str">
-        <v>Förstärkning för en grå insignal vid varje skärm-headroom: blått komprimerar, rött expanderar, vitt lämnar den oförändrad. Prickade linjer markerar kurvorna i taggen, den heldragna basen och den bärnstensfärgade reglaget; den streckade diagonalen är där insignalen når skärmens topp. Klicka för att flytta reglaget.</v>
+        <v>Förstärkning över alla headroom</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Input (stops relative to HDR reference white)</v>
+        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
       </c>
       <c r="B569" t="str">
-        <v>Insignal (steg relativt HDR-referensvitt)</v>
+        <v>Förstärkning för en grå insignal vid varje skärm-headroom: blått komprimerar, rött expanderar, vitt lämnar den oförändrad. Prickade linjer markerar kurvorna i taggen, den heldragna basen och den bärnstensfärgade reglaget; den streckade diagonalen är där insignalen når skärmens topp. Klicka för att flytta reglaget.</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Display headroom (stops)</v>
+        <v>Input (stops relative to HDR reference white)</v>
       </c>
       <c r="B570" t="str">
-        <v>Skärm-headroom (steg)</v>
+        <v>Insignal (steg relativt HDR-referensvitt)</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Gain (stops)</v>
+        <v>Display headroom (stops)</v>
       </c>
       <c r="B571" t="str">
-        <v>Förstärkning (steg)</v>
+        <v>Skärm-headroom (steg)</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>Curve in the tag</v>
+        <v>Gain (stops)</v>
       </c>
       <c r="B572" t="str">
-        <v>Kurva i taggen</v>
+        <v>Förstärkning (steg)</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>Baseline</v>
+        <v>Curve in the tag</v>
       </c>
       <c r="B573" t="str">
-        <v>Bas</v>
+        <v>Kurva i taggen</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Slider</v>
+        <v>Baseline</v>
       </c>
       <c r="B574" t="str">
-        <v>Reglage</v>
+        <v>Bas</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>Input = display peak</v>
+        <v>Slider</v>
       </c>
       <c r="B575" t="str">
-        <v>Insignal = skärmens topp</v>
+        <v>Reglage</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>Grey tone curves by headroom</v>
+        <v>Input = display peak</v>
       </c>
       <c r="B576" t="str">
-        <v>Grå tonkurvor per headroom</v>
+        <v>Insignal = skärmens topp</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
+        <v>Grey tone curves by headroom</v>
       </c>
       <c r="B577" t="str">
-        <v>Den grå tonkurvan vid varje headroom som taggen lagrar, färgad från lågt (blått) till högt (rött), med reglagets kurva i bärnsten. Båda axlarna är i steg, så diagonalen betyder ingen förändring.</v>
+        <v>Grå tonkurvor per headroom</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>Output (stops relative to HDR reference white)</v>
+        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
       </c>
       <c r="B578" t="str">
-        <v>Utsignal (steg relativt HDR-referensvitt)</v>
+        <v>Den grå tonkurvan vid varje headroom som taggen lagrar, färgad från lågt (blått) till högt (rött), med reglagets kurva i bärnsten. Båda axlarna är i steg, så diagonalen betyder ingen förändring.</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>{h} stops</v>
+        <v>Output (stops relative to HDR reference white)</v>
       </c>
       <c r="B579" t="str">
-        <v>{h} steg</v>
+        <v>Utsignal (steg relativt HDR-referensvitt)</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>{h} stops (baseline)</v>
+        <v>{h} stops</v>
       </c>
       <c r="B580" t="str">
-        <v>{h} steg (bas)</v>
+        <v>{h} steg</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>At {h} stops (slider)</v>
+        <v>{h} stops (baseline)</v>
       </c>
       <c r="B581" t="str">
-        <v>Vid {h} steg (reglage)</v>
+        <v>{h} steg (bas)</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>At {h} stops (slider)</v>
       </c>
       <c r="B582" t="str">
-        <v>Kurvor i taggen, efter utrymme: {list} steg. Bas {b} steg, HDR-referensvitt {w} cd/m².</v>
+        <v>Vid {h} steg (reglage)</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B583" t="str">
-        <v>Det här utrymmet ligger utanför taggens kurvor, så närmaste kurva används oförändrad – biblioteket extrapolerar inte bortom dem.</v>
+        <v>Kurvor i taggen, efter utrymme: {list} steg. Bas {b} steg, HDR-referensvitt {w} cd/m².</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B584" t="str">
-        <v>Vissa lutningar är härledda (PCHIP) och inte lagrade i taggen. Härledningen rekonstruerar ett SMPTE-avsnitt, så betrakta de kurvornas form som preliminär.</v>
+        <v>Det här utrymmet ligger utanför taggens kurvor, så närmaste kurva används oförändrad – biblioteket extrapolerar inte bortom dem.</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B585" t="str">
-        <v>Taggen begär tonmappning mot referensvitt, så dess kurvor konstrueras av biblioteket i stället för att läsas från filen (en konstruktion från ett kommittéutkast).</v>
+        <v>Vissa lutningar är härledda (PCHIP) och inte lagrade i taggen. Härledningen rekonstruerar ett SMPTE-avsnitt, så betrakta de kurvornas form som preliminär.</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B586" t="str">
-        <v>Inga alternativa bilder: taggen begär ingen tonmappning, bara en begränsning till skärmens färgvolym.</v>
+        <v>Taggen begär tonmappning mot referensvitt, så dess kurvor konstrueras av biblioteket i stället för att läsas från filen (en konstruktion från ett kommittéutkast).</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B587" t="str">
-        <v>De två kurvorna som blandas vid detta utrymme blandar färgkanalerna olika, så det finns ingen enskild förstärkningskurva att rita. Tonkurvan nedan är ändå exakt.</v>
+        <v>Inga alternativa bilder: taggen begär ingen tonmappning, bara en begränsning till skärmens färgvolym.</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B588" t="str">
-        <v>Kurva vid {h} steg (ingen förstärkning)</v>
+        <v>De två kurvorna som blandas vid detta utrymme blandar färgkanalerna olika, så det finns ingen enskild förstärkningskurva att rita. Tonkurvan nedan är ändå exakt.</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Curve at {h} stops</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B589" t="str">
-        <v>Kurva vid {h} steg</v>
+        <v>Kurva vid {h} steg (ingen förstärkning)</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B590" t="str">
-        <v>Tillämpad vid {h} steg</v>
+        <v>Kurva vid {h} steg</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B591" t="str">
-        <v>Förstärkning vid detta utrymme</v>
+        <v>Tillämpad vid {h} steg</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B592" t="str">
-        <v>Blandad indata (linjär, 1,0 = HDR-referensvitt)</v>
+        <v>Förstärkning vid detta utrymme</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B593" t="str">
-        <v>Förstärkning (log2-steg)</v>
+        <v>Blandad indata (linjär, 1,0 = HDR-referensvitt)</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B594" t="str">
-        <v>Gråskalans tonkurva vid detta utrymme</v>
+        <v>Förstärkning (log2-steg)</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B595" t="str">
-        <v>Indata (× HDR-referensvitt)</v>
+        <v>Gråskalans tonkurva vid detta utrymme</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B596" t="str">
-        <v>Utdata (× HDR-referensvitt)</v>
+        <v>Indata (× HDR-referensvitt)</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>No change</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B597" t="str">
-        <v>Ingen ändring</v>
+        <v>Utdata (× HDR-referensvitt)</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>No change</v>
       </c>
       <c r="B598" t="str">
-        <v>Skärmens topp vid {h} steg</v>
+        <v>Ingen ändring</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>Output at {h} stops</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B599" t="str">
-        <v>Utdata vid {h} steg</v>
+        <v>Skärmens topp vid {h} steg</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B600" t="str">
-        <v>HDR, färgomfång och pixelförhållande uppdateras när fönstret flyttas till en skärm där de skiljer sig.</v>
+        <v>Utdata vid {h} steg</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Identify displays</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B601" t="str">
-        <v>Identifiera skärmar</v>
+        <v>HDR, färgomfång och pixelförhållande uppdateras när fönstret flyttas till en skärm där de skiljer sig.</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Identify displays</v>
       </c>
       <c r="B602" t="str">
-        <v>Ber om tillåtelse att se vilken skärm fönstret ligger på, så att panelen även uppdateras mellan likadana skärmar och visar HDR-utrymme där webbläsaren exponerar det.</v>
+        <v>Identifiera skärmar</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B603" t="str">
-        <v>Följer vilken skärm fönstret ligger på.</v>
+        <v>Ber om tillåtelse att se vilken skärm fönstret ligger på, så att panelen även uppdateras mellan likadana skärmar och visar HDR-utrymme där webbläsaren exponerar det.</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B604" t="str">
-        <v>Tillåtelse att identifiera skärmar nekades. Den kan ändras i webbplatsens inställningar.</v>
+        <v>Följer vilken skärm fönstret ligger på.</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B605" t="str">
-        <v>Den här webbläsaren kan inte identifiera skärmar; bara den automatiska uppdateringen ovan gäller.</v>
+        <v>Tillåtelse att identifiera skärmar nekades. Den kan ändras i webbplatsens inställningar.</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Could not identify displays.</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B606" t="str">
-        <v>Kunde inte identifiera skärmar.</v>
+        <v>Den här webbläsaren kan inte identifiera skärmar; bara den automatiska uppdateringen ovan gäller.</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>Display events</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B607" t="str">
-        <v>Skärmhändelser</v>
+        <v>Kunde inte identifiera skärmar.</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Display events</v>
       </c>
       <c r="B608" t="str">
-        <v>Inga händelser än. Dra fönstret till en annan skärm.</v>
+        <v>Skärmhändelser</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>Colour primaries</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B609" t="str">
-        <v>Färgprimärer</v>
+        <v>Inga händelser än. Dra fönstret till en annan skärm.</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>Transfer characteristics</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B610" t="str">
-        <v>Överföringsfunktion</v>
+        <v>Färgprimärer</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>Matrix coefficients</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B611" t="str">
-        <v>Matriskoefficienter</v>
+        <v>Överföringsfunktion</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>Video full-range flag</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B612" t="str">
-        <v>Flagga för fullt videoomfång</v>
+        <v>Matriskoefficienter</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>Full range</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B613" t="str">
-        <v>Fullt omfång</v>
+        <v>Flagga för fullt videoomfång</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>Narrow range</v>
+        <v>Full range</v>
       </c>
       <c r="B614" t="str">
-        <v>Begränsat omfång</v>
+        <v>Fullt omfång</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Narrow range</v>
       </c>
       <c r="B615" t="str">
-        <v>inte tilldelad av ITU-T H.273</v>
+        <v>Begränsat omfång</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B616" t="str">
-        <v>Färgprimärer 2 (Ospecificerad) hänvisar till profilen själv — primärerna hämtas från färgämnestaggarna och inte från den här taggen.</v>
+        <v>inte tilldelad av ITU-T H.273</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B617" t="str">
-        <v>De fyra reserverade byten i den här taggen är inte alla noll.</v>
+        <v>Färgprimärer 2 (Ospecificerad) hänvisar till profilen själv — primärerna hämtas från färgämnestaggarna och inte från den här taggen.</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>REPORT</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B618" t="str">
-        <v>RAPPORT</v>
+        <v>De fyra reserverade byten i den här taggen är inte alla noll.</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>FAIL</v>
+        <v>REPORT</v>
       </c>
       <c r="B619" t="str">
-        <v>UNDERKÄND</v>
+        <v>RAPPORT</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>checks</v>
+        <v>FAIL</v>
       </c>
       <c r="B620" t="str">
-        <v>kontroller</v>
+        <v>UNDERKÄND</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>checks</v>
       </c>
       <c r="B621" t="str">
-        <v>Genererad av iccPawgReport (iccDEV) · checklista från ICC Profile Assessment Working Group.</v>
+        <v>kontroller</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B622" t="str">
-        <v>ICC-profilverktyg · drivs av IccProfLib</v>
+        <v>Genererad av iccPawgReport (iccDEV) · checklista från ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>ICC Profile Tool</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B623" t="str">
-        <v>ICC-profilverktyg</v>
+        <v>ICC-profilverktyg · drivs av IccProfLib</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>Powered by {lib}</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B624" t="str">
-        <v>Drivs av {lib}</v>
+        <v>ICC-profilverktyg</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>Subscribe</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B625" t="str">
-        <v>Prenumerera</v>
+        <v>Drivs av {lib}</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Subscribe</v>
       </c>
       <c r="B626" t="str">
-        <v>Få besked om nya profiletool-versioner</v>
+        <v>Prenumerera</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>Get notified about new releases</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B627" t="str">
-        <v>Få besked om nya versioner</v>
+        <v>Få besked om nya profiletool-versioner</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>Close</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B628" t="str">
-        <v>Stäng</v>
+        <v>Få besked om nya versioner</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Close</v>
       </c>
       <c r="B629" t="str">
-        <v>Vi mejlar dig när en ny större eller mindre version av profiletool släpps. Patchversioner hoppas över. Din adress granskas manuellt innan den läggs till.</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>Email address</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B630" t="str">
-        <v>E-postadress</v>
+        <v>Vi mejlar dig när en ny större eller mindre version av profiletool släpps. Patchversioner hoppas över. Din adress granskas manuellt innan den läggs till.</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>you@example.com</v>
+        <v>Email address</v>
       </c>
       <c r="B631" t="str">
-        <v>du@exempel.com</v>
+        <v>E-postadress</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>How will you use profiletool?</v>
+        <v>you@example.com</v>
       </c>
       <c r="B632" t="str">
-        <v>Hur kommer du att använda profiletool?</v>
+        <v>du@exempel.com</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>(optional)</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B633" t="str">
-        <v>(valfritt)</v>
+        <v>Hur kommer du att använda profiletool?</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>(optional)</v>
       </c>
       <c r="B634" t="str">
-        <v>t.ex. utvärdera ICC-profiler för tryckkalibrering</v>
+        <v>(valfritt)</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B635" t="str">
-        <v>Jag godkänner att ta emot e-post om profiletool-versioner. Jag kan avsluta prenumerationen när som helst.</v>
+        <v>t.ex. utvärdera ICC-profiler för tryckkalibrering</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>Cancel</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B636" t="str">
-        <v>Avbryt</v>
+        <v>Jag godkänner att ta emot e-post om profiletool-versioner. Jag kan avsluta prenumerationen när som helst.</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>Subscribe</v>
+        <v>Cancel</v>
       </c>
       <c r="B637" t="str">
-        <v>Prenumerera</v>
+        <v>Avbryt</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B638" t="str">
-        <v>Tack — vi hör av oss.</v>
+        <v>Prenumerera</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B639" t="str">
-        <v>När du har godkänts får du ett välkomstmejl. Därefter hör du bara från oss när en ny version av profiletool släpps.</v>
+        <v>Tack — vi hör av oss.</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>Close</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B640" t="str">
-        <v>Stäng</v>
+        <v>När du har godkänts får du ett välkomstmejl. Därefter hör du bara från oss när en ny version av profiletool släpps.</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Privacy notice</v>
+        <v>Close</v>
       </c>
       <c r="B641" t="str">
-        <v>Integritetsmeddelande</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B642" t="str">
-        <v>Ange en giltig e-postadress.</v>
+        <v>Integritetsmeddelande</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B643" t="str">
-        <v>För många förfrågningar. Försök igen senare.</v>
+        <v>Ange en giltig e-postadress.</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B644" t="str">
-        <v>Kontrollera formuläret och försök igen.</v>
+        <v>För många förfrågningar. Försök igen senare.</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B645" t="str">
-        <v>Det gick inte att skicka din förfrågan. Försök igen.</v>
+        <v>Kontrollera formuläret och försök igen.</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B646" t="str">
-        <v>Nätverksfel. Försök igen.</v>
+        <v>Det gick inte att skicka din förfrågan. Försök igen.</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>Error:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B647" t="str">
-        <v>Fel:</v>
+        <v>Nätverksfel. Försök igen.</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>Convert to XML</v>
+        <v>Error:</v>
       </c>
       <c r="B648" t="str">
-        <v>Konvertera till XML</v>
+        <v>Fel:</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B649" t="str">
-        <v>Konvertera till JSON</v>
+        <v>Konvertera till XML</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B650" t="str">
-        <v>Konvertera till ICC</v>
+        <v>Konvertera till JSON</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B651" t="str">
-        <v>Konverterar till XML…</v>
+        <v>Konvertera till ICC</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B652" t="str">
-        <v>Konverterar till JSON…</v>
+        <v>Konverterar till XML…</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B653" t="str">
-        <v>Konverterar till ICC…</v>
+        <v>Konverterar till JSON…</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B654" t="str">
-        <v>Läs in ICC-profil</v>
+        <v>Konverterar till ICC…</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B655" t="str">
-        <v>Släppzon för ICC-profilfiler</v>
+        <v>Läs in ICC-profil</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>Profile ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B656" t="str">
-        <v>Profil-ID</v>
+        <v>Släppzon för ICC-profilfiler</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>No tags found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B657" t="str">
-        <v>Inga taggar hittades.</v>
+        <v>Profil-ID</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
-        <v>Tag Name</v>
+        <v>No tags found.</v>
       </c>
       <c r="B658" t="str">
-        <v>Taggnamn</v>
+        <v>Inga taggar hittades.</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="str">
-        <v>ID</v>
+        <v>Tag Name</v>
       </c>
       <c r="B659" t="str">
-        <v>ID</v>
+        <v>Taggnamn</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
       <c r="B660" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="str">
-        <v>Size</v>
+        <v>Offset</v>
       </c>
       <c r="B661" t="str">
-        <v>Storlek</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="str">
-        <v>Pad</v>
+        <v>Size</v>
       </c>
       <c r="B662" t="str">
-        <v>Utfyllnad</v>
+        <v>Storlek</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="str">
-        <v>Bytes changed since load</v>
+        <v>Pad</v>
       </c>
       <c r="B663" t="str">
-        <v>Byte ändrade sedan inläsning</v>
+        <v>Utfyllnad</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="str">
-        <v>Type</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B664" t="str">
-        <v>Typ</v>
+        <v>Byte ändrade sedan inläsning</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="str">
-        <v>Array of {type}</v>
+        <v>Type</v>
       </c>
       <c r="B665" t="str">
-        <v>Array av {type}</v>
+        <v>Typ</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="str">
-        <v>(No content)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B666" t="str">
-        <v>(Inget innehåll)</v>
+        <v>Array av {type}</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="str">
-        <v>bytes</v>
+        <v>(No content)</v>
       </c>
       <c r="B667" t="str">
-        <v>byte</v>
+        <v>(Inget innehåll)</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="str">
-        <v>Loading full description…</v>
+        <v>bytes</v>
       </c>
       <c r="B668" t="str">
-        <v>Läser in fullständig beskrivning…</v>
+        <v>byte</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="str">
-        <v>Could not load full description:</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B669" t="str">
-        <v>Kunde inte läsa in fullständig beskrivning:</v>
+        <v>Läser in fullständig beskrivning…</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B670" t="str">
-        <v>Den här profilen kunde inte tolkas helt och får inte tillämpas. Huvudet och taggkatalogen nedan visas endast för granskning.</v>
+        <v>Kunde inte läsa in fullständig beskrivning:</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B671" t="str">
-        <v>Tagginnehåll otillgängligt — profilen kunde inte tolkas helt.</v>
+        <v>Den här profilen kunde inte tolkas helt och får inte tillämpas. Huvudet och taggkatalogen nedan visas endast för granskning.</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="str">
-        <v>No validation output</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B672" t="str">
-        <v>Ingen valideringsutdata</v>
+        <v>Tagginnehåll otillgängligt — profilen kunde inte tolkas helt.</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="str">
-        <v>Profile is valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B673" t="str">
-        <v>Profilen är giltig</v>
+        <v>Ingen valideringsutdata</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B674" t="str">
-        <v>Profilen har varning(ar)</v>
+        <v>Profilen är giltig</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B675" t="str">
-        <v>Profilen följer inte specifikationen</v>
+        <v>Profilen har varning(ar)</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B676" t="str">
-        <v>Kritiskt valideringsfel</v>
+        <v>Profilen följer inte specifikationen</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B677" t="str">
-        <v>Okänd valideringsstatus</v>
+        <v>Kritiskt valideringsfel</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B678" t="str">
-        <v>Kritiskt — visas endast för granskning</v>
+        <v>Okänd valideringsstatus</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B679" t="str">
-        <v>Inga varningar eller fel hittades.</v>
+        <v>Kritiskt — visas endast för granskning</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="str">
-        <v>Valid</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B680" t="str">
-        <v>Giltig</v>
+        <v>Inga varningar eller fel hittades.</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="str">
-        <v>Warning</v>
+        <v>Valid</v>
       </c>
       <c r="B681" t="str">
-        <v>Varning</v>
+        <v>Giltig</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="str">
-        <v>Error</v>
+        <v>Warning</v>
       </c>
       <c r="B682" t="str">
-        <v>Fel</v>
+        <v>Varning</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="str">
-        <v>Unknown</v>
+        <v>Error</v>
       </c>
       <c r="B683" t="str">
-        <v>Okänd</v>
+        <v>Fel</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="str">
-        <v>Pass</v>
+        <v>Unknown</v>
       </c>
       <c r="B684" t="str">
-        <v>Godkänd</v>
+        <v>Okänd</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="B685" t="str">
-        <v>Underkänd</v>
+        <v>Godkänd</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="str">
-        <v>View in context</v>
+        <v>Fail</v>
       </c>
       <c r="B686" t="str">
-        <v>Visa i sammanhang</v>
+        <v>Underkänd</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="str">
-        <v>Validation detail</v>
+        <v>View in context</v>
       </c>
       <c r="B687" t="str">
-        <v>Valideringsdetalj</v>
+        <v>Visa i sammanhang</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="str">
-        <v>Triggered by</v>
+        <v>Validation detail</v>
       </c>
       <c r="B688" t="str">
-        <v>Utlöst av</v>
+        <v>Valideringsdetalj</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="str">
-        <v>Field</v>
+        <v>Triggered by</v>
       </c>
       <c r="B689" t="str">
-        <v>Fält</v>
+        <v>Utlöst av</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="str">
-        <v>Current value</v>
+        <v>Field</v>
       </c>
       <c r="B690" t="str">
-        <v>Aktuellt värde</v>
+        <v>Fält</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="str">
-        <v>Required: 0</v>
+        <v>Current value</v>
       </c>
       <c r="B691" t="str">
-        <v>Krävs: 0</v>
+        <v>Aktuellt värde</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="str">
-        <v>Expected: {value}</v>
+        <v>Required: 0</v>
       </c>
       <c r="B692" t="str">
-        <v>Förväntat: {value}</v>
+        <v>Krävs: 0</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="str">
-        <v>Invalid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B693" t="str">
-        <v>Ogiltigt</v>
+        <v>Förväntat: {value}</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Invalid</v>
       </c>
       <c r="B694" t="str">
-        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
+        <v>Ogiltigt</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="str">
-        <v>Close</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B695" t="str">
-        <v>Stäng</v>
+        <v>Det här resultatet kunde inte kopplas till ett specifikt fält.</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="str">
-        <v>Loading XML editor…</v>
+        <v>Close</v>
       </c>
       <c r="B696" t="str">
-        <v>Läser in XML-redigeraren…</v>
+        <v>Stäng</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B697" t="str">
-        <v>Läser in JSON-redigeraren…</v>
+        <v>Läser in XML-redigeraren…</v>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B698" t="str">
-        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>Läser in JSON-redigeraren…</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B699" t="str">
-        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
+        <v>Du har osparade XML-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B700" t="str">
-        <v>● osparade XML-ändringar</v>
+        <v>Du har osparade JSON-ändringar. Skriv över dem med en ny konvertering från ICC-profilen?</v>
       </c>
     </row>
     <row r="701">
       <c r="A701" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B701" t="str">
-        <v>● osparade JSON-ändringar</v>
+        <v>● osparade XML-ändringar</v>
       </c>
     </row>
     <row r="702">
       <c r="A702" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B702" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
+        <v>● osparade JSON-ändringar</v>
       </c>
     </row>
     <row r="703">
       <c r="A703" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B703" t="str">
-        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
+        <v>Klicka på &lt;em&gt;Konvertera till XML&lt;/em&gt; för att skapa en redigerbar XML-representation av denna profil. XML produceras av samma IccLibXML-kodväg som verktyget &lt;code&gt;IccToXml&lt;/code&gt; använder.</v>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B704" t="str">
-        <v>indrag</v>
+        <v>Klicka på &lt;em&gt;Konvertera till JSON&lt;/em&gt; för att skapa en redigerbar JSON-representation av denna profil. JSON produceras av samma IccLibJSON-kodväg som verktyget &lt;code&gt;IccToJson&lt;/code&gt; använder.</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="str">
-        <v>sort keys</v>
+        <v>indent</v>
       </c>
       <c r="B705" t="str">
-        <v>sortera nycklar</v>
+        <v>indrag</v>
       </c>
     </row>
     <row r="706">
       <c r="A706" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B706" t="str">
+        <v>sortera nycklar</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B706" t="str">
+      <c r="B707" t="str">
         <v>Profilen skrevs från ändringarna, men omvalideringen misslyckades:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B706"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B707"/>
   </ignoredErrors>
 </worksheet>
 </file>